--- a/data/input/universe_series.xlsx
+++ b/data/input/universe_series.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mid_open" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mid_close" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="mid_close" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="mid_open" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="bid_close" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -481,7 +481,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>6834.59</v>
+        <v>6878.96</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -496,34 +496,34 @@
         <v>46072</v>
       </c>
       <c r="B3" t="n">
-        <v>25234.3</v>
+        <v>25033.6</v>
       </c>
       <c r="C3" t="n">
-        <v>10679.1</v>
+        <v>10670.2</v>
       </c>
       <c r="D3" t="n">
-        <v>6879.21</v>
+        <v>6865.84</v>
       </c>
       <c r="E3" t="n">
-        <v>49646.3</v>
+        <v>49410</v>
       </c>
       <c r="F3" t="n">
-        <v>24896.8</v>
+        <v>24817.3</v>
       </c>
       <c r="G3" t="n">
-        <v>8424.9</v>
+        <v>8417.9</v>
       </c>
       <c r="H3" t="n">
-        <v>57517.5</v>
+        <v>57084.2</v>
       </c>
       <c r="I3" t="n">
-        <v>26847.6</v>
+        <v>26796.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2656.25</v>
+        <v>2661.95</v>
       </c>
       <c r="K3" t="n">
-        <v>6097.6</v>
+        <v>6065.4</v>
       </c>
     </row>
     <row r="4">
@@ -531,34 +531,34 @@
         <v>46073</v>
       </c>
       <c r="B4" t="n">
-        <v>25034.1</v>
+        <v>25236.6</v>
       </c>
       <c r="C4" t="n">
-        <v>10670.3</v>
+        <v>10720.4</v>
       </c>
       <c r="D4" t="n">
-        <v>6865.97</v>
+        <v>6910.63</v>
       </c>
       <c r="E4" t="n">
-        <v>49410.5</v>
+        <v>49624.8</v>
       </c>
       <c r="F4" t="n">
-        <v>24817.5</v>
+        <v>25016.2</v>
       </c>
       <c r="G4" t="n">
-        <v>8418.1</v>
+        <v>8535.4</v>
       </c>
       <c r="H4" t="n">
-        <v>57086.7</v>
+        <v>57088.3</v>
       </c>
       <c r="I4" t="n">
-        <v>26796.9</v>
+        <v>26863.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2662.05</v>
+        <v>2662.2</v>
       </c>
       <c r="K4" t="n">
-        <v>6065.5</v>
+        <v>6135.1</v>
       </c>
     </row>
     <row r="5">
@@ -566,34 +566,34 @@
         <v>46075</v>
       </c>
       <c r="B5" t="n">
-        <v>25208.9</v>
+        <v>25176</v>
       </c>
       <c r="C5" t="n">
-        <v>10712.6</v>
+        <v>10703.4</v>
       </c>
       <c r="D5" t="n">
-        <v>6903.7</v>
+        <v>6892.28</v>
       </c>
       <c r="E5" t="n">
-        <v>49576.3</v>
+        <v>49528.4</v>
       </c>
       <c r="F5" t="n">
-        <v>24973.5</v>
+        <v>24911.3</v>
       </c>
       <c r="G5" t="n">
-        <v>8526.200000000001</v>
+        <v>8515.200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>57079</v>
+        <v>56981.6</v>
       </c>
       <c r="I5" t="n">
-        <v>26846.7</v>
+        <v>26826.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2656.55</v>
+        <v>2652.65</v>
       </c>
       <c r="K5" t="n">
-        <v>6128.4</v>
+        <v>6120.4</v>
       </c>
     </row>
     <row r="6">
@@ -601,34 +601,34 @@
         <v>46076</v>
       </c>
       <c r="B6" t="n">
-        <v>25175.6</v>
+        <v>24996.5</v>
       </c>
       <c r="C6" t="n">
-        <v>10703.3</v>
+        <v>10692.7</v>
       </c>
       <c r="D6" t="n">
-        <v>6892.15</v>
+        <v>6844.309999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>49528.9</v>
+        <v>48839.5</v>
       </c>
       <c r="F6" t="n">
-        <v>24910.7</v>
+        <v>24735.3</v>
       </c>
       <c r="G6" t="n">
-        <v>8515.1</v>
+        <v>8506.6</v>
       </c>
       <c r="H6" t="n">
-        <v>56979.1</v>
+        <v>56665.8</v>
       </c>
       <c r="I6" t="n">
-        <v>26826.2</v>
+        <v>26891.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2652.45</v>
+        <v>2621.45</v>
       </c>
       <c r="K6" t="n">
-        <v>6120.3</v>
+        <v>6123.3</v>
       </c>
     </row>
     <row r="7">
@@ -636,34 +636,34 @@
         <v>46077</v>
       </c>
       <c r="B7" t="n">
-        <v>24996.1</v>
+        <v>25039.3</v>
       </c>
       <c r="C7" t="n">
-        <v>10692.6</v>
+        <v>10712.4</v>
       </c>
       <c r="D7" t="n">
-        <v>6844.559999999999</v>
+        <v>6892.08</v>
       </c>
       <c r="E7" t="n">
-        <v>48840</v>
+        <v>49177.5</v>
       </c>
       <c r="F7" t="n">
-        <v>24735.1</v>
+        <v>24995.3</v>
       </c>
       <c r="G7" t="n">
-        <v>8506.5</v>
+        <v>8539.9</v>
       </c>
       <c r="H7" t="n">
-        <v>56693.3</v>
+        <v>57912</v>
       </c>
       <c r="I7" t="n">
-        <v>26891.6</v>
+        <v>26766.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2621.75</v>
+        <v>2651.55</v>
       </c>
       <c r="K7" t="n">
-        <v>6123.2</v>
+        <v>6136.1</v>
       </c>
     </row>
     <row r="8">
@@ -671,34 +671,34 @@
         <v>46078</v>
       </c>
       <c r="B8" t="n">
-        <v>25038.9</v>
+        <v>25181.3</v>
       </c>
       <c r="C8" t="n">
-        <v>10712.3</v>
+        <v>10804.4</v>
       </c>
       <c r="D8" t="n">
-        <v>6891.95</v>
+        <v>6937.66</v>
       </c>
       <c r="E8" t="n">
-        <v>49176.5</v>
+        <v>49392</v>
       </c>
       <c r="F8" t="n">
-        <v>24995</v>
+        <v>25270</v>
       </c>
       <c r="G8" t="n">
-        <v>8539.799999999999</v>
+        <v>8569.6</v>
       </c>
       <c r="H8" t="n">
-        <v>57919.5</v>
+        <v>59285.1</v>
       </c>
       <c r="I8" t="n">
-        <v>26766</v>
+        <v>26950</v>
       </c>
       <c r="J8" t="n">
-        <v>2651.45</v>
+        <v>2660.65</v>
       </c>
       <c r="K8" t="n">
-        <v>6136</v>
+        <v>6175.7</v>
       </c>
     </row>
     <row r="9">
@@ -706,34 +706,34 @@
         <v>46079</v>
       </c>
       <c r="B9" t="n">
-        <v>25180.7</v>
+        <v>25253.3</v>
       </c>
       <c r="C9" t="n">
-        <v>10804.3</v>
+        <v>10835.1</v>
       </c>
       <c r="D9" t="n">
-        <v>6937.41</v>
+        <v>6882.360000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>49392.5</v>
+        <v>49229.6</v>
       </c>
       <c r="F9" t="n">
-        <v>25270.1</v>
+        <v>24955.6</v>
       </c>
       <c r="G9" t="n">
-        <v>8569.5</v>
+        <v>8611.700000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>59282.6</v>
+        <v>58435</v>
       </c>
       <c r="I9" t="n">
-        <v>26949.5</v>
+        <v>26389.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2660.95</v>
+        <v>2655.55</v>
       </c>
       <c r="K9" t="n">
-        <v>6175.6</v>
+        <v>6150.7</v>
       </c>
     </row>
     <row r="10">
@@ -741,34 +741,34 @@
         <v>46080</v>
       </c>
       <c r="B10" t="n">
-        <v>25252.1</v>
+        <v>25143.7</v>
       </c>
       <c r="C10" t="n">
-        <v>10834.9</v>
+        <v>10862.7</v>
       </c>
       <c r="D10" t="n">
-        <v>6881.99</v>
+        <v>6865.58</v>
       </c>
       <c r="E10" t="n">
-        <v>49229.1</v>
+        <v>48858.5</v>
       </c>
       <c r="F10" t="n">
-        <v>24955.4</v>
+        <v>24914.4</v>
       </c>
       <c r="G10" t="n">
-        <v>8611.299999999999</v>
+        <v>8530.6</v>
       </c>
       <c r="H10" t="n">
-        <v>58385</v>
+        <v>58612.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26389</v>
+        <v>26490.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2655.45</v>
+        <v>2626.65</v>
       </c>
       <c r="K10" t="n">
-        <v>6150.4</v>
+        <v>6095.38</v>
       </c>
     </row>
     <row r="11">
@@ -776,34 +776,34 @@
         <v>46082</v>
       </c>
       <c r="B11" t="n">
-        <v>24967.8</v>
+        <v>24946.3</v>
       </c>
       <c r="C11" t="n">
-        <v>10810.3</v>
+        <v>10811.6</v>
       </c>
       <c r="D11" t="n">
-        <v>6817.17</v>
+        <v>6805.95</v>
       </c>
       <c r="E11" t="n">
-        <v>48514.6</v>
+        <v>48368.8</v>
       </c>
       <c r="F11" t="n">
-        <v>24680.4</v>
+        <v>24696.7</v>
       </c>
       <c r="G11" t="n">
-        <v>8470.9</v>
+        <v>8466.4</v>
       </c>
       <c r="H11" t="n">
-        <v>57705.8</v>
+        <v>57488.1</v>
       </c>
       <c r="I11" t="n">
-        <v>26383</v>
+        <v>26350.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2605.05</v>
+        <v>2591.25</v>
       </c>
       <c r="K11" t="n">
-        <v>6052.78</v>
+        <v>6049.58</v>
       </c>
     </row>
     <row r="12">
@@ -811,34 +811,34 @@
         <v>46083</v>
       </c>
       <c r="B12" t="n">
-        <v>24947.2</v>
+        <v>24582.2</v>
       </c>
       <c r="C12" t="n">
-        <v>10811.7</v>
+        <v>10789.5</v>
       </c>
       <c r="D12" t="n">
-        <v>6806.2</v>
+        <v>6867.940000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>48369.8</v>
+        <v>48823.6</v>
       </c>
       <c r="F12" t="n">
-        <v>24696.9</v>
+        <v>24935.3</v>
       </c>
       <c r="G12" t="n">
-        <v>8466.6</v>
+        <v>8387.700000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>57483.1</v>
+        <v>57713.1</v>
       </c>
       <c r="I12" t="n">
-        <v>26351.1</v>
+        <v>26156.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2591.15</v>
+        <v>2650.85</v>
       </c>
       <c r="K12" t="n">
-        <v>6049.78</v>
+        <v>5982.2</v>
       </c>
     </row>
     <row r="13">
@@ -846,34 +846,34 @@
         <v>46084</v>
       </c>
       <c r="B13" t="n">
-        <v>24583</v>
+        <v>23985</v>
       </c>
       <c r="C13" t="n">
-        <v>10789.6</v>
+        <v>10517.1</v>
       </c>
       <c r="D13" t="n">
-        <v>6868.190000000001</v>
+        <v>6802.5</v>
       </c>
       <c r="E13" t="n">
-        <v>48825.6</v>
+        <v>48413.3</v>
       </c>
       <c r="F13" t="n">
-        <v>24937</v>
+        <v>24668</v>
       </c>
       <c r="G13" t="n">
-        <v>8388</v>
+        <v>8165.4</v>
       </c>
       <c r="H13" t="n">
-        <v>57710.6</v>
+        <v>54951.7</v>
       </c>
       <c r="I13" t="n">
-        <v>26157.2</v>
+        <v>25468.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2651.05</v>
+        <v>2603.45</v>
       </c>
       <c r="K13" t="n">
-        <v>5982.4</v>
+        <v>5813.3</v>
       </c>
     </row>
     <row r="14">
@@ -881,34 +881,34 @@
         <v>46085</v>
       </c>
       <c r="B14" t="n">
-        <v>23985.8</v>
+        <v>24302.2</v>
       </c>
       <c r="C14" t="n">
-        <v>10517.2</v>
+        <v>10626.8</v>
       </c>
       <c r="D14" t="n">
-        <v>6802.75</v>
+        <v>6878.04</v>
       </c>
       <c r="E14" t="n">
-        <v>48412.8</v>
+        <v>48753.2</v>
       </c>
       <c r="F14" t="n">
-        <v>24667.6</v>
+        <v>25137.1</v>
       </c>
       <c r="G14" t="n">
-        <v>8166.5</v>
+        <v>8204</v>
       </c>
       <c r="H14" t="n">
-        <v>54976.7</v>
+        <v>56232.9</v>
       </c>
       <c r="I14" t="n">
-        <v>25468.9</v>
+        <v>25602.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2603.55</v>
+        <v>2635.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5813.5</v>
+        <v>5901.9</v>
       </c>
     </row>
     <row r="15">
@@ -916,34 +916,34 @@
         <v>46086</v>
       </c>
       <c r="B15" t="n">
-        <v>24301.8</v>
+        <v>23866.2</v>
       </c>
       <c r="C15" t="n">
-        <v>10626.7</v>
+        <v>10407.9</v>
       </c>
       <c r="D15" t="n">
-        <v>6877.92</v>
+        <v>6834.43</v>
       </c>
       <c r="E15" t="n">
-        <v>48752.7</v>
+        <v>48034</v>
       </c>
       <c r="F15" t="n">
-        <v>25137</v>
+        <v>25031.4</v>
       </c>
       <c r="G15" t="n">
-        <v>8203.9</v>
+        <v>8059.2</v>
       </c>
       <c r="H15" t="n">
-        <v>56215.4</v>
+        <v>54563.2</v>
       </c>
       <c r="I15" t="n">
-        <v>25602.6</v>
+        <v>25202.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2635.75</v>
+        <v>2592.85</v>
       </c>
       <c r="K15" t="n">
-        <v>5901.8</v>
+        <v>5793.6</v>
       </c>
     </row>
     <row r="16">
@@ -951,34 +951,34 @@
         <v>46087</v>
       </c>
       <c r="B16" t="n">
-        <v>23867</v>
+        <v>23640.3</v>
       </c>
       <c r="C16" t="n">
-        <v>10408</v>
+        <v>10318.8</v>
       </c>
       <c r="D16" t="n">
-        <v>6834.68</v>
+        <v>6733.23</v>
       </c>
       <c r="E16" t="n">
-        <v>48032.8</v>
+        <v>47434.2</v>
       </c>
       <c r="F16" t="n">
-        <v>25032.3</v>
+        <v>24634.2</v>
       </c>
       <c r="G16" t="n">
-        <v>8059.4</v>
+        <v>8017.2</v>
       </c>
       <c r="H16" t="n">
-        <v>54575.7</v>
+        <v>54029.9</v>
       </c>
       <c r="I16" t="n">
-        <v>25202.9</v>
+        <v>25325.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2592.75</v>
+        <v>2522</v>
       </c>
       <c r="K16" t="n">
-        <v>5793.8</v>
+        <v>5723.03</v>
       </c>
     </row>
     <row r="17">
@@ -986,34 +986,34 @@
         <v>46089</v>
       </c>
       <c r="B17" t="n">
-        <v>23357.4</v>
+        <v>23222.3</v>
       </c>
       <c r="C17" t="n">
-        <v>10244.7</v>
+        <v>10195.8</v>
       </c>
       <c r="D17" t="n">
-        <v>6678.34</v>
+        <v>6622.45</v>
       </c>
       <c r="E17" t="n">
-        <v>46831</v>
+        <v>46613</v>
       </c>
       <c r="F17" t="n">
-        <v>24403</v>
+        <v>24187.4</v>
       </c>
       <c r="G17" t="n">
-        <v>7921.2</v>
+        <v>7873</v>
       </c>
       <c r="H17" t="n">
-        <v>53227.3</v>
+        <v>52216.5</v>
       </c>
       <c r="I17" t="n">
-        <v>25160.3</v>
+        <v>25042.2</v>
       </c>
       <c r="J17" t="n">
-        <v>2493.15</v>
+        <v>2433.35</v>
       </c>
       <c r="K17" t="n">
-        <v>5654.6</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="18">
@@ -1021,34 +1021,34 @@
         <v>46090</v>
       </c>
       <c r="B18" t="n">
-        <v>23221.9</v>
+        <v>23703.1</v>
       </c>
       <c r="C18" t="n">
-        <v>10195.7</v>
+        <v>10307.8</v>
       </c>
       <c r="D18" t="n">
-        <v>6623.07</v>
+        <v>6766.07</v>
       </c>
       <c r="E18" t="n">
-        <v>46616</v>
+        <v>47534.3</v>
       </c>
       <c r="F18" t="n">
-        <v>24187.3</v>
+        <v>24854.1</v>
       </c>
       <c r="G18" t="n">
-        <v>7872.9</v>
+        <v>8000.3</v>
       </c>
       <c r="H18" t="n">
-        <v>52231.5</v>
+        <v>54259.6</v>
       </c>
       <c r="I18" t="n">
-        <v>25042</v>
+        <v>25545.7</v>
       </c>
       <c r="J18" t="n">
-        <v>2433.75</v>
+        <v>2534.05</v>
       </c>
       <c r="K18" t="n">
-        <v>5615.8</v>
+        <v>5764.7</v>
       </c>
     </row>
     <row r="19">
@@ -1056,34 +1056,34 @@
         <v>46091</v>
       </c>
       <c r="B19" t="n">
-        <v>23702.6</v>
+        <v>23809.1</v>
       </c>
       <c r="C19" t="n">
-        <v>10307.7</v>
+        <v>10385.1</v>
       </c>
       <c r="D19" t="n">
-        <v>6765.95</v>
+        <v>6791.25</v>
       </c>
       <c r="E19" t="n">
-        <v>47534.8</v>
+        <v>47744.5</v>
       </c>
       <c r="F19" t="n">
-        <v>24854</v>
+        <v>24990.4</v>
       </c>
       <c r="G19" t="n">
-        <v>8000.2</v>
+        <v>7996.9</v>
       </c>
       <c r="H19" t="n">
-        <v>54251.3</v>
+        <v>55066.9</v>
       </c>
       <c r="I19" t="n">
-        <v>25545.5</v>
+        <v>25945.2</v>
       </c>
       <c r="J19" t="n">
-        <v>2534.15</v>
+        <v>2552.05</v>
       </c>
       <c r="K19" t="n">
-        <v>5764.6</v>
+        <v>5786.9</v>
       </c>
     </row>
     <row r="20">
@@ -1091,34 +1091,34 @@
         <v>46092</v>
       </c>
       <c r="B20" t="n">
-        <v>23812.8</v>
+        <v>23465.2</v>
       </c>
       <c r="C20" t="n">
-        <v>10385.4</v>
+        <v>10272.4</v>
       </c>
       <c r="D20" t="n">
-        <v>6792.13</v>
+        <v>6724.610000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>47746.5</v>
+        <v>47030.3</v>
       </c>
       <c r="F20" t="n">
-        <v>24991.9</v>
+        <v>24768.1</v>
       </c>
       <c r="G20" t="n">
-        <v>7998.1</v>
+        <v>7976.9</v>
       </c>
       <c r="H20" t="n">
-        <v>55064.4</v>
+        <v>54158</v>
       </c>
       <c r="I20" t="n">
-        <v>25946.7</v>
+        <v>25634.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2552.65</v>
+        <v>2505.75</v>
       </c>
       <c r="K20" t="n">
-        <v>5787.8</v>
+        <v>5752.63</v>
       </c>
     </row>
     <row r="21">
@@ -1126,34 +1126,34 @@
         <v>46093</v>
       </c>
       <c r="B21" t="n">
-        <v>23466.3</v>
+        <v>23495</v>
       </c>
       <c r="C21" t="n">
-        <v>10272.5</v>
+        <v>10283.7</v>
       </c>
       <c r="D21" t="n">
-        <v>6724.49</v>
+        <v>6676.01</v>
       </c>
       <c r="E21" t="n">
-        <v>47199.39999999999</v>
+        <v>46739.9</v>
       </c>
       <c r="F21" t="n">
-        <v>24768</v>
+        <v>24514</v>
       </c>
       <c r="G21" t="n">
-        <v>7977.3</v>
+        <v>7964.5</v>
       </c>
       <c r="H21" t="n">
-        <v>54153</v>
+        <v>53462.2</v>
       </c>
       <c r="I21" t="n">
-        <v>25635.2</v>
+        <v>25453.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2506.45</v>
+        <v>2490.95</v>
       </c>
       <c r="K21" t="n">
-        <v>5752.93</v>
+        <v>5725.3</v>
       </c>
     </row>
     <row r="22">
@@ -1161,34 +1161,34 @@
         <v>46094</v>
       </c>
       <c r="B22" t="n">
-        <v>23493.9</v>
+        <v>23329.3</v>
       </c>
       <c r="C22" t="n">
-        <v>10283.6</v>
+        <v>10240.1</v>
       </c>
       <c r="D22" t="n">
-        <v>6675.76</v>
+        <v>6621.04</v>
       </c>
       <c r="E22" t="n">
-        <v>46740.4</v>
+        <v>46475.1</v>
       </c>
       <c r="F22" t="n">
-        <v>24514.1</v>
+        <v>24321.2</v>
       </c>
       <c r="G22" t="n">
-        <v>7964.1</v>
+        <v>7875.6</v>
       </c>
       <c r="H22" t="n">
-        <v>53442.2</v>
+        <v>53150.3</v>
       </c>
       <c r="I22" t="n">
-        <v>25453.2</v>
+        <v>25400.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2490.75</v>
+        <v>2474.5</v>
       </c>
       <c r="K22" t="n">
-        <v>5725</v>
+        <v>5689.36</v>
       </c>
     </row>
     <row r="23">
@@ -1196,34 +1196,34 @@
         <v>46096</v>
       </c>
       <c r="B23" t="n">
-        <v>23369.4</v>
+        <v>23428.6</v>
       </c>
       <c r="C23" t="n">
-        <v>10252.1</v>
+        <v>10268.8</v>
       </c>
       <c r="D23" t="n">
-        <v>6618.15</v>
+        <v>6645.48</v>
       </c>
       <c r="E23" t="n">
-        <v>46472</v>
+        <v>46641.8</v>
       </c>
       <c r="F23" t="n">
-        <v>24304.8</v>
+        <v>24424</v>
       </c>
       <c r="G23" t="n">
-        <v>7899.3</v>
+        <v>7919.5</v>
       </c>
       <c r="H23" t="n">
-        <v>52934.6</v>
+        <v>53651.9</v>
       </c>
       <c r="I23" t="n">
-        <v>25421.2</v>
+        <v>25450.7</v>
       </c>
       <c r="J23" t="n">
-        <v>2472.65</v>
+        <v>2489.45</v>
       </c>
       <c r="K23" t="n">
-        <v>5699.4</v>
+        <v>5713.9</v>
       </c>
     </row>
     <row r="24">
@@ -1231,34 +1231,34 @@
         <v>46097</v>
       </c>
       <c r="B24" t="n">
-        <v>23429.7</v>
+        <v>23625.4</v>
       </c>
       <c r="C24" t="n">
-        <v>10268.7</v>
+        <v>10347</v>
       </c>
       <c r="D24" t="n">
-        <v>6645.73</v>
+        <v>6698.12</v>
       </c>
       <c r="E24" t="n">
-        <v>46642.3</v>
+        <v>46926.7</v>
       </c>
       <c r="F24" t="n">
-        <v>24424.7</v>
+        <v>24652</v>
       </c>
       <c r="G24" t="n">
-        <v>7919.2</v>
+        <v>7949</v>
       </c>
       <c r="H24" t="n">
-        <v>53659.4</v>
+        <v>54337.6</v>
       </c>
       <c r="I24" t="n">
-        <v>25450.6</v>
+        <v>25861.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2489.55</v>
+        <v>2501.65</v>
       </c>
       <c r="K24" t="n">
-        <v>5714.1</v>
+        <v>5754.2</v>
       </c>
     </row>
     <row r="25">
@@ -1266,34 +1266,34 @@
         <v>46098</v>
       </c>
       <c r="B25" t="n">
-        <v>23624.3</v>
+        <v>23670.5</v>
       </c>
       <c r="C25" t="n">
-        <v>10347.1</v>
+        <v>10362.5</v>
       </c>
       <c r="D25" t="n">
-        <v>6697.87</v>
+        <v>6711.68</v>
       </c>
       <c r="E25" t="n">
-        <v>46926.2</v>
+        <v>46944.6</v>
       </c>
       <c r="F25" t="n">
-        <v>24651.7</v>
+        <v>24775.5</v>
       </c>
       <c r="G25" t="n">
-        <v>7949.3</v>
+        <v>7956.2</v>
       </c>
       <c r="H25" t="n">
-        <v>54340.1</v>
+        <v>54274.4</v>
       </c>
       <c r="I25" t="n">
-        <v>25861.8</v>
+        <v>25859.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2501.55</v>
+        <v>2517.85</v>
       </c>
       <c r="K25" t="n">
-        <v>5754</v>
+        <v>5756.4</v>
       </c>
     </row>
     <row r="26">
@@ -1301,34 +1301,34 @@
         <v>46099</v>
       </c>
       <c r="B26" t="n">
-        <v>23669.4</v>
+        <v>23169.5</v>
       </c>
       <c r="C26" t="n">
-        <v>10362.4</v>
+        <v>10221.1</v>
       </c>
       <c r="D26" t="n">
-        <v>6711.43</v>
+        <v>6698.99</v>
       </c>
       <c r="E26" t="n">
-        <v>46944.1</v>
+        <v>46157</v>
       </c>
       <c r="F26" t="n">
-        <v>24776</v>
+        <v>24395.2</v>
       </c>
       <c r="G26" t="n">
-        <v>7955.8</v>
+        <v>7897.7</v>
       </c>
       <c r="H26" t="n">
-        <v>54291.9</v>
+        <v>53599.6</v>
       </c>
       <c r="I26" t="n">
-        <v>25859.1</v>
+        <v>25416.9</v>
       </c>
       <c r="J26" t="n">
-        <v>2517.65</v>
+        <v>2474.45</v>
       </c>
       <c r="K26" t="n">
-        <v>5756.1</v>
+        <v>5655.5</v>
       </c>
     </row>
     <row r="27">
@@ -1336,32 +1336,32 @@
         <v>46100</v>
       </c>
       <c r="B27" t="n">
-        <v>23171.8</v>
+        <v>23019.7</v>
       </c>
       <c r="C27" t="n">
-        <v>10221.2</v>
+        <v>10069.6</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>46158</v>
+        <v>46139.2</v>
       </c>
       <c r="F27" t="n">
-        <v>24394.9</v>
+        <v>24407.7</v>
       </c>
       <c r="G27" t="n">
-        <v>7898.5</v>
+        <v>7842.7</v>
       </c>
       <c r="H27" t="n">
-        <v>53624.6</v>
+        <v>53401.2</v>
       </c>
       <c r="I27" t="n">
-        <v>25417.7</v>
+        <v>25368.8</v>
       </c>
       <c r="J27" t="n">
-        <v>2474.35</v>
+        <v>2508.55</v>
       </c>
       <c r="K27" t="n">
-        <v>5656.1</v>
+        <v>5655.4</v>
       </c>
     </row>
     <row r="28">
@@ -1369,34 +1369,34 @@
         <v>46101</v>
       </c>
       <c r="B28" t="n">
-        <v>23020.2</v>
+        <v>22214.3</v>
       </c>
       <c r="C28" t="n">
-        <v>10069.7</v>
+        <v>9839.299999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>6619.34</v>
+        <v>6537.12</v>
       </c>
       <c r="E28" t="n">
-        <v>46139.7</v>
+        <v>45803.1</v>
       </c>
       <c r="F28" t="n">
-        <v>24407.8</v>
+        <v>24000.4</v>
       </c>
       <c r="G28" t="n">
-        <v>7843</v>
+        <v>7613.8</v>
       </c>
       <c r="H28" t="n">
-        <v>53403.2</v>
+        <v>51317.2</v>
       </c>
       <c r="I28" t="n">
-        <v>25369.1</v>
+        <v>24770.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2508.75</v>
+        <v>2452.1</v>
       </c>
       <c r="K28" t="n">
-        <v>5655.6</v>
+        <v>5474.95</v>
       </c>
     </row>
     <row r="29">
@@ -1404,34 +1404,34 @@
         <v>46103</v>
       </c>
       <c r="B29" t="n">
-        <v>21912.6</v>
+        <v>21975.6</v>
       </c>
       <c r="C29" t="n">
-        <v>9776</v>
+        <v>9794.1</v>
       </c>
       <c r="D29" t="n">
-        <v>6460.09</v>
+        <v>6488.5</v>
       </c>
       <c r="E29" t="n">
-        <v>45343.8</v>
+        <v>45538.6</v>
       </c>
       <c r="F29" t="n">
-        <v>23718.3</v>
+        <v>23794.4</v>
       </c>
       <c r="G29" t="n">
-        <v>7513</v>
+        <v>7540.6</v>
       </c>
       <c r="H29" t="n">
-        <v>50808.8</v>
+        <v>51180.5</v>
       </c>
       <c r="I29" t="n">
-        <v>24609.8</v>
+        <v>24659.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2420.35</v>
+        <v>2432.65</v>
       </c>
       <c r="K29" t="n">
-        <v>5402.6</v>
+        <v>5419.6</v>
       </c>
     </row>
     <row r="30">
@@ -1439,34 +1439,34 @@
         <v>46104</v>
       </c>
       <c r="B30" t="n">
-        <v>21979.4</v>
+        <v>22845</v>
       </c>
       <c r="C30" t="n">
-        <v>9794.299999999999</v>
+        <v>9963.6</v>
       </c>
       <c r="D30" t="n">
-        <v>6488.75</v>
+        <v>6594.07</v>
       </c>
       <c r="E30" t="n">
-        <v>45541.6</v>
+        <v>46290.6</v>
       </c>
       <c r="F30" t="n">
-        <v>23797.5</v>
+        <v>24241.8</v>
       </c>
       <c r="G30" t="n">
-        <v>7541.9</v>
+        <v>7798.8</v>
       </c>
       <c r="H30" t="n">
-        <v>51188</v>
+        <v>53018.2</v>
       </c>
       <c r="I30" t="n">
-        <v>24660.8</v>
+        <v>24982.7</v>
       </c>
       <c r="J30" t="n">
-        <v>2433.15</v>
+        <v>2500.55</v>
       </c>
       <c r="K30" t="n">
-        <v>5420.5</v>
+        <v>5617.7</v>
       </c>
     </row>
     <row r="31">
@@ -1474,34 +1474,34 @@
         <v>46105</v>
       </c>
       <c r="B31" t="n">
-        <v>22844.5</v>
+        <v>22891</v>
       </c>
       <c r="C31" t="n">
-        <v>9963.5</v>
+        <v>10015.3</v>
       </c>
       <c r="D31" t="n">
-        <v>6593.95</v>
+        <v>6599.97</v>
       </c>
       <c r="E31" t="n">
-        <v>46286.1</v>
+        <v>46448</v>
       </c>
       <c r="F31" t="n">
-        <v>24241.5</v>
+        <v>24205</v>
       </c>
       <c r="G31" t="n">
-        <v>7798.6</v>
+        <v>7815.7</v>
       </c>
       <c r="H31" t="n">
-        <v>52995.7</v>
+        <v>53500.6</v>
       </c>
       <c r="I31" t="n">
-        <v>24982.4</v>
+        <v>25050.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2500.15</v>
+        <v>2535.75</v>
       </c>
       <c r="K31" t="n">
-        <v>5617.6</v>
+        <v>5645.68</v>
       </c>
     </row>
     <row r="32">
@@ -1509,34 +1509,34 @@
         <v>46106</v>
       </c>
       <c r="B32" t="n">
-        <v>22889.8</v>
+        <v>22870.1</v>
       </c>
       <c r="C32" t="n">
-        <v>10015.1</v>
+        <v>10085.7</v>
       </c>
       <c r="D32" t="n">
-        <v>6599.72</v>
+        <v>6581</v>
       </c>
       <c r="E32" t="n">
-        <v>46448.5</v>
+        <v>46359.5</v>
       </c>
       <c r="F32" t="n">
-        <v>24204.9</v>
+        <v>24114.6</v>
       </c>
       <c r="G32" t="n">
-        <v>7815.3</v>
+        <v>7815.5</v>
       </c>
       <c r="H32" t="n">
-        <v>53498.1</v>
+        <v>53878.5</v>
       </c>
       <c r="I32" t="n">
-        <v>25050</v>
+        <v>25259.3</v>
       </c>
       <c r="J32" t="n">
-        <v>2535.85</v>
+        <v>2530.75</v>
       </c>
       <c r="K32" t="n">
-        <v>5645.38</v>
+        <v>5621.51</v>
       </c>
     </row>
     <row r="33">
@@ -1544,34 +1544,34 @@
         <v>46107</v>
       </c>
       <c r="B33" t="n">
-        <v>22871.3</v>
+        <v>22692.5</v>
       </c>
       <c r="C33" t="n">
-        <v>10085.8</v>
+        <v>9965.799999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>6581.25</v>
+        <v>6506.25</v>
       </c>
       <c r="E33" t="n">
-        <v>46358.7</v>
+        <v>46181.1</v>
       </c>
       <c r="F33" t="n">
-        <v>24114.4</v>
+        <v>23682.7</v>
       </c>
       <c r="G33" t="n">
-        <v>7815.9</v>
+        <v>7780.5</v>
       </c>
       <c r="H33" t="n">
-        <v>53886</v>
+        <v>52923.6</v>
       </c>
       <c r="I33" t="n">
-        <v>25259.7</v>
+        <v>24768.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2530.85</v>
+        <v>2508.55</v>
       </c>
       <c r="K33" t="n">
-        <v>5621.81</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="34">
@@ -1579,34 +1579,34 @@
         <v>46108</v>
       </c>
       <c r="B34" t="n">
-        <v>22693.7</v>
+        <v>22101.1</v>
       </c>
       <c r="C34" t="n">
-        <v>9966</v>
+        <v>9895.299999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>6506.5</v>
+        <v>6355.25</v>
       </c>
       <c r="E34" t="n">
-        <v>46185</v>
+        <v>45061.5</v>
       </c>
       <c r="F34" t="n">
-        <v>23682.9</v>
+        <v>23069.6</v>
       </c>
       <c r="G34" t="n">
-        <v>7780.9</v>
+        <v>7646.4</v>
       </c>
       <c r="H34" t="n">
-        <v>52941.1</v>
+        <v>51137.7</v>
       </c>
       <c r="I34" t="n">
-        <v>24769.2</v>
+        <v>24627.5</v>
       </c>
       <c r="J34" t="n">
-        <v>2508.75</v>
+        <v>2443.2</v>
       </c>
       <c r="K34" t="n">
-        <v>5573.3</v>
+        <v>5455.22</v>
       </c>
     </row>
     <row r="35">
@@ -1614,34 +1614,34 @@
         <v>46110</v>
       </c>
       <c r="B35" t="n">
-        <v>22033.7</v>
+        <v>22031.4</v>
       </c>
       <c r="C35" t="n">
-        <v>9881.700000000001</v>
+        <v>9879.4</v>
       </c>
       <c r="D35" t="n">
-        <v>6337.22</v>
+        <v>6340.21</v>
       </c>
       <c r="E35" t="n">
-        <v>44942.8</v>
+        <v>44945.6</v>
       </c>
       <c r="F35" t="n">
-        <v>23006</v>
+        <v>23027.2</v>
       </c>
       <c r="G35" t="n">
-        <v>7623.5</v>
+        <v>7618.7</v>
       </c>
       <c r="H35" t="n">
-        <v>50871.5</v>
+        <v>50609</v>
       </c>
       <c r="I35" t="n">
-        <v>24599.6</v>
+        <v>24593.4</v>
       </c>
       <c r="J35" t="n">
-        <v>2435.15</v>
+        <v>2430.85</v>
       </c>
       <c r="K35" t="n">
-        <v>5438.9</v>
+        <v>5435.4</v>
       </c>
     </row>
     <row r="36">
@@ -1649,34 +1649,34 @@
         <v>46111</v>
       </c>
       <c r="B36" t="n">
-        <v>22030.8</v>
+        <v>22434.6</v>
       </c>
       <c r="C36" t="n">
-        <v>9879.299999999999</v>
+        <v>10070.4</v>
       </c>
       <c r="D36" t="n">
-        <v>6340.08</v>
+        <v>6341.38</v>
       </c>
       <c r="E36" t="n">
-        <v>44943.2</v>
+        <v>45225.5</v>
       </c>
       <c r="F36" t="n">
-        <v>23027</v>
+        <v>22920.3</v>
       </c>
       <c r="G36" t="n">
-        <v>7618.6</v>
+        <v>7722.7</v>
       </c>
       <c r="H36" t="n">
-        <v>50611.5</v>
+        <v>51054.8</v>
       </c>
       <c r="I36" t="n">
-        <v>24593.1</v>
+        <v>24724.4</v>
       </c>
       <c r="J36" t="n">
-        <v>2430.65</v>
+        <v>2409.85</v>
       </c>
       <c r="K36" t="n">
-        <v>5435.2</v>
+        <v>5500.9</v>
       </c>
     </row>
     <row r="37">
@@ -1684,34 +1684,34 @@
         <v>46112</v>
       </c>
       <c r="B37" t="n">
-        <v>22434.1</v>
+        <v>23026.2</v>
       </c>
       <c r="C37" t="n">
-        <v>10070.3</v>
+        <v>10279.9</v>
       </c>
       <c r="D37" t="n">
-        <v>6341.26</v>
+        <v>6530.15</v>
       </c>
       <c r="E37" t="n">
-        <v>45226</v>
+        <v>46230.95</v>
       </c>
       <c r="F37" t="n">
-        <v>22920</v>
+        <v>23777.1</v>
       </c>
       <c r="G37" t="n">
-        <v>7722.4</v>
+        <v>7921.4</v>
       </c>
       <c r="H37" t="n">
-        <v>51049.8</v>
+        <v>53050.8</v>
       </c>
       <c r="I37" t="n">
-        <v>24724.2</v>
+        <v>25317.1</v>
       </c>
       <c r="J37" t="n">
-        <v>2409.75</v>
+        <v>2494.15</v>
       </c>
       <c r="K37" t="n">
-        <v>5500.7</v>
+        <v>5653.5</v>
       </c>
     </row>
     <row r="38">
@@ -1719,34 +1719,34 @@
         <v>46113</v>
       </c>
       <c r="B38" t="n">
-        <v>23025</v>
+        <v>23289</v>
       </c>
       <c r="C38" t="n">
-        <v>10279.8</v>
+        <v>10416.2</v>
       </c>
       <c r="D38" t="n">
-        <v>6529.9</v>
+        <v>6572.13</v>
       </c>
       <c r="E38" t="n">
-        <v>46313.4</v>
+        <v>46561.8</v>
       </c>
       <c r="F38" t="n">
-        <v>23775.3</v>
+        <v>23996.1</v>
       </c>
       <c r="G38" t="n">
-        <v>7921</v>
+        <v>7976.6</v>
       </c>
       <c r="H38" t="n">
-        <v>53025.8</v>
+        <v>54233.9</v>
       </c>
       <c r="I38" t="n">
-        <v>25316.6</v>
+        <v>25315.3</v>
       </c>
       <c r="J38" t="n">
-        <v>2494.05</v>
+        <v>2510.15</v>
       </c>
       <c r="K38" t="n">
-        <v>5653.2</v>
+        <v>5720.9</v>
       </c>
     </row>
     <row r="39">
@@ -1754,34 +1754,34 @@
         <v>46114</v>
       </c>
       <c r="B39" t="n">
-        <v>23290.2</v>
+        <v>23217.6</v>
       </c>
       <c r="C39" t="n">
-        <v>10416.3</v>
+        <v>10451.6</v>
       </c>
       <c r="D39" t="n">
-        <v>6572.38</v>
+        <v>6583.360000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>46564.3</v>
+        <v>46522.4</v>
       </c>
       <c r="F39" t="n">
-        <v>23997.5</v>
+        <v>24030.5</v>
       </c>
       <c r="G39" t="n">
-        <v>7977.1</v>
+        <v>7990.9</v>
       </c>
       <c r="H39" t="n">
-        <v>54235.3</v>
+        <v>53247.5</v>
       </c>
       <c r="I39" t="n">
-        <v>25315.7</v>
+        <v>25270.4</v>
       </c>
       <c r="J39" t="n">
-        <v>2510.35</v>
+        <v>2530.55</v>
       </c>
       <c r="K39" t="n">
-        <v>5721.2</v>
+        <v>5701.47</v>
       </c>
     </row>
     <row r="40">
@@ -1789,34 +1789,34 @@
         <v>46115</v>
       </c>
       <c r="B40" t="n">
-        <v>23218.1</v>
+        <v>23127.3</v>
       </c>
       <c r="C40" t="n">
-        <v>10451.7</v>
+        <v>10432</v>
       </c>
       <c r="D40" t="n">
-        <v>6583.43</v>
+        <v>6563.67</v>
       </c>
       <c r="E40" t="n">
-        <v>46522.1</v>
+        <v>46407.7</v>
       </c>
       <c r="F40" t="n">
-        <v>24030.1</v>
+        <v>23957.4</v>
       </c>
       <c r="G40" t="n">
-        <v>7991</v>
+        <v>7960.4</v>
       </c>
       <c r="H40" t="n">
-        <v>53243.7</v>
+        <v>53165.2</v>
       </c>
       <c r="I40" t="n">
-        <v>25270.6</v>
+        <v>25188.7</v>
       </c>
       <c r="J40" t="n">
-        <v>2530.45</v>
+        <v>2519.65</v>
       </c>
       <c r="K40" t="n">
-        <v>5701.57</v>
+        <v>5679.77</v>
       </c>
     </row>
     <row r="41">
@@ -1824,34 +1824,34 @@
         <v>46117</v>
       </c>
       <c r="B41" t="n">
-        <v>23043.8</v>
+        <v>23052.9</v>
       </c>
       <c r="C41" t="n">
-        <v>10414.5</v>
+        <v>10416.4</v>
       </c>
       <c r="D41" t="n">
-        <v>6541.72</v>
+        <v>6547.57</v>
       </c>
       <c r="E41" t="n">
-        <v>46240.7</v>
+        <v>46258.3</v>
       </c>
       <c r="F41" t="n">
-        <v>23893</v>
+        <v>23907.8</v>
       </c>
       <c r="G41" t="n">
-        <v>7931.5</v>
+        <v>7934.5</v>
       </c>
       <c r="H41" t="n">
-        <v>53059.2</v>
+        <v>52872.6</v>
       </c>
       <c r="I41" t="n">
-        <v>25149.7</v>
+        <v>25153.9</v>
       </c>
       <c r="J41" t="n">
-        <v>2508.95</v>
+        <v>2510.85</v>
       </c>
       <c r="K41" t="n">
-        <v>5659.6</v>
+        <v>5661.8</v>
       </c>
     </row>
     <row r="42">
@@ -1859,34 +1859,34 @@
         <v>46118</v>
       </c>
       <c r="B42" t="n">
-        <v>23053.5</v>
+        <v>23295.1</v>
       </c>
       <c r="C42" t="n">
-        <v>10416.5</v>
+        <v>10477.6</v>
       </c>
       <c r="D42" t="n">
-        <v>6547.7</v>
+        <v>6603.96</v>
       </c>
       <c r="E42" t="n">
-        <v>46257.8</v>
+        <v>46709.5</v>
       </c>
       <c r="F42" t="n">
-        <v>23908.4</v>
+        <v>24134.7</v>
       </c>
       <c r="G42" t="n">
-        <v>7934.6</v>
+        <v>8026.1</v>
       </c>
       <c r="H42" t="n">
-        <v>52875.1</v>
+        <v>53883.7</v>
       </c>
       <c r="I42" t="n">
-        <v>25154.1</v>
+        <v>25312</v>
       </c>
       <c r="J42" t="n">
-        <v>2510.95</v>
+        <v>2536.65</v>
       </c>
       <c r="K42" t="n">
-        <v>5662</v>
+        <v>5727.1</v>
       </c>
     </row>
     <row r="43">
@@ -1894,34 +1894,34 @@
         <v>46119</v>
       </c>
       <c r="B43" t="n">
-        <v>23295.6</v>
+        <v>23802.3</v>
       </c>
       <c r="C43" t="n">
-        <v>10477.7</v>
+        <v>10557.1</v>
       </c>
       <c r="D43" t="n">
-        <v>6604.09</v>
+        <v>6752.42</v>
       </c>
       <c r="E43" t="n">
-        <v>46712</v>
+        <v>47545.8</v>
       </c>
       <c r="F43" t="n">
-        <v>24134.8</v>
+        <v>24748.9</v>
       </c>
       <c r="G43" t="n">
-        <v>8026.3</v>
+        <v>8193.700000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>53882.5</v>
+        <v>55942.4</v>
       </c>
       <c r="I43" t="n">
-        <v>25312.2</v>
+        <v>25620.5</v>
       </c>
       <c r="J43" t="n">
-        <v>2536.45</v>
+        <v>2623.75</v>
       </c>
       <c r="K43" t="n">
-        <v>5727.2</v>
+        <v>5845.7</v>
       </c>
     </row>
     <row r="44">
@@ -1929,34 +1929,34 @@
         <v>46120</v>
       </c>
       <c r="B44" t="n">
-        <v>23801.8</v>
+        <v>24005.2</v>
       </c>
       <c r="C44" t="n">
-        <v>10557</v>
+        <v>10659.2</v>
       </c>
       <c r="D44" t="n">
-        <v>6752.54</v>
+        <v>6775.84</v>
       </c>
       <c r="E44" t="n">
-        <v>47546.3</v>
+        <v>47886.5</v>
       </c>
       <c r="F44" t="n">
-        <v>24748.8</v>
+        <v>24864</v>
       </c>
       <c r="G44" t="n">
-        <v>8193.6</v>
+        <v>8274.200000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>55944</v>
+        <v>56750.7</v>
       </c>
       <c r="I44" t="n">
-        <v>25620.3</v>
+        <v>25877.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2623.35</v>
+        <v>2621.15</v>
       </c>
       <c r="K44" t="n">
-        <v>5845.6</v>
+        <v>5913.6</v>
       </c>
     </row>
     <row r="45">
@@ -1964,34 +1964,34 @@
         <v>46121</v>
       </c>
       <c r="B45" t="n">
-        <v>24005.1</v>
+        <v>23860.1</v>
       </c>
       <c r="C45" t="n">
-        <v>10659</v>
+        <v>10594.9</v>
       </c>
       <c r="D45" t="n">
-        <v>6775.83</v>
+        <v>6816.9</v>
       </c>
       <c r="E45" t="n">
-        <v>47885.9</v>
+        <v>48155.1</v>
       </c>
       <c r="F45" t="n">
-        <v>24863.4</v>
+        <v>25042.9</v>
       </c>
       <c r="G45" t="n">
-        <v>8273.9</v>
+        <v>8252.299999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>56735.7</v>
+        <v>56487.1</v>
       </c>
       <c r="I45" t="n">
-        <v>25877.4</v>
+        <v>25916.1</v>
       </c>
       <c r="J45" t="n">
-        <v>2621.05</v>
+        <v>2635.65</v>
       </c>
       <c r="K45" t="n">
-        <v>5913.4</v>
+        <v>5900.9</v>
       </c>
     </row>
     <row r="46">
@@ -1999,34 +1999,34 @@
         <v>46122</v>
       </c>
       <c r="B46" t="n">
-        <v>23860.6</v>
+        <v>23823.9</v>
       </c>
       <c r="C46" t="n">
-        <v>10595</v>
+        <v>10605.1</v>
       </c>
       <c r="D46" t="n">
-        <v>6817.02</v>
+        <v>6825.55</v>
       </c>
       <c r="E46" t="n">
-        <v>48155.6</v>
+        <v>47972</v>
       </c>
       <c r="F46" t="n">
-        <v>25043.1</v>
+        <v>25164.7</v>
       </c>
       <c r="G46" t="n">
-        <v>8252.5</v>
+        <v>8266.799999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>56495.2</v>
+        <v>57406.8</v>
       </c>
       <c r="I46" t="n">
-        <v>25916.3</v>
+        <v>25948.9</v>
       </c>
       <c r="J46" t="n">
-        <v>2635.55</v>
+        <v>2636.3</v>
       </c>
       <c r="K46" t="n">
-        <v>5901</v>
+        <v>5928.91</v>
       </c>
     </row>
     <row r="47">
@@ -2034,34 +2034,34 @@
         <v>46124</v>
       </c>
       <c r="B47" t="n">
-        <v>23474</v>
+        <v>23438.1</v>
       </c>
       <c r="C47" t="n">
-        <v>10530.4</v>
+        <v>10523</v>
       </c>
       <c r="D47" t="n">
-        <v>6743.52</v>
+        <v>6740.55</v>
       </c>
       <c r="E47" t="n">
-        <v>47455.9</v>
+        <v>47403</v>
       </c>
       <c r="F47" t="n">
-        <v>24777</v>
+        <v>24791.8</v>
       </c>
       <c r="G47" t="n">
-        <v>8147</v>
+        <v>8130.9</v>
       </c>
       <c r="H47" t="n">
-        <v>56086.6</v>
+        <v>56085.5</v>
       </c>
       <c r="I47" t="n">
-        <v>25787.6</v>
+        <v>25770.2</v>
       </c>
       <c r="J47" t="n">
-        <v>2592.45</v>
+        <v>2587.85</v>
       </c>
       <c r="K47" t="n">
-        <v>5843.5</v>
+        <v>5831.8</v>
       </c>
     </row>
     <row r="48">
@@ -2069,34 +2069,34 @@
         <v>46125</v>
       </c>
       <c r="B48" t="n">
-        <v>23437.6</v>
+        <v>23965.5</v>
       </c>
       <c r="C48" t="n">
-        <v>10522.9</v>
+        <v>10617.9</v>
       </c>
       <c r="D48" t="n">
-        <v>6740.42</v>
+        <v>6890.15</v>
       </c>
       <c r="E48" t="n">
-        <v>47402.5</v>
+        <v>48227.7</v>
       </c>
       <c r="F48" t="n">
-        <v>24791.7</v>
+        <v>25435.7</v>
       </c>
       <c r="G48" t="n">
-        <v>8130.6</v>
+        <v>8268.299999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>56100.3</v>
+        <v>57698.9</v>
       </c>
       <c r="I48" t="n">
-        <v>25770</v>
+        <v>25968.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2587.75</v>
+        <v>2678.15</v>
       </c>
       <c r="K48" t="n">
-        <v>5831.6</v>
+        <v>5947.3</v>
       </c>
     </row>
     <row r="49">
@@ -2104,34 +2104,34 @@
         <v>46126</v>
       </c>
       <c r="B49" t="n">
-        <v>23966.1</v>
+        <v>24054.9</v>
       </c>
       <c r="C49" t="n">
-        <v>10618</v>
+        <v>10624.6</v>
       </c>
       <c r="D49" t="n">
-        <v>6890.22</v>
+        <v>6967.77</v>
       </c>
       <c r="E49" t="n">
-        <v>48228.3</v>
+        <v>48537.7</v>
       </c>
       <c r="F49" t="n">
-        <v>25435.8</v>
+        <v>25830.8</v>
       </c>
       <c r="G49" t="n">
-        <v>8268.4</v>
+        <v>8326.9</v>
       </c>
       <c r="H49" t="n">
-        <v>57701.4</v>
+        <v>58706</v>
       </c>
       <c r="I49" t="n">
-        <v>25968.4</v>
+        <v>26212.7</v>
       </c>
       <c r="J49" t="n">
-        <v>2678.25</v>
+        <v>2705.55</v>
       </c>
       <c r="K49" t="n">
-        <v>5947.4</v>
+        <v>5986.4</v>
       </c>
     </row>
     <row r="50">
@@ -2139,34 +2139,34 @@
         <v>46127</v>
       </c>
       <c r="B50" t="n">
-        <v>24055.4</v>
+        <v>24107.1</v>
       </c>
       <c r="C50" t="n">
-        <v>10624.7</v>
+        <v>10556.1</v>
       </c>
       <c r="D50" t="n">
-        <v>6967.84</v>
+        <v>7028.29</v>
       </c>
       <c r="E50" t="n">
-        <v>48538.2</v>
+        <v>48527.8</v>
       </c>
       <c r="F50" t="n">
-        <v>25830.9</v>
+        <v>26229.3</v>
       </c>
       <c r="G50" t="n">
-        <v>8327</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>58703.5</v>
+        <v>58563.8</v>
       </c>
       <c r="I50" t="n">
-        <v>26212.9</v>
+        <v>26130.4</v>
       </c>
       <c r="J50" t="n">
-        <v>2705.65</v>
+        <v>2716.35</v>
       </c>
       <c r="K50" t="n">
-        <v>5986.5</v>
+        <v>5946.9</v>
       </c>
     </row>
     <row r="51">
@@ -2174,34 +2174,34 @@
         <v>46128</v>
       </c>
       <c r="B51" t="n">
-        <v>24107.7</v>
+        <v>24140.9</v>
       </c>
       <c r="C51" t="n">
-        <v>10556</v>
+        <v>10590.9</v>
       </c>
       <c r="D51" t="n">
-        <v>7028.42</v>
+        <v>7046.74</v>
       </c>
       <c r="E51" t="n">
-        <v>48526.8</v>
+        <v>48661.1</v>
       </c>
       <c r="F51" t="n">
-        <v>26229.9</v>
+        <v>26321.7</v>
       </c>
       <c r="G51" t="n">
-        <v>8264.700000000001</v>
+        <v>8266.4</v>
       </c>
       <c r="H51" t="n">
-        <v>58576.3</v>
+        <v>59430.4</v>
       </c>
       <c r="I51" t="n">
-        <v>26130.7</v>
+        <v>26236.3</v>
       </c>
       <c r="J51" t="n">
-        <v>2716.45</v>
+        <v>2725.15</v>
       </c>
       <c r="K51" t="n">
-        <v>5947.1</v>
+        <v>5920.67</v>
       </c>
     </row>
     <row r="52">
@@ -2209,34 +2209,34 @@
         <v>46129</v>
       </c>
       <c r="B52" t="n">
-        <v>24139.8</v>
+        <v>24651.9</v>
       </c>
       <c r="C52" t="n">
-        <v>10590.7</v>
+        <v>10697.9</v>
       </c>
       <c r="D52" t="n">
-        <v>7046.58</v>
+        <v>7126.42</v>
       </c>
       <c r="E52" t="n">
-        <v>48661.6</v>
+        <v>49453</v>
       </c>
       <c r="F52" t="n">
-        <v>26321.6</v>
+        <v>26684.1</v>
       </c>
       <c r="G52" t="n">
-        <v>8266.200000000001</v>
+        <v>8407.9</v>
       </c>
       <c r="H52" t="n">
-        <v>59431</v>
+        <v>59693.4</v>
       </c>
       <c r="I52" t="n">
-        <v>26235.9</v>
+        <v>26504.1</v>
       </c>
       <c r="J52" t="n">
-        <v>2725.05</v>
+        <v>2777.8</v>
       </c>
       <c r="K52" t="n">
-        <v>5920.47</v>
+        <v>6036.51</v>
       </c>
     </row>
   </sheetData>
@@ -2312,7 +2312,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>6878.96</v>
+        <v>6834.59</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -2327,34 +2327,34 @@
         <v>46072</v>
       </c>
       <c r="B3" t="n">
-        <v>25033.6</v>
+        <v>25234.3</v>
       </c>
       <c r="C3" t="n">
-        <v>10670.2</v>
+        <v>10679.1</v>
       </c>
       <c r="D3" t="n">
-        <v>6865.84</v>
+        <v>6879.21</v>
       </c>
       <c r="E3" t="n">
-        <v>49410</v>
+        <v>49646.3</v>
       </c>
       <c r="F3" t="n">
-        <v>24817.3</v>
+        <v>24896.8</v>
       </c>
       <c r="G3" t="n">
-        <v>8417.9</v>
+        <v>8424.9</v>
       </c>
       <c r="H3" t="n">
-        <v>57084.2</v>
+        <v>57517.5</v>
       </c>
       <c r="I3" t="n">
-        <v>26796.7</v>
+        <v>26847.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2661.95</v>
+        <v>2656.25</v>
       </c>
       <c r="K3" t="n">
-        <v>6065.4</v>
+        <v>6097.6</v>
       </c>
     </row>
     <row r="4">
@@ -2362,34 +2362,34 @@
         <v>46073</v>
       </c>
       <c r="B4" t="n">
-        <v>25236.6</v>
+        <v>25034.1</v>
       </c>
       <c r="C4" t="n">
-        <v>10720.4</v>
+        <v>10670.3</v>
       </c>
       <c r="D4" t="n">
-        <v>6910.63</v>
+        <v>6865.97</v>
       </c>
       <c r="E4" t="n">
-        <v>49624.8</v>
+        <v>49410.5</v>
       </c>
       <c r="F4" t="n">
-        <v>25016.2</v>
+        <v>24817.5</v>
       </c>
       <c r="G4" t="n">
-        <v>8535.4</v>
+        <v>8418.1</v>
       </c>
       <c r="H4" t="n">
-        <v>57088.3</v>
+        <v>57086.7</v>
       </c>
       <c r="I4" t="n">
-        <v>26863.4</v>
+        <v>26796.9</v>
       </c>
       <c r="J4" t="n">
-        <v>2662.2</v>
+        <v>2662.05</v>
       </c>
       <c r="K4" t="n">
-        <v>6135.1</v>
+        <v>6065.5</v>
       </c>
     </row>
     <row r="5">
@@ -2397,34 +2397,34 @@
         <v>46075</v>
       </c>
       <c r="B5" t="n">
-        <v>25176</v>
+        <v>25208.9</v>
       </c>
       <c r="C5" t="n">
-        <v>10703.4</v>
+        <v>10712.6</v>
       </c>
       <c r="D5" t="n">
-        <v>6892.28</v>
+        <v>6903.7</v>
       </c>
       <c r="E5" t="n">
-        <v>49528.4</v>
+        <v>49576.3</v>
       </c>
       <c r="F5" t="n">
-        <v>24911.3</v>
+        <v>24973.5</v>
       </c>
       <c r="G5" t="n">
-        <v>8515.200000000001</v>
+        <v>8526.200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>56981.6</v>
+        <v>57079</v>
       </c>
       <c r="I5" t="n">
-        <v>26826.4</v>
+        <v>26846.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2652.65</v>
+        <v>2656.55</v>
       </c>
       <c r="K5" t="n">
-        <v>6120.4</v>
+        <v>6128.4</v>
       </c>
     </row>
     <row r="6">
@@ -2432,34 +2432,34 @@
         <v>46076</v>
       </c>
       <c r="B6" t="n">
-        <v>24996.5</v>
+        <v>25175.6</v>
       </c>
       <c r="C6" t="n">
-        <v>10692.7</v>
+        <v>10703.3</v>
       </c>
       <c r="D6" t="n">
-        <v>6844.309999999999</v>
+        <v>6892.15</v>
       </c>
       <c r="E6" t="n">
-        <v>48839.5</v>
+        <v>49528.9</v>
       </c>
       <c r="F6" t="n">
-        <v>24735.3</v>
+        <v>24910.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8506.6</v>
+        <v>8515.1</v>
       </c>
       <c r="H6" t="n">
-        <v>56665.8</v>
+        <v>56979.1</v>
       </c>
       <c r="I6" t="n">
-        <v>26891.9</v>
+        <v>26826.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2621.45</v>
+        <v>2652.45</v>
       </c>
       <c r="K6" t="n">
-        <v>6123.3</v>
+        <v>6120.3</v>
       </c>
     </row>
     <row r="7">
@@ -2467,34 +2467,34 @@
         <v>46077</v>
       </c>
       <c r="B7" t="n">
-        <v>25039.3</v>
+        <v>24996.1</v>
       </c>
       <c r="C7" t="n">
-        <v>10712.4</v>
+        <v>10692.6</v>
       </c>
       <c r="D7" t="n">
-        <v>6892.08</v>
+        <v>6844.559999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>49177.5</v>
+        <v>48840</v>
       </c>
       <c r="F7" t="n">
-        <v>24995.3</v>
+        <v>24735.1</v>
       </c>
       <c r="G7" t="n">
-        <v>8539.9</v>
+        <v>8506.5</v>
       </c>
       <c r="H7" t="n">
-        <v>57912</v>
+        <v>56693.3</v>
       </c>
       <c r="I7" t="n">
-        <v>26766.2</v>
+        <v>26891.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2651.55</v>
+        <v>2621.75</v>
       </c>
       <c r="K7" t="n">
-        <v>6136.1</v>
+        <v>6123.2</v>
       </c>
     </row>
     <row r="8">
@@ -2502,34 +2502,34 @@
         <v>46078</v>
       </c>
       <c r="B8" t="n">
-        <v>25181.3</v>
+        <v>25038.9</v>
       </c>
       <c r="C8" t="n">
-        <v>10804.4</v>
+        <v>10712.3</v>
       </c>
       <c r="D8" t="n">
-        <v>6937.66</v>
+        <v>6891.95</v>
       </c>
       <c r="E8" t="n">
-        <v>49392</v>
+        <v>49176.5</v>
       </c>
       <c r="F8" t="n">
-        <v>25270</v>
+        <v>24995</v>
       </c>
       <c r="G8" t="n">
-        <v>8569.6</v>
+        <v>8539.799999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>59285.1</v>
+        <v>57919.5</v>
       </c>
       <c r="I8" t="n">
-        <v>26950</v>
+        <v>26766</v>
       </c>
       <c r="J8" t="n">
-        <v>2660.65</v>
+        <v>2651.45</v>
       </c>
       <c r="K8" t="n">
-        <v>6175.7</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="9">
@@ -2537,34 +2537,34 @@
         <v>46079</v>
       </c>
       <c r="B9" t="n">
-        <v>25253.3</v>
+        <v>25180.7</v>
       </c>
       <c r="C9" t="n">
-        <v>10835.1</v>
+        <v>10804.3</v>
       </c>
       <c r="D9" t="n">
-        <v>6882.360000000001</v>
+        <v>6937.41</v>
       </c>
       <c r="E9" t="n">
-        <v>49229.6</v>
+        <v>49392.5</v>
       </c>
       <c r="F9" t="n">
-        <v>24955.6</v>
+        <v>25270.1</v>
       </c>
       <c r="G9" t="n">
-        <v>8611.700000000001</v>
+        <v>8569.5</v>
       </c>
       <c r="H9" t="n">
-        <v>58435</v>
+        <v>59282.6</v>
       </c>
       <c r="I9" t="n">
-        <v>26389.6</v>
+        <v>26949.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2655.55</v>
+        <v>2660.95</v>
       </c>
       <c r="K9" t="n">
-        <v>6150.7</v>
+        <v>6175.6</v>
       </c>
     </row>
     <row r="10">
@@ -2572,34 +2572,34 @@
         <v>46080</v>
       </c>
       <c r="B10" t="n">
-        <v>25143.7</v>
+        <v>25252.1</v>
       </c>
       <c r="C10" t="n">
-        <v>10862.7</v>
+        <v>10834.9</v>
       </c>
       <c r="D10" t="n">
-        <v>6865.58</v>
+        <v>6881.99</v>
       </c>
       <c r="E10" t="n">
-        <v>48858.5</v>
+        <v>49229.1</v>
       </c>
       <c r="F10" t="n">
-        <v>24914.4</v>
+        <v>24955.4</v>
       </c>
       <c r="G10" t="n">
-        <v>8530.6</v>
+        <v>8611.299999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>58612.7</v>
+        <v>58385</v>
       </c>
       <c r="I10" t="n">
-        <v>26490.4</v>
+        <v>26389</v>
       </c>
       <c r="J10" t="n">
-        <v>2626.65</v>
+        <v>2655.45</v>
       </c>
       <c r="K10" t="n">
-        <v>6095.38</v>
+        <v>6150.4</v>
       </c>
     </row>
     <row r="11">
@@ -2607,34 +2607,34 @@
         <v>46082</v>
       </c>
       <c r="B11" t="n">
-        <v>24946.3</v>
+        <v>24967.8</v>
       </c>
       <c r="C11" t="n">
-        <v>10811.6</v>
+        <v>10810.3</v>
       </c>
       <c r="D11" t="n">
-        <v>6805.95</v>
+        <v>6817.17</v>
       </c>
       <c r="E11" t="n">
-        <v>48368.8</v>
+        <v>48514.6</v>
       </c>
       <c r="F11" t="n">
-        <v>24696.7</v>
+        <v>24680.4</v>
       </c>
       <c r="G11" t="n">
-        <v>8466.4</v>
+        <v>8470.9</v>
       </c>
       <c r="H11" t="n">
-        <v>57488.1</v>
+        <v>57705.8</v>
       </c>
       <c r="I11" t="n">
-        <v>26350.6</v>
+        <v>26383</v>
       </c>
       <c r="J11" t="n">
-        <v>2591.25</v>
+        <v>2605.05</v>
       </c>
       <c r="K11" t="n">
-        <v>6049.58</v>
+        <v>6052.78</v>
       </c>
     </row>
     <row r="12">
@@ -2642,34 +2642,34 @@
         <v>46083</v>
       </c>
       <c r="B12" t="n">
-        <v>24582.2</v>
+        <v>24947.2</v>
       </c>
       <c r="C12" t="n">
-        <v>10789.5</v>
+        <v>10811.7</v>
       </c>
       <c r="D12" t="n">
-        <v>6867.940000000001</v>
+        <v>6806.2</v>
       </c>
       <c r="E12" t="n">
-        <v>48823.6</v>
+        <v>48369.8</v>
       </c>
       <c r="F12" t="n">
-        <v>24935.3</v>
+        <v>24696.9</v>
       </c>
       <c r="G12" t="n">
-        <v>8387.700000000001</v>
+        <v>8466.6</v>
       </c>
       <c r="H12" t="n">
-        <v>57713.1</v>
+        <v>57483.1</v>
       </c>
       <c r="I12" t="n">
-        <v>26156.8</v>
+        <v>26351.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2650.85</v>
+        <v>2591.15</v>
       </c>
       <c r="K12" t="n">
-        <v>5982.2</v>
+        <v>6049.78</v>
       </c>
     </row>
     <row r="13">
@@ -2677,34 +2677,34 @@
         <v>46084</v>
       </c>
       <c r="B13" t="n">
-        <v>23985</v>
+        <v>24583</v>
       </c>
       <c r="C13" t="n">
-        <v>10517.1</v>
+        <v>10789.6</v>
       </c>
       <c r="D13" t="n">
-        <v>6802.5</v>
+        <v>6868.190000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>48413.3</v>
+        <v>48825.6</v>
       </c>
       <c r="F13" t="n">
-        <v>24668</v>
+        <v>24937</v>
       </c>
       <c r="G13" t="n">
-        <v>8165.4</v>
+        <v>8388</v>
       </c>
       <c r="H13" t="n">
-        <v>54951.7</v>
+        <v>57710.6</v>
       </c>
       <c r="I13" t="n">
-        <v>25468.5</v>
+        <v>26157.2</v>
       </c>
       <c r="J13" t="n">
-        <v>2603.45</v>
+        <v>2651.05</v>
       </c>
       <c r="K13" t="n">
-        <v>5813.3</v>
+        <v>5982.4</v>
       </c>
     </row>
     <row r="14">
@@ -2712,34 +2712,34 @@
         <v>46085</v>
       </c>
       <c r="B14" t="n">
-        <v>24302.2</v>
+        <v>23985.8</v>
       </c>
       <c r="C14" t="n">
-        <v>10626.8</v>
+        <v>10517.2</v>
       </c>
       <c r="D14" t="n">
-        <v>6878.04</v>
+        <v>6802.75</v>
       </c>
       <c r="E14" t="n">
-        <v>48753.2</v>
+        <v>48412.8</v>
       </c>
       <c r="F14" t="n">
-        <v>25137.1</v>
+        <v>24667.6</v>
       </c>
       <c r="G14" t="n">
-        <v>8204</v>
+        <v>8166.5</v>
       </c>
       <c r="H14" t="n">
-        <v>56232.9</v>
+        <v>54976.7</v>
       </c>
       <c r="I14" t="n">
-        <v>25602.8</v>
+        <v>25468.9</v>
       </c>
       <c r="J14" t="n">
-        <v>2635.85</v>
+        <v>2603.55</v>
       </c>
       <c r="K14" t="n">
-        <v>5901.9</v>
+        <v>5813.5</v>
       </c>
     </row>
     <row r="15">
@@ -2747,34 +2747,34 @@
         <v>46086</v>
       </c>
       <c r="B15" t="n">
-        <v>23866.2</v>
+        <v>24301.8</v>
       </c>
       <c r="C15" t="n">
-        <v>10407.9</v>
+        <v>10626.7</v>
       </c>
       <c r="D15" t="n">
-        <v>6834.43</v>
+        <v>6877.92</v>
       </c>
       <c r="E15" t="n">
-        <v>48034</v>
+        <v>48752.7</v>
       </c>
       <c r="F15" t="n">
-        <v>25031.4</v>
+        <v>25137</v>
       </c>
       <c r="G15" t="n">
-        <v>8059.2</v>
+        <v>8203.9</v>
       </c>
       <c r="H15" t="n">
-        <v>54563.2</v>
+        <v>56215.4</v>
       </c>
       <c r="I15" t="n">
-        <v>25202.5</v>
+        <v>25602.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2592.85</v>
+        <v>2635.75</v>
       </c>
       <c r="K15" t="n">
-        <v>5793.6</v>
+        <v>5901.8</v>
       </c>
     </row>
     <row r="16">
@@ -2782,34 +2782,34 @@
         <v>46087</v>
       </c>
       <c r="B16" t="n">
-        <v>23640.3</v>
+        <v>23867</v>
       </c>
       <c r="C16" t="n">
-        <v>10318.8</v>
+        <v>10408</v>
       </c>
       <c r="D16" t="n">
-        <v>6733.23</v>
+        <v>6834.68</v>
       </c>
       <c r="E16" t="n">
-        <v>47434.2</v>
+        <v>48032.8</v>
       </c>
       <c r="F16" t="n">
-        <v>24634.2</v>
+        <v>25032.3</v>
       </c>
       <c r="G16" t="n">
-        <v>8017.2</v>
+        <v>8059.4</v>
       </c>
       <c r="H16" t="n">
-        <v>54029.9</v>
+        <v>54575.7</v>
       </c>
       <c r="I16" t="n">
-        <v>25325.2</v>
+        <v>25202.9</v>
       </c>
       <c r="J16" t="n">
-        <v>2522</v>
+        <v>2592.75</v>
       </c>
       <c r="K16" t="n">
-        <v>5723.03</v>
+        <v>5793.8</v>
       </c>
     </row>
     <row r="17">
@@ -2817,34 +2817,34 @@
         <v>46089</v>
       </c>
       <c r="B17" t="n">
-        <v>23222.3</v>
+        <v>23357.4</v>
       </c>
       <c r="C17" t="n">
-        <v>10195.8</v>
+        <v>10244.7</v>
       </c>
       <c r="D17" t="n">
-        <v>6622.45</v>
+        <v>6678.34</v>
       </c>
       <c r="E17" t="n">
-        <v>46613</v>
+        <v>46831</v>
       </c>
       <c r="F17" t="n">
-        <v>24187.4</v>
+        <v>24403</v>
       </c>
       <c r="G17" t="n">
-        <v>7873</v>
+        <v>7921.2</v>
       </c>
       <c r="H17" t="n">
-        <v>52216.5</v>
+        <v>53227.3</v>
       </c>
       <c r="I17" t="n">
-        <v>25042.2</v>
+        <v>25160.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2433.35</v>
+        <v>2493.15</v>
       </c>
       <c r="K17" t="n">
-        <v>5615.9</v>
+        <v>5654.6</v>
       </c>
     </row>
     <row r="18">
@@ -2852,34 +2852,34 @@
         <v>46090</v>
       </c>
       <c r="B18" t="n">
-        <v>23703.1</v>
+        <v>23221.9</v>
       </c>
       <c r="C18" t="n">
-        <v>10307.8</v>
+        <v>10195.7</v>
       </c>
       <c r="D18" t="n">
-        <v>6766.07</v>
+        <v>6623.07</v>
       </c>
       <c r="E18" t="n">
-        <v>47534.3</v>
+        <v>46616</v>
       </c>
       <c r="F18" t="n">
-        <v>24854.1</v>
+        <v>24187.3</v>
       </c>
       <c r="G18" t="n">
-        <v>8000.3</v>
+        <v>7872.9</v>
       </c>
       <c r="H18" t="n">
-        <v>54259.6</v>
+        <v>52231.5</v>
       </c>
       <c r="I18" t="n">
-        <v>25545.7</v>
+        <v>25042</v>
       </c>
       <c r="J18" t="n">
-        <v>2534.05</v>
+        <v>2433.75</v>
       </c>
       <c r="K18" t="n">
-        <v>5764.7</v>
+        <v>5615.8</v>
       </c>
     </row>
     <row r="19">
@@ -2887,34 +2887,34 @@
         <v>46091</v>
       </c>
       <c r="B19" t="n">
-        <v>23809.1</v>
+        <v>23702.6</v>
       </c>
       <c r="C19" t="n">
-        <v>10385.1</v>
+        <v>10307.7</v>
       </c>
       <c r="D19" t="n">
-        <v>6791.25</v>
+        <v>6765.95</v>
       </c>
       <c r="E19" t="n">
-        <v>47744.5</v>
+        <v>47534.8</v>
       </c>
       <c r="F19" t="n">
-        <v>24990.4</v>
+        <v>24854</v>
       </c>
       <c r="G19" t="n">
-        <v>7996.9</v>
+        <v>8000.2</v>
       </c>
       <c r="H19" t="n">
-        <v>55066.9</v>
+        <v>54251.3</v>
       </c>
       <c r="I19" t="n">
-        <v>25945.2</v>
+        <v>25545.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2552.05</v>
+        <v>2534.15</v>
       </c>
       <c r="K19" t="n">
-        <v>5786.9</v>
+        <v>5764.6</v>
       </c>
     </row>
     <row r="20">
@@ -2922,34 +2922,34 @@
         <v>46092</v>
       </c>
       <c r="B20" t="n">
-        <v>23465.2</v>
+        <v>23812.8</v>
       </c>
       <c r="C20" t="n">
-        <v>10272.4</v>
+        <v>10385.4</v>
       </c>
       <c r="D20" t="n">
-        <v>6724.610000000001</v>
+        <v>6792.13</v>
       </c>
       <c r="E20" t="n">
-        <v>47030.3</v>
+        <v>47746.5</v>
       </c>
       <c r="F20" t="n">
-        <v>24768.1</v>
+        <v>24991.9</v>
       </c>
       <c r="G20" t="n">
-        <v>7976.9</v>
+        <v>7998.1</v>
       </c>
       <c r="H20" t="n">
-        <v>54158</v>
+        <v>55064.4</v>
       </c>
       <c r="I20" t="n">
-        <v>25634.7</v>
+        <v>25946.7</v>
       </c>
       <c r="J20" t="n">
-        <v>2505.75</v>
+        <v>2552.65</v>
       </c>
       <c r="K20" t="n">
-        <v>5752.63</v>
+        <v>5787.8</v>
       </c>
     </row>
     <row r="21">
@@ -2957,34 +2957,34 @@
         <v>46093</v>
       </c>
       <c r="B21" t="n">
-        <v>23495</v>
+        <v>23466.3</v>
       </c>
       <c r="C21" t="n">
-        <v>10283.7</v>
+        <v>10272.5</v>
       </c>
       <c r="D21" t="n">
-        <v>6676.01</v>
+        <v>6724.49</v>
       </c>
       <c r="E21" t="n">
-        <v>46739.9</v>
+        <v>47199.39999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>24514</v>
+        <v>24768</v>
       </c>
       <c r="G21" t="n">
-        <v>7964.5</v>
+        <v>7977.3</v>
       </c>
       <c r="H21" t="n">
-        <v>53462.2</v>
+        <v>54153</v>
       </c>
       <c r="I21" t="n">
-        <v>25453.6</v>
+        <v>25635.2</v>
       </c>
       <c r="J21" t="n">
-        <v>2490.95</v>
+        <v>2506.45</v>
       </c>
       <c r="K21" t="n">
-        <v>5725.3</v>
+        <v>5752.93</v>
       </c>
     </row>
     <row r="22">
@@ -2992,34 +2992,34 @@
         <v>46094</v>
       </c>
       <c r="B22" t="n">
-        <v>23329.3</v>
+        <v>23493.9</v>
       </c>
       <c r="C22" t="n">
-        <v>10240.1</v>
+        <v>10283.6</v>
       </c>
       <c r="D22" t="n">
-        <v>6621.04</v>
+        <v>6675.76</v>
       </c>
       <c r="E22" t="n">
-        <v>46475.1</v>
+        <v>46740.4</v>
       </c>
       <c r="F22" t="n">
-        <v>24321.2</v>
+        <v>24514.1</v>
       </c>
       <c r="G22" t="n">
-        <v>7875.6</v>
+        <v>7964.1</v>
       </c>
       <c r="H22" t="n">
-        <v>53150.3</v>
+        <v>53442.2</v>
       </c>
       <c r="I22" t="n">
-        <v>25400.4</v>
+        <v>25453.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2474.5</v>
+        <v>2490.75</v>
       </c>
       <c r="K22" t="n">
-        <v>5689.36</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="23">
@@ -3027,34 +3027,34 @@
         <v>46096</v>
       </c>
       <c r="B23" t="n">
-        <v>23428.6</v>
+        <v>23369.4</v>
       </c>
       <c r="C23" t="n">
-        <v>10268.8</v>
+        <v>10252.1</v>
       </c>
       <c r="D23" t="n">
-        <v>6645.48</v>
+        <v>6618.15</v>
       </c>
       <c r="E23" t="n">
-        <v>46641.8</v>
+        <v>46472</v>
       </c>
       <c r="F23" t="n">
-        <v>24424</v>
+        <v>24304.8</v>
       </c>
       <c r="G23" t="n">
-        <v>7919.5</v>
+        <v>7899.3</v>
       </c>
       <c r="H23" t="n">
-        <v>53651.9</v>
+        <v>52934.6</v>
       </c>
       <c r="I23" t="n">
-        <v>25450.7</v>
+        <v>25421.2</v>
       </c>
       <c r="J23" t="n">
-        <v>2489.45</v>
+        <v>2472.65</v>
       </c>
       <c r="K23" t="n">
-        <v>5713.9</v>
+        <v>5699.4</v>
       </c>
     </row>
     <row r="24">
@@ -3062,34 +3062,34 @@
         <v>46097</v>
       </c>
       <c r="B24" t="n">
-        <v>23625.4</v>
+        <v>23429.7</v>
       </c>
       <c r="C24" t="n">
-        <v>10347</v>
+        <v>10268.7</v>
       </c>
       <c r="D24" t="n">
-        <v>6698.12</v>
+        <v>6645.73</v>
       </c>
       <c r="E24" t="n">
-        <v>46926.7</v>
+        <v>46642.3</v>
       </c>
       <c r="F24" t="n">
-        <v>24652</v>
+        <v>24424.7</v>
       </c>
       <c r="G24" t="n">
-        <v>7949</v>
+        <v>7919.2</v>
       </c>
       <c r="H24" t="n">
-        <v>54337.6</v>
+        <v>53659.4</v>
       </c>
       <c r="I24" t="n">
-        <v>25861.7</v>
+        <v>25450.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2501.65</v>
+        <v>2489.55</v>
       </c>
       <c r="K24" t="n">
-        <v>5754.2</v>
+        <v>5714.1</v>
       </c>
     </row>
     <row r="25">
@@ -3097,34 +3097,34 @@
         <v>46098</v>
       </c>
       <c r="B25" t="n">
-        <v>23670.5</v>
+        <v>23624.3</v>
       </c>
       <c r="C25" t="n">
-        <v>10362.5</v>
+        <v>10347.1</v>
       </c>
       <c r="D25" t="n">
-        <v>6711.68</v>
+        <v>6697.87</v>
       </c>
       <c r="E25" t="n">
-        <v>46944.6</v>
+        <v>46926.2</v>
       </c>
       <c r="F25" t="n">
-        <v>24775.5</v>
+        <v>24651.7</v>
       </c>
       <c r="G25" t="n">
-        <v>7956.2</v>
+        <v>7949.3</v>
       </c>
       <c r="H25" t="n">
-        <v>54274.4</v>
+        <v>54340.1</v>
       </c>
       <c r="I25" t="n">
-        <v>25859.5</v>
+        <v>25861.8</v>
       </c>
       <c r="J25" t="n">
-        <v>2517.85</v>
+        <v>2501.55</v>
       </c>
       <c r="K25" t="n">
-        <v>5756.4</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="26">
@@ -3132,34 +3132,34 @@
         <v>46099</v>
       </c>
       <c r="B26" t="n">
-        <v>23169.5</v>
+        <v>23669.4</v>
       </c>
       <c r="C26" t="n">
-        <v>10221.1</v>
+        <v>10362.4</v>
       </c>
       <c r="D26" t="n">
-        <v>6698.99</v>
+        <v>6711.43</v>
       </c>
       <c r="E26" t="n">
-        <v>46157</v>
+        <v>46944.1</v>
       </c>
       <c r="F26" t="n">
-        <v>24395.2</v>
+        <v>24776</v>
       </c>
       <c r="G26" t="n">
-        <v>7897.7</v>
+        <v>7955.8</v>
       </c>
       <c r="H26" t="n">
-        <v>53599.6</v>
+        <v>54291.9</v>
       </c>
       <c r="I26" t="n">
-        <v>25416.9</v>
+        <v>25859.1</v>
       </c>
       <c r="J26" t="n">
-        <v>2474.45</v>
+        <v>2517.65</v>
       </c>
       <c r="K26" t="n">
-        <v>5655.5</v>
+        <v>5756.1</v>
       </c>
     </row>
     <row r="27">
@@ -3167,32 +3167,32 @@
         <v>46100</v>
       </c>
       <c r="B27" t="n">
-        <v>23019.7</v>
+        <v>23171.8</v>
       </c>
       <c r="C27" t="n">
-        <v>10069.6</v>
+        <v>10221.2</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>46139.2</v>
+        <v>46158</v>
       </c>
       <c r="F27" t="n">
-        <v>24407.7</v>
+        <v>24394.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7842.7</v>
+        <v>7898.5</v>
       </c>
       <c r="H27" t="n">
-        <v>53401.2</v>
+        <v>53624.6</v>
       </c>
       <c r="I27" t="n">
-        <v>25368.8</v>
+        <v>25417.7</v>
       </c>
       <c r="J27" t="n">
-        <v>2508.55</v>
+        <v>2474.35</v>
       </c>
       <c r="K27" t="n">
-        <v>5655.4</v>
+        <v>5656.1</v>
       </c>
     </row>
     <row r="28">
@@ -3200,34 +3200,34 @@
         <v>46101</v>
       </c>
       <c r="B28" t="n">
-        <v>22214.3</v>
+        <v>23020.2</v>
       </c>
       <c r="C28" t="n">
-        <v>9839.299999999999</v>
+        <v>10069.7</v>
       </c>
       <c r="D28" t="n">
-        <v>6537.12</v>
+        <v>6619.34</v>
       </c>
       <c r="E28" t="n">
-        <v>45803.1</v>
+        <v>46139.7</v>
       </c>
       <c r="F28" t="n">
-        <v>24000.4</v>
+        <v>24407.8</v>
       </c>
       <c r="G28" t="n">
-        <v>7613.8</v>
+        <v>7843</v>
       </c>
       <c r="H28" t="n">
-        <v>51317.2</v>
+        <v>53403.2</v>
       </c>
       <c r="I28" t="n">
-        <v>24770.8</v>
+        <v>25369.1</v>
       </c>
       <c r="J28" t="n">
-        <v>2452.1</v>
+        <v>2508.75</v>
       </c>
       <c r="K28" t="n">
-        <v>5474.95</v>
+        <v>5655.6</v>
       </c>
     </row>
     <row r="29">
@@ -3235,34 +3235,34 @@
         <v>46103</v>
       </c>
       <c r="B29" t="n">
-        <v>21975.6</v>
+        <v>21912.6</v>
       </c>
       <c r="C29" t="n">
-        <v>9794.1</v>
+        <v>9776</v>
       </c>
       <c r="D29" t="n">
-        <v>6488.5</v>
+        <v>6460.09</v>
       </c>
       <c r="E29" t="n">
-        <v>45538.6</v>
+        <v>45343.8</v>
       </c>
       <c r="F29" t="n">
-        <v>23794.4</v>
+        <v>23718.3</v>
       </c>
       <c r="G29" t="n">
-        <v>7540.6</v>
+        <v>7513</v>
       </c>
       <c r="H29" t="n">
-        <v>51180.5</v>
+        <v>50808.8</v>
       </c>
       <c r="I29" t="n">
-        <v>24659.3</v>
+        <v>24609.8</v>
       </c>
       <c r="J29" t="n">
-        <v>2432.65</v>
+        <v>2420.35</v>
       </c>
       <c r="K29" t="n">
-        <v>5419.6</v>
+        <v>5402.6</v>
       </c>
     </row>
     <row r="30">
@@ -3270,34 +3270,34 @@
         <v>46104</v>
       </c>
       <c r="B30" t="n">
-        <v>22845</v>
+        <v>21979.4</v>
       </c>
       <c r="C30" t="n">
-        <v>9963.6</v>
+        <v>9794.299999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>6594.07</v>
+        <v>6488.75</v>
       </c>
       <c r="E30" t="n">
-        <v>46290.6</v>
+        <v>45541.6</v>
       </c>
       <c r="F30" t="n">
-        <v>24241.8</v>
+        <v>23797.5</v>
       </c>
       <c r="G30" t="n">
-        <v>7798.8</v>
+        <v>7541.9</v>
       </c>
       <c r="H30" t="n">
-        <v>53018.2</v>
+        <v>51188</v>
       </c>
       <c r="I30" t="n">
-        <v>24982.7</v>
+        <v>24660.8</v>
       </c>
       <c r="J30" t="n">
-        <v>2500.55</v>
+        <v>2433.15</v>
       </c>
       <c r="K30" t="n">
-        <v>5617.7</v>
+        <v>5420.5</v>
       </c>
     </row>
     <row r="31">
@@ -3305,34 +3305,34 @@
         <v>46105</v>
       </c>
       <c r="B31" t="n">
-        <v>22891</v>
+        <v>22844.5</v>
       </c>
       <c r="C31" t="n">
-        <v>10015.3</v>
+        <v>9963.5</v>
       </c>
       <c r="D31" t="n">
-        <v>6599.97</v>
+        <v>6593.95</v>
       </c>
       <c r="E31" t="n">
-        <v>46448</v>
+        <v>46286.1</v>
       </c>
       <c r="F31" t="n">
-        <v>24205</v>
+        <v>24241.5</v>
       </c>
       <c r="G31" t="n">
-        <v>7815.7</v>
+        <v>7798.6</v>
       </c>
       <c r="H31" t="n">
-        <v>53500.6</v>
+        <v>52995.7</v>
       </c>
       <c r="I31" t="n">
-        <v>25050.4</v>
+        <v>24982.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2535.75</v>
+        <v>2500.15</v>
       </c>
       <c r="K31" t="n">
-        <v>5645.68</v>
+        <v>5617.6</v>
       </c>
     </row>
     <row r="32">
@@ -3340,34 +3340,34 @@
         <v>46106</v>
       </c>
       <c r="B32" t="n">
-        <v>22870.1</v>
+        <v>22889.8</v>
       </c>
       <c r="C32" t="n">
-        <v>10085.7</v>
+        <v>10015.1</v>
       </c>
       <c r="D32" t="n">
-        <v>6581</v>
+        <v>6599.72</v>
       </c>
       <c r="E32" t="n">
-        <v>46359.5</v>
+        <v>46448.5</v>
       </c>
       <c r="F32" t="n">
-        <v>24114.6</v>
+        <v>24204.9</v>
       </c>
       <c r="G32" t="n">
-        <v>7815.5</v>
+        <v>7815.3</v>
       </c>
       <c r="H32" t="n">
-        <v>53878.5</v>
+        <v>53498.1</v>
       </c>
       <c r="I32" t="n">
-        <v>25259.3</v>
+        <v>25050</v>
       </c>
       <c r="J32" t="n">
-        <v>2530.75</v>
+        <v>2535.85</v>
       </c>
       <c r="K32" t="n">
-        <v>5621.51</v>
+        <v>5645.38</v>
       </c>
     </row>
     <row r="33">
@@ -3375,34 +3375,34 @@
         <v>46107</v>
       </c>
       <c r="B33" t="n">
-        <v>22692.5</v>
+        <v>22871.3</v>
       </c>
       <c r="C33" t="n">
-        <v>9965.799999999999</v>
+        <v>10085.8</v>
       </c>
       <c r="D33" t="n">
-        <v>6506.25</v>
+        <v>6581.25</v>
       </c>
       <c r="E33" t="n">
-        <v>46181.1</v>
+        <v>46358.7</v>
       </c>
       <c r="F33" t="n">
-        <v>23682.7</v>
+        <v>24114.4</v>
       </c>
       <c r="G33" t="n">
-        <v>7780.5</v>
+        <v>7815.9</v>
       </c>
       <c r="H33" t="n">
-        <v>52923.6</v>
+        <v>53886</v>
       </c>
       <c r="I33" t="n">
-        <v>24768.8</v>
+        <v>25259.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2508.55</v>
+        <v>2530.85</v>
       </c>
       <c r="K33" t="n">
-        <v>5573</v>
+        <v>5621.81</v>
       </c>
     </row>
     <row r="34">
@@ -3410,34 +3410,34 @@
         <v>46108</v>
       </c>
       <c r="B34" t="n">
-        <v>22101.1</v>
+        <v>22693.7</v>
       </c>
       <c r="C34" t="n">
-        <v>9895.299999999999</v>
+        <v>9966</v>
       </c>
       <c r="D34" t="n">
-        <v>6355.25</v>
+        <v>6506.5</v>
       </c>
       <c r="E34" t="n">
-        <v>45061.5</v>
+        <v>46185</v>
       </c>
       <c r="F34" t="n">
-        <v>23069.6</v>
+        <v>23682.9</v>
       </c>
       <c r="G34" t="n">
-        <v>7646.4</v>
+        <v>7780.9</v>
       </c>
       <c r="H34" t="n">
-        <v>51137.7</v>
+        <v>52941.1</v>
       </c>
       <c r="I34" t="n">
-        <v>24627.5</v>
+        <v>24769.2</v>
       </c>
       <c r="J34" t="n">
-        <v>2443.2</v>
+        <v>2508.75</v>
       </c>
       <c r="K34" t="n">
-        <v>5455.22</v>
+        <v>5573.3</v>
       </c>
     </row>
     <row r="35">
@@ -3445,34 +3445,34 @@
         <v>46110</v>
       </c>
       <c r="B35" t="n">
-        <v>22031.4</v>
+        <v>22033.7</v>
       </c>
       <c r="C35" t="n">
-        <v>9879.4</v>
+        <v>9881.700000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>6340.21</v>
+        <v>6337.22</v>
       </c>
       <c r="E35" t="n">
-        <v>44945.6</v>
+        <v>44942.8</v>
       </c>
       <c r="F35" t="n">
-        <v>23027.2</v>
+        <v>23006</v>
       </c>
       <c r="G35" t="n">
-        <v>7618.7</v>
+        <v>7623.5</v>
       </c>
       <c r="H35" t="n">
-        <v>50609</v>
+        <v>50871.5</v>
       </c>
       <c r="I35" t="n">
-        <v>24593.4</v>
+        <v>24599.6</v>
       </c>
       <c r="J35" t="n">
-        <v>2430.85</v>
+        <v>2435.15</v>
       </c>
       <c r="K35" t="n">
-        <v>5435.4</v>
+        <v>5438.9</v>
       </c>
     </row>
     <row r="36">
@@ -3480,34 +3480,34 @@
         <v>46111</v>
       </c>
       <c r="B36" t="n">
-        <v>22434.6</v>
+        <v>22030.8</v>
       </c>
       <c r="C36" t="n">
-        <v>10070.4</v>
+        <v>9879.299999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>6341.38</v>
+        <v>6340.08</v>
       </c>
       <c r="E36" t="n">
-        <v>45225.5</v>
+        <v>44943.2</v>
       </c>
       <c r="F36" t="n">
-        <v>22920.3</v>
+        <v>23027</v>
       </c>
       <c r="G36" t="n">
-        <v>7722.7</v>
+        <v>7618.6</v>
       </c>
       <c r="H36" t="n">
-        <v>51054.8</v>
+        <v>50611.5</v>
       </c>
       <c r="I36" t="n">
-        <v>24724.4</v>
+        <v>24593.1</v>
       </c>
       <c r="J36" t="n">
-        <v>2409.85</v>
+        <v>2430.65</v>
       </c>
       <c r="K36" t="n">
-        <v>5500.9</v>
+        <v>5435.2</v>
       </c>
     </row>
     <row r="37">
@@ -3515,34 +3515,34 @@
         <v>46112</v>
       </c>
       <c r="B37" t="n">
-        <v>23026.2</v>
+        <v>22434.1</v>
       </c>
       <c r="C37" t="n">
-        <v>10279.9</v>
+        <v>10070.3</v>
       </c>
       <c r="D37" t="n">
-        <v>6530.15</v>
+        <v>6341.26</v>
       </c>
       <c r="E37" t="n">
-        <v>46230.95</v>
+        <v>45226</v>
       </c>
       <c r="F37" t="n">
-        <v>23777.1</v>
+        <v>22920</v>
       </c>
       <c r="G37" t="n">
-        <v>7921.4</v>
+        <v>7722.4</v>
       </c>
       <c r="H37" t="n">
-        <v>53050.8</v>
+        <v>51049.8</v>
       </c>
       <c r="I37" t="n">
-        <v>25317.1</v>
+        <v>24724.2</v>
       </c>
       <c r="J37" t="n">
-        <v>2494.15</v>
+        <v>2409.75</v>
       </c>
       <c r="K37" t="n">
-        <v>5653.5</v>
+        <v>5500.7</v>
       </c>
     </row>
     <row r="38">
@@ -3550,34 +3550,34 @@
         <v>46113</v>
       </c>
       <c r="B38" t="n">
-        <v>23289</v>
+        <v>23025</v>
       </c>
       <c r="C38" t="n">
-        <v>10416.2</v>
+        <v>10279.8</v>
       </c>
       <c r="D38" t="n">
-        <v>6572.13</v>
+        <v>6529.9</v>
       </c>
       <c r="E38" t="n">
-        <v>46561.8</v>
+        <v>46313.4</v>
       </c>
       <c r="F38" t="n">
-        <v>23996.1</v>
+        <v>23775.3</v>
       </c>
       <c r="G38" t="n">
-        <v>7976.6</v>
+        <v>7921</v>
       </c>
       <c r="H38" t="n">
-        <v>54233.9</v>
+        <v>53025.8</v>
       </c>
       <c r="I38" t="n">
-        <v>25315.3</v>
+        <v>25316.6</v>
       </c>
       <c r="J38" t="n">
-        <v>2510.15</v>
+        <v>2494.05</v>
       </c>
       <c r="K38" t="n">
-        <v>5720.9</v>
+        <v>5653.2</v>
       </c>
     </row>
     <row r="39">
@@ -3585,34 +3585,34 @@
         <v>46114</v>
       </c>
       <c r="B39" t="n">
-        <v>23217.6</v>
+        <v>23290.2</v>
       </c>
       <c r="C39" t="n">
-        <v>10451.6</v>
+        <v>10416.3</v>
       </c>
       <c r="D39" t="n">
-        <v>6583.360000000001</v>
+        <v>6572.38</v>
       </c>
       <c r="E39" t="n">
-        <v>46522.4</v>
+        <v>46564.3</v>
       </c>
       <c r="F39" t="n">
-        <v>24030.5</v>
+        <v>23997.5</v>
       </c>
       <c r="G39" t="n">
-        <v>7990.9</v>
+        <v>7977.1</v>
       </c>
       <c r="H39" t="n">
-        <v>53247.5</v>
+        <v>54235.3</v>
       </c>
       <c r="I39" t="n">
-        <v>25270.4</v>
+        <v>25315.7</v>
       </c>
       <c r="J39" t="n">
-        <v>2530.55</v>
+        <v>2510.35</v>
       </c>
       <c r="K39" t="n">
-        <v>5701.47</v>
+        <v>5721.2</v>
       </c>
     </row>
     <row r="40">
@@ -3620,34 +3620,34 @@
         <v>46115</v>
       </c>
       <c r="B40" t="n">
-        <v>23127.3</v>
+        <v>23218.1</v>
       </c>
       <c r="C40" t="n">
-        <v>10432</v>
+        <v>10451.7</v>
       </c>
       <c r="D40" t="n">
-        <v>6563.67</v>
+        <v>6583.43</v>
       </c>
       <c r="E40" t="n">
-        <v>46407.7</v>
+        <v>46522.1</v>
       </c>
       <c r="F40" t="n">
-        <v>23957.4</v>
+        <v>24030.1</v>
       </c>
       <c r="G40" t="n">
-        <v>7960.4</v>
+        <v>7991</v>
       </c>
       <c r="H40" t="n">
-        <v>53165.2</v>
+        <v>53243.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25188.7</v>
+        <v>25270.6</v>
       </c>
       <c r="J40" t="n">
-        <v>2519.65</v>
+        <v>2530.45</v>
       </c>
       <c r="K40" t="n">
-        <v>5679.77</v>
+        <v>5701.57</v>
       </c>
     </row>
     <row r="41">
@@ -3655,34 +3655,34 @@
         <v>46117</v>
       </c>
       <c r="B41" t="n">
-        <v>23052.9</v>
+        <v>23043.8</v>
       </c>
       <c r="C41" t="n">
-        <v>10416.4</v>
+        <v>10414.5</v>
       </c>
       <c r="D41" t="n">
-        <v>6547.57</v>
+        <v>6541.72</v>
       </c>
       <c r="E41" t="n">
-        <v>46258.3</v>
+        <v>46240.7</v>
       </c>
       <c r="F41" t="n">
-        <v>23907.8</v>
+        <v>23893</v>
       </c>
       <c r="G41" t="n">
-        <v>7934.5</v>
+        <v>7931.5</v>
       </c>
       <c r="H41" t="n">
-        <v>52872.6</v>
+        <v>53059.2</v>
       </c>
       <c r="I41" t="n">
-        <v>25153.9</v>
+        <v>25149.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2510.85</v>
+        <v>2508.95</v>
       </c>
       <c r="K41" t="n">
-        <v>5661.8</v>
+        <v>5659.6</v>
       </c>
     </row>
     <row r="42">
@@ -3690,34 +3690,34 @@
         <v>46118</v>
       </c>
       <c r="B42" t="n">
-        <v>23295.1</v>
+        <v>23053.5</v>
       </c>
       <c r="C42" t="n">
-        <v>10477.6</v>
+        <v>10416.5</v>
       </c>
       <c r="D42" t="n">
-        <v>6603.96</v>
+        <v>6547.7</v>
       </c>
       <c r="E42" t="n">
-        <v>46709.5</v>
+        <v>46257.8</v>
       </c>
       <c r="F42" t="n">
-        <v>24134.7</v>
+        <v>23908.4</v>
       </c>
       <c r="G42" t="n">
-        <v>8026.1</v>
+        <v>7934.6</v>
       </c>
       <c r="H42" t="n">
-        <v>53883.7</v>
+        <v>52875.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25312</v>
+        <v>25154.1</v>
       </c>
       <c r="J42" t="n">
-        <v>2536.65</v>
+        <v>2510.95</v>
       </c>
       <c r="K42" t="n">
-        <v>5727.1</v>
+        <v>5662</v>
       </c>
     </row>
     <row r="43">
@@ -3725,34 +3725,34 @@
         <v>46119</v>
       </c>
       <c r="B43" t="n">
-        <v>23802.3</v>
+        <v>23295.6</v>
       </c>
       <c r="C43" t="n">
-        <v>10557.1</v>
+        <v>10477.7</v>
       </c>
       <c r="D43" t="n">
-        <v>6752.42</v>
+        <v>6604.09</v>
       </c>
       <c r="E43" t="n">
-        <v>47545.8</v>
+        <v>46712</v>
       </c>
       <c r="F43" t="n">
-        <v>24748.9</v>
+        <v>24134.8</v>
       </c>
       <c r="G43" t="n">
-        <v>8193.700000000001</v>
+        <v>8026.3</v>
       </c>
       <c r="H43" t="n">
-        <v>55942.4</v>
+        <v>53882.5</v>
       </c>
       <c r="I43" t="n">
-        <v>25620.5</v>
+        <v>25312.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2623.75</v>
+        <v>2536.45</v>
       </c>
       <c r="K43" t="n">
-        <v>5845.7</v>
+        <v>5727.2</v>
       </c>
     </row>
     <row r="44">
@@ -3760,34 +3760,34 @@
         <v>46120</v>
       </c>
       <c r="B44" t="n">
-        <v>24005.2</v>
+        <v>23801.8</v>
       </c>
       <c r="C44" t="n">
-        <v>10659.2</v>
+        <v>10557</v>
       </c>
       <c r="D44" t="n">
-        <v>6775.84</v>
+        <v>6752.54</v>
       </c>
       <c r="E44" t="n">
-        <v>47886.5</v>
+        <v>47546.3</v>
       </c>
       <c r="F44" t="n">
-        <v>24864</v>
+        <v>24748.8</v>
       </c>
       <c r="G44" t="n">
-        <v>8274.200000000001</v>
+        <v>8193.6</v>
       </c>
       <c r="H44" t="n">
-        <v>56750.7</v>
+        <v>55944</v>
       </c>
       <c r="I44" t="n">
-        <v>25877.5</v>
+        <v>25620.3</v>
       </c>
       <c r="J44" t="n">
-        <v>2621.15</v>
+        <v>2623.35</v>
       </c>
       <c r="K44" t="n">
-        <v>5913.6</v>
+        <v>5845.6</v>
       </c>
     </row>
     <row r="45">
@@ -3795,34 +3795,34 @@
         <v>46121</v>
       </c>
       <c r="B45" t="n">
-        <v>23860.1</v>
+        <v>24005.1</v>
       </c>
       <c r="C45" t="n">
-        <v>10594.9</v>
+        <v>10659</v>
       </c>
       <c r="D45" t="n">
-        <v>6816.9</v>
+        <v>6775.83</v>
       </c>
       <c r="E45" t="n">
-        <v>48155.1</v>
+        <v>47885.9</v>
       </c>
       <c r="F45" t="n">
-        <v>25042.9</v>
+        <v>24863.4</v>
       </c>
       <c r="G45" t="n">
-        <v>8252.299999999999</v>
+        <v>8273.9</v>
       </c>
       <c r="H45" t="n">
-        <v>56487.1</v>
+        <v>56735.7</v>
       </c>
       <c r="I45" t="n">
-        <v>25916.1</v>
+        <v>25877.4</v>
       </c>
       <c r="J45" t="n">
-        <v>2635.65</v>
+        <v>2621.05</v>
       </c>
       <c r="K45" t="n">
-        <v>5900.9</v>
+        <v>5913.4</v>
       </c>
     </row>
     <row r="46">
@@ -3830,34 +3830,34 @@
         <v>46122</v>
       </c>
       <c r="B46" t="n">
-        <v>23823.9</v>
+        <v>23860.6</v>
       </c>
       <c r="C46" t="n">
-        <v>10605.1</v>
+        <v>10595</v>
       </c>
       <c r="D46" t="n">
-        <v>6825.55</v>
+        <v>6817.02</v>
       </c>
       <c r="E46" t="n">
-        <v>47972</v>
+        <v>48155.6</v>
       </c>
       <c r="F46" t="n">
-        <v>25164.7</v>
+        <v>25043.1</v>
       </c>
       <c r="G46" t="n">
-        <v>8266.799999999999</v>
+        <v>8252.5</v>
       </c>
       <c r="H46" t="n">
-        <v>57406.8</v>
+        <v>56495.2</v>
       </c>
       <c r="I46" t="n">
-        <v>25948.9</v>
+        <v>25916.3</v>
       </c>
       <c r="J46" t="n">
-        <v>2636.3</v>
+        <v>2635.55</v>
       </c>
       <c r="K46" t="n">
-        <v>5928.91</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="47">
@@ -3865,34 +3865,34 @@
         <v>46124</v>
       </c>
       <c r="B47" t="n">
-        <v>23438.1</v>
+        <v>23474</v>
       </c>
       <c r="C47" t="n">
-        <v>10523</v>
+        <v>10530.4</v>
       </c>
       <c r="D47" t="n">
-        <v>6740.55</v>
+        <v>6743.52</v>
       </c>
       <c r="E47" t="n">
-        <v>47403</v>
+        <v>47455.9</v>
       </c>
       <c r="F47" t="n">
-        <v>24791.8</v>
+        <v>24777</v>
       </c>
       <c r="G47" t="n">
-        <v>8130.9</v>
+        <v>8147</v>
       </c>
       <c r="H47" t="n">
-        <v>56085.5</v>
+        <v>56086.6</v>
       </c>
       <c r="I47" t="n">
-        <v>25770.2</v>
+        <v>25787.6</v>
       </c>
       <c r="J47" t="n">
-        <v>2587.85</v>
+        <v>2592.45</v>
       </c>
       <c r="K47" t="n">
-        <v>5831.8</v>
+        <v>5843.5</v>
       </c>
     </row>
     <row r="48">
@@ -3900,34 +3900,34 @@
         <v>46125</v>
       </c>
       <c r="B48" t="n">
-        <v>23965.5</v>
+        <v>23437.6</v>
       </c>
       <c r="C48" t="n">
-        <v>10617.9</v>
+        <v>10522.9</v>
       </c>
       <c r="D48" t="n">
-        <v>6890.15</v>
+        <v>6740.42</v>
       </c>
       <c r="E48" t="n">
-        <v>48227.7</v>
+        <v>47402.5</v>
       </c>
       <c r="F48" t="n">
-        <v>25435.7</v>
+        <v>24791.7</v>
       </c>
       <c r="G48" t="n">
-        <v>8268.299999999999</v>
+        <v>8130.6</v>
       </c>
       <c r="H48" t="n">
-        <v>57698.9</v>
+        <v>56100.3</v>
       </c>
       <c r="I48" t="n">
-        <v>25968.2</v>
+        <v>25770</v>
       </c>
       <c r="J48" t="n">
-        <v>2678.15</v>
+        <v>2587.75</v>
       </c>
       <c r="K48" t="n">
-        <v>5947.3</v>
+        <v>5831.6</v>
       </c>
     </row>
     <row r="49">
@@ -3935,34 +3935,34 @@
         <v>46126</v>
       </c>
       <c r="B49" t="n">
-        <v>24054.9</v>
+        <v>23966.1</v>
       </c>
       <c r="C49" t="n">
-        <v>10624.6</v>
+        <v>10618</v>
       </c>
       <c r="D49" t="n">
-        <v>6967.77</v>
+        <v>6890.22</v>
       </c>
       <c r="E49" t="n">
-        <v>48537.7</v>
+        <v>48228.3</v>
       </c>
       <c r="F49" t="n">
-        <v>25830.8</v>
+        <v>25435.8</v>
       </c>
       <c r="G49" t="n">
-        <v>8326.9</v>
+        <v>8268.4</v>
       </c>
       <c r="H49" t="n">
-        <v>58706</v>
+        <v>57701.4</v>
       </c>
       <c r="I49" t="n">
-        <v>26212.7</v>
+        <v>25968.4</v>
       </c>
       <c r="J49" t="n">
-        <v>2705.55</v>
+        <v>2678.25</v>
       </c>
       <c r="K49" t="n">
-        <v>5986.4</v>
+        <v>5947.4</v>
       </c>
     </row>
     <row r="50">
@@ -3970,34 +3970,34 @@
         <v>46127</v>
       </c>
       <c r="B50" t="n">
-        <v>24107.1</v>
+        <v>24055.4</v>
       </c>
       <c r="C50" t="n">
-        <v>10556.1</v>
+        <v>10624.7</v>
       </c>
       <c r="D50" t="n">
-        <v>7028.29</v>
+        <v>6967.84</v>
       </c>
       <c r="E50" t="n">
-        <v>48527.8</v>
+        <v>48538.2</v>
       </c>
       <c r="F50" t="n">
-        <v>26229.3</v>
+        <v>25830.9</v>
       </c>
       <c r="G50" t="n">
-        <v>8264.799999999999</v>
+        <v>8327</v>
       </c>
       <c r="H50" t="n">
-        <v>58563.8</v>
+        <v>58703.5</v>
       </c>
       <c r="I50" t="n">
-        <v>26130.4</v>
+        <v>26212.9</v>
       </c>
       <c r="J50" t="n">
-        <v>2716.35</v>
+        <v>2705.65</v>
       </c>
       <c r="K50" t="n">
-        <v>5946.9</v>
+        <v>5986.5</v>
       </c>
     </row>
     <row r="51">
@@ -4005,34 +4005,34 @@
         <v>46128</v>
       </c>
       <c r="B51" t="n">
-        <v>24140.9</v>
+        <v>24107.7</v>
       </c>
       <c r="C51" t="n">
-        <v>10590.9</v>
+        <v>10556</v>
       </c>
       <c r="D51" t="n">
-        <v>7046.74</v>
+        <v>7028.42</v>
       </c>
       <c r="E51" t="n">
-        <v>48661.1</v>
+        <v>48526.8</v>
       </c>
       <c r="F51" t="n">
-        <v>26321.7</v>
+        <v>26229.9</v>
       </c>
       <c r="G51" t="n">
-        <v>8266.4</v>
+        <v>8264.700000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>59430.4</v>
+        <v>58576.3</v>
       </c>
       <c r="I51" t="n">
-        <v>26236.3</v>
+        <v>26130.7</v>
       </c>
       <c r="J51" t="n">
-        <v>2725.15</v>
+        <v>2716.45</v>
       </c>
       <c r="K51" t="n">
-        <v>5920.67</v>
+        <v>5947.1</v>
       </c>
     </row>
     <row r="52">
@@ -4040,34 +4040,34 @@
         <v>46129</v>
       </c>
       <c r="B52" t="n">
-        <v>24651.9</v>
+        <v>24139.8</v>
       </c>
       <c r="C52" t="n">
-        <v>10697.9</v>
+        <v>10590.7</v>
       </c>
       <c r="D52" t="n">
-        <v>7126.42</v>
+        <v>7046.58</v>
       </c>
       <c r="E52" t="n">
-        <v>49453</v>
+        <v>48661.6</v>
       </c>
       <c r="F52" t="n">
-        <v>26684.1</v>
+        <v>26321.6</v>
       </c>
       <c r="G52" t="n">
-        <v>8407.9</v>
+        <v>8266.200000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>59693.4</v>
+        <v>59431</v>
       </c>
       <c r="I52" t="n">
-        <v>26504.1</v>
+        <v>26235.9</v>
       </c>
       <c r="J52" t="n">
-        <v>2777.8</v>
+        <v>2725.05</v>
       </c>
       <c r="K52" t="n">
-        <v>6036.51</v>
+        <v>5920.47</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/universe_series.xlsx
+++ b/data/input/universe_series.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="bid_close" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="mid_open" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="mid_close" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mid_open" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="bid_close" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,13 +495,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>6878.66</v>
+        <v>6834.59</v>
       </c>
       <c r="D2" t="n">
-        <v>1.17877</v>
+        <v>1.18506</v>
       </c>
       <c r="E2" t="n">
-        <v>1.34943</v>
+        <v>1.356285</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -522,7 +522,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>6519.3</v>
+        <v>6248.200000000001</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -538,41 +538,41 @@
         <v>46072</v>
       </c>
       <c r="B4" t="n">
-        <v>10668.2</v>
+        <v>10679.1</v>
       </c>
       <c r="C4" t="n">
-        <v>6865.54</v>
+        <v>6879.21</v>
       </c>
       <c r="D4" t="n">
-        <v>1.17683</v>
+        <v>1.178825</v>
       </c>
       <c r="E4" t="n">
-        <v>1.34592</v>
+        <v>1.349495</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>25030.1</v>
+        <v>25234.3</v>
       </c>
       <c r="H4" t="n">
-        <v>49407.6</v>
+        <v>49646.3</v>
       </c>
       <c r="I4" t="n">
-        <v>24816.3</v>
+        <v>24896.8</v>
       </c>
       <c r="J4" t="n">
-        <v>6063.9</v>
+        <v>6097.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2661.8</v>
+        <v>2656.25</v>
       </c>
       <c r="L4" t="n">
-        <v>8415.9</v>
+        <v>8424.9</v>
       </c>
       <c r="M4" t="n">
-        <v>57080.7</v>
+        <v>57517.5</v>
       </c>
       <c r="N4" t="n">
-        <v>26781.7</v>
+        <v>26847.6</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>6670.8</v>
+        <v>6522.200000000001</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -600,41 +600,41 @@
         <v>46073</v>
       </c>
       <c r="B6" t="n">
-        <v>10718.4</v>
+        <v>10670.3</v>
       </c>
       <c r="C6" t="n">
-        <v>6909.88</v>
+        <v>6865.97</v>
       </c>
       <c r="D6" t="n">
-        <v>1.17797</v>
+        <v>1.17689</v>
       </c>
       <c r="E6" t="n">
-        <v>1.34765</v>
+        <v>1.345955</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>25233.1</v>
+        <v>25034.1</v>
       </c>
       <c r="H6" t="n">
-        <v>49619.9</v>
+        <v>49410.5</v>
       </c>
       <c r="I6" t="n">
-        <v>25013.7</v>
+        <v>24817.5</v>
       </c>
       <c r="J6" t="n">
-        <v>6133.6</v>
+        <v>6065.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2661.7</v>
+        <v>2662.05</v>
       </c>
       <c r="L6" t="n">
-        <v>8533.4</v>
+        <v>8418.1</v>
       </c>
       <c r="M6" t="n">
-        <v>57073.3</v>
+        <v>57086.7</v>
       </c>
       <c r="N6" t="n">
-        <v>26848.4</v>
+        <v>26796.9</v>
       </c>
     </row>
     <row r="7">
@@ -646,7 +646,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>6628.3</v>
+        <v>6672.200000000001</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -662,41 +662,41 @@
         <v>46075</v>
       </c>
       <c r="B8" t="n">
-        <v>10701.4</v>
+        <v>10712.6</v>
       </c>
       <c r="C8" t="n">
-        <v>6891.98</v>
+        <v>6903.7</v>
       </c>
       <c r="D8" t="n">
-        <v>1.18328</v>
+        <v>1.179725</v>
       </c>
       <c r="E8" t="n">
-        <v>1.35316</v>
+        <v>1.349105</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>25172.5</v>
+        <v>25208.9</v>
       </c>
       <c r="H8" t="n">
-        <v>49526</v>
+        <v>49576.3</v>
       </c>
       <c r="I8" t="n">
-        <v>24910.3</v>
+        <v>24973.5</v>
       </c>
       <c r="J8" t="n">
-        <v>6118.9</v>
+        <v>6128.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2652.5</v>
+        <v>2656.55</v>
       </c>
       <c r="L8" t="n">
-        <v>8513.200000000001</v>
+        <v>8526.200000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>56978.1</v>
+        <v>57079</v>
       </c>
       <c r="N8" t="n">
-        <v>26811.4</v>
+        <v>26846.7</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>6556.3</v>
+        <v>6573.9</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -724,41 +724,41 @@
         <v>46076</v>
       </c>
       <c r="B10" t="n">
-        <v>10690.7</v>
+        <v>10703.3</v>
       </c>
       <c r="C10" t="n">
-        <v>6844.01</v>
+        <v>6892.15</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17928</v>
+        <v>1.1833</v>
       </c>
       <c r="E10" t="n">
-        <v>1.34948</v>
+        <v>1.353215</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>24993</v>
+        <v>25175.6</v>
       </c>
       <c r="H10" t="n">
-        <v>48837.1</v>
+        <v>49528.9</v>
       </c>
       <c r="I10" t="n">
-        <v>24734.3</v>
+        <v>24910.7</v>
       </c>
       <c r="J10" t="n">
-        <v>6121.8</v>
+        <v>6120.3</v>
       </c>
       <c r="K10" t="n">
-        <v>2621.3</v>
+        <v>2652.45</v>
       </c>
       <c r="L10" t="n">
-        <v>8504.6</v>
+        <v>8515.1</v>
       </c>
       <c r="M10" t="n">
-        <v>56662.3</v>
+        <v>56979.1</v>
       </c>
       <c r="N10" t="n">
-        <v>26876.9</v>
+        <v>26826.2</v>
       </c>
     </row>
     <row r="11">
@@ -770,7 +770,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>6674.9</v>
+        <v>6557.799999999999</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -786,41 +786,41 @@
         <v>46077</v>
       </c>
       <c r="B12" t="n">
-        <v>10710.4</v>
+        <v>10692.6</v>
       </c>
       <c r="C12" t="n">
-        <v>6891.78</v>
+        <v>6844.559999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1774</v>
+        <v>1.179315</v>
       </c>
       <c r="E12" t="n">
-        <v>1.34956</v>
+        <v>1.349545</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>25035.8</v>
+        <v>24996.1</v>
       </c>
       <c r="H12" t="n">
-        <v>49175.1</v>
+        <v>48840</v>
       </c>
       <c r="I12" t="n">
-        <v>24994.3</v>
+        <v>24735.1</v>
       </c>
       <c r="J12" t="n">
-        <v>6134.6</v>
+        <v>6123.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2651.4</v>
+        <v>2621.75</v>
       </c>
       <c r="L12" t="n">
-        <v>8537.9</v>
+        <v>8506.5</v>
       </c>
       <c r="M12" t="n">
-        <v>57908.5</v>
+        <v>56693.3</v>
       </c>
       <c r="N12" t="n">
-        <v>26751.2</v>
+        <v>26891.6</v>
       </c>
     </row>
     <row r="13">
@@ -832,7 +832,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>6597.5</v>
+        <v>6675.299999999999</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -848,41 +848,41 @@
         <v>46078</v>
       </c>
       <c r="B14" t="n">
-        <v>10802.4</v>
+        <v>10712.3</v>
       </c>
       <c r="C14" t="n">
-        <v>6937.36</v>
+        <v>6891.95</v>
       </c>
       <c r="D14" t="n">
-        <v>1.18151</v>
+        <v>1.17746</v>
       </c>
       <c r="E14" t="n">
-        <v>1.35576</v>
+        <v>1.349615</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>25177.8</v>
+        <v>25038.9</v>
       </c>
       <c r="H14" t="n">
-        <v>49389.6</v>
+        <v>49176.5</v>
       </c>
       <c r="I14" t="n">
-        <v>25269</v>
+        <v>24995</v>
       </c>
       <c r="J14" t="n">
-        <v>6174.2</v>
+        <v>6136</v>
       </c>
       <c r="K14" t="n">
-        <v>2660.5</v>
+        <v>2651.45</v>
       </c>
       <c r="L14" t="n">
-        <v>8567.6</v>
+        <v>8539.799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>59281.6</v>
+        <v>57919.5</v>
       </c>
       <c r="N14" t="n">
-        <v>26935</v>
+        <v>26766</v>
       </c>
     </row>
     <row r="15">
@@ -894,7 +894,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>6555.2</v>
+        <v>6599.1</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -910,41 +910,41 @@
         <v>46079</v>
       </c>
       <c r="B16" t="n">
-        <v>10833.1</v>
+        <v>10804.3</v>
       </c>
       <c r="C16" t="n">
-        <v>6882.06</v>
+        <v>6937.41</v>
       </c>
       <c r="D16" t="n">
-        <v>1.18032</v>
+        <v>1.18153</v>
       </c>
       <c r="E16" t="n">
-        <v>1.34911</v>
+        <v>1.355835</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>25249.8</v>
+        <v>25180.7</v>
       </c>
       <c r="H16" t="n">
-        <v>49227.2</v>
+        <v>49392.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24954.6</v>
+        <v>25270.1</v>
       </c>
       <c r="J16" t="n">
-        <v>6149.2</v>
+        <v>6175.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2655.4</v>
+        <v>2660.95</v>
       </c>
       <c r="L16" t="n">
-        <v>8609.700000000001</v>
+        <v>8569.5</v>
       </c>
       <c r="M16" t="n">
-        <v>58431.5</v>
+        <v>59282.6</v>
       </c>
       <c r="N16" t="n">
-        <v>26374.6</v>
+        <v>26949.5</v>
       </c>
     </row>
     <row r="17">
@@ -956,7 +956,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>6530.4</v>
+        <v>6556.700000000001</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -972,41 +972,41 @@
         <v>46080</v>
       </c>
       <c r="B18" t="n">
-        <v>10860.7</v>
+        <v>10834.9</v>
       </c>
       <c r="C18" t="n">
-        <v>6864.83</v>
+        <v>6881.99</v>
       </c>
       <c r="D18" t="n">
-        <v>1.18146</v>
+        <v>1.180345</v>
       </c>
       <c r="E18" t="n">
-        <v>1.34768</v>
+        <v>1.349145</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>25140.2</v>
+        <v>25252.1</v>
       </c>
       <c r="H18" t="n">
-        <v>48853.6</v>
+        <v>49229.1</v>
       </c>
       <c r="I18" t="n">
-        <v>24913.4</v>
+        <v>24955.4</v>
       </c>
       <c r="J18" t="n">
-        <v>6093.88</v>
+        <v>6150.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2626.5</v>
+        <v>2655.45</v>
       </c>
       <c r="L18" t="n">
-        <v>8528.6</v>
+        <v>8611.299999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>58609.2</v>
+        <v>58385</v>
       </c>
       <c r="N18" t="n">
-        <v>26475.4</v>
+        <v>26389</v>
       </c>
     </row>
     <row r="19">
@@ -1018,7 +1018,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>6724.1</v>
+        <v>6531.700000000001</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1034,41 +1034,41 @@
         <v>46082</v>
       </c>
       <c r="B20" t="n">
-        <v>10809.6</v>
+        <v>10810.3</v>
       </c>
       <c r="C20" t="n">
-        <v>6805.65</v>
+        <v>6817.17</v>
       </c>
       <c r="D20" t="n">
-        <v>1.17591</v>
+        <v>1.176735</v>
       </c>
       <c r="E20" t="n">
-        <v>1.34048</v>
+        <v>1.34183</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>24942.8</v>
+        <v>24967.8</v>
       </c>
       <c r="H20" t="n">
-        <v>48366.4</v>
+        <v>48514.6</v>
       </c>
       <c r="I20" t="n">
-        <v>24695.7</v>
+        <v>24680.4</v>
       </c>
       <c r="J20" t="n">
-        <v>6048.08</v>
+        <v>6052.78</v>
       </c>
       <c r="K20" t="n">
-        <v>2591.1</v>
+        <v>2605.05</v>
       </c>
       <c r="L20" t="n">
-        <v>8464.4</v>
+        <v>8470.9</v>
       </c>
       <c r="M20" t="n">
-        <v>57484.6</v>
+        <v>57705.8</v>
       </c>
       <c r="N20" t="n">
-        <v>26335.6</v>
+        <v>26383</v>
       </c>
     </row>
     <row r="21">
@@ -1080,7 +1080,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>7098.9</v>
+        <v>7359.799999999999</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1096,41 +1096,41 @@
         <v>46083</v>
       </c>
       <c r="B22" t="n">
-        <v>10787.5</v>
+        <v>10811.7</v>
       </c>
       <c r="C22" t="n">
-        <v>6867.64</v>
+        <v>6806.2</v>
       </c>
       <c r="D22" t="n">
-        <v>1.16939</v>
+        <v>1.17591</v>
       </c>
       <c r="E22" t="n">
-        <v>1.34077</v>
+        <v>1.340465</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>24578.7</v>
+        <v>24947.2</v>
       </c>
       <c r="H22" t="n">
-        <v>48821.2</v>
+        <v>48369.8</v>
       </c>
       <c r="I22" t="n">
-        <v>24934.3</v>
+        <v>24696.9</v>
       </c>
       <c r="J22" t="n">
-        <v>5980.7</v>
+        <v>6049.78</v>
       </c>
       <c r="K22" t="n">
-        <v>2650.7</v>
+        <v>2591.15</v>
       </c>
       <c r="L22" t="n">
-        <v>8385.700000000001</v>
+        <v>8466.6</v>
       </c>
       <c r="M22" t="n">
-        <v>57709.6</v>
+        <v>57483.1</v>
       </c>
       <c r="N22" t="n">
-        <v>26141.8</v>
+        <v>26351.1</v>
       </c>
     </row>
     <row r="23">
@@ -1142,7 +1142,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>7240.5</v>
+        <v>7101.6</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1158,41 +1158,41 @@
         <v>46084</v>
       </c>
       <c r="B24" t="n">
-        <v>10515.1</v>
+        <v>10789.6</v>
       </c>
       <c r="C24" t="n">
-        <v>6802.2</v>
+        <v>6868.190000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>1.16107</v>
+        <v>1.169445</v>
       </c>
       <c r="E24" t="n">
-        <v>1.33507</v>
+        <v>1.340805</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>23981.5</v>
+        <v>24583</v>
       </c>
       <c r="H24" t="n">
-        <v>48410.9</v>
+        <v>48825.6</v>
       </c>
       <c r="I24" t="n">
-        <v>24667</v>
+        <v>24937</v>
       </c>
       <c r="J24" t="n">
-        <v>5811.8</v>
+        <v>5982.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2603.3</v>
+        <v>2651.05</v>
       </c>
       <c r="L24" t="n">
-        <v>8163.4</v>
+        <v>8388</v>
       </c>
       <c r="M24" t="n">
-        <v>54948.2</v>
+        <v>57710.6</v>
       </c>
       <c r="N24" t="n">
-        <v>25453.5</v>
+        <v>26157.2</v>
       </c>
     </row>
     <row r="25">
@@ -1204,7 +1204,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>7494.8</v>
+        <v>7242.6</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1220,41 +1220,41 @@
         <v>46085</v>
       </c>
       <c r="B26" t="n">
-        <v>10624.8</v>
+        <v>10517.2</v>
       </c>
       <c r="C26" t="n">
-        <v>6877.74</v>
+        <v>6802.75</v>
       </c>
       <c r="D26" t="n">
-        <v>1.16346</v>
+        <v>1.16112</v>
       </c>
       <c r="E26" t="n">
-        <v>1.33688</v>
+        <v>1.335135</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>24298.7</v>
+        <v>23985.8</v>
       </c>
       <c r="H26" t="n">
-        <v>48750.8</v>
+        <v>48412.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25136.1</v>
+        <v>24667.6</v>
       </c>
       <c r="J26" t="n">
-        <v>5900.4</v>
+        <v>5813.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2635.7</v>
+        <v>2603.55</v>
       </c>
       <c r="L26" t="n">
-        <v>8202</v>
+        <v>8166.5</v>
       </c>
       <c r="M26" t="n">
-        <v>56229.4</v>
+        <v>54976.7</v>
       </c>
       <c r="N26" t="n">
-        <v>25587.8</v>
+        <v>25468.9</v>
       </c>
     </row>
     <row r="27">
@@ -1266,7 +1266,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>7664.1</v>
+        <v>7498.5</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1282,41 +1282,41 @@
         <v>46086</v>
       </c>
       <c r="B28" t="n">
-        <v>10405.9</v>
+        <v>10626.7</v>
       </c>
       <c r="C28" t="n">
-        <v>6834.13</v>
+        <v>6877.92</v>
       </c>
       <c r="D28" t="n">
-        <v>1.16064</v>
+        <v>1.163485</v>
       </c>
       <c r="E28" t="n">
-        <v>1.33552</v>
+        <v>1.336905</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>23862.7</v>
+        <v>24301.8</v>
       </c>
       <c r="H28" t="n">
-        <v>48031.6</v>
+        <v>48752.7</v>
       </c>
       <c r="I28" t="n">
-        <v>25030.4</v>
+        <v>25137</v>
       </c>
       <c r="J28" t="n">
-        <v>5792.1</v>
+        <v>5901.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2592.7</v>
+        <v>2635.75</v>
       </c>
       <c r="L28" t="n">
-        <v>8057.2</v>
+        <v>8203.9</v>
       </c>
       <c r="M28" t="n">
-        <v>54559.7</v>
+        <v>56215.4</v>
       </c>
       <c r="N28" t="n">
-        <v>25187.5</v>
+        <v>25602.6</v>
       </c>
     </row>
     <row r="29">
@@ -1328,7 +1328,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>7885.6</v>
+        <v>7665.700000000001</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1344,41 +1344,41 @@
         <v>46087</v>
       </c>
       <c r="B30" t="n">
-        <v>10316.8</v>
+        <v>10408</v>
       </c>
       <c r="C30" t="n">
-        <v>6732.48</v>
+        <v>6834.68</v>
       </c>
       <c r="D30" t="n">
-        <v>1.16139</v>
+        <v>1.16068</v>
       </c>
       <c r="E30" t="n">
-        <v>1.34039</v>
+        <v>1.335575</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>23636.8</v>
+        <v>23867</v>
       </c>
       <c r="H30" t="n">
-        <v>47429.3</v>
+        <v>48032.8</v>
       </c>
       <c r="I30" t="n">
-        <v>24631.7</v>
+        <v>25032.3</v>
       </c>
       <c r="J30" t="n">
-        <v>5721.53</v>
+        <v>5793.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2521.5</v>
+        <v>2592.75</v>
       </c>
       <c r="L30" t="n">
-        <v>8015.2</v>
+        <v>8059.4</v>
       </c>
       <c r="M30" t="n">
-        <v>54014.9</v>
+        <v>54575.7</v>
       </c>
       <c r="N30" t="n">
-        <v>25310.2</v>
+        <v>25202.9</v>
       </c>
     </row>
     <row r="31">
@@ -1390,7 +1390,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>8943.9</v>
+        <v>7886.9</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1406,41 +1406,41 @@
         <v>46089</v>
       </c>
       <c r="B32" t="n">
-        <v>10193.8</v>
+        <v>10244.7</v>
       </c>
       <c r="C32" t="n">
-        <v>6622.15</v>
+        <v>6678.34</v>
       </c>
       <c r="D32" t="n">
-        <v>1.15241</v>
+        <v>1.154965</v>
       </c>
       <c r="E32" t="n">
-        <v>1.33047</v>
+        <v>1.33393</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>23218.8</v>
+        <v>23357.4</v>
       </c>
       <c r="H32" t="n">
-        <v>46610.6</v>
+        <v>46831</v>
       </c>
       <c r="I32" t="n">
-        <v>24186.4</v>
+        <v>24403</v>
       </c>
       <c r="J32" t="n">
-        <v>5614.4</v>
+        <v>5654.6</v>
       </c>
       <c r="K32" t="n">
-        <v>2433.2</v>
+        <v>2493.15</v>
       </c>
       <c r="L32" t="n">
-        <v>7871</v>
+        <v>7921.2</v>
       </c>
       <c r="M32" t="n">
-        <v>52213</v>
+        <v>53227.3</v>
       </c>
       <c r="N32" t="n">
-        <v>25027.2</v>
+        <v>25160.3</v>
       </c>
     </row>
     <row r="33">
@@ -1452,7 +1452,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>11224.7</v>
+        <v>9555</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -1468,41 +1468,41 @@
         <v>46090</v>
       </c>
       <c r="B34" t="n">
-        <v>10305.8</v>
+        <v>10195.7</v>
       </c>
       <c r="C34" t="n">
-        <v>6765.77</v>
+        <v>6623.07</v>
       </c>
       <c r="D34" t="n">
-        <v>1.16157</v>
+        <v>1.1524</v>
       </c>
       <c r="E34" t="n">
-        <v>1.3424</v>
+        <v>1.330495</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>23699.6</v>
+        <v>23221.9</v>
       </c>
       <c r="H34" t="n">
-        <v>47531.9</v>
+        <v>46616</v>
       </c>
       <c r="I34" t="n">
-        <v>24853.1</v>
+        <v>24187.3</v>
       </c>
       <c r="J34" t="n">
-        <v>5763.2</v>
+        <v>5615.8</v>
       </c>
       <c r="K34" t="n">
-        <v>2533.9</v>
+        <v>2433.75</v>
       </c>
       <c r="L34" t="n">
-        <v>7998.3</v>
+        <v>7872.9</v>
       </c>
       <c r="M34" t="n">
-        <v>54256.1</v>
+        <v>52231.5</v>
       </c>
       <c r="N34" t="n">
-        <v>25530.7</v>
+        <v>25042</v>
       </c>
     </row>
     <row r="35">
@@ -1514,7 +1514,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>8801.5</v>
+        <v>11229.7</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1530,41 +1530,41 @@
         <v>46091</v>
       </c>
       <c r="B36" t="n">
-        <v>10383.1</v>
+        <v>10307.7</v>
       </c>
       <c r="C36" t="n">
-        <v>6790.95</v>
+        <v>6765.95</v>
       </c>
       <c r="D36" t="n">
-        <v>1.16115</v>
+        <v>1.161575</v>
       </c>
       <c r="E36" t="n">
-        <v>1.34194</v>
+        <v>1.342415</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>23805.6</v>
+        <v>23702.6</v>
       </c>
       <c r="H36" t="n">
-        <v>47742.1</v>
+        <v>47534.8</v>
       </c>
       <c r="I36" t="n">
-        <v>24989.4</v>
+        <v>24854</v>
       </c>
       <c r="J36" t="n">
-        <v>5785.4</v>
+        <v>5764.6</v>
       </c>
       <c r="K36" t="n">
-        <v>2551.9</v>
+        <v>2534.15</v>
       </c>
       <c r="L36" t="n">
-        <v>7994.9</v>
+        <v>8000.2</v>
       </c>
       <c r="M36" t="n">
-        <v>55063.4</v>
+        <v>54251.3</v>
       </c>
       <c r="N36" t="n">
-        <v>25930.2</v>
+        <v>25545.5</v>
       </c>
     </row>
     <row r="37">
@@ -1576,7 +1576,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>8210.4</v>
+        <v>8805.6</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1592,41 +1592,41 @@
         <v>46092</v>
       </c>
       <c r="B38" t="n">
-        <v>10270.4</v>
+        <v>10385.4</v>
       </c>
       <c r="C38" t="n">
-        <v>6724.31</v>
+        <v>6792.13</v>
       </c>
       <c r="D38" t="n">
-        <v>1.15422</v>
+        <v>1.161165</v>
       </c>
       <c r="E38" t="n">
-        <v>1.33821</v>
+        <v>1.341995</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>23461.7</v>
+        <v>23812.8</v>
       </c>
       <c r="H38" t="n">
-        <v>47027.9</v>
+        <v>47746.5</v>
       </c>
       <c r="I38" t="n">
-        <v>24767.1</v>
+        <v>24991.9</v>
       </c>
       <c r="J38" t="n">
-        <v>5751.13</v>
+        <v>5787.8</v>
       </c>
       <c r="K38" t="n">
-        <v>2505.6</v>
+        <v>2552.65</v>
       </c>
       <c r="L38" t="n">
-        <v>7974.9</v>
+        <v>7998.1</v>
       </c>
       <c r="M38" t="n">
-        <v>54154.5</v>
+        <v>55064.4</v>
       </c>
       <c r="N38" t="n">
-        <v>25619.7</v>
+        <v>25946.7</v>
       </c>
     </row>
     <row r="39">
@@ -1638,7 +1638,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>9363.9</v>
+        <v>8214</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1654,41 +1654,41 @@
         <v>46093</v>
       </c>
       <c r="B40" t="n">
-        <v>10281.7</v>
+        <v>10272.5</v>
       </c>
       <c r="C40" t="n">
-        <v>6675.71</v>
+        <v>6724.49</v>
       </c>
       <c r="D40" t="n">
-        <v>1.15202</v>
+        <v>1.154255</v>
       </c>
       <c r="E40" t="n">
-        <v>1.33507</v>
+        <v>1.338185</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>23491.5</v>
+        <v>23466.3</v>
       </c>
       <c r="H40" t="n">
-        <v>46737.5</v>
+        <v>47199.39999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>24513</v>
+        <v>24768</v>
       </c>
       <c r="J40" t="n">
-        <v>5723.8</v>
+        <v>5752.93</v>
       </c>
       <c r="K40" t="n">
-        <v>2490.8</v>
+        <v>2506.45</v>
       </c>
       <c r="L40" t="n">
-        <v>7962.5</v>
+        <v>7977.3</v>
       </c>
       <c r="M40" t="n">
-        <v>53458.7</v>
+        <v>54153</v>
       </c>
       <c r="N40" t="n">
-        <v>25438.6</v>
+        <v>25635.2</v>
       </c>
     </row>
     <row r="41">
@@ -1700,7 +1700,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>9466</v>
+        <v>9365.799999999999</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1716,41 +1716,41 @@
         <v>46094</v>
       </c>
       <c r="B42" t="n">
-        <v>10238.1</v>
+        <v>10283.6</v>
       </c>
       <c r="C42" t="n">
-        <v>6620.29</v>
+        <v>6675.76</v>
       </c>
       <c r="D42" t="n">
-        <v>1.14162</v>
+        <v>1.152075</v>
       </c>
       <c r="E42" t="n">
-        <v>1.3218</v>
+        <v>1.335135</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>23327.9</v>
+        <v>23493.9</v>
       </c>
       <c r="H42" t="n">
-        <v>46470.2</v>
+        <v>46740.4</v>
       </c>
       <c r="I42" t="n">
-        <v>24318.7</v>
+        <v>24514.1</v>
       </c>
       <c r="J42" t="n">
-        <v>5688.61</v>
+        <v>5725</v>
       </c>
       <c r="K42" t="n">
-        <v>2474</v>
+        <v>2490.75</v>
       </c>
       <c r="L42" t="n">
-        <v>7874.6</v>
+        <v>7964.1</v>
       </c>
       <c r="M42" t="n">
-        <v>53135.3</v>
+        <v>53442.2</v>
       </c>
       <c r="N42" t="n">
-        <v>25385.4</v>
+        <v>25453.2</v>
       </c>
     </row>
     <row r="43">
@@ -1762,7 +1762,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>9764</v>
+        <v>9467.6</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -1778,41 +1778,41 @@
         <v>46096</v>
       </c>
       <c r="B44" t="n">
-        <v>10266.8</v>
+        <v>10252.1</v>
       </c>
       <c r="C44" t="n">
-        <v>6645.18</v>
+        <v>6618.15</v>
       </c>
       <c r="D44" t="n">
-        <v>1.14355</v>
+        <v>1.14245</v>
       </c>
       <c r="E44" t="n">
-        <v>1.3245</v>
+        <v>1.32235</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>23425.1</v>
+        <v>23369.4</v>
       </c>
       <c r="H44" t="n">
-        <v>46639.4</v>
+        <v>46472</v>
       </c>
       <c r="I44" t="n">
-        <v>24423</v>
+        <v>24304.8</v>
       </c>
       <c r="J44" t="n">
-        <v>5712.4</v>
+        <v>5699.4</v>
       </c>
       <c r="K44" t="n">
-        <v>2489.3</v>
+        <v>2472.65</v>
       </c>
       <c r="L44" t="n">
-        <v>7917.5</v>
+        <v>7899.3</v>
       </c>
       <c r="M44" t="n">
-        <v>53648.4</v>
+        <v>52934.6</v>
       </c>
       <c r="N44" t="n">
-        <v>25435.7</v>
+        <v>25421.2</v>
       </c>
     </row>
     <row r="45">
@@ -1824,7 +1824,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>9776.299999999999</v>
+        <v>9994.9</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1840,41 +1840,41 @@
         <v>46097</v>
       </c>
       <c r="B46" t="n">
-        <v>10345</v>
+        <v>10268.7</v>
       </c>
       <c r="C46" t="n">
-        <v>6697.82</v>
+        <v>6645.73</v>
       </c>
       <c r="D46" t="n">
-        <v>1.14977</v>
+        <v>1.143575</v>
       </c>
       <c r="E46" t="n">
-        <v>1.33114</v>
+        <v>1.324585</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>23621.9</v>
+        <v>23429.7</v>
       </c>
       <c r="H46" t="n">
-        <v>46924.3</v>
+        <v>46642.3</v>
       </c>
       <c r="I46" t="n">
-        <v>24651</v>
+        <v>24424.7</v>
       </c>
       <c r="J46" t="n">
-        <v>5752.7</v>
+        <v>5714.1</v>
       </c>
       <c r="K46" t="n">
-        <v>2501.5</v>
+        <v>2489.55</v>
       </c>
       <c r="L46" t="n">
-        <v>7947</v>
+        <v>7919.2</v>
       </c>
       <c r="M46" t="n">
-        <v>54334.1</v>
+        <v>53659.4</v>
       </c>
       <c r="N46" t="n">
-        <v>25846.7</v>
+        <v>25450.6</v>
       </c>
     </row>
     <row r="47">
@@ -1886,7 +1886,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>9525</v>
+        <v>9779.1</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -1902,41 +1902,41 @@
         <v>46098</v>
       </c>
       <c r="B48" t="n">
-        <v>10360.5</v>
+        <v>10347.1</v>
       </c>
       <c r="C48" t="n">
-        <v>6711.38</v>
+        <v>6697.87</v>
       </c>
       <c r="D48" t="n">
-        <v>1.15383</v>
+        <v>1.149825</v>
       </c>
       <c r="E48" t="n">
-        <v>1.33558</v>
+        <v>1.331205</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>23667</v>
+        <v>23624.3</v>
       </c>
       <c r="H48" t="n">
-        <v>46942.2</v>
+        <v>46926.2</v>
       </c>
       <c r="I48" t="n">
-        <v>24774.5</v>
+        <v>24651.7</v>
       </c>
       <c r="J48" t="n">
-        <v>5754.9</v>
+        <v>5754</v>
       </c>
       <c r="K48" t="n">
-        <v>2517.7</v>
+        <v>2501.55</v>
       </c>
       <c r="L48" t="n">
-        <v>7954.2</v>
+        <v>7949.3</v>
       </c>
       <c r="M48" t="n">
-        <v>54270.9</v>
+        <v>54340.1</v>
       </c>
       <c r="N48" t="n">
-        <v>25844.5</v>
+        <v>25861.8</v>
       </c>
     </row>
     <row r="49">
@@ -1948,7 +1948,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>9247.700000000001</v>
+        <v>9527.5</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -1964,41 +1964,41 @@
         <v>46099</v>
       </c>
       <c r="B50" t="n">
-        <v>10219.1</v>
+        <v>10362.4</v>
       </c>
       <c r="C50" t="n">
-        <v>6698.79</v>
+        <v>6711.43</v>
       </c>
       <c r="D50" t="n">
-        <v>1.14628</v>
+        <v>1.153925</v>
       </c>
       <c r="E50" t="n">
-        <v>1.32638</v>
+        <v>1.33579</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>23166</v>
+        <v>23669.4</v>
       </c>
       <c r="H50" t="n">
-        <v>46154.6</v>
+        <v>46944.1</v>
       </c>
       <c r="I50" t="n">
-        <v>24394.2</v>
+        <v>24776</v>
       </c>
       <c r="J50" t="n">
-        <v>5654</v>
+        <v>5756.1</v>
       </c>
       <c r="K50" t="n">
-        <v>2474.3</v>
+        <v>2517.65</v>
       </c>
       <c r="L50" t="n">
-        <v>7895.7</v>
+        <v>7955.8</v>
       </c>
       <c r="M50" t="n">
-        <v>53596.1</v>
+        <v>54291.9</v>
       </c>
       <c r="N50" t="n">
-        <v>25401.9</v>
+        <v>25859.1</v>
       </c>
     </row>
     <row r="51">
@@ -2010,7 +2010,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>9647.9</v>
+        <v>9251.700000000001</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -2026,39 +2026,39 @@
         <v>46100</v>
       </c>
       <c r="B52" t="n">
-        <v>10067.6</v>
+        <v>10221.2</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>1.15762</v>
+        <v>1.146285</v>
       </c>
       <c r="E52" t="n">
-        <v>1.34236</v>
+        <v>1.326415</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>23016.2</v>
+        <v>23171.8</v>
       </c>
       <c r="H52" t="n">
-        <v>46136.8</v>
+        <v>46158</v>
       </c>
       <c r="I52" t="n">
-        <v>24406.7</v>
+        <v>24394.9</v>
       </c>
       <c r="J52" t="n">
-        <v>5653.9</v>
+        <v>5656.1</v>
       </c>
       <c r="K52" t="n">
-        <v>2508.4</v>
+        <v>2474.35</v>
       </c>
       <c r="L52" t="n">
-        <v>7840.7</v>
+        <v>7898.5</v>
       </c>
       <c r="M52" t="n">
-        <v>53397.7</v>
+        <v>53624.6</v>
       </c>
       <c r="N52" t="n">
-        <v>25353.8</v>
+        <v>25417.7</v>
       </c>
     </row>
     <row r="53">
@@ -2070,7 +2070,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>9384.4</v>
+        <v>9653.200000000001</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -2086,41 +2086,41 @@
         <v>46101</v>
       </c>
       <c r="B54" t="n">
-        <v>9837.299999999999</v>
+        <v>10069.7</v>
       </c>
       <c r="C54" t="n">
-        <v>6536.37</v>
+        <v>6619.34</v>
       </c>
       <c r="D54" t="n">
-        <v>1.15679</v>
+        <v>1.15766</v>
       </c>
       <c r="E54" t="n">
-        <v>1.33356</v>
+        <v>1.342445</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>22210.8</v>
+        <v>23020.2</v>
       </c>
       <c r="H54" t="n">
-        <v>45798.2</v>
+        <v>46139.7</v>
       </c>
       <c r="I54" t="n">
-        <v>23997.9</v>
+        <v>24407.8</v>
       </c>
       <c r="J54" t="n">
-        <v>5473.45</v>
+        <v>5655.6</v>
       </c>
       <c r="K54" t="n">
-        <v>2451.6</v>
+        <v>2508.75</v>
       </c>
       <c r="L54" t="n">
-        <v>7611.8</v>
+        <v>7843</v>
       </c>
       <c r="M54" t="n">
-        <v>51302.2</v>
+        <v>53403.2</v>
       </c>
       <c r="N54" t="n">
-        <v>24755.8</v>
+        <v>25369.1</v>
       </c>
     </row>
     <row r="55">
@@ -2132,7 +2132,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>9788.799999999999</v>
+        <v>9387.1</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -2148,41 +2148,41 @@
         <v>46103</v>
       </c>
       <c r="B56" t="n">
-        <v>9792.1</v>
+        <v>9776</v>
       </c>
       <c r="C56" t="n">
-        <v>6488.2</v>
+        <v>6460.09</v>
       </c>
       <c r="D56" t="n">
-        <v>1.1562</v>
+        <v>1.153725</v>
       </c>
       <c r="E56" t="n">
-        <v>1.33332</v>
+        <v>1.33387</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>21972.1</v>
+        <v>21912.6</v>
       </c>
       <c r="H56" t="n">
-        <v>45536.2</v>
+        <v>45343.8</v>
       </c>
       <c r="I56" t="n">
-        <v>23793.4</v>
+        <v>23718.3</v>
       </c>
       <c r="J56" t="n">
-        <v>5418.1</v>
+        <v>5402.6</v>
       </c>
       <c r="K56" t="n">
-        <v>2432.5</v>
+        <v>2420.35</v>
       </c>
       <c r="L56" t="n">
-        <v>7538.6</v>
+        <v>7513</v>
       </c>
       <c r="M56" t="n">
-        <v>51177</v>
+        <v>50808.8</v>
       </c>
       <c r="N56" t="n">
-        <v>24644.3</v>
+        <v>24609.8</v>
       </c>
     </row>
     <row r="57">
@@ -2194,7 +2194,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>9883.200000000001</v>
+        <v>10008.4</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -2210,41 +2210,41 @@
         <v>46104</v>
       </c>
       <c r="B58" t="n">
-        <v>9961.6</v>
+        <v>9794.299999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>6593.77</v>
+        <v>6488.75</v>
       </c>
       <c r="D58" t="n">
-        <v>1.16077</v>
+        <v>1.156255</v>
       </c>
       <c r="E58" t="n">
-        <v>1.34255</v>
+        <v>1.333485</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>22841.5</v>
+        <v>21979.4</v>
       </c>
       <c r="H58" t="n">
-        <v>46288.2</v>
+        <v>45541.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24240.8</v>
+        <v>23797.5</v>
       </c>
       <c r="J58" t="n">
-        <v>5616.2</v>
+        <v>5420.5</v>
       </c>
       <c r="K58" t="n">
-        <v>2500.4</v>
+        <v>2433.15</v>
       </c>
       <c r="L58" t="n">
-        <v>7796.8</v>
+        <v>7541.9</v>
       </c>
       <c r="M58" t="n">
-        <v>53014.7</v>
+        <v>51188</v>
       </c>
       <c r="N58" t="n">
-        <v>24967.7</v>
+        <v>24660.8</v>
       </c>
     </row>
     <row r="59">
@@ -2256,7 +2256,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>9121</v>
+        <v>9884.4</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -2272,41 +2272,41 @@
         <v>46105</v>
       </c>
       <c r="B60" t="n">
-        <v>10013.3</v>
+        <v>9963.5</v>
       </c>
       <c r="C60" t="n">
-        <v>6599.67</v>
+        <v>6593.95</v>
       </c>
       <c r="D60" t="n">
-        <v>1.1613</v>
+        <v>1.16081</v>
       </c>
       <c r="E60" t="n">
-        <v>1.34141</v>
+        <v>1.342665</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>22887.5</v>
+        <v>22844.5</v>
       </c>
       <c r="H60" t="n">
-        <v>46445.6</v>
+        <v>46286.1</v>
       </c>
       <c r="I60" t="n">
-        <v>24204</v>
+        <v>24241.5</v>
       </c>
       <c r="J60" t="n">
-        <v>5644.18</v>
+        <v>5617.6</v>
       </c>
       <c r="K60" t="n">
-        <v>2535.6</v>
+        <v>2500.15</v>
       </c>
       <c r="L60" t="n">
-        <v>7813.7</v>
+        <v>7798.6</v>
       </c>
       <c r="M60" t="n">
-        <v>53497.1</v>
+        <v>52995.7</v>
       </c>
       <c r="N60" t="n">
-        <v>25035.4</v>
+        <v>24982.4</v>
       </c>
     </row>
     <row r="61">
@@ -2318,7 +2318,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>8852.799999999999</v>
+        <v>9123.700000000001</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -2334,41 +2334,41 @@
         <v>46106</v>
       </c>
       <c r="B62" t="n">
-        <v>10083.7</v>
+        <v>10015.1</v>
       </c>
       <c r="C62" t="n">
-        <v>6580.7</v>
+        <v>6599.72</v>
       </c>
       <c r="D62" t="n">
-        <v>1.15614</v>
+        <v>1.161335</v>
       </c>
       <c r="E62" t="n">
-        <v>1.33631</v>
+        <v>1.341465</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>22866.6</v>
+        <v>22889.8</v>
       </c>
       <c r="H62" t="n">
-        <v>46357.1</v>
+        <v>46448.5</v>
       </c>
       <c r="I62" t="n">
-        <v>24113.6</v>
+        <v>24204.9</v>
       </c>
       <c r="J62" t="n">
-        <v>5620.01</v>
+        <v>5645.38</v>
       </c>
       <c r="K62" t="n">
-        <v>2530.6</v>
+        <v>2535.85</v>
       </c>
       <c r="L62" t="n">
-        <v>7813.5</v>
+        <v>7815.3</v>
       </c>
       <c r="M62" t="n">
-        <v>53875</v>
+        <v>53498.1</v>
       </c>
       <c r="N62" t="n">
-        <v>25244.3</v>
+        <v>25050</v>
       </c>
     </row>
     <row r="63">
@@ -2380,7 +2380,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>9115.299999999999</v>
+        <v>8856.6</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -2396,41 +2396,41 @@
         <v>46107</v>
       </c>
       <c r="B64" t="n">
-        <v>9963.799999999999</v>
+        <v>10085.8</v>
       </c>
       <c r="C64" t="n">
-        <v>6505.95</v>
+        <v>6581.25</v>
       </c>
       <c r="D64" t="n">
-        <v>1.15345</v>
+        <v>1.156175</v>
       </c>
       <c r="E64" t="n">
-        <v>1.33334</v>
+        <v>1.336365</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>22689</v>
+        <v>22871.3</v>
       </c>
       <c r="H64" t="n">
-        <v>46178.7</v>
+        <v>46358.7</v>
       </c>
       <c r="I64" t="n">
-        <v>23681.7</v>
+        <v>24114.4</v>
       </c>
       <c r="J64" t="n">
-        <v>5571.5</v>
+        <v>5621.81</v>
       </c>
       <c r="K64" t="n">
-        <v>2508.4</v>
+        <v>2530.85</v>
       </c>
       <c r="L64" t="n">
-        <v>7778.5</v>
+        <v>7815.9</v>
       </c>
       <c r="M64" t="n">
-        <v>52920.1</v>
+        <v>53886</v>
       </c>
       <c r="N64" t="n">
-        <v>24753.8</v>
+        <v>25259.7</v>
       </c>
     </row>
     <row r="65">
@@ -2442,7 +2442,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>9272.4</v>
+        <v>9118.1</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -2458,41 +2458,41 @@
         <v>46108</v>
       </c>
       <c r="B66" t="n">
-        <v>9893.299999999999</v>
+        <v>9966</v>
       </c>
       <c r="C66" t="n">
-        <v>6354.5</v>
+        <v>6506.5</v>
       </c>
       <c r="D66" t="n">
-        <v>1.15067</v>
+        <v>1.15342</v>
       </c>
       <c r="E66" t="n">
-        <v>1.32591</v>
+        <v>1.333305</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>22097.6</v>
+        <v>22693.7</v>
       </c>
       <c r="H66" t="n">
-        <v>45056.6</v>
+        <v>46185</v>
       </c>
       <c r="I66" t="n">
-        <v>23067.1</v>
+        <v>23682.9</v>
       </c>
       <c r="J66" t="n">
-        <v>5453.72</v>
+        <v>5573.3</v>
       </c>
       <c r="K66" t="n">
-        <v>2442.7</v>
+        <v>2508.75</v>
       </c>
       <c r="L66" t="n">
-        <v>7644.4</v>
+        <v>7780.9</v>
       </c>
       <c r="M66" t="n">
-        <v>51122.7</v>
+        <v>52941.1</v>
       </c>
       <c r="N66" t="n">
-        <v>24612.5</v>
+        <v>24769.2</v>
       </c>
     </row>
     <row r="67">
@@ -2504,7 +2504,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>9973.4</v>
+        <v>9273.9</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -2520,41 +2520,41 @@
         <v>46110</v>
       </c>
       <c r="B68" t="n">
-        <v>9877.4</v>
+        <v>9881.700000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>6339.91</v>
+        <v>6337.22</v>
       </c>
       <c r="D68" t="n">
-        <v>1.14879</v>
+        <v>1.15081</v>
       </c>
       <c r="E68" t="n">
-        <v>1.32377</v>
+        <v>1.32634</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>22027.9</v>
+        <v>22033.7</v>
       </c>
       <c r="H68" t="n">
-        <v>44943.2</v>
+        <v>44942.8</v>
       </c>
       <c r="I68" t="n">
-        <v>23026.2</v>
+        <v>23006</v>
       </c>
       <c r="J68" t="n">
-        <v>5433.9</v>
+        <v>5438.9</v>
       </c>
       <c r="K68" t="n">
-        <v>2430.7</v>
+        <v>2435.15</v>
       </c>
       <c r="L68" t="n">
-        <v>7616.7</v>
+        <v>7623.5</v>
       </c>
       <c r="M68" t="n">
-        <v>50601.5</v>
+        <v>50871.5</v>
       </c>
       <c r="N68" t="n">
-        <v>24578.4</v>
+        <v>24599.6</v>
       </c>
     </row>
     <row r="69">
@@ -2566,7 +2566,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>9974</v>
+        <v>10049.7</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -2582,41 +2582,41 @@
         <v>46111</v>
       </c>
       <c r="B70" t="n">
-        <v>10068.4</v>
+        <v>9879.299999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>6341.08</v>
+        <v>6340.08</v>
       </c>
       <c r="D70" t="n">
-        <v>1.14593</v>
+        <v>1.148845</v>
       </c>
       <c r="E70" t="n">
-        <v>1.31792</v>
+        <v>1.323865</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>22431.1</v>
+        <v>22030.8</v>
       </c>
       <c r="H70" t="n">
-        <v>45223.1</v>
+        <v>44943.2</v>
       </c>
       <c r="I70" t="n">
-        <v>22919.3</v>
+        <v>23027</v>
       </c>
       <c r="J70" t="n">
-        <v>5499.4</v>
+        <v>5435.2</v>
       </c>
       <c r="K70" t="n">
-        <v>2409.7</v>
+        <v>2430.65</v>
       </c>
       <c r="L70" t="n">
-        <v>7720.7</v>
+        <v>7618.6</v>
       </c>
       <c r="M70" t="n">
-        <v>51047.3</v>
+        <v>50611.5</v>
       </c>
       <c r="N70" t="n">
-        <v>24709.4</v>
+        <v>24593.1</v>
       </c>
     </row>
     <row r="71">
@@ -2628,7 +2628,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>10066.5</v>
+        <v>9975.9</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -2644,41 +2644,41 @@
         <v>46112</v>
       </c>
       <c r="B72" t="n">
-        <v>10277.9</v>
+        <v>10070.3</v>
       </c>
       <c r="C72" t="n">
-        <v>6529.85</v>
+        <v>6341.26</v>
       </c>
       <c r="D72" t="n">
-        <v>1.15583</v>
+        <v>1.145925</v>
       </c>
       <c r="E72" t="n">
-        <v>1.32294</v>
+        <v>1.317965</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>23022.7</v>
+        <v>22434.1</v>
       </c>
       <c r="H72" t="n">
-        <v>46229.5</v>
+        <v>45226</v>
       </c>
       <c r="I72" t="n">
-        <v>23776.1</v>
+        <v>22920</v>
       </c>
       <c r="J72" t="n">
-        <v>5652</v>
+        <v>5500.7</v>
       </c>
       <c r="K72" t="n">
-        <v>2494</v>
+        <v>2409.75</v>
       </c>
       <c r="L72" t="n">
-        <v>7919.4</v>
+        <v>7722.4</v>
       </c>
       <c r="M72" t="n">
-        <v>53043.3</v>
+        <v>51049.8</v>
       </c>
       <c r="N72" t="n">
-        <v>25302.1</v>
+        <v>24724.2</v>
       </c>
     </row>
     <row r="73">
@@ -2690,7 +2690,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>9966.700000000001</v>
+        <v>10068.6</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
@@ -2706,41 +2706,41 @@
         <v>46113</v>
       </c>
       <c r="B74" t="n">
-        <v>10414.2</v>
+        <v>10279.8</v>
       </c>
       <c r="C74" t="n">
-        <v>6571.83</v>
+        <v>6529.9</v>
       </c>
       <c r="D74" t="n">
-        <v>1.15905</v>
+        <v>1.155885</v>
       </c>
       <c r="E74" t="n">
-        <v>1.33055</v>
+        <v>1.32306</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>23285.5</v>
+        <v>23025</v>
       </c>
       <c r="H74" t="n">
-        <v>46559.4</v>
+        <v>46313.4</v>
       </c>
       <c r="I74" t="n">
-        <v>23995.1</v>
+        <v>23775.3</v>
       </c>
       <c r="J74" t="n">
-        <v>5719.4</v>
+        <v>5653.2</v>
       </c>
       <c r="K74" t="n">
-        <v>2510</v>
+        <v>2494.05</v>
       </c>
       <c r="L74" t="n">
-        <v>7974.6</v>
+        <v>7921</v>
       </c>
       <c r="M74" t="n">
-        <v>54226.4</v>
+        <v>53025.8</v>
       </c>
       <c r="N74" t="n">
-        <v>25300.3</v>
+        <v>25316.6</v>
       </c>
     </row>
     <row r="75">
@@ -2752,7 +2752,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>10092.7</v>
+        <v>9968.9</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
@@ -2768,41 +2768,41 @@
         <v>46114</v>
       </c>
       <c r="B76" t="n">
-        <v>10449.6</v>
+        <v>10416.3</v>
       </c>
       <c r="C76" t="n">
-        <v>6583.06</v>
+        <v>6572.38</v>
       </c>
       <c r="D76" t="n">
-        <v>1.15397</v>
+        <v>1.159125</v>
       </c>
       <c r="E76" t="n">
-        <v>1.32248</v>
+        <v>1.33069</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>23214.1</v>
+        <v>23290.2</v>
       </c>
       <c r="H76" t="n">
-        <v>46520</v>
+        <v>46564.3</v>
       </c>
       <c r="I76" t="n">
-        <v>24029.5</v>
+        <v>23997.5</v>
       </c>
       <c r="J76" t="n">
-        <v>5699.97</v>
+        <v>5721.2</v>
       </c>
       <c r="K76" t="n">
-        <v>2530.4</v>
+        <v>2510.35</v>
       </c>
       <c r="L76" t="n">
-        <v>7988.9</v>
+        <v>7977.1</v>
       </c>
       <c r="M76" t="n">
-        <v>53240</v>
+        <v>54235.3</v>
       </c>
       <c r="N76" t="n">
-        <v>25255.4</v>
+        <v>25315.7</v>
       </c>
     </row>
     <row r="77">
@@ -2814,7 +2814,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>10578.6</v>
+        <v>10094.8</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
@@ -2830,41 +2830,41 @@
         <v>46115</v>
       </c>
       <c r="B78" t="n">
-        <v>10430</v>
+        <v>10451.7</v>
       </c>
       <c r="C78" t="n">
-        <v>6563.37</v>
+        <v>6583.43</v>
       </c>
       <c r="D78" t="n">
-        <v>1.15154</v>
+        <v>1.154005</v>
       </c>
       <c r="E78" t="n">
-        <v>1.31987</v>
+        <v>1.322595</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>23123.8</v>
+        <v>23218.1</v>
       </c>
       <c r="H78" t="n">
-        <v>46405.9</v>
+        <v>46522.1</v>
       </c>
       <c r="I78" t="n">
-        <v>23956.4</v>
+        <v>24030.1</v>
       </c>
       <c r="J78" t="n">
-        <v>5678.27</v>
+        <v>5701.57</v>
       </c>
       <c r="K78" t="n">
-        <v>2519.5</v>
+        <v>2530.45</v>
       </c>
       <c r="L78" t="n">
-        <v>7958.4</v>
+        <v>7991</v>
       </c>
       <c r="M78" t="n">
-        <v>53150.2</v>
+        <v>53243.7</v>
       </c>
       <c r="N78" t="n">
-        <v>25173.7</v>
+        <v>25270.6</v>
       </c>
     </row>
     <row r="79">
@@ -2872,37 +2872,37 @@
         <v>46117</v>
       </c>
       <c r="B79" t="n">
-        <v>10414.4</v>
+        <v>10414.5</v>
       </c>
       <c r="C79" t="n">
-        <v>6547.27</v>
+        <v>6541.72</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>23049.4</v>
+        <v>23043.8</v>
       </c>
       <c r="H79" t="n">
-        <v>46255.9</v>
+        <v>46240.7</v>
       </c>
       <c r="I79" t="n">
-        <v>23906.8</v>
+        <v>23893</v>
       </c>
       <c r="J79" t="n">
-        <v>5660.3</v>
+        <v>5659.6</v>
       </c>
       <c r="K79" t="n">
-        <v>2510.7</v>
+        <v>2508.95</v>
       </c>
       <c r="L79" t="n">
-        <v>7932.5</v>
+        <v>7931.5</v>
       </c>
       <c r="M79" t="n">
-        <v>52865.1</v>
+        <v>53059.2</v>
       </c>
       <c r="N79" t="n">
-        <v>25138.9</v>
+        <v>25149.7</v>
       </c>
     </row>
     <row r="80">
@@ -2914,7 +2914,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>10417.9</v>
+        <v>10542.1</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -2930,41 +2930,41 @@
         <v>46118</v>
       </c>
       <c r="B81" t="n">
-        <v>10475.6</v>
+        <v>10416.5</v>
       </c>
       <c r="C81" t="n">
-        <v>6603.66</v>
+        <v>6547.7</v>
       </c>
       <c r="D81" t="n">
-        <v>1.15422</v>
+        <v>1.151625</v>
       </c>
       <c r="E81" t="n">
-        <v>1.32328</v>
+        <v>1.319585</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>23291.6</v>
+        <v>23053.5</v>
       </c>
       <c r="H81" t="n">
-        <v>46707.1</v>
+        <v>46257.8</v>
       </c>
       <c r="I81" t="n">
-        <v>24133.7</v>
+        <v>23908.4</v>
       </c>
       <c r="J81" t="n">
-        <v>5725.6</v>
+        <v>5662</v>
       </c>
       <c r="K81" t="n">
-        <v>2536.5</v>
+        <v>2510.95</v>
       </c>
       <c r="L81" t="n">
-        <v>8024.1</v>
+        <v>7934.6</v>
       </c>
       <c r="M81" t="n">
-        <v>53876.2</v>
+        <v>52875.1</v>
       </c>
       <c r="N81" t="n">
-        <v>25297</v>
+        <v>25154.1</v>
       </c>
     </row>
     <row r="82">
@@ -2976,7 +2976,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>10673.3</v>
+        <v>10421</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -2992,41 +2992,41 @@
         <v>46119</v>
       </c>
       <c r="B83" t="n">
-        <v>10555.1</v>
+        <v>10477.7</v>
       </c>
       <c r="C83" t="n">
-        <v>6752.12</v>
+        <v>6604.09</v>
       </c>
       <c r="D83" t="n">
-        <v>1.16675</v>
+        <v>1.154235</v>
       </c>
       <c r="E83" t="n">
-        <v>1.33725</v>
+        <v>1.323335</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>23798.8</v>
+        <v>23295.6</v>
       </c>
       <c r="H83" t="n">
-        <v>47543.4</v>
+        <v>46712</v>
       </c>
       <c r="I83" t="n">
-        <v>24747.9</v>
+        <v>24134.8</v>
       </c>
       <c r="J83" t="n">
-        <v>5844.2</v>
+        <v>5727.2</v>
       </c>
       <c r="K83" t="n">
-        <v>2623.6</v>
+        <v>2536.45</v>
       </c>
       <c r="L83" t="n">
-        <v>8191.7</v>
+        <v>8026.3</v>
       </c>
       <c r="M83" t="n">
-        <v>55934.9</v>
+        <v>53882.5</v>
       </c>
       <c r="N83" t="n">
-        <v>25605.5</v>
+        <v>25312.2</v>
       </c>
     </row>
     <row r="84">
@@ -3038,7 +3038,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>9108.299999999999</v>
+        <v>10675.9</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -3054,41 +3054,41 @@
         <v>46120</v>
       </c>
       <c r="B85" t="n">
-        <v>10657.2</v>
+        <v>10557</v>
       </c>
       <c r="C85" t="n">
-        <v>6775.54</v>
+        <v>6752.54</v>
       </c>
       <c r="D85" t="n">
-        <v>1.16623</v>
+        <v>1.16686</v>
       </c>
       <c r="E85" t="n">
-        <v>1.33971</v>
+        <v>1.337415</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>24001.7</v>
+        <v>23801.8</v>
       </c>
       <c r="H85" t="n">
-        <v>47884.1</v>
+        <v>47546.3</v>
       </c>
       <c r="I85" t="n">
-        <v>24863</v>
+        <v>24748.8</v>
       </c>
       <c r="J85" t="n">
-        <v>5912.1</v>
+        <v>5845.6</v>
       </c>
       <c r="K85" t="n">
-        <v>2621</v>
+        <v>2623.35</v>
       </c>
       <c r="L85" t="n">
-        <v>8272.200000000001</v>
+        <v>8193.6</v>
       </c>
       <c r="M85" t="n">
-        <v>56743.2</v>
+        <v>55944</v>
       </c>
       <c r="N85" t="n">
-        <v>25862.5</v>
+        <v>25620.3</v>
       </c>
     </row>
     <row r="86">
@@ -3100,7 +3100,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>9242.9</v>
+        <v>9110.5</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -3116,41 +3116,41 @@
         <v>46121</v>
       </c>
       <c r="B87" t="n">
-        <v>10592.9</v>
+        <v>10659</v>
       </c>
       <c r="C87" t="n">
-        <v>6816.6</v>
+        <v>6775.83</v>
       </c>
       <c r="D87" t="n">
-        <v>1.16936</v>
+        <v>1.166245</v>
       </c>
       <c r="E87" t="n">
-        <v>1.34273</v>
+        <v>1.339775</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>23856.6</v>
+        <v>24005.1</v>
       </c>
       <c r="H87" t="n">
-        <v>48152.7</v>
+        <v>47885.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25041.9</v>
+        <v>24863.4</v>
       </c>
       <c r="J87" t="n">
-        <v>5899.4</v>
+        <v>5913.4</v>
       </c>
       <c r="K87" t="n">
-        <v>2635.5</v>
+        <v>2621.05</v>
       </c>
       <c r="L87" t="n">
-        <v>8250.299999999999</v>
+        <v>8273.9</v>
       </c>
       <c r="M87" t="n">
-        <v>56479.6</v>
+        <v>56735.7</v>
       </c>
       <c r="N87" t="n">
-        <v>25901.1</v>
+        <v>25877.4</v>
       </c>
     </row>
     <row r="88">
@@ -3162,7 +3162,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>9240.299999999999</v>
+        <v>9244.799999999999</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -3178,41 +3178,41 @@
         <v>46122</v>
       </c>
       <c r="B89" t="n">
-        <v>10603.1</v>
+        <v>10595</v>
       </c>
       <c r="C89" t="n">
-        <v>6824.8</v>
+        <v>6817.02</v>
       </c>
       <c r="D89" t="n">
-        <v>1.17227</v>
+        <v>1.169385</v>
       </c>
       <c r="E89" t="n">
-        <v>1.34564</v>
+        <v>1.342795</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>23820.4</v>
+        <v>23860.6</v>
       </c>
       <c r="H89" t="n">
-        <v>47967.1</v>
+        <v>48155.6</v>
       </c>
       <c r="I89" t="n">
-        <v>25162.2</v>
+        <v>25043.1</v>
       </c>
       <c r="J89" t="n">
-        <v>5927.41</v>
+        <v>5901</v>
       </c>
       <c r="K89" t="n">
-        <v>2635.8</v>
+        <v>2635.55</v>
       </c>
       <c r="L89" t="n">
-        <v>8264.799999999999</v>
+        <v>8252.5</v>
       </c>
       <c r="M89" t="n">
-        <v>57391.8</v>
+        <v>56495.2</v>
       </c>
       <c r="N89" t="n">
-        <v>25933.9</v>
+        <v>25916.3</v>
       </c>
     </row>
     <row r="90">
@@ -3224,7 +3224,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>9110.799999999999</v>
+        <v>9243</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
@@ -3240,41 +3240,41 @@
         <v>46124</v>
       </c>
       <c r="B91" t="n">
-        <v>10521</v>
+        <v>10530.4</v>
       </c>
       <c r="C91" t="n">
-        <v>6740.25</v>
+        <v>6743.52</v>
       </c>
       <c r="D91" t="n">
-        <v>1.16721</v>
+        <v>1.1676</v>
       </c>
       <c r="E91" t="n">
-        <v>1.33938</v>
+        <v>1.34652</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>23434.6</v>
+        <v>23474</v>
       </c>
       <c r="H91" t="n">
-        <v>47400.6</v>
+        <v>47455.9</v>
       </c>
       <c r="I91" t="n">
-        <v>24790.8</v>
+        <v>24777</v>
       </c>
       <c r="J91" t="n">
-        <v>5830.3</v>
+        <v>5843.5</v>
       </c>
       <c r="K91" t="n">
-        <v>2587.7</v>
+        <v>2592.45</v>
       </c>
       <c r="L91" t="n">
-        <v>8128.9</v>
+        <v>8147</v>
       </c>
       <c r="M91" t="n">
-        <v>56078</v>
+        <v>56086.6</v>
       </c>
       <c r="N91" t="n">
-        <v>25755.2</v>
+        <v>25787.6</v>
       </c>
     </row>
     <row r="92">
@@ -3286,7 +3286,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>9807</v>
+        <v>9660.4</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -3302,41 +3302,41 @@
         <v>46125</v>
       </c>
       <c r="B93" t="n">
-        <v>10615.9</v>
+        <v>10522.9</v>
       </c>
       <c r="C93" t="n">
-        <v>6889.85</v>
+        <v>6740.42</v>
       </c>
       <c r="D93" t="n">
-        <v>1.17609</v>
+        <v>1.167225</v>
       </c>
       <c r="E93" t="n">
-        <v>1.35099</v>
+        <v>1.339425</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>23962</v>
+        <v>23437.6</v>
       </c>
       <c r="H93" t="n">
-        <v>48225.3</v>
+        <v>47402.5</v>
       </c>
       <c r="I93" t="n">
-        <v>25434.7</v>
+        <v>24791.7</v>
       </c>
       <c r="J93" t="n">
-        <v>5945.8</v>
+        <v>5831.6</v>
       </c>
       <c r="K93" t="n">
-        <v>2678</v>
+        <v>2587.75</v>
       </c>
       <c r="L93" t="n">
-        <v>8266.299999999999</v>
+        <v>8130.6</v>
       </c>
       <c r="M93" t="n">
-        <v>57691.4</v>
+        <v>56100.3</v>
       </c>
       <c r="N93" t="n">
-        <v>25953.2</v>
+        <v>25770</v>
       </c>
     </row>
     <row r="94">
@@ -3348,7 +3348,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>9263.799999999999</v>
+        <v>9809.9</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -3364,41 +3364,41 @@
         <v>46126</v>
       </c>
       <c r="B95" t="n">
-        <v>10622.6</v>
+        <v>10618</v>
       </c>
       <c r="C95" t="n">
-        <v>6967.47</v>
+        <v>6890.22</v>
       </c>
       <c r="D95" t="n">
-        <v>1.17944</v>
+        <v>1.176105</v>
       </c>
       <c r="E95" t="n">
-        <v>1.3568</v>
+        <v>1.351055</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>24051.4</v>
+        <v>23966.1</v>
       </c>
       <c r="H95" t="n">
-        <v>48535.3</v>
+        <v>48228.3</v>
       </c>
       <c r="I95" t="n">
-        <v>25829.8</v>
+        <v>25435.8</v>
       </c>
       <c r="J95" t="n">
-        <v>5984.9</v>
+        <v>5947.4</v>
       </c>
       <c r="K95" t="n">
-        <v>2705.4</v>
+        <v>2678.25</v>
       </c>
       <c r="L95" t="n">
-        <v>8324.9</v>
+        <v>8268.4</v>
       </c>
       <c r="M95" t="n">
-        <v>58698.5</v>
+        <v>57701.4</v>
       </c>
       <c r="N95" t="n">
-        <v>26197.7</v>
+        <v>25968.4</v>
       </c>
     </row>
     <row r="96">
@@ -3410,7 +3410,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>8866.6</v>
+        <v>9266.6</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -3426,41 +3426,41 @@
         <v>46127</v>
       </c>
       <c r="B97" t="n">
-        <v>10554.1</v>
+        <v>10624.7</v>
       </c>
       <c r="C97" t="n">
-        <v>7027.99</v>
+        <v>6967.84</v>
       </c>
       <c r="D97" t="n">
-        <v>1.18019</v>
+        <v>1.179485</v>
       </c>
       <c r="E97" t="n">
-        <v>1.35671</v>
+        <v>1.356865</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>24103.6</v>
+        <v>24055.4</v>
       </c>
       <c r="H97" t="n">
-        <v>48525.4</v>
+        <v>48538.2</v>
       </c>
       <c r="I97" t="n">
-        <v>26228.3</v>
+        <v>25830.9</v>
       </c>
       <c r="J97" t="n">
-        <v>5945.4</v>
+        <v>5986.5</v>
       </c>
       <c r="K97" t="n">
-        <v>2716.2</v>
+        <v>2705.65</v>
       </c>
       <c r="L97" t="n">
-        <v>8262.799999999999</v>
+        <v>8327</v>
       </c>
       <c r="M97" t="n">
-        <v>58556.3</v>
+        <v>58703.5</v>
       </c>
       <c r="N97" t="n">
-        <v>26115.4</v>
+        <v>26212.9</v>
       </c>
     </row>
     <row r="98">
@@ -3472,7 +3472,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>8866</v>
+        <v>8869.299999999999</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
@@ -3488,41 +3488,41 @@
         <v>46128</v>
       </c>
       <c r="B99" t="n">
-        <v>10588.9</v>
+        <v>10556</v>
       </c>
       <c r="C99" t="n">
-        <v>7046.44</v>
+        <v>7028.42</v>
       </c>
       <c r="D99" t="n">
-        <v>1.1785</v>
+        <v>1.180245</v>
       </c>
       <c r="E99" t="n">
-        <v>1.35314</v>
+        <v>1.356845</v>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>24137.4</v>
+        <v>24107.7</v>
       </c>
       <c r="H99" t="n">
-        <v>48658.7</v>
+        <v>48526.8</v>
       </c>
       <c r="I99" t="n">
-        <v>26320.7</v>
+        <v>26229.9</v>
       </c>
       <c r="J99" t="n">
-        <v>5919.17</v>
+        <v>5947.1</v>
       </c>
       <c r="K99" t="n">
-        <v>2725</v>
+        <v>2716.45</v>
       </c>
       <c r="L99" t="n">
-        <v>8264.4</v>
+        <v>8264.700000000001</v>
       </c>
       <c r="M99" t="n">
-        <v>59422.9</v>
+        <v>58576.3</v>
       </c>
       <c r="N99" t="n">
-        <v>26221.3</v>
+        <v>26130.7</v>
       </c>
     </row>
     <row r="100">
@@ -3534,7 +3534,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>9027.799999999999</v>
+        <v>8868.1</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
@@ -3550,41 +3550,41 @@
         <v>46129</v>
       </c>
       <c r="B101" t="n">
-        <v>10695.9</v>
+        <v>10590.7</v>
       </c>
       <c r="C101" t="n">
-        <v>7125.67</v>
+        <v>7046.58</v>
       </c>
       <c r="D101" t="n">
-        <v>1.17606</v>
+        <v>1.178535</v>
       </c>
       <c r="E101" t="n">
-        <v>1.35102</v>
+        <v>1.353225</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>24648.4</v>
+        <v>24139.8</v>
       </c>
       <c r="H101" t="n">
-        <v>49448.1</v>
+        <v>48661.6</v>
       </c>
       <c r="I101" t="n">
-        <v>26681.6</v>
+        <v>26321.6</v>
       </c>
       <c r="J101" t="n">
-        <v>6035.01</v>
+        <v>5920.47</v>
       </c>
       <c r="K101" t="n">
-        <v>2777.3</v>
+        <v>2725.05</v>
       </c>
       <c r="L101" t="n">
-        <v>8405.9</v>
+        <v>8266.200000000001</v>
       </c>
       <c r="M101" t="n">
-        <v>59678.4</v>
+        <v>59431</v>
       </c>
       <c r="N101" t="n">
-        <v>26489.1</v>
+        <v>26235.9</v>
       </c>
     </row>
     <row r="102">
@@ -3596,7 +3596,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>8413.6</v>
+        <v>9031.1</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
@@ -3606,6 +3606,28 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>1.17366</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.35162</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3618,7 +3640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6805,6 +6827,28 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>1.17332</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.348555</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6817,7 +6861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6893,13 +6937,13 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>6834.59</v>
+        <v>6878.66</v>
       </c>
       <c r="D2" t="n">
-        <v>1.18506</v>
+        <v>1.17877</v>
       </c>
       <c r="E2" t="n">
-        <v>1.356285</v>
+        <v>1.34943</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
@@ -6920,7 +6964,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>6248.200000000001</v>
+        <v>6519.3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -6936,41 +6980,41 @@
         <v>46072</v>
       </c>
       <c r="B4" t="n">
-        <v>10679.1</v>
+        <v>10668.2</v>
       </c>
       <c r="C4" t="n">
-        <v>6879.21</v>
+        <v>6865.54</v>
       </c>
       <c r="D4" t="n">
-        <v>1.178825</v>
+        <v>1.17683</v>
       </c>
       <c r="E4" t="n">
-        <v>1.349495</v>
+        <v>1.34592</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>25234.3</v>
+        <v>25030.1</v>
       </c>
       <c r="H4" t="n">
-        <v>49646.3</v>
+        <v>49407.6</v>
       </c>
       <c r="I4" t="n">
-        <v>24896.8</v>
+        <v>24816.3</v>
       </c>
       <c r="J4" t="n">
-        <v>6097.6</v>
+        <v>6063.9</v>
       </c>
       <c r="K4" t="n">
-        <v>2656.25</v>
+        <v>2661.8</v>
       </c>
       <c r="L4" t="n">
-        <v>8424.9</v>
+        <v>8415.9</v>
       </c>
       <c r="M4" t="n">
-        <v>57517.5</v>
+        <v>57080.7</v>
       </c>
       <c r="N4" t="n">
-        <v>26847.6</v>
+        <v>26781.7</v>
       </c>
     </row>
     <row r="5">
@@ -6982,7 +7026,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>6522.200000000001</v>
+        <v>6670.8</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -6998,41 +7042,41 @@
         <v>46073</v>
       </c>
       <c r="B6" t="n">
-        <v>10670.3</v>
+        <v>10718.4</v>
       </c>
       <c r="C6" t="n">
-        <v>6865.97</v>
+        <v>6909.88</v>
       </c>
       <c r="D6" t="n">
-        <v>1.17689</v>
+        <v>1.17797</v>
       </c>
       <c r="E6" t="n">
-        <v>1.345955</v>
+        <v>1.34765</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>25034.1</v>
+        <v>25233.1</v>
       </c>
       <c r="H6" t="n">
-        <v>49410.5</v>
+        <v>49619.9</v>
       </c>
       <c r="I6" t="n">
-        <v>24817.5</v>
+        <v>25013.7</v>
       </c>
       <c r="J6" t="n">
-        <v>6065.5</v>
+        <v>6133.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2662.05</v>
+        <v>2661.7</v>
       </c>
       <c r="L6" t="n">
-        <v>8418.1</v>
+        <v>8533.4</v>
       </c>
       <c r="M6" t="n">
-        <v>57086.7</v>
+        <v>57073.3</v>
       </c>
       <c r="N6" t="n">
-        <v>26796.9</v>
+        <v>26848.4</v>
       </c>
     </row>
     <row r="7">
@@ -7044,7 +7088,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>6672.200000000001</v>
+        <v>6628.3</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -7060,41 +7104,41 @@
         <v>46075</v>
       </c>
       <c r="B8" t="n">
-        <v>10712.6</v>
+        <v>10701.4</v>
       </c>
       <c r="C8" t="n">
-        <v>6903.7</v>
+        <v>6891.98</v>
       </c>
       <c r="D8" t="n">
-        <v>1.179725</v>
+        <v>1.18328</v>
       </c>
       <c r="E8" t="n">
-        <v>1.349105</v>
+        <v>1.35316</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>25208.9</v>
+        <v>25172.5</v>
       </c>
       <c r="H8" t="n">
-        <v>49576.3</v>
+        <v>49526</v>
       </c>
       <c r="I8" t="n">
-        <v>24973.5</v>
+        <v>24910.3</v>
       </c>
       <c r="J8" t="n">
-        <v>6128.4</v>
+        <v>6118.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2656.55</v>
+        <v>2652.5</v>
       </c>
       <c r="L8" t="n">
-        <v>8526.200000000001</v>
+        <v>8513.200000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>57079</v>
+        <v>56978.1</v>
       </c>
       <c r="N8" t="n">
-        <v>26846.7</v>
+        <v>26811.4</v>
       </c>
     </row>
     <row r="9">
@@ -7106,7 +7150,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>6573.9</v>
+        <v>6556.3</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -7122,41 +7166,41 @@
         <v>46076</v>
       </c>
       <c r="B10" t="n">
-        <v>10703.3</v>
+        <v>10690.7</v>
       </c>
       <c r="C10" t="n">
-        <v>6892.15</v>
+        <v>6844.01</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1833</v>
+        <v>1.17928</v>
       </c>
       <c r="E10" t="n">
-        <v>1.353215</v>
+        <v>1.34948</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>25175.6</v>
+        <v>24993</v>
       </c>
       <c r="H10" t="n">
-        <v>49528.9</v>
+        <v>48837.1</v>
       </c>
       <c r="I10" t="n">
-        <v>24910.7</v>
+        <v>24734.3</v>
       </c>
       <c r="J10" t="n">
-        <v>6120.3</v>
+        <v>6121.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2652.45</v>
+        <v>2621.3</v>
       </c>
       <c r="L10" t="n">
-        <v>8515.1</v>
+        <v>8504.6</v>
       </c>
       <c r="M10" t="n">
-        <v>56979.1</v>
+        <v>56662.3</v>
       </c>
       <c r="N10" t="n">
-        <v>26826.2</v>
+        <v>26876.9</v>
       </c>
     </row>
     <row r="11">
@@ -7168,7 +7212,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>6557.799999999999</v>
+        <v>6674.9</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -7184,41 +7228,41 @@
         <v>46077</v>
       </c>
       <c r="B12" t="n">
-        <v>10692.6</v>
+        <v>10710.4</v>
       </c>
       <c r="C12" t="n">
-        <v>6844.559999999999</v>
+        <v>6891.78</v>
       </c>
       <c r="D12" t="n">
-        <v>1.179315</v>
+        <v>1.1774</v>
       </c>
       <c r="E12" t="n">
-        <v>1.349545</v>
+        <v>1.34956</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>24996.1</v>
+        <v>25035.8</v>
       </c>
       <c r="H12" t="n">
-        <v>48840</v>
+        <v>49175.1</v>
       </c>
       <c r="I12" t="n">
-        <v>24735.1</v>
+        <v>24994.3</v>
       </c>
       <c r="J12" t="n">
-        <v>6123.2</v>
+        <v>6134.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2621.75</v>
+        <v>2651.4</v>
       </c>
       <c r="L12" t="n">
-        <v>8506.5</v>
+        <v>8537.9</v>
       </c>
       <c r="M12" t="n">
-        <v>56693.3</v>
+        <v>57908.5</v>
       </c>
       <c r="N12" t="n">
-        <v>26891.6</v>
+        <v>26751.2</v>
       </c>
     </row>
     <row r="13">
@@ -7230,7 +7274,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>6675.299999999999</v>
+        <v>6597.5</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -7246,41 +7290,41 @@
         <v>46078</v>
       </c>
       <c r="B14" t="n">
-        <v>10712.3</v>
+        <v>10802.4</v>
       </c>
       <c r="C14" t="n">
-        <v>6891.95</v>
+        <v>6937.36</v>
       </c>
       <c r="D14" t="n">
-        <v>1.17746</v>
+        <v>1.18151</v>
       </c>
       <c r="E14" t="n">
-        <v>1.349615</v>
+        <v>1.35576</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>25038.9</v>
+        <v>25177.8</v>
       </c>
       <c r="H14" t="n">
-        <v>49176.5</v>
+        <v>49389.6</v>
       </c>
       <c r="I14" t="n">
-        <v>24995</v>
+        <v>25269</v>
       </c>
       <c r="J14" t="n">
-        <v>6136</v>
+        <v>6174.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2651.45</v>
+        <v>2660.5</v>
       </c>
       <c r="L14" t="n">
-        <v>8539.799999999999</v>
+        <v>8567.6</v>
       </c>
       <c r="M14" t="n">
-        <v>57919.5</v>
+        <v>59281.6</v>
       </c>
       <c r="N14" t="n">
-        <v>26766</v>
+        <v>26935</v>
       </c>
     </row>
     <row r="15">
@@ -7292,7 +7336,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>6599.1</v>
+        <v>6555.2</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -7308,41 +7352,41 @@
         <v>46079</v>
       </c>
       <c r="B16" t="n">
-        <v>10804.3</v>
+        <v>10833.1</v>
       </c>
       <c r="C16" t="n">
-        <v>6937.41</v>
+        <v>6882.06</v>
       </c>
       <c r="D16" t="n">
-        <v>1.18153</v>
+        <v>1.18032</v>
       </c>
       <c r="E16" t="n">
-        <v>1.355835</v>
+        <v>1.34911</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>25180.7</v>
+        <v>25249.8</v>
       </c>
       <c r="H16" t="n">
-        <v>49392.5</v>
+        <v>49227.2</v>
       </c>
       <c r="I16" t="n">
-        <v>25270.1</v>
+        <v>24954.6</v>
       </c>
       <c r="J16" t="n">
-        <v>6175.6</v>
+        <v>6149.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2660.95</v>
+        <v>2655.4</v>
       </c>
       <c r="L16" t="n">
-        <v>8569.5</v>
+        <v>8609.700000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>59282.6</v>
+        <v>58431.5</v>
       </c>
       <c r="N16" t="n">
-        <v>26949.5</v>
+        <v>26374.6</v>
       </c>
     </row>
     <row r="17">
@@ -7354,7 +7398,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>6556.700000000001</v>
+        <v>6530.4</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -7370,41 +7414,41 @@
         <v>46080</v>
       </c>
       <c r="B18" t="n">
-        <v>10834.9</v>
+        <v>10860.7</v>
       </c>
       <c r="C18" t="n">
-        <v>6881.99</v>
+        <v>6864.83</v>
       </c>
       <c r="D18" t="n">
-        <v>1.180345</v>
+        <v>1.18146</v>
       </c>
       <c r="E18" t="n">
-        <v>1.349145</v>
+        <v>1.34768</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>25252.1</v>
+        <v>25140.2</v>
       </c>
       <c r="H18" t="n">
-        <v>49229.1</v>
+        <v>48853.6</v>
       </c>
       <c r="I18" t="n">
-        <v>24955.4</v>
+        <v>24913.4</v>
       </c>
       <c r="J18" t="n">
-        <v>6150.4</v>
+        <v>6093.88</v>
       </c>
       <c r="K18" t="n">
-        <v>2655.45</v>
+        <v>2626.5</v>
       </c>
       <c r="L18" t="n">
-        <v>8611.299999999999</v>
+        <v>8528.6</v>
       </c>
       <c r="M18" t="n">
-        <v>58385</v>
+        <v>58609.2</v>
       </c>
       <c r="N18" t="n">
-        <v>26389</v>
+        <v>26475.4</v>
       </c>
     </row>
     <row r="19">
@@ -7416,7 +7460,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>6531.700000000001</v>
+        <v>6724.1</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -7432,41 +7476,41 @@
         <v>46082</v>
       </c>
       <c r="B20" t="n">
-        <v>10810.3</v>
+        <v>10809.6</v>
       </c>
       <c r="C20" t="n">
-        <v>6817.17</v>
+        <v>6805.65</v>
       </c>
       <c r="D20" t="n">
-        <v>1.176735</v>
+        <v>1.17591</v>
       </c>
       <c r="E20" t="n">
-        <v>1.34183</v>
+        <v>1.34048</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>24967.8</v>
+        <v>24942.8</v>
       </c>
       <c r="H20" t="n">
-        <v>48514.6</v>
+        <v>48366.4</v>
       </c>
       <c r="I20" t="n">
-        <v>24680.4</v>
+        <v>24695.7</v>
       </c>
       <c r="J20" t="n">
-        <v>6052.78</v>
+        <v>6048.08</v>
       </c>
       <c r="K20" t="n">
-        <v>2605.05</v>
+        <v>2591.1</v>
       </c>
       <c r="L20" t="n">
-        <v>8470.9</v>
+        <v>8464.4</v>
       </c>
       <c r="M20" t="n">
-        <v>57705.8</v>
+        <v>57484.6</v>
       </c>
       <c r="N20" t="n">
-        <v>26383</v>
+        <v>26335.6</v>
       </c>
     </row>
     <row r="21">
@@ -7478,7 +7522,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>7359.799999999999</v>
+        <v>7098.9</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -7494,41 +7538,41 @@
         <v>46083</v>
       </c>
       <c r="B22" t="n">
-        <v>10811.7</v>
+        <v>10787.5</v>
       </c>
       <c r="C22" t="n">
-        <v>6806.2</v>
+        <v>6867.64</v>
       </c>
       <c r="D22" t="n">
-        <v>1.17591</v>
+        <v>1.16939</v>
       </c>
       <c r="E22" t="n">
-        <v>1.340465</v>
+        <v>1.34077</v>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>24947.2</v>
+        <v>24578.7</v>
       </c>
       <c r="H22" t="n">
-        <v>48369.8</v>
+        <v>48821.2</v>
       </c>
       <c r="I22" t="n">
-        <v>24696.9</v>
+        <v>24934.3</v>
       </c>
       <c r="J22" t="n">
-        <v>6049.78</v>
+        <v>5980.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2591.15</v>
+        <v>2650.7</v>
       </c>
       <c r="L22" t="n">
-        <v>8466.6</v>
+        <v>8385.700000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>57483.1</v>
+        <v>57709.6</v>
       </c>
       <c r="N22" t="n">
-        <v>26351.1</v>
+        <v>26141.8</v>
       </c>
     </row>
     <row r="23">
@@ -7540,7 +7584,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>7101.6</v>
+        <v>7240.5</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -7556,41 +7600,41 @@
         <v>46084</v>
       </c>
       <c r="B24" t="n">
-        <v>10789.6</v>
+        <v>10515.1</v>
       </c>
       <c r="C24" t="n">
-        <v>6868.190000000001</v>
+        <v>6802.2</v>
       </c>
       <c r="D24" t="n">
-        <v>1.169445</v>
+        <v>1.16107</v>
       </c>
       <c r="E24" t="n">
-        <v>1.340805</v>
+        <v>1.33507</v>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>24583</v>
+        <v>23981.5</v>
       </c>
       <c r="H24" t="n">
-        <v>48825.6</v>
+        <v>48410.9</v>
       </c>
       <c r="I24" t="n">
-        <v>24937</v>
+        <v>24667</v>
       </c>
       <c r="J24" t="n">
-        <v>5982.4</v>
+        <v>5811.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2651.05</v>
+        <v>2603.3</v>
       </c>
       <c r="L24" t="n">
-        <v>8388</v>
+        <v>8163.4</v>
       </c>
       <c r="M24" t="n">
-        <v>57710.6</v>
+        <v>54948.2</v>
       </c>
       <c r="N24" t="n">
-        <v>26157.2</v>
+        <v>25453.5</v>
       </c>
     </row>
     <row r="25">
@@ -7602,7 +7646,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>7242.6</v>
+        <v>7494.8</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -7618,41 +7662,41 @@
         <v>46085</v>
       </c>
       <c r="B26" t="n">
-        <v>10517.2</v>
+        <v>10624.8</v>
       </c>
       <c r="C26" t="n">
-        <v>6802.75</v>
+        <v>6877.74</v>
       </c>
       <c r="D26" t="n">
-        <v>1.16112</v>
+        <v>1.16346</v>
       </c>
       <c r="E26" t="n">
-        <v>1.335135</v>
+        <v>1.33688</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>23985.8</v>
+        <v>24298.7</v>
       </c>
       <c r="H26" t="n">
-        <v>48412.8</v>
+        <v>48750.8</v>
       </c>
       <c r="I26" t="n">
-        <v>24667.6</v>
+        <v>25136.1</v>
       </c>
       <c r="J26" t="n">
-        <v>5813.5</v>
+        <v>5900.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2603.55</v>
+        <v>2635.7</v>
       </c>
       <c r="L26" t="n">
-        <v>8166.5</v>
+        <v>8202</v>
       </c>
       <c r="M26" t="n">
-        <v>54976.7</v>
+        <v>56229.4</v>
       </c>
       <c r="N26" t="n">
-        <v>25468.9</v>
+        <v>25587.8</v>
       </c>
     </row>
     <row r="27">
@@ -7664,7 +7708,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>7498.5</v>
+        <v>7664.1</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -7680,41 +7724,41 @@
         <v>46086</v>
       </c>
       <c r="B28" t="n">
-        <v>10626.7</v>
+        <v>10405.9</v>
       </c>
       <c r="C28" t="n">
-        <v>6877.92</v>
+        <v>6834.13</v>
       </c>
       <c r="D28" t="n">
-        <v>1.163485</v>
+        <v>1.16064</v>
       </c>
       <c r="E28" t="n">
-        <v>1.336905</v>
+        <v>1.33552</v>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>24301.8</v>
+        <v>23862.7</v>
       </c>
       <c r="H28" t="n">
-        <v>48752.7</v>
+        <v>48031.6</v>
       </c>
       <c r="I28" t="n">
-        <v>25137</v>
+        <v>25030.4</v>
       </c>
       <c r="J28" t="n">
-        <v>5901.8</v>
+        <v>5792.1</v>
       </c>
       <c r="K28" t="n">
-        <v>2635.75</v>
+        <v>2592.7</v>
       </c>
       <c r="L28" t="n">
-        <v>8203.9</v>
+        <v>8057.2</v>
       </c>
       <c r="M28" t="n">
-        <v>56215.4</v>
+        <v>54559.7</v>
       </c>
       <c r="N28" t="n">
-        <v>25602.6</v>
+        <v>25187.5</v>
       </c>
     </row>
     <row r="29">
@@ -7726,7 +7770,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>7665.700000000001</v>
+        <v>7885.6</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -7742,41 +7786,41 @@
         <v>46087</v>
       </c>
       <c r="B30" t="n">
-        <v>10408</v>
+        <v>10316.8</v>
       </c>
       <c r="C30" t="n">
-        <v>6834.68</v>
+        <v>6732.48</v>
       </c>
       <c r="D30" t="n">
-        <v>1.16068</v>
+        <v>1.16139</v>
       </c>
       <c r="E30" t="n">
-        <v>1.335575</v>
+        <v>1.34039</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>23867</v>
+        <v>23636.8</v>
       </c>
       <c r="H30" t="n">
-        <v>48032.8</v>
+        <v>47429.3</v>
       </c>
       <c r="I30" t="n">
-        <v>25032.3</v>
+        <v>24631.7</v>
       </c>
       <c r="J30" t="n">
-        <v>5793.8</v>
+        <v>5721.53</v>
       </c>
       <c r="K30" t="n">
-        <v>2592.75</v>
+        <v>2521.5</v>
       </c>
       <c r="L30" t="n">
-        <v>8059.4</v>
+        <v>8015.2</v>
       </c>
       <c r="M30" t="n">
-        <v>54575.7</v>
+        <v>54014.9</v>
       </c>
       <c r="N30" t="n">
-        <v>25202.9</v>
+        <v>25310.2</v>
       </c>
     </row>
     <row r="31">
@@ -7788,7 +7832,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>7886.9</v>
+        <v>8943.9</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -7804,41 +7848,41 @@
         <v>46089</v>
       </c>
       <c r="B32" t="n">
-        <v>10244.7</v>
+        <v>10193.8</v>
       </c>
       <c r="C32" t="n">
-        <v>6678.34</v>
+        <v>6622.15</v>
       </c>
       <c r="D32" t="n">
-        <v>1.154965</v>
+        <v>1.15241</v>
       </c>
       <c r="E32" t="n">
-        <v>1.33393</v>
+        <v>1.33047</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>23357.4</v>
+        <v>23218.8</v>
       </c>
       <c r="H32" t="n">
-        <v>46831</v>
+        <v>46610.6</v>
       </c>
       <c r="I32" t="n">
-        <v>24403</v>
+        <v>24186.4</v>
       </c>
       <c r="J32" t="n">
-        <v>5654.6</v>
+        <v>5614.4</v>
       </c>
       <c r="K32" t="n">
-        <v>2493.15</v>
+        <v>2433.2</v>
       </c>
       <c r="L32" t="n">
-        <v>7921.2</v>
+        <v>7871</v>
       </c>
       <c r="M32" t="n">
-        <v>53227.3</v>
+        <v>52213</v>
       </c>
       <c r="N32" t="n">
-        <v>25160.3</v>
+        <v>25027.2</v>
       </c>
     </row>
     <row r="33">
@@ -7850,7 +7894,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
-        <v>9555</v>
+        <v>11224.7</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -7866,41 +7910,41 @@
         <v>46090</v>
       </c>
       <c r="B34" t="n">
-        <v>10195.7</v>
+        <v>10305.8</v>
       </c>
       <c r="C34" t="n">
-        <v>6623.07</v>
+        <v>6765.77</v>
       </c>
       <c r="D34" t="n">
-        <v>1.1524</v>
+        <v>1.16157</v>
       </c>
       <c r="E34" t="n">
-        <v>1.330495</v>
+        <v>1.3424</v>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>23221.9</v>
+        <v>23699.6</v>
       </c>
       <c r="H34" t="n">
-        <v>46616</v>
+        <v>47531.9</v>
       </c>
       <c r="I34" t="n">
-        <v>24187.3</v>
+        <v>24853.1</v>
       </c>
       <c r="J34" t="n">
-        <v>5615.8</v>
+        <v>5763.2</v>
       </c>
       <c r="K34" t="n">
-        <v>2433.75</v>
+        <v>2533.9</v>
       </c>
       <c r="L34" t="n">
-        <v>7872.9</v>
+        <v>7998.3</v>
       </c>
       <c r="M34" t="n">
-        <v>52231.5</v>
+        <v>54256.1</v>
       </c>
       <c r="N34" t="n">
-        <v>25042</v>
+        <v>25530.7</v>
       </c>
     </row>
     <row r="35">
@@ -7912,7 +7956,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>11229.7</v>
+        <v>8801.5</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -7928,41 +7972,41 @@
         <v>46091</v>
       </c>
       <c r="B36" t="n">
-        <v>10307.7</v>
+        <v>10383.1</v>
       </c>
       <c r="C36" t="n">
-        <v>6765.95</v>
+        <v>6790.95</v>
       </c>
       <c r="D36" t="n">
-        <v>1.161575</v>
+        <v>1.16115</v>
       </c>
       <c r="E36" t="n">
-        <v>1.342415</v>
+        <v>1.34194</v>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>23702.6</v>
+        <v>23805.6</v>
       </c>
       <c r="H36" t="n">
-        <v>47534.8</v>
+        <v>47742.1</v>
       </c>
       <c r="I36" t="n">
-        <v>24854</v>
+        <v>24989.4</v>
       </c>
       <c r="J36" t="n">
-        <v>5764.6</v>
+        <v>5785.4</v>
       </c>
       <c r="K36" t="n">
-        <v>2534.15</v>
+        <v>2551.9</v>
       </c>
       <c r="L36" t="n">
-        <v>8000.2</v>
+        <v>7994.9</v>
       </c>
       <c r="M36" t="n">
-        <v>54251.3</v>
+        <v>55063.4</v>
       </c>
       <c r="N36" t="n">
-        <v>25545.5</v>
+        <v>25930.2</v>
       </c>
     </row>
     <row r="37">
@@ -7974,7 +8018,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>8805.6</v>
+        <v>8210.4</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -7990,41 +8034,41 @@
         <v>46092</v>
       </c>
       <c r="B38" t="n">
-        <v>10385.4</v>
+        <v>10270.4</v>
       </c>
       <c r="C38" t="n">
-        <v>6792.13</v>
+        <v>6724.31</v>
       </c>
       <c r="D38" t="n">
-        <v>1.161165</v>
+        <v>1.15422</v>
       </c>
       <c r="E38" t="n">
-        <v>1.341995</v>
+        <v>1.33821</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>23812.8</v>
+        <v>23461.7</v>
       </c>
       <c r="H38" t="n">
-        <v>47746.5</v>
+        <v>47027.9</v>
       </c>
       <c r="I38" t="n">
-        <v>24991.9</v>
+        <v>24767.1</v>
       </c>
       <c r="J38" t="n">
-        <v>5787.8</v>
+        <v>5751.13</v>
       </c>
       <c r="K38" t="n">
-        <v>2552.65</v>
+        <v>2505.6</v>
       </c>
       <c r="L38" t="n">
-        <v>7998.1</v>
+        <v>7974.9</v>
       </c>
       <c r="M38" t="n">
-        <v>55064.4</v>
+        <v>54154.5</v>
       </c>
       <c r="N38" t="n">
-        <v>25946.7</v>
+        <v>25619.7</v>
       </c>
     </row>
     <row r="39">
@@ -8036,7 +8080,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>8214</v>
+        <v>9363.9</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -8052,41 +8096,41 @@
         <v>46093</v>
       </c>
       <c r="B40" t="n">
-        <v>10272.5</v>
+        <v>10281.7</v>
       </c>
       <c r="C40" t="n">
-        <v>6724.49</v>
+        <v>6675.71</v>
       </c>
       <c r="D40" t="n">
-        <v>1.154255</v>
+        <v>1.15202</v>
       </c>
       <c r="E40" t="n">
-        <v>1.338185</v>
+        <v>1.33507</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>23466.3</v>
+        <v>23491.5</v>
       </c>
       <c r="H40" t="n">
-        <v>47199.39999999999</v>
+        <v>46737.5</v>
       </c>
       <c r="I40" t="n">
-        <v>24768</v>
+        <v>24513</v>
       </c>
       <c r="J40" t="n">
-        <v>5752.93</v>
+        <v>5723.8</v>
       </c>
       <c r="K40" t="n">
-        <v>2506.45</v>
+        <v>2490.8</v>
       </c>
       <c r="L40" t="n">
-        <v>7977.3</v>
+        <v>7962.5</v>
       </c>
       <c r="M40" t="n">
-        <v>54153</v>
+        <v>53458.7</v>
       </c>
       <c r="N40" t="n">
-        <v>25635.2</v>
+        <v>25438.6</v>
       </c>
     </row>
     <row r="41">
@@ -8098,7 +8142,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>9365.799999999999</v>
+        <v>9466</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -8114,41 +8158,41 @@
         <v>46094</v>
       </c>
       <c r="B42" t="n">
-        <v>10283.6</v>
+        <v>10238.1</v>
       </c>
       <c r="C42" t="n">
-        <v>6675.76</v>
+        <v>6620.29</v>
       </c>
       <c r="D42" t="n">
-        <v>1.152075</v>
+        <v>1.14162</v>
       </c>
       <c r="E42" t="n">
-        <v>1.335135</v>
+        <v>1.3218</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>23493.9</v>
+        <v>23327.9</v>
       </c>
       <c r="H42" t="n">
-        <v>46740.4</v>
+        <v>46470.2</v>
       </c>
       <c r="I42" t="n">
-        <v>24514.1</v>
+        <v>24318.7</v>
       </c>
       <c r="J42" t="n">
-        <v>5725</v>
+        <v>5688.61</v>
       </c>
       <c r="K42" t="n">
-        <v>2490.75</v>
+        <v>2474</v>
       </c>
       <c r="L42" t="n">
-        <v>7964.1</v>
+        <v>7874.6</v>
       </c>
       <c r="M42" t="n">
-        <v>53442.2</v>
+        <v>53135.3</v>
       </c>
       <c r="N42" t="n">
-        <v>25453.2</v>
+        <v>25385.4</v>
       </c>
     </row>
     <row r="43">
@@ -8160,7 +8204,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>9467.6</v>
+        <v>9764</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -8176,41 +8220,41 @@
         <v>46096</v>
       </c>
       <c r="B44" t="n">
-        <v>10252.1</v>
+        <v>10266.8</v>
       </c>
       <c r="C44" t="n">
-        <v>6618.15</v>
+        <v>6645.18</v>
       </c>
       <c r="D44" t="n">
-        <v>1.14245</v>
+        <v>1.14355</v>
       </c>
       <c r="E44" t="n">
-        <v>1.32235</v>
+        <v>1.3245</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>23369.4</v>
+        <v>23425.1</v>
       </c>
       <c r="H44" t="n">
-        <v>46472</v>
+        <v>46639.4</v>
       </c>
       <c r="I44" t="n">
-        <v>24304.8</v>
+        <v>24423</v>
       </c>
       <c r="J44" t="n">
-        <v>5699.4</v>
+        <v>5712.4</v>
       </c>
       <c r="K44" t="n">
-        <v>2472.65</v>
+        <v>2489.3</v>
       </c>
       <c r="L44" t="n">
-        <v>7899.3</v>
+        <v>7917.5</v>
       </c>
       <c r="M44" t="n">
-        <v>52934.6</v>
+        <v>53648.4</v>
       </c>
       <c r="N44" t="n">
-        <v>25421.2</v>
+        <v>25435.7</v>
       </c>
     </row>
     <row r="45">
@@ -8222,7 +8266,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>9994.9</v>
+        <v>9776.299999999999</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -8238,41 +8282,41 @@
         <v>46097</v>
       </c>
       <c r="B46" t="n">
-        <v>10268.7</v>
+        <v>10345</v>
       </c>
       <c r="C46" t="n">
-        <v>6645.73</v>
+        <v>6697.82</v>
       </c>
       <c r="D46" t="n">
-        <v>1.143575</v>
+        <v>1.14977</v>
       </c>
       <c r="E46" t="n">
-        <v>1.324585</v>
+        <v>1.33114</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>23429.7</v>
+        <v>23621.9</v>
       </c>
       <c r="H46" t="n">
-        <v>46642.3</v>
+        <v>46924.3</v>
       </c>
       <c r="I46" t="n">
-        <v>24424.7</v>
+        <v>24651</v>
       </c>
       <c r="J46" t="n">
-        <v>5714.1</v>
+        <v>5752.7</v>
       </c>
       <c r="K46" t="n">
-        <v>2489.55</v>
+        <v>2501.5</v>
       </c>
       <c r="L46" t="n">
-        <v>7919.2</v>
+        <v>7947</v>
       </c>
       <c r="M46" t="n">
-        <v>53659.4</v>
+        <v>54334.1</v>
       </c>
       <c r="N46" t="n">
-        <v>25450.6</v>
+        <v>25846.7</v>
       </c>
     </row>
     <row r="47">
@@ -8284,7 +8328,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>9779.1</v>
+        <v>9525</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -8300,41 +8344,41 @@
         <v>46098</v>
       </c>
       <c r="B48" t="n">
-        <v>10347.1</v>
+        <v>10360.5</v>
       </c>
       <c r="C48" t="n">
-        <v>6697.87</v>
+        <v>6711.38</v>
       </c>
       <c r="D48" t="n">
-        <v>1.149825</v>
+        <v>1.15383</v>
       </c>
       <c r="E48" t="n">
-        <v>1.331205</v>
+        <v>1.33558</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>23624.3</v>
+        <v>23667</v>
       </c>
       <c r="H48" t="n">
-        <v>46926.2</v>
+        <v>46942.2</v>
       </c>
       <c r="I48" t="n">
-        <v>24651.7</v>
+        <v>24774.5</v>
       </c>
       <c r="J48" t="n">
-        <v>5754</v>
+        <v>5754.9</v>
       </c>
       <c r="K48" t="n">
-        <v>2501.55</v>
+        <v>2517.7</v>
       </c>
       <c r="L48" t="n">
-        <v>7949.3</v>
+        <v>7954.2</v>
       </c>
       <c r="M48" t="n">
-        <v>54340.1</v>
+        <v>54270.9</v>
       </c>
       <c r="N48" t="n">
-        <v>25861.8</v>
+        <v>25844.5</v>
       </c>
     </row>
     <row r="49">
@@ -8346,7 +8390,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>9527.5</v>
+        <v>9247.700000000001</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -8362,41 +8406,41 @@
         <v>46099</v>
       </c>
       <c r="B50" t="n">
-        <v>10362.4</v>
+        <v>10219.1</v>
       </c>
       <c r="C50" t="n">
-        <v>6711.43</v>
+        <v>6698.79</v>
       </c>
       <c r="D50" t="n">
-        <v>1.153925</v>
+        <v>1.14628</v>
       </c>
       <c r="E50" t="n">
-        <v>1.33579</v>
+        <v>1.32638</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>23669.4</v>
+        <v>23166</v>
       </c>
       <c r="H50" t="n">
-        <v>46944.1</v>
+        <v>46154.6</v>
       </c>
       <c r="I50" t="n">
-        <v>24776</v>
+        <v>24394.2</v>
       </c>
       <c r="J50" t="n">
-        <v>5756.1</v>
+        <v>5654</v>
       </c>
       <c r="K50" t="n">
-        <v>2517.65</v>
+        <v>2474.3</v>
       </c>
       <c r="L50" t="n">
-        <v>7955.8</v>
+        <v>7895.7</v>
       </c>
       <c r="M50" t="n">
-        <v>54291.9</v>
+        <v>53596.1</v>
       </c>
       <c r="N50" t="n">
-        <v>25859.1</v>
+        <v>25401.9</v>
       </c>
     </row>
     <row r="51">
@@ -8408,7 +8452,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
-        <v>9251.700000000001</v>
+        <v>9647.9</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -8424,39 +8468,39 @@
         <v>46100</v>
       </c>
       <c r="B52" t="n">
-        <v>10221.2</v>
+        <v>10067.6</v>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>1.146285</v>
+        <v>1.15762</v>
       </c>
       <c r="E52" t="n">
-        <v>1.326415</v>
+        <v>1.34236</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>23171.8</v>
+        <v>23016.2</v>
       </c>
       <c r="H52" t="n">
-        <v>46158</v>
+        <v>46136.8</v>
       </c>
       <c r="I52" t="n">
-        <v>24394.9</v>
+        <v>24406.7</v>
       </c>
       <c r="J52" t="n">
-        <v>5656.1</v>
+        <v>5653.9</v>
       </c>
       <c r="K52" t="n">
-        <v>2474.35</v>
+        <v>2508.4</v>
       </c>
       <c r="L52" t="n">
-        <v>7898.5</v>
+        <v>7840.7</v>
       </c>
       <c r="M52" t="n">
-        <v>53624.6</v>
+        <v>53397.7</v>
       </c>
       <c r="N52" t="n">
-        <v>25417.7</v>
+        <v>25353.8</v>
       </c>
     </row>
     <row r="53">
@@ -8468,7 +8512,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>9653.200000000001</v>
+        <v>9384.4</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -8484,41 +8528,41 @@
         <v>46101</v>
       </c>
       <c r="B54" t="n">
-        <v>10069.7</v>
+        <v>9837.299999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>6619.34</v>
+        <v>6536.37</v>
       </c>
       <c r="D54" t="n">
-        <v>1.15766</v>
+        <v>1.15679</v>
       </c>
       <c r="E54" t="n">
-        <v>1.342445</v>
+        <v>1.33356</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>23020.2</v>
+        <v>22210.8</v>
       </c>
       <c r="H54" t="n">
-        <v>46139.7</v>
+        <v>45798.2</v>
       </c>
       <c r="I54" t="n">
-        <v>24407.8</v>
+        <v>23997.9</v>
       </c>
       <c r="J54" t="n">
-        <v>5655.6</v>
+        <v>5473.45</v>
       </c>
       <c r="K54" t="n">
-        <v>2508.75</v>
+        <v>2451.6</v>
       </c>
       <c r="L54" t="n">
-        <v>7843</v>
+        <v>7611.8</v>
       </c>
       <c r="M54" t="n">
-        <v>53403.2</v>
+        <v>51302.2</v>
       </c>
       <c r="N54" t="n">
-        <v>25369.1</v>
+        <v>24755.8</v>
       </c>
     </row>
     <row r="55">
@@ -8530,7 +8574,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
-        <v>9387.1</v>
+        <v>9788.799999999999</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -8546,41 +8590,41 @@
         <v>46103</v>
       </c>
       <c r="B56" t="n">
-        <v>9776</v>
+        <v>9792.1</v>
       </c>
       <c r="C56" t="n">
-        <v>6460.09</v>
+        <v>6488.2</v>
       </c>
       <c r="D56" t="n">
-        <v>1.153725</v>
+        <v>1.1562</v>
       </c>
       <c r="E56" t="n">
-        <v>1.33387</v>
+        <v>1.33332</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>21912.6</v>
+        <v>21972.1</v>
       </c>
       <c r="H56" t="n">
-        <v>45343.8</v>
+        <v>45536.2</v>
       </c>
       <c r="I56" t="n">
-        <v>23718.3</v>
+        <v>23793.4</v>
       </c>
       <c r="J56" t="n">
-        <v>5402.6</v>
+        <v>5418.1</v>
       </c>
       <c r="K56" t="n">
-        <v>2420.35</v>
+        <v>2432.5</v>
       </c>
       <c r="L56" t="n">
-        <v>7513</v>
+        <v>7538.6</v>
       </c>
       <c r="M56" t="n">
-        <v>50808.8</v>
+        <v>51177</v>
       </c>
       <c r="N56" t="n">
-        <v>24609.8</v>
+        <v>24644.3</v>
       </c>
     </row>
     <row r="57">
@@ -8592,7 +8636,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>10008.4</v>
+        <v>9883.200000000001</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -8608,41 +8652,41 @@
         <v>46104</v>
       </c>
       <c r="B58" t="n">
-        <v>9794.299999999999</v>
+        <v>9961.6</v>
       </c>
       <c r="C58" t="n">
-        <v>6488.75</v>
+        <v>6593.77</v>
       </c>
       <c r="D58" t="n">
-        <v>1.156255</v>
+        <v>1.16077</v>
       </c>
       <c r="E58" t="n">
-        <v>1.333485</v>
+        <v>1.34255</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>21979.4</v>
+        <v>22841.5</v>
       </c>
       <c r="H58" t="n">
-        <v>45541.6</v>
+        <v>46288.2</v>
       </c>
       <c r="I58" t="n">
-        <v>23797.5</v>
+        <v>24240.8</v>
       </c>
       <c r="J58" t="n">
-        <v>5420.5</v>
+        <v>5616.2</v>
       </c>
       <c r="K58" t="n">
-        <v>2433.15</v>
+        <v>2500.4</v>
       </c>
       <c r="L58" t="n">
-        <v>7541.9</v>
+        <v>7796.8</v>
       </c>
       <c r="M58" t="n">
-        <v>51188</v>
+        <v>53014.7</v>
       </c>
       <c r="N58" t="n">
-        <v>24660.8</v>
+        <v>24967.7</v>
       </c>
     </row>
     <row r="59">
@@ -8654,7 +8698,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>9884.4</v>
+        <v>9121</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -8670,41 +8714,41 @@
         <v>46105</v>
       </c>
       <c r="B60" t="n">
-        <v>9963.5</v>
+        <v>10013.3</v>
       </c>
       <c r="C60" t="n">
-        <v>6593.95</v>
+        <v>6599.67</v>
       </c>
       <c r="D60" t="n">
-        <v>1.16081</v>
+        <v>1.1613</v>
       </c>
       <c r="E60" t="n">
-        <v>1.342665</v>
+        <v>1.34141</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>22844.5</v>
+        <v>22887.5</v>
       </c>
       <c r="H60" t="n">
-        <v>46286.1</v>
+        <v>46445.6</v>
       </c>
       <c r="I60" t="n">
-        <v>24241.5</v>
+        <v>24204</v>
       </c>
       <c r="J60" t="n">
-        <v>5617.6</v>
+        <v>5644.18</v>
       </c>
       <c r="K60" t="n">
-        <v>2500.15</v>
+        <v>2535.6</v>
       </c>
       <c r="L60" t="n">
-        <v>7798.6</v>
+        <v>7813.7</v>
       </c>
       <c r="M60" t="n">
-        <v>52995.7</v>
+        <v>53497.1</v>
       </c>
       <c r="N60" t="n">
-        <v>24982.4</v>
+        <v>25035.4</v>
       </c>
     </row>
     <row r="61">
@@ -8716,7 +8760,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>9123.700000000001</v>
+        <v>8852.799999999999</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -8732,41 +8776,41 @@
         <v>46106</v>
       </c>
       <c r="B62" t="n">
-        <v>10015.1</v>
+        <v>10083.7</v>
       </c>
       <c r="C62" t="n">
-        <v>6599.72</v>
+        <v>6580.7</v>
       </c>
       <c r="D62" t="n">
-        <v>1.161335</v>
+        <v>1.15614</v>
       </c>
       <c r="E62" t="n">
-        <v>1.341465</v>
+        <v>1.33631</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>22889.8</v>
+        <v>22866.6</v>
       </c>
       <c r="H62" t="n">
-        <v>46448.5</v>
+        <v>46357.1</v>
       </c>
       <c r="I62" t="n">
-        <v>24204.9</v>
+        <v>24113.6</v>
       </c>
       <c r="J62" t="n">
-        <v>5645.38</v>
+        <v>5620.01</v>
       </c>
       <c r="K62" t="n">
-        <v>2535.85</v>
+        <v>2530.6</v>
       </c>
       <c r="L62" t="n">
-        <v>7815.3</v>
+        <v>7813.5</v>
       </c>
       <c r="M62" t="n">
-        <v>53498.1</v>
+        <v>53875</v>
       </c>
       <c r="N62" t="n">
-        <v>25050</v>
+        <v>25244.3</v>
       </c>
     </row>
     <row r="63">
@@ -8778,7 +8822,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>8856.6</v>
+        <v>9115.299999999999</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -8794,41 +8838,41 @@
         <v>46107</v>
       </c>
       <c r="B64" t="n">
-        <v>10085.8</v>
+        <v>9963.799999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>6581.25</v>
+        <v>6505.95</v>
       </c>
       <c r="D64" t="n">
-        <v>1.156175</v>
+        <v>1.15345</v>
       </c>
       <c r="E64" t="n">
-        <v>1.336365</v>
+        <v>1.33334</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>22871.3</v>
+        <v>22689</v>
       </c>
       <c r="H64" t="n">
-        <v>46358.7</v>
+        <v>46178.7</v>
       </c>
       <c r="I64" t="n">
-        <v>24114.4</v>
+        <v>23681.7</v>
       </c>
       <c r="J64" t="n">
-        <v>5621.81</v>
+        <v>5571.5</v>
       </c>
       <c r="K64" t="n">
-        <v>2530.85</v>
+        <v>2508.4</v>
       </c>
       <c r="L64" t="n">
-        <v>7815.9</v>
+        <v>7778.5</v>
       </c>
       <c r="M64" t="n">
-        <v>53886</v>
+        <v>52920.1</v>
       </c>
       <c r="N64" t="n">
-        <v>25259.7</v>
+        <v>24753.8</v>
       </c>
     </row>
     <row r="65">
@@ -8840,7 +8884,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>9118.1</v>
+        <v>9272.4</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -8856,41 +8900,41 @@
         <v>46108</v>
       </c>
       <c r="B66" t="n">
-        <v>9966</v>
+        <v>9893.299999999999</v>
       </c>
       <c r="C66" t="n">
-        <v>6506.5</v>
+        <v>6354.5</v>
       </c>
       <c r="D66" t="n">
-        <v>1.15342</v>
+        <v>1.15067</v>
       </c>
       <c r="E66" t="n">
-        <v>1.333305</v>
+        <v>1.32591</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>22693.7</v>
+        <v>22097.6</v>
       </c>
       <c r="H66" t="n">
-        <v>46185</v>
+        <v>45056.6</v>
       </c>
       <c r="I66" t="n">
-        <v>23682.9</v>
+        <v>23067.1</v>
       </c>
       <c r="J66" t="n">
-        <v>5573.3</v>
+        <v>5453.72</v>
       </c>
       <c r="K66" t="n">
-        <v>2508.75</v>
+        <v>2442.7</v>
       </c>
       <c r="L66" t="n">
-        <v>7780.9</v>
+        <v>7644.4</v>
       </c>
       <c r="M66" t="n">
-        <v>52941.1</v>
+        <v>51122.7</v>
       </c>
       <c r="N66" t="n">
-        <v>24769.2</v>
+        <v>24612.5</v>
       </c>
     </row>
     <row r="67">
@@ -8902,7 +8946,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>9273.9</v>
+        <v>9973.4</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -8918,41 +8962,41 @@
         <v>46110</v>
       </c>
       <c r="B68" t="n">
-        <v>9881.700000000001</v>
+        <v>9877.4</v>
       </c>
       <c r="C68" t="n">
-        <v>6337.22</v>
+        <v>6339.91</v>
       </c>
       <c r="D68" t="n">
-        <v>1.15081</v>
+        <v>1.14879</v>
       </c>
       <c r="E68" t="n">
-        <v>1.32634</v>
+        <v>1.32377</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>22033.7</v>
+        <v>22027.9</v>
       </c>
       <c r="H68" t="n">
-        <v>44942.8</v>
+        <v>44943.2</v>
       </c>
       <c r="I68" t="n">
-        <v>23006</v>
+        <v>23026.2</v>
       </c>
       <c r="J68" t="n">
-        <v>5438.9</v>
+        <v>5433.9</v>
       </c>
       <c r="K68" t="n">
-        <v>2435.15</v>
+        <v>2430.7</v>
       </c>
       <c r="L68" t="n">
-        <v>7623.5</v>
+        <v>7616.7</v>
       </c>
       <c r="M68" t="n">
-        <v>50871.5</v>
+        <v>50601.5</v>
       </c>
       <c r="N68" t="n">
-        <v>24599.6</v>
+        <v>24578.4</v>
       </c>
     </row>
     <row r="69">
@@ -8964,7 +9008,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>10049.7</v>
+        <v>9974</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -8980,41 +9024,41 @@
         <v>46111</v>
       </c>
       <c r="B70" t="n">
-        <v>9879.299999999999</v>
+        <v>10068.4</v>
       </c>
       <c r="C70" t="n">
-        <v>6340.08</v>
+        <v>6341.08</v>
       </c>
       <c r="D70" t="n">
-        <v>1.148845</v>
+        <v>1.14593</v>
       </c>
       <c r="E70" t="n">
-        <v>1.323865</v>
+        <v>1.31792</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>22030.8</v>
+        <v>22431.1</v>
       </c>
       <c r="H70" t="n">
-        <v>44943.2</v>
+        <v>45223.1</v>
       </c>
       <c r="I70" t="n">
-        <v>23027</v>
+        <v>22919.3</v>
       </c>
       <c r="J70" t="n">
-        <v>5435.2</v>
+        <v>5499.4</v>
       </c>
       <c r="K70" t="n">
-        <v>2430.65</v>
+        <v>2409.7</v>
       </c>
       <c r="L70" t="n">
-        <v>7618.6</v>
+        <v>7720.7</v>
       </c>
       <c r="M70" t="n">
-        <v>50611.5</v>
+        <v>51047.3</v>
       </c>
       <c r="N70" t="n">
-        <v>24593.1</v>
+        <v>24709.4</v>
       </c>
     </row>
     <row r="71">
@@ -9026,7 +9070,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>9975.9</v>
+        <v>10066.5</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
@@ -9042,41 +9086,41 @@
         <v>46112</v>
       </c>
       <c r="B72" t="n">
-        <v>10070.3</v>
+        <v>10277.9</v>
       </c>
       <c r="C72" t="n">
-        <v>6341.26</v>
+        <v>6529.85</v>
       </c>
       <c r="D72" t="n">
-        <v>1.145925</v>
+        <v>1.15583</v>
       </c>
       <c r="E72" t="n">
-        <v>1.317965</v>
+        <v>1.32294</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>22434.1</v>
+        <v>23022.7</v>
       </c>
       <c r="H72" t="n">
-        <v>45226</v>
+        <v>46229.5</v>
       </c>
       <c r="I72" t="n">
-        <v>22920</v>
+        <v>23776.1</v>
       </c>
       <c r="J72" t="n">
-        <v>5500.7</v>
+        <v>5652</v>
       </c>
       <c r="K72" t="n">
-        <v>2409.75</v>
+        <v>2494</v>
       </c>
       <c r="L72" t="n">
-        <v>7722.4</v>
+        <v>7919.4</v>
       </c>
       <c r="M72" t="n">
-        <v>51049.8</v>
+        <v>53043.3</v>
       </c>
       <c r="N72" t="n">
-        <v>24724.2</v>
+        <v>25302.1</v>
       </c>
     </row>
     <row r="73">
@@ -9088,7 +9132,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>10068.6</v>
+        <v>9966.700000000001</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
@@ -9104,41 +9148,41 @@
         <v>46113</v>
       </c>
       <c r="B74" t="n">
-        <v>10279.8</v>
+        <v>10414.2</v>
       </c>
       <c r="C74" t="n">
-        <v>6529.9</v>
+        <v>6571.83</v>
       </c>
       <c r="D74" t="n">
-        <v>1.155885</v>
+        <v>1.15905</v>
       </c>
       <c r="E74" t="n">
-        <v>1.32306</v>
+        <v>1.33055</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
-        <v>23025</v>
+        <v>23285.5</v>
       </c>
       <c r="H74" t="n">
-        <v>46313.4</v>
+        <v>46559.4</v>
       </c>
       <c r="I74" t="n">
-        <v>23775.3</v>
+        <v>23995.1</v>
       </c>
       <c r="J74" t="n">
-        <v>5653.2</v>
+        <v>5719.4</v>
       </c>
       <c r="K74" t="n">
-        <v>2494.05</v>
+        <v>2510</v>
       </c>
       <c r="L74" t="n">
-        <v>7921</v>
+        <v>7974.6</v>
       </c>
       <c r="M74" t="n">
-        <v>53025.8</v>
+        <v>54226.4</v>
       </c>
       <c r="N74" t="n">
-        <v>25316.6</v>
+        <v>25300.3</v>
       </c>
     </row>
     <row r="75">
@@ -9150,7 +9194,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>9968.9</v>
+        <v>10092.7</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
@@ -9166,41 +9210,41 @@
         <v>46114</v>
       </c>
       <c r="B76" t="n">
-        <v>10416.3</v>
+        <v>10449.6</v>
       </c>
       <c r="C76" t="n">
-        <v>6572.38</v>
+        <v>6583.06</v>
       </c>
       <c r="D76" t="n">
-        <v>1.159125</v>
+        <v>1.15397</v>
       </c>
       <c r="E76" t="n">
-        <v>1.33069</v>
+        <v>1.32248</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>23290.2</v>
+        <v>23214.1</v>
       </c>
       <c r="H76" t="n">
-        <v>46564.3</v>
+        <v>46520</v>
       </c>
       <c r="I76" t="n">
-        <v>23997.5</v>
+        <v>24029.5</v>
       </c>
       <c r="J76" t="n">
-        <v>5721.2</v>
+        <v>5699.97</v>
       </c>
       <c r="K76" t="n">
-        <v>2510.35</v>
+        <v>2530.4</v>
       </c>
       <c r="L76" t="n">
-        <v>7977.1</v>
+        <v>7988.9</v>
       </c>
       <c r="M76" t="n">
-        <v>54235.3</v>
+        <v>53240</v>
       </c>
       <c r="N76" t="n">
-        <v>25315.7</v>
+        <v>25255.4</v>
       </c>
     </row>
     <row r="77">
@@ -9212,7 +9256,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>10094.8</v>
+        <v>10578.6</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
@@ -9228,41 +9272,41 @@
         <v>46115</v>
       </c>
       <c r="B78" t="n">
-        <v>10451.7</v>
+        <v>10430</v>
       </c>
       <c r="C78" t="n">
-        <v>6583.43</v>
+        <v>6563.37</v>
       </c>
       <c r="D78" t="n">
-        <v>1.154005</v>
+        <v>1.15154</v>
       </c>
       <c r="E78" t="n">
-        <v>1.322595</v>
+        <v>1.31987</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>23218.1</v>
+        <v>23123.8</v>
       </c>
       <c r="H78" t="n">
-        <v>46522.1</v>
+        <v>46405.9</v>
       </c>
       <c r="I78" t="n">
-        <v>24030.1</v>
+        <v>23956.4</v>
       </c>
       <c r="J78" t="n">
-        <v>5701.57</v>
+        <v>5678.27</v>
       </c>
       <c r="K78" t="n">
-        <v>2530.45</v>
+        <v>2519.5</v>
       </c>
       <c r="L78" t="n">
-        <v>7991</v>
+        <v>7958.4</v>
       </c>
       <c r="M78" t="n">
-        <v>53243.7</v>
+        <v>53150.2</v>
       </c>
       <c r="N78" t="n">
-        <v>25270.6</v>
+        <v>25173.7</v>
       </c>
     </row>
     <row r="79">
@@ -9270,37 +9314,37 @@
         <v>46117</v>
       </c>
       <c r="B79" t="n">
-        <v>10414.5</v>
+        <v>10414.4</v>
       </c>
       <c r="C79" t="n">
-        <v>6541.72</v>
+        <v>6547.27</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>23043.8</v>
+        <v>23049.4</v>
       </c>
       <c r="H79" t="n">
-        <v>46240.7</v>
+        <v>46255.9</v>
       </c>
       <c r="I79" t="n">
-        <v>23893</v>
+        <v>23906.8</v>
       </c>
       <c r="J79" t="n">
-        <v>5659.6</v>
+        <v>5660.3</v>
       </c>
       <c r="K79" t="n">
-        <v>2508.95</v>
+        <v>2510.7</v>
       </c>
       <c r="L79" t="n">
-        <v>7931.5</v>
+        <v>7932.5</v>
       </c>
       <c r="M79" t="n">
-        <v>53059.2</v>
+        <v>52865.1</v>
       </c>
       <c r="N79" t="n">
-        <v>25149.7</v>
+        <v>25138.9</v>
       </c>
     </row>
     <row r="80">
@@ -9312,7 +9356,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>10542.1</v>
+        <v>10417.9</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -9328,41 +9372,41 @@
         <v>46118</v>
       </c>
       <c r="B81" t="n">
-        <v>10416.5</v>
+        <v>10475.6</v>
       </c>
       <c r="C81" t="n">
-        <v>6547.7</v>
+        <v>6603.66</v>
       </c>
       <c r="D81" t="n">
-        <v>1.151625</v>
+        <v>1.15422</v>
       </c>
       <c r="E81" t="n">
-        <v>1.319585</v>
+        <v>1.32328</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>23053.5</v>
+        <v>23291.6</v>
       </c>
       <c r="H81" t="n">
-        <v>46257.8</v>
+        <v>46707.1</v>
       </c>
       <c r="I81" t="n">
-        <v>23908.4</v>
+        <v>24133.7</v>
       </c>
       <c r="J81" t="n">
-        <v>5662</v>
+        <v>5725.6</v>
       </c>
       <c r="K81" t="n">
-        <v>2510.95</v>
+        <v>2536.5</v>
       </c>
       <c r="L81" t="n">
-        <v>7934.6</v>
+        <v>8024.1</v>
       </c>
       <c r="M81" t="n">
-        <v>52875.1</v>
+        <v>53876.2</v>
       </c>
       <c r="N81" t="n">
-        <v>25154.1</v>
+        <v>25297</v>
       </c>
     </row>
     <row r="82">
@@ -9374,7 +9418,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>10421</v>
+        <v>10673.3</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
@@ -9390,41 +9434,41 @@
         <v>46119</v>
       </c>
       <c r="B83" t="n">
-        <v>10477.7</v>
+        <v>10555.1</v>
       </c>
       <c r="C83" t="n">
-        <v>6604.09</v>
+        <v>6752.12</v>
       </c>
       <c r="D83" t="n">
-        <v>1.154235</v>
+        <v>1.16675</v>
       </c>
       <c r="E83" t="n">
-        <v>1.323335</v>
+        <v>1.33725</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>23295.6</v>
+        <v>23798.8</v>
       </c>
       <c r="H83" t="n">
-        <v>46712</v>
+        <v>47543.4</v>
       </c>
       <c r="I83" t="n">
-        <v>24134.8</v>
+        <v>24747.9</v>
       </c>
       <c r="J83" t="n">
-        <v>5727.2</v>
+        <v>5844.2</v>
       </c>
       <c r="K83" t="n">
-        <v>2536.45</v>
+        <v>2623.6</v>
       </c>
       <c r="L83" t="n">
-        <v>8026.3</v>
+        <v>8191.7</v>
       </c>
       <c r="M83" t="n">
-        <v>53882.5</v>
+        <v>55934.9</v>
       </c>
       <c r="N83" t="n">
-        <v>25312.2</v>
+        <v>25605.5</v>
       </c>
     </row>
     <row r="84">
@@ -9436,7 +9480,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="n">
-        <v>10675.9</v>
+        <v>9108.299999999999</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
@@ -9452,41 +9496,41 @@
         <v>46120</v>
       </c>
       <c r="B85" t="n">
-        <v>10557</v>
+        <v>10657.2</v>
       </c>
       <c r="C85" t="n">
-        <v>6752.54</v>
+        <v>6775.54</v>
       </c>
       <c r="D85" t="n">
-        <v>1.16686</v>
+        <v>1.16623</v>
       </c>
       <c r="E85" t="n">
-        <v>1.337415</v>
+        <v>1.33971</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
-        <v>23801.8</v>
+        <v>24001.7</v>
       </c>
       <c r="H85" t="n">
-        <v>47546.3</v>
+        <v>47884.1</v>
       </c>
       <c r="I85" t="n">
-        <v>24748.8</v>
+        <v>24863</v>
       </c>
       <c r="J85" t="n">
-        <v>5845.6</v>
+        <v>5912.1</v>
       </c>
       <c r="K85" t="n">
-        <v>2623.35</v>
+        <v>2621</v>
       </c>
       <c r="L85" t="n">
-        <v>8193.6</v>
+        <v>8272.200000000001</v>
       </c>
       <c r="M85" t="n">
-        <v>55944</v>
+        <v>56743.2</v>
       </c>
       <c r="N85" t="n">
-        <v>25620.3</v>
+        <v>25862.5</v>
       </c>
     </row>
     <row r="86">
@@ -9498,7 +9542,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
-        <v>9110.5</v>
+        <v>9242.9</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -9514,41 +9558,41 @@
         <v>46121</v>
       </c>
       <c r="B87" t="n">
-        <v>10659</v>
+        <v>10592.9</v>
       </c>
       <c r="C87" t="n">
-        <v>6775.83</v>
+        <v>6816.6</v>
       </c>
       <c r="D87" t="n">
-        <v>1.166245</v>
+        <v>1.16936</v>
       </c>
       <c r="E87" t="n">
-        <v>1.339775</v>
+        <v>1.34273</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
-        <v>24005.1</v>
+        <v>23856.6</v>
       </c>
       <c r="H87" t="n">
-        <v>47885.9</v>
+        <v>48152.7</v>
       </c>
       <c r="I87" t="n">
-        <v>24863.4</v>
+        <v>25041.9</v>
       </c>
       <c r="J87" t="n">
-        <v>5913.4</v>
+        <v>5899.4</v>
       </c>
       <c r="K87" t="n">
-        <v>2621.05</v>
+        <v>2635.5</v>
       </c>
       <c r="L87" t="n">
-        <v>8273.9</v>
+        <v>8250.299999999999</v>
       </c>
       <c r="M87" t="n">
-        <v>56735.7</v>
+        <v>56479.6</v>
       </c>
       <c r="N87" t="n">
-        <v>25877.4</v>
+        <v>25901.1</v>
       </c>
     </row>
     <row r="88">
@@ -9560,7 +9604,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>9244.799999999999</v>
+        <v>9240.299999999999</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
@@ -9576,41 +9620,41 @@
         <v>46122</v>
       </c>
       <c r="B89" t="n">
-        <v>10595</v>
+        <v>10603.1</v>
       </c>
       <c r="C89" t="n">
-        <v>6817.02</v>
+        <v>6824.8</v>
       </c>
       <c r="D89" t="n">
-        <v>1.169385</v>
+        <v>1.17227</v>
       </c>
       <c r="E89" t="n">
-        <v>1.342795</v>
+        <v>1.34564</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>23860.6</v>
+        <v>23820.4</v>
       </c>
       <c r="H89" t="n">
-        <v>48155.6</v>
+        <v>47967.1</v>
       </c>
       <c r="I89" t="n">
-        <v>25043.1</v>
+        <v>25162.2</v>
       </c>
       <c r="J89" t="n">
-        <v>5901</v>
+        <v>5927.41</v>
       </c>
       <c r="K89" t="n">
-        <v>2635.55</v>
+        <v>2635.8</v>
       </c>
       <c r="L89" t="n">
-        <v>8252.5</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="M89" t="n">
-        <v>56495.2</v>
+        <v>57391.8</v>
       </c>
       <c r="N89" t="n">
-        <v>25916.3</v>
+        <v>25933.9</v>
       </c>
     </row>
     <row r="90">
@@ -9622,7 +9666,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>9243</v>
+        <v>9110.799999999999</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
@@ -9638,41 +9682,41 @@
         <v>46124</v>
       </c>
       <c r="B91" t="n">
-        <v>10530.4</v>
+        <v>10521</v>
       </c>
       <c r="C91" t="n">
-        <v>6743.52</v>
+        <v>6740.25</v>
       </c>
       <c r="D91" t="n">
-        <v>1.1676</v>
+        <v>1.16721</v>
       </c>
       <c r="E91" t="n">
-        <v>1.34652</v>
+        <v>1.33938</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>23474</v>
+        <v>23434.6</v>
       </c>
       <c r="H91" t="n">
-        <v>47455.9</v>
+        <v>47400.6</v>
       </c>
       <c r="I91" t="n">
-        <v>24777</v>
+        <v>24790.8</v>
       </c>
       <c r="J91" t="n">
-        <v>5843.5</v>
+        <v>5830.3</v>
       </c>
       <c r="K91" t="n">
-        <v>2592.45</v>
+        <v>2587.7</v>
       </c>
       <c r="L91" t="n">
-        <v>8147</v>
+        <v>8128.9</v>
       </c>
       <c r="M91" t="n">
-        <v>56086.6</v>
+        <v>56078</v>
       </c>
       <c r="N91" t="n">
-        <v>25787.6</v>
+        <v>25755.2</v>
       </c>
     </row>
     <row r="92">
@@ -9684,7 +9728,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>9660.4</v>
+        <v>9807</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -9700,41 +9744,41 @@
         <v>46125</v>
       </c>
       <c r="B93" t="n">
-        <v>10522.9</v>
+        <v>10615.9</v>
       </c>
       <c r="C93" t="n">
-        <v>6740.42</v>
+        <v>6889.85</v>
       </c>
       <c r="D93" t="n">
-        <v>1.167225</v>
+        <v>1.17609</v>
       </c>
       <c r="E93" t="n">
-        <v>1.339425</v>
+        <v>1.35099</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>23437.6</v>
+        <v>23962</v>
       </c>
       <c r="H93" t="n">
-        <v>47402.5</v>
+        <v>48225.3</v>
       </c>
       <c r="I93" t="n">
-        <v>24791.7</v>
+        <v>25434.7</v>
       </c>
       <c r="J93" t="n">
-        <v>5831.6</v>
+        <v>5945.8</v>
       </c>
       <c r="K93" t="n">
-        <v>2587.75</v>
+        <v>2678</v>
       </c>
       <c r="L93" t="n">
-        <v>8130.6</v>
+        <v>8266.299999999999</v>
       </c>
       <c r="M93" t="n">
-        <v>56100.3</v>
+        <v>57691.4</v>
       </c>
       <c r="N93" t="n">
-        <v>25770</v>
+        <v>25953.2</v>
       </c>
     </row>
     <row r="94">
@@ -9746,7 +9790,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>9809.9</v>
+        <v>9263.799999999999</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -9762,41 +9806,41 @@
         <v>46126</v>
       </c>
       <c r="B95" t="n">
-        <v>10618</v>
+        <v>10622.6</v>
       </c>
       <c r="C95" t="n">
-        <v>6890.22</v>
+        <v>6967.47</v>
       </c>
       <c r="D95" t="n">
-        <v>1.176105</v>
+        <v>1.17944</v>
       </c>
       <c r="E95" t="n">
-        <v>1.351055</v>
+        <v>1.3568</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>23966.1</v>
+        <v>24051.4</v>
       </c>
       <c r="H95" t="n">
-        <v>48228.3</v>
+        <v>48535.3</v>
       </c>
       <c r="I95" t="n">
-        <v>25435.8</v>
+        <v>25829.8</v>
       </c>
       <c r="J95" t="n">
-        <v>5947.4</v>
+        <v>5984.9</v>
       </c>
       <c r="K95" t="n">
-        <v>2678.25</v>
+        <v>2705.4</v>
       </c>
       <c r="L95" t="n">
-        <v>8268.4</v>
+        <v>8324.9</v>
       </c>
       <c r="M95" t="n">
-        <v>57701.4</v>
+        <v>58698.5</v>
       </c>
       <c r="N95" t="n">
-        <v>25968.4</v>
+        <v>26197.7</v>
       </c>
     </row>
     <row r="96">
@@ -9808,7 +9852,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>9266.6</v>
+        <v>8866.6</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -9824,41 +9868,41 @@
         <v>46127</v>
       </c>
       <c r="B97" t="n">
-        <v>10624.7</v>
+        <v>10554.1</v>
       </c>
       <c r="C97" t="n">
-        <v>6967.84</v>
+        <v>7027.99</v>
       </c>
       <c r="D97" t="n">
-        <v>1.179485</v>
+        <v>1.18019</v>
       </c>
       <c r="E97" t="n">
-        <v>1.356865</v>
+        <v>1.35671</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>24055.4</v>
+        <v>24103.6</v>
       </c>
       <c r="H97" t="n">
-        <v>48538.2</v>
+        <v>48525.4</v>
       </c>
       <c r="I97" t="n">
-        <v>25830.9</v>
+        <v>26228.3</v>
       </c>
       <c r="J97" t="n">
-        <v>5986.5</v>
+        <v>5945.4</v>
       </c>
       <c r="K97" t="n">
-        <v>2705.65</v>
+        <v>2716.2</v>
       </c>
       <c r="L97" t="n">
-        <v>8327</v>
+        <v>8262.799999999999</v>
       </c>
       <c r="M97" t="n">
-        <v>58703.5</v>
+        <v>58556.3</v>
       </c>
       <c r="N97" t="n">
-        <v>26212.9</v>
+        <v>26115.4</v>
       </c>
     </row>
     <row r="98">
@@ -9870,7 +9914,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>8869.299999999999</v>
+        <v>8866</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
@@ -9886,41 +9930,41 @@
         <v>46128</v>
       </c>
       <c r="B99" t="n">
-        <v>10556</v>
+        <v>10588.9</v>
       </c>
       <c r="C99" t="n">
-        <v>7028.42</v>
+        <v>7046.44</v>
       </c>
       <c r="D99" t="n">
-        <v>1.180245</v>
+        <v>1.1785</v>
       </c>
       <c r="E99" t="n">
-        <v>1.356845</v>
+        <v>1.35314</v>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>24107.7</v>
+        <v>24137.4</v>
       </c>
       <c r="H99" t="n">
-        <v>48526.8</v>
+        <v>48658.7</v>
       </c>
       <c r="I99" t="n">
-        <v>26229.9</v>
+        <v>26320.7</v>
       </c>
       <c r="J99" t="n">
-        <v>5947.1</v>
+        <v>5919.17</v>
       </c>
       <c r="K99" t="n">
-        <v>2716.45</v>
+        <v>2725</v>
       </c>
       <c r="L99" t="n">
-        <v>8264.700000000001</v>
+        <v>8264.4</v>
       </c>
       <c r="M99" t="n">
-        <v>58576.3</v>
+        <v>59422.9</v>
       </c>
       <c r="N99" t="n">
-        <v>26130.7</v>
+        <v>26221.3</v>
       </c>
     </row>
     <row r="100">
@@ -9932,7 +9976,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="n">
-        <v>8868.1</v>
+        <v>9027.799999999999</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
@@ -9948,41 +9992,41 @@
         <v>46129</v>
       </c>
       <c r="B101" t="n">
-        <v>10590.7</v>
+        <v>10695.9</v>
       </c>
       <c r="C101" t="n">
-        <v>7046.58</v>
+        <v>7125.67</v>
       </c>
       <c r="D101" t="n">
-        <v>1.178535</v>
+        <v>1.17606</v>
       </c>
       <c r="E101" t="n">
-        <v>1.353225</v>
+        <v>1.35102</v>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>24139.8</v>
+        <v>24648.4</v>
       </c>
       <c r="H101" t="n">
-        <v>48661.6</v>
+        <v>49448.1</v>
       </c>
       <c r="I101" t="n">
-        <v>26321.6</v>
+        <v>26681.6</v>
       </c>
       <c r="J101" t="n">
-        <v>5920.47</v>
+        <v>6035.01</v>
       </c>
       <c r="K101" t="n">
-        <v>2725.05</v>
+        <v>2777.3</v>
       </c>
       <c r="L101" t="n">
-        <v>8266.200000000001</v>
+        <v>8405.9</v>
       </c>
       <c r="M101" t="n">
-        <v>59431</v>
+        <v>59678.4</v>
       </c>
       <c r="N101" t="n">
-        <v>26235.9</v>
+        <v>26489.1</v>
       </c>
     </row>
     <row r="102">
@@ -9994,7 +10038,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="n">
-        <v>9031.1</v>
+        <v>8413.6</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
@@ -10005,6 +10049,28 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
     </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>1.17316</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.34801</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/input/universe_series.xlsx
+++ b/data/input/universe_series.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mid_close" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="bid_close" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="mid_open" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="bid_close" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mid_close" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,10 +495,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.178815</v>
+        <v>1.17877</v>
       </c>
       <c r="D2" t="n">
-        <v>1.349475</v>
+        <v>1.34943</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -509,7 +509,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6878.96</v>
+        <v>6878.66</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -518,7 +518,7 @@
         <v>46071.20833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>6521.200000000001</v>
+        <v>6519.3</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -539,40 +539,40 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.17686</v>
+        <v>1.17683</v>
       </c>
       <c r="D4" t="n">
-        <v>1.345965</v>
+        <v>1.34592</v>
       </c>
       <c r="E4" t="n">
-        <v>8417.9</v>
+        <v>8415.9</v>
       </c>
       <c r="F4" t="n">
-        <v>25033.6</v>
+        <v>25030.1</v>
       </c>
       <c r="G4" t="n">
-        <v>49410</v>
+        <v>49407.6</v>
       </c>
       <c r="H4" t="n">
-        <v>10670.2</v>
+        <v>10668.2</v>
       </c>
       <c r="I4" t="n">
-        <v>26796.7</v>
+        <v>26781.7</v>
       </c>
       <c r="J4" t="n">
-        <v>24817.3</v>
+        <v>24816.3</v>
       </c>
       <c r="K4" t="n">
-        <v>57084.2</v>
+        <v>57080.7</v>
       </c>
       <c r="L4" t="n">
-        <v>2661.95</v>
+        <v>2661.8</v>
       </c>
       <c r="M4" t="n">
-        <v>6865.84</v>
+        <v>6865.54</v>
       </c>
       <c r="N4" t="n">
-        <v>6065.4</v>
+        <v>6063.9</v>
       </c>
     </row>
     <row r="5">
@@ -580,7 +580,7 @@
         <v>46072.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>6672.200000000001</v>
+        <v>6670.8</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -601,40 +601,40 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.17822</v>
+        <v>1.17797</v>
       </c>
       <c r="D6" t="n">
-        <v>1.348245</v>
+        <v>1.34765</v>
       </c>
       <c r="E6" t="n">
-        <v>8535.4</v>
+        <v>8533.4</v>
       </c>
       <c r="F6" t="n">
-        <v>25236.6</v>
+        <v>25233.1</v>
       </c>
       <c r="G6" t="n">
-        <v>49624.8</v>
+        <v>49619.9</v>
       </c>
       <c r="H6" t="n">
-        <v>10720.4</v>
+        <v>10718.4</v>
       </c>
       <c r="I6" t="n">
-        <v>26863.4</v>
+        <v>26848.4</v>
       </c>
       <c r="J6" t="n">
-        <v>25016.2</v>
+        <v>25013.7</v>
       </c>
       <c r="K6" t="n">
-        <v>57088.3</v>
+        <v>57073.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2662.2</v>
+        <v>2661.7</v>
       </c>
       <c r="M6" t="n">
-        <v>6910.63</v>
+        <v>6909.88</v>
       </c>
       <c r="N6" t="n">
-        <v>6135.1</v>
+        <v>6133.6</v>
       </c>
     </row>
     <row r="7">
@@ -642,7 +642,7 @@
         <v>46073.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>6630.200000000001</v>
+        <v>6628.3</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -663,40 +663,40 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.18331</v>
+        <v>1.18328</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353205</v>
+        <v>1.35316</v>
       </c>
       <c r="E8" t="n">
-        <v>8515.200000000001</v>
+        <v>8513.200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>25176</v>
+        <v>25172.5</v>
       </c>
       <c r="G8" t="n">
-        <v>49528.4</v>
+        <v>49526</v>
       </c>
       <c r="H8" t="n">
-        <v>10703.4</v>
+        <v>10701.4</v>
       </c>
       <c r="I8" t="n">
-        <v>26826.4</v>
+        <v>26811.4</v>
       </c>
       <c r="J8" t="n">
-        <v>24911.3</v>
+        <v>24910.3</v>
       </c>
       <c r="K8" t="n">
-        <v>56981.6</v>
+        <v>56978.1</v>
       </c>
       <c r="L8" t="n">
-        <v>2652.65</v>
+        <v>2652.5</v>
       </c>
       <c r="M8" t="n">
-        <v>6892.28</v>
+        <v>6891.98</v>
       </c>
       <c r="N8" t="n">
-        <v>6120.4</v>
+        <v>6118.9</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         <v>46075.20833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>6557.700000000001</v>
+        <v>6556.3</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -725,40 +725,40 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.179325</v>
+        <v>1.17928</v>
       </c>
       <c r="D10" t="n">
-        <v>1.349555</v>
+        <v>1.34948</v>
       </c>
       <c r="E10" t="n">
-        <v>8506.6</v>
+        <v>8504.6</v>
       </c>
       <c r="F10" t="n">
-        <v>24996.5</v>
+        <v>24993</v>
       </c>
       <c r="G10" t="n">
-        <v>48839.5</v>
+        <v>48837.1</v>
       </c>
       <c r="H10" t="n">
-        <v>10692.7</v>
+        <v>10690.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26891.9</v>
+        <v>26876.9</v>
       </c>
       <c r="J10" t="n">
-        <v>24735.3</v>
+        <v>24734.3</v>
       </c>
       <c r="K10" t="n">
-        <v>56665.8</v>
+        <v>56662.3</v>
       </c>
       <c r="L10" t="n">
-        <v>2621.45</v>
+        <v>2621.3</v>
       </c>
       <c r="M10" t="n">
-        <v>6844.309999999999</v>
+        <v>6844.01</v>
       </c>
       <c r="N10" t="n">
-        <v>6123.3</v>
+        <v>6121.8</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>46076.20833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>6676.299999999999</v>
+        <v>6674.9</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -787,40 +787,40 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.17743</v>
+        <v>1.1774</v>
       </c>
       <c r="D12" t="n">
-        <v>1.349605</v>
+        <v>1.34956</v>
       </c>
       <c r="E12" t="n">
-        <v>8539.9</v>
+        <v>8537.9</v>
       </c>
       <c r="F12" t="n">
-        <v>25039.3</v>
+        <v>25035.8</v>
       </c>
       <c r="G12" t="n">
-        <v>49177.5</v>
+        <v>49175.1</v>
       </c>
       <c r="H12" t="n">
-        <v>10712.4</v>
+        <v>10710.4</v>
       </c>
       <c r="I12" t="n">
-        <v>26766.2</v>
+        <v>26751.2</v>
       </c>
       <c r="J12" t="n">
-        <v>24995.3</v>
+        <v>24994.3</v>
       </c>
       <c r="K12" t="n">
-        <v>57912</v>
+        <v>57908.5</v>
       </c>
       <c r="L12" t="n">
-        <v>2651.55</v>
+        <v>2651.4</v>
       </c>
       <c r="M12" t="n">
-        <v>6892.08</v>
+        <v>6891.78</v>
       </c>
       <c r="N12" t="n">
-        <v>6136.1</v>
+        <v>6134.6</v>
       </c>
     </row>
     <row r="13">
@@ -828,7 +828,7 @@
         <v>46077.20833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>6598.9</v>
+        <v>6597.5</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -849,40 +849,40 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.18154</v>
+        <v>1.18151</v>
       </c>
       <c r="D14" t="n">
-        <v>1.355805</v>
+        <v>1.35576</v>
       </c>
       <c r="E14" t="n">
-        <v>8569.6</v>
+        <v>8567.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25181.3</v>
+        <v>25177.8</v>
       </c>
       <c r="G14" t="n">
-        <v>49392</v>
+        <v>49389.6</v>
       </c>
       <c r="H14" t="n">
-        <v>10804.4</v>
+        <v>10802.4</v>
       </c>
       <c r="I14" t="n">
-        <v>26950</v>
+        <v>26935</v>
       </c>
       <c r="J14" t="n">
-        <v>25270</v>
+        <v>25269</v>
       </c>
       <c r="K14" t="n">
-        <v>59285.1</v>
+        <v>59281.6</v>
       </c>
       <c r="L14" t="n">
-        <v>2660.65</v>
+        <v>2660.5</v>
       </c>
       <c r="M14" t="n">
-        <v>6937.66</v>
+        <v>6937.36</v>
       </c>
       <c r="N14" t="n">
-        <v>6175.7</v>
+        <v>6174.2</v>
       </c>
     </row>
     <row r="15">
@@ -890,7 +890,7 @@
         <v>46078.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>6556.6</v>
+        <v>6555.2</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -911,40 +911,40 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.180365</v>
+        <v>1.18032</v>
       </c>
       <c r="D16" t="n">
-        <v>1.349155</v>
+        <v>1.34911</v>
       </c>
       <c r="E16" t="n">
-        <v>8611.700000000001</v>
+        <v>8609.700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>25253.3</v>
+        <v>25249.8</v>
       </c>
       <c r="G16" t="n">
-        <v>49229.6</v>
+        <v>49227.2</v>
       </c>
       <c r="H16" t="n">
-        <v>10835.1</v>
+        <v>10833.1</v>
       </c>
       <c r="I16" t="n">
-        <v>26389.6</v>
+        <v>26374.6</v>
       </c>
       <c r="J16" t="n">
-        <v>24955.6</v>
+        <v>24954.6</v>
       </c>
       <c r="K16" t="n">
-        <v>58435</v>
+        <v>58431.5</v>
       </c>
       <c r="L16" t="n">
-        <v>2655.55</v>
+        <v>2655.4</v>
       </c>
       <c r="M16" t="n">
-        <v>6882.360000000001</v>
+        <v>6882.06</v>
       </c>
       <c r="N16" t="n">
-        <v>6150.7</v>
+        <v>6149.2</v>
       </c>
     </row>
     <row r="17">
@@ -952,7 +952,7 @@
         <v>46079.20833333334</v>
       </c>
       <c r="B17" t="n">
-        <v>6531.799999999999</v>
+        <v>6530.4</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -973,40 +973,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.18179</v>
+        <v>1.18146</v>
       </c>
       <c r="D18" t="n">
-        <v>1.34806</v>
+        <v>1.34768</v>
       </c>
       <c r="E18" t="n">
-        <v>8530.6</v>
+        <v>8528.6</v>
       </c>
       <c r="F18" t="n">
-        <v>25143.7</v>
+        <v>25140.2</v>
       </c>
       <c r="G18" t="n">
-        <v>48858.5</v>
+        <v>48853.6</v>
       </c>
       <c r="H18" t="n">
-        <v>10862.7</v>
+        <v>10860.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26490.4</v>
+        <v>26475.4</v>
       </c>
       <c r="J18" t="n">
-        <v>24914.4</v>
+        <v>24913.4</v>
       </c>
       <c r="K18" t="n">
-        <v>58612.7</v>
+        <v>58609.2</v>
       </c>
       <c r="L18" t="n">
-        <v>2626.65</v>
+        <v>2626.5</v>
       </c>
       <c r="M18" t="n">
-        <v>6865.58</v>
+        <v>6864.83</v>
       </c>
       <c r="N18" t="n">
-        <v>6095.38</v>
+        <v>6093.88</v>
       </c>
     </row>
     <row r="19">
@@ -1014,7 +1014,7 @@
         <v>46080.20833333334</v>
       </c>
       <c r="B19" t="n">
-        <v>6725.5</v>
+        <v>6724.1</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -1035,40 +1035,40 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1.17594</v>
+        <v>1.17591</v>
       </c>
       <c r="D20" t="n">
-        <v>1.340525</v>
+        <v>1.34048</v>
       </c>
       <c r="E20" t="n">
-        <v>8466.4</v>
+        <v>8464.4</v>
       </c>
       <c r="F20" t="n">
-        <v>24946.3</v>
+        <v>24942.8</v>
       </c>
       <c r="G20" t="n">
-        <v>48368.8</v>
+        <v>48366.4</v>
       </c>
       <c r="H20" t="n">
-        <v>10811.6</v>
+        <v>10809.6</v>
       </c>
       <c r="I20" t="n">
-        <v>26350.6</v>
+        <v>26335.6</v>
       </c>
       <c r="J20" t="n">
-        <v>24696.7</v>
+        <v>24695.7</v>
       </c>
       <c r="K20" t="n">
-        <v>57488.1</v>
+        <v>57484.6</v>
       </c>
       <c r="L20" t="n">
-        <v>2591.25</v>
+        <v>2591.1</v>
       </c>
       <c r="M20" t="n">
-        <v>6805.95</v>
+        <v>6805.65</v>
       </c>
       <c r="N20" t="n">
-        <v>6049.58</v>
+        <v>6048.08</v>
       </c>
     </row>
     <row r="21">
@@ -1076,7 +1076,7 @@
         <v>46082.20833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>7100.799999999999</v>
+        <v>7098.9</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1097,40 +1097,40 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.169435</v>
+        <v>1.16939</v>
       </c>
       <c r="D22" t="n">
-        <v>1.340815</v>
+        <v>1.34077</v>
       </c>
       <c r="E22" t="n">
-        <v>8387.700000000001</v>
+        <v>8385.700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>24582.2</v>
+        <v>24578.7</v>
       </c>
       <c r="G22" t="n">
-        <v>48823.6</v>
+        <v>48821.2</v>
       </c>
       <c r="H22" t="n">
-        <v>10789.5</v>
+        <v>10787.5</v>
       </c>
       <c r="I22" t="n">
-        <v>26156.8</v>
+        <v>26141.8</v>
       </c>
       <c r="J22" t="n">
-        <v>24935.3</v>
+        <v>24934.3</v>
       </c>
       <c r="K22" t="n">
-        <v>57713.1</v>
+        <v>57709.6</v>
       </c>
       <c r="L22" t="n">
-        <v>2650.85</v>
+        <v>2650.7</v>
       </c>
       <c r="M22" t="n">
-        <v>6867.940000000001</v>
+        <v>6867.64</v>
       </c>
       <c r="N22" t="n">
-        <v>5982.2</v>
+        <v>5980.7</v>
       </c>
     </row>
     <row r="23">
@@ -1138,7 +1138,7 @@
         <v>46083.20833333334</v>
       </c>
       <c r="B23" t="n">
-        <v>7242.4</v>
+        <v>7240.5</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1159,40 +1159,40 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1.1611</v>
+        <v>1.16107</v>
       </c>
       <c r="D24" t="n">
-        <v>1.335115</v>
+        <v>1.33507</v>
       </c>
       <c r="E24" t="n">
-        <v>8165.4</v>
+        <v>8163.4</v>
       </c>
       <c r="F24" t="n">
-        <v>23985</v>
+        <v>23981.5</v>
       </c>
       <c r="G24" t="n">
-        <v>48413.3</v>
+        <v>48410.9</v>
       </c>
       <c r="H24" t="n">
-        <v>10517.1</v>
+        <v>10515.1</v>
       </c>
       <c r="I24" t="n">
-        <v>25468.5</v>
+        <v>25453.5</v>
       </c>
       <c r="J24" t="n">
-        <v>24668</v>
+        <v>24667</v>
       </c>
       <c r="K24" t="n">
-        <v>54951.7</v>
+        <v>54948.2</v>
       </c>
       <c r="L24" t="n">
-        <v>2603.45</v>
+        <v>2603.3</v>
       </c>
       <c r="M24" t="n">
-        <v>6802.5</v>
+        <v>6802.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5813.3</v>
+        <v>5811.8</v>
       </c>
     </row>
     <row r="25">
@@ -1200,7 +1200,7 @@
         <v>46084.20833333334</v>
       </c>
       <c r="B25" t="n">
-        <v>7496.700000000001</v>
+        <v>7494.8</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.163505</v>
+        <v>1.16346</v>
       </c>
       <c r="D26" t="n">
-        <v>1.336925</v>
+        <v>1.33688</v>
       </c>
       <c r="E26" t="n">
-        <v>8204</v>
+        <v>8202</v>
       </c>
       <c r="F26" t="n">
-        <v>24302.2</v>
+        <v>24298.7</v>
       </c>
       <c r="G26" t="n">
-        <v>48753.2</v>
+        <v>48750.8</v>
       </c>
       <c r="H26" t="n">
-        <v>10626.8</v>
+        <v>10624.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25602.8</v>
+        <v>25587.8</v>
       </c>
       <c r="J26" t="n">
-        <v>25137.1</v>
+        <v>25136.1</v>
       </c>
       <c r="K26" t="n">
-        <v>56232.9</v>
+        <v>56229.4</v>
       </c>
       <c r="L26" t="n">
-        <v>2635.85</v>
+        <v>2635.7</v>
       </c>
       <c r="M26" t="n">
-        <v>6878.04</v>
+        <v>6877.74</v>
       </c>
       <c r="N26" t="n">
-        <v>5901.9</v>
+        <v>5900.4</v>
       </c>
     </row>
     <row r="27">
@@ -1262,7 +1262,7 @@
         <v>46085.20833333334</v>
       </c>
       <c r="B27" t="n">
-        <v>7666</v>
+        <v>7664.1</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1283,40 +1283,40 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.16067</v>
+        <v>1.16064</v>
       </c>
       <c r="D28" t="n">
-        <v>1.335565</v>
+        <v>1.33552</v>
       </c>
       <c r="E28" t="n">
-        <v>8059.2</v>
+        <v>8057.2</v>
       </c>
       <c r="F28" t="n">
-        <v>23866.2</v>
+        <v>23862.7</v>
       </c>
       <c r="G28" t="n">
-        <v>48034</v>
+        <v>48031.6</v>
       </c>
       <c r="H28" t="n">
-        <v>10407.9</v>
+        <v>10405.9</v>
       </c>
       <c r="I28" t="n">
-        <v>25202.5</v>
+        <v>25187.5</v>
       </c>
       <c r="J28" t="n">
-        <v>25031.4</v>
+        <v>25030.4</v>
       </c>
       <c r="K28" t="n">
-        <v>54563.2</v>
+        <v>54559.7</v>
       </c>
       <c r="L28" t="n">
-        <v>2592.85</v>
+        <v>2592.7</v>
       </c>
       <c r="M28" t="n">
-        <v>6834.43</v>
+        <v>6834.13</v>
       </c>
       <c r="N28" t="n">
-        <v>5793.6</v>
+        <v>5792.1</v>
       </c>
     </row>
     <row r="29">
@@ -1324,7 +1324,7 @@
         <v>46086.20833333334</v>
       </c>
       <c r="B29" t="n">
-        <v>7887.5</v>
+        <v>7885.6</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1345,40 +1345,40 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1.161695</v>
+        <v>1.16139</v>
       </c>
       <c r="D30" t="n">
-        <v>1.340985</v>
+        <v>1.34039</v>
       </c>
       <c r="E30" t="n">
-        <v>8017.2</v>
+        <v>8015.2</v>
       </c>
       <c r="F30" t="n">
-        <v>23640.3</v>
+        <v>23636.8</v>
       </c>
       <c r="G30" t="n">
-        <v>47434.2</v>
+        <v>47429.3</v>
       </c>
       <c r="H30" t="n">
-        <v>10318.8</v>
+        <v>10316.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25325.2</v>
+        <v>25310.2</v>
       </c>
       <c r="J30" t="n">
-        <v>24634.2</v>
+        <v>24631.7</v>
       </c>
       <c r="K30" t="n">
-        <v>54029.9</v>
+        <v>54014.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2522</v>
+        <v>2521.5</v>
       </c>
       <c r="M30" t="n">
-        <v>6733.23</v>
+        <v>6732.48</v>
       </c>
       <c r="N30" t="n">
-        <v>5723.03</v>
+        <v>5721.53</v>
       </c>
     </row>
     <row r="31">
@@ -1386,7 +1386,7 @@
         <v>46087.20833333334</v>
       </c>
       <c r="B31" t="n">
-        <v>8947.799999999999</v>
+        <v>8943.9</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1407,40 +1407,40 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.152455</v>
+        <v>1.15241</v>
       </c>
       <c r="D32" t="n">
-        <v>1.330515</v>
+        <v>1.33047</v>
       </c>
       <c r="E32" t="n">
-        <v>7873</v>
+        <v>7871</v>
       </c>
       <c r="F32" t="n">
-        <v>23222.3</v>
+        <v>23218.8</v>
       </c>
       <c r="G32" t="n">
-        <v>46613</v>
+        <v>46610.6</v>
       </c>
       <c r="H32" t="n">
-        <v>10195.8</v>
+        <v>10193.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25042.2</v>
+        <v>25027.2</v>
       </c>
       <c r="J32" t="n">
-        <v>24187.4</v>
+        <v>24186.4</v>
       </c>
       <c r="K32" t="n">
-        <v>52216.5</v>
+        <v>52213</v>
       </c>
       <c r="L32" t="n">
-        <v>2433.35</v>
+        <v>2433.2</v>
       </c>
       <c r="M32" t="n">
-        <v>6622.45</v>
+        <v>6622.15</v>
       </c>
       <c r="N32" t="n">
-        <v>5615.9</v>
+        <v>5614.4</v>
       </c>
     </row>
     <row r="33">
@@ -1448,7 +1448,7 @@
         <v>46089.20833333334</v>
       </c>
       <c r="B33" t="n">
-        <v>11228.6</v>
+        <v>11224.7</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1469,40 +1469,40 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.161615</v>
+        <v>1.16157</v>
       </c>
       <c r="D34" t="n">
-        <v>1.342445</v>
+        <v>1.3424</v>
       </c>
       <c r="E34" t="n">
-        <v>8000.3</v>
+        <v>7998.3</v>
       </c>
       <c r="F34" t="n">
-        <v>23703.1</v>
+        <v>23699.6</v>
       </c>
       <c r="G34" t="n">
-        <v>47534.3</v>
+        <v>47531.9</v>
       </c>
       <c r="H34" t="n">
-        <v>10307.8</v>
+        <v>10305.8</v>
       </c>
       <c r="I34" t="n">
-        <v>25545.7</v>
+        <v>25530.7</v>
       </c>
       <c r="J34" t="n">
-        <v>24854.1</v>
+        <v>24853.1</v>
       </c>
       <c r="K34" t="n">
-        <v>54259.6</v>
+        <v>54256.1</v>
       </c>
       <c r="L34" t="n">
-        <v>2534.05</v>
+        <v>2533.9</v>
       </c>
       <c r="M34" t="n">
-        <v>6766.07</v>
+        <v>6765.77</v>
       </c>
       <c r="N34" t="n">
-        <v>5764.7</v>
+        <v>5763.2</v>
       </c>
     </row>
     <row r="35">
@@ -1510,7 +1510,7 @@
         <v>46090.16666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>8805.4</v>
+        <v>8801.5</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -1531,40 +1531,40 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.161195</v>
+        <v>1.16115</v>
       </c>
       <c r="D36" t="n">
-        <v>1.341985</v>
+        <v>1.34194</v>
       </c>
       <c r="E36" t="n">
-        <v>7996.9</v>
+        <v>7994.9</v>
       </c>
       <c r="F36" t="n">
-        <v>23809.1</v>
+        <v>23805.6</v>
       </c>
       <c r="G36" t="n">
-        <v>47744.5</v>
+        <v>47742.1</v>
       </c>
       <c r="H36" t="n">
-        <v>10385.1</v>
+        <v>10383.1</v>
       </c>
       <c r="I36" t="n">
-        <v>25945.2</v>
+        <v>25930.2</v>
       </c>
       <c r="J36" t="n">
-        <v>24990.4</v>
+        <v>24989.4</v>
       </c>
       <c r="K36" t="n">
-        <v>55066.9</v>
+        <v>55063.4</v>
       </c>
       <c r="L36" t="n">
-        <v>2552.05</v>
+        <v>2551.9</v>
       </c>
       <c r="M36" t="n">
-        <v>6791.25</v>
+        <v>6790.95</v>
       </c>
       <c r="N36" t="n">
-        <v>5786.9</v>
+        <v>5785.4</v>
       </c>
     </row>
     <row r="37">
@@ -1572,7 +1572,7 @@
         <v>46091.16666666666</v>
       </c>
       <c r="B37" t="n">
-        <v>8214.299999999999</v>
+        <v>8210.4</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -1593,40 +1593,40 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1.154265</v>
+        <v>1.15422</v>
       </c>
       <c r="D38" t="n">
-        <v>1.338255</v>
+        <v>1.33821</v>
       </c>
       <c r="E38" t="n">
-        <v>7976.9</v>
+        <v>7974.9</v>
       </c>
       <c r="F38" t="n">
-        <v>23465.2</v>
+        <v>23461.7</v>
       </c>
       <c r="G38" t="n">
-        <v>47030.3</v>
+        <v>47027.9</v>
       </c>
       <c r="H38" t="n">
-        <v>10272.4</v>
+        <v>10270.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25634.7</v>
+        <v>25619.7</v>
       </c>
       <c r="J38" t="n">
-        <v>24768.1</v>
+        <v>24767.1</v>
       </c>
       <c r="K38" t="n">
-        <v>54158</v>
+        <v>54154.5</v>
       </c>
       <c r="L38" t="n">
-        <v>2505.75</v>
+        <v>2505.6</v>
       </c>
       <c r="M38" t="n">
-        <v>6724.610000000001</v>
+        <v>6724.31</v>
       </c>
       <c r="N38" t="n">
-        <v>5752.63</v>
+        <v>5751.13</v>
       </c>
     </row>
     <row r="39">
@@ -1634,7 +1634,7 @@
         <v>46092.16666666666</v>
       </c>
       <c r="B39" t="n">
-        <v>9366.299999999999</v>
+        <v>9363.9</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -1655,40 +1655,40 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1.152065</v>
+        <v>1.15202</v>
       </c>
       <c r="D40" t="n">
-        <v>1.335115</v>
+        <v>1.33507</v>
       </c>
       <c r="E40" t="n">
-        <v>7964.5</v>
+        <v>7962.5</v>
       </c>
       <c r="F40" t="n">
-        <v>23495</v>
+        <v>23491.5</v>
       </c>
       <c r="G40" t="n">
-        <v>46739.9</v>
+        <v>46737.5</v>
       </c>
       <c r="H40" t="n">
-        <v>10283.7</v>
+        <v>10281.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25453.6</v>
+        <v>25438.6</v>
       </c>
       <c r="J40" t="n">
-        <v>24514</v>
+        <v>24513</v>
       </c>
       <c r="K40" t="n">
-        <v>53462.2</v>
+        <v>53458.7</v>
       </c>
       <c r="L40" t="n">
-        <v>2490.95</v>
+        <v>2490.8</v>
       </c>
       <c r="M40" t="n">
-        <v>6676.01</v>
+        <v>6675.71</v>
       </c>
       <c r="N40" t="n">
-        <v>5725.3</v>
+        <v>5723.8</v>
       </c>
     </row>
     <row r="41">
@@ -1696,7 +1696,7 @@
         <v>46093.16666666666</v>
       </c>
       <c r="B41" t="n">
-        <v>9468.4</v>
+        <v>9466</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -1717,40 +1717,40 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.141665</v>
+        <v>1.14162</v>
       </c>
       <c r="D42" t="n">
-        <v>1.32235</v>
+        <v>1.3218</v>
       </c>
       <c r="E42" t="n">
-        <v>7875.6</v>
+        <v>7874.6</v>
       </c>
       <c r="F42" t="n">
-        <v>23329.3</v>
+        <v>23327.9</v>
       </c>
       <c r="G42" t="n">
-        <v>46475.1</v>
+        <v>46470.2</v>
       </c>
       <c r="H42" t="n">
-        <v>10240.1</v>
+        <v>10238.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25400.4</v>
+        <v>25385.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24321.2</v>
+        <v>24318.7</v>
       </c>
       <c r="K42" t="n">
-        <v>53150.3</v>
+        <v>53135.3</v>
       </c>
       <c r="L42" t="n">
-        <v>2474.5</v>
+        <v>2474</v>
       </c>
       <c r="M42" t="n">
-        <v>6621.04</v>
+        <v>6620.29</v>
       </c>
       <c r="N42" t="n">
-        <v>5689.36</v>
+        <v>5688.61</v>
       </c>
     </row>
     <row r="43">
@@ -1758,7 +1758,7 @@
         <v>46094.16666666666</v>
       </c>
       <c r="B43" t="n">
-        <v>9766.4</v>
+        <v>9764</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -1779,40 +1779,40 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1.143595</v>
+        <v>1.14355</v>
       </c>
       <c r="D44" t="n">
-        <v>1.324575</v>
+        <v>1.3245</v>
       </c>
       <c r="E44" t="n">
-        <v>7919.5</v>
+        <v>7917.5</v>
       </c>
       <c r="F44" t="n">
-        <v>23428.6</v>
+        <v>23425.1</v>
       </c>
       <c r="G44" t="n">
-        <v>46641.8</v>
+        <v>46639.4</v>
       </c>
       <c r="H44" t="n">
-        <v>10268.8</v>
+        <v>10266.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25450.7</v>
+        <v>25435.7</v>
       </c>
       <c r="J44" t="n">
-        <v>24424</v>
+        <v>24423</v>
       </c>
       <c r="K44" t="n">
-        <v>53651.9</v>
+        <v>53648.4</v>
       </c>
       <c r="L44" t="n">
-        <v>2489.45</v>
+        <v>2489.3</v>
       </c>
       <c r="M44" t="n">
-        <v>6645.48</v>
+        <v>6645.18</v>
       </c>
       <c r="N44" t="n">
-        <v>5713.9</v>
+        <v>5712.4</v>
       </c>
     </row>
     <row r="45">
@@ -1820,7 +1820,7 @@
         <v>46096.16666666666</v>
       </c>
       <c r="B45" t="n">
-        <v>9778.700000000001</v>
+        <v>9776.299999999999</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -1841,40 +1841,40 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1.149815</v>
+        <v>1.14977</v>
       </c>
       <c r="D46" t="n">
-        <v>1.331215</v>
+        <v>1.33114</v>
       </c>
       <c r="E46" t="n">
-        <v>7949</v>
+        <v>7947</v>
       </c>
       <c r="F46" t="n">
-        <v>23625.4</v>
+        <v>23621.9</v>
       </c>
       <c r="G46" t="n">
-        <v>46926.7</v>
+        <v>46924.3</v>
       </c>
       <c r="H46" t="n">
-        <v>10347</v>
+        <v>10345</v>
       </c>
       <c r="I46" t="n">
-        <v>25861.7</v>
+        <v>25846.7</v>
       </c>
       <c r="J46" t="n">
-        <v>24652</v>
+        <v>24651</v>
       </c>
       <c r="K46" t="n">
-        <v>54337.6</v>
+        <v>54334.1</v>
       </c>
       <c r="L46" t="n">
-        <v>2501.65</v>
+        <v>2501.5</v>
       </c>
       <c r="M46" t="n">
-        <v>6698.12</v>
+        <v>6697.82</v>
       </c>
       <c r="N46" t="n">
-        <v>5754.2</v>
+        <v>5752.7</v>
       </c>
     </row>
     <row r="47">
@@ -1882,7 +1882,7 @@
         <v>46097.16666666666</v>
       </c>
       <c r="B47" t="n">
-        <v>9527.4</v>
+        <v>9525</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -1903,40 +1903,40 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1.153885</v>
+        <v>1.15383</v>
       </c>
       <c r="D48" t="n">
-        <v>1.33575</v>
+        <v>1.33558</v>
       </c>
       <c r="E48" t="n">
-        <v>7956.2</v>
+        <v>7954.2</v>
       </c>
       <c r="F48" t="n">
-        <v>23670.5</v>
+        <v>23667</v>
       </c>
       <c r="G48" t="n">
-        <v>46944.6</v>
+        <v>46942.2</v>
       </c>
       <c r="H48" t="n">
-        <v>10362.5</v>
+        <v>10360.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25859.5</v>
+        <v>25844.5</v>
       </c>
       <c r="J48" t="n">
-        <v>24775.5</v>
+        <v>24774.5</v>
       </c>
       <c r="K48" t="n">
-        <v>54274.4</v>
+        <v>54270.9</v>
       </c>
       <c r="L48" t="n">
-        <v>2517.85</v>
+        <v>2517.7</v>
       </c>
       <c r="M48" t="n">
-        <v>6711.68</v>
+        <v>6711.38</v>
       </c>
       <c r="N48" t="n">
-        <v>5756.4</v>
+        <v>5754.9</v>
       </c>
     </row>
     <row r="49">
@@ -1944,7 +1944,7 @@
         <v>46098.16666666666</v>
       </c>
       <c r="B49" t="n">
-        <v>9250.1</v>
+        <v>9247.700000000001</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -1965,40 +1965,40 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.146325</v>
+        <v>1.14628</v>
       </c>
       <c r="D50" t="n">
-        <v>1.326425</v>
+        <v>1.32638</v>
       </c>
       <c r="E50" t="n">
-        <v>7897.7</v>
+        <v>7895.7</v>
       </c>
       <c r="F50" t="n">
-        <v>23169.5</v>
+        <v>23166</v>
       </c>
       <c r="G50" t="n">
-        <v>46157</v>
+        <v>46154.6</v>
       </c>
       <c r="H50" t="n">
-        <v>10221.1</v>
+        <v>10219.1</v>
       </c>
       <c r="I50" t="n">
-        <v>25416.9</v>
+        <v>25401.9</v>
       </c>
       <c r="J50" t="n">
-        <v>24395.2</v>
+        <v>24394.2</v>
       </c>
       <c r="K50" t="n">
-        <v>53599.6</v>
+        <v>53596.1</v>
       </c>
       <c r="L50" t="n">
-        <v>2474.45</v>
+        <v>2474.3</v>
       </c>
       <c r="M50" t="n">
-        <v>6698.99</v>
+        <v>6698.79</v>
       </c>
       <c r="N50" t="n">
-        <v>5655.5</v>
+        <v>5654</v>
       </c>
     </row>
     <row r="51">
@@ -2006,7 +2006,7 @@
         <v>46099.16666666666</v>
       </c>
       <c r="B51" t="n">
-        <v>9650.299999999999</v>
+        <v>9647.9</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -2027,38 +2027,38 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.15765</v>
+        <v>1.15762</v>
       </c>
       <c r="D52" t="n">
-        <v>1.342435</v>
+        <v>1.34236</v>
       </c>
       <c r="E52" t="n">
-        <v>7842.7</v>
+        <v>7840.7</v>
       </c>
       <c r="F52" t="n">
-        <v>23019.7</v>
+        <v>23016.2</v>
       </c>
       <c r="G52" t="n">
-        <v>46139.2</v>
+        <v>46136.8</v>
       </c>
       <c r="H52" t="n">
-        <v>10069.6</v>
+        <v>10067.6</v>
       </c>
       <c r="I52" t="n">
-        <v>25368.8</v>
+        <v>25353.8</v>
       </c>
       <c r="J52" t="n">
-        <v>24407.7</v>
+        <v>24406.7</v>
       </c>
       <c r="K52" t="n">
-        <v>53401.2</v>
+        <v>53397.7</v>
       </c>
       <c r="L52" t="n">
-        <v>2508.55</v>
+        <v>2508.4</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>5655.4</v>
+        <v>5653.9</v>
       </c>
     </row>
     <row r="53">
@@ -2066,7 +2066,7 @@
         <v>46100.16666666666</v>
       </c>
       <c r="B53" t="n">
-        <v>9386.799999999999</v>
+        <v>9384.4</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -2087,40 +2087,40 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.15709</v>
+        <v>1.15679</v>
       </c>
       <c r="D54" t="n">
-        <v>1.33411</v>
+        <v>1.33356</v>
       </c>
       <c r="E54" t="n">
-        <v>7613.8</v>
+        <v>7611.8</v>
       </c>
       <c r="F54" t="n">
-        <v>22214.3</v>
+        <v>22210.8</v>
       </c>
       <c r="G54" t="n">
-        <v>45803.1</v>
+        <v>45798.2</v>
       </c>
       <c r="H54" t="n">
-        <v>9839.299999999999</v>
+        <v>9837.299999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>24770.8</v>
+        <v>24755.8</v>
       </c>
       <c r="J54" t="n">
-        <v>24000.4</v>
+        <v>23997.9</v>
       </c>
       <c r="K54" t="n">
-        <v>51317.2</v>
+        <v>51302.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2452.1</v>
+        <v>2451.6</v>
       </c>
       <c r="M54" t="n">
-        <v>6537.12</v>
+        <v>6536.37</v>
       </c>
       <c r="N54" t="n">
-        <v>5474.95</v>
+        <v>5473.45</v>
       </c>
     </row>
     <row r="55">
@@ -2128,7 +2128,7 @@
         <v>46101.16666666666</v>
       </c>
       <c r="B55" t="n">
-        <v>9792.700000000001</v>
+        <v>9788.799999999999</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -2149,40 +2149,40 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.156245</v>
+        <v>1.1562</v>
       </c>
       <c r="D56" t="n">
-        <v>1.333395</v>
+        <v>1.33332</v>
       </c>
       <c r="E56" t="n">
-        <v>7540.6</v>
+        <v>7538.6</v>
       </c>
       <c r="F56" t="n">
-        <v>21975.6</v>
+        <v>21972.1</v>
       </c>
       <c r="G56" t="n">
-        <v>45538.6</v>
+        <v>45536.2</v>
       </c>
       <c r="H56" t="n">
-        <v>9794.1</v>
+        <v>9792.1</v>
       </c>
       <c r="I56" t="n">
-        <v>24659.3</v>
+        <v>24644.3</v>
       </c>
       <c r="J56" t="n">
-        <v>23794.4</v>
+        <v>23793.4</v>
       </c>
       <c r="K56" t="n">
-        <v>51180.5</v>
+        <v>51177</v>
       </c>
       <c r="L56" t="n">
-        <v>2432.65</v>
+        <v>2432.5</v>
       </c>
       <c r="M56" t="n">
-        <v>6488.5</v>
+        <v>6488.2</v>
       </c>
       <c r="N56" t="n">
-        <v>5419.6</v>
+        <v>5418.1</v>
       </c>
     </row>
     <row r="57">
@@ -2190,7 +2190,7 @@
         <v>46103.16666666666</v>
       </c>
       <c r="B57" t="n">
-        <v>9885.6</v>
+        <v>9883.200000000001</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -2211,40 +2211,40 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.1608</v>
+        <v>1.16077</v>
       </c>
       <c r="D58" t="n">
-        <v>1.342625</v>
+        <v>1.34255</v>
       </c>
       <c r="E58" t="n">
-        <v>7798.8</v>
+        <v>7796.8</v>
       </c>
       <c r="F58" t="n">
-        <v>22845</v>
+        <v>22841.5</v>
       </c>
       <c r="G58" t="n">
-        <v>46290.6</v>
+        <v>46288.2</v>
       </c>
       <c r="H58" t="n">
-        <v>9963.6</v>
+        <v>9961.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24982.7</v>
+        <v>24967.7</v>
       </c>
       <c r="J58" t="n">
-        <v>24241.8</v>
+        <v>24240.8</v>
       </c>
       <c r="K58" t="n">
-        <v>53018.2</v>
+        <v>53014.7</v>
       </c>
       <c r="L58" t="n">
-        <v>2500.55</v>
+        <v>2500.4</v>
       </c>
       <c r="M58" t="n">
-        <v>6594.07</v>
+        <v>6593.77</v>
       </c>
       <c r="N58" t="n">
-        <v>5617.7</v>
+        <v>5616.2</v>
       </c>
     </row>
     <row r="59">
@@ -2252,7 +2252,7 @@
         <v>46104.16666666666</v>
       </c>
       <c r="B59" t="n">
-        <v>9123.4</v>
+        <v>9121</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -2273,40 +2273,40 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.161345</v>
+        <v>1.1613</v>
       </c>
       <c r="D60" t="n">
-        <v>1.341485</v>
+        <v>1.34141</v>
       </c>
       <c r="E60" t="n">
-        <v>7815.7</v>
+        <v>7813.7</v>
       </c>
       <c r="F60" t="n">
-        <v>22891</v>
+        <v>22887.5</v>
       </c>
       <c r="G60" t="n">
-        <v>46448</v>
+        <v>46445.6</v>
       </c>
       <c r="H60" t="n">
-        <v>10015.3</v>
+        <v>10013.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25050.4</v>
+        <v>25035.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24205</v>
+        <v>24204</v>
       </c>
       <c r="K60" t="n">
-        <v>53500.6</v>
+        <v>53497.1</v>
       </c>
       <c r="L60" t="n">
-        <v>2535.75</v>
+        <v>2535.6</v>
       </c>
       <c r="M60" t="n">
-        <v>6599.97</v>
+        <v>6599.67</v>
       </c>
       <c r="N60" t="n">
-        <v>5645.68</v>
+        <v>5644.18</v>
       </c>
     </row>
     <row r="61">
@@ -2314,7 +2314,7 @@
         <v>46105.16666666666</v>
       </c>
       <c r="B61" t="n">
-        <v>8855.200000000001</v>
+        <v>8852.799999999999</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -2335,40 +2335,40 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.156185</v>
+        <v>1.15614</v>
       </c>
       <c r="D62" t="n">
-        <v>1.336385</v>
+        <v>1.33631</v>
       </c>
       <c r="E62" t="n">
-        <v>7815.5</v>
+        <v>7813.5</v>
       </c>
       <c r="F62" t="n">
-        <v>22870.1</v>
+        <v>22866.6</v>
       </c>
       <c r="G62" t="n">
-        <v>46359.5</v>
+        <v>46357.1</v>
       </c>
       <c r="H62" t="n">
-        <v>10085.7</v>
+        <v>10083.7</v>
       </c>
       <c r="I62" t="n">
-        <v>25259.3</v>
+        <v>25244.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24114.6</v>
+        <v>24113.6</v>
       </c>
       <c r="K62" t="n">
-        <v>53878.5</v>
+        <v>53875</v>
       </c>
       <c r="L62" t="n">
-        <v>2530.75</v>
+        <v>2530.6</v>
       </c>
       <c r="M62" t="n">
-        <v>6581</v>
+        <v>6580.7</v>
       </c>
       <c r="N62" t="n">
-        <v>5621.51</v>
+        <v>5620.01</v>
       </c>
     </row>
     <row r="63">
@@ -2376,7 +2376,7 @@
         <v>46106.16666666666</v>
       </c>
       <c r="B63" t="n">
-        <v>9117.700000000001</v>
+        <v>9115.299999999999</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -2397,40 +2397,40 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.153495</v>
+        <v>1.15345</v>
       </c>
       <c r="D64" t="n">
-        <v>1.333415</v>
+        <v>1.33334</v>
       </c>
       <c r="E64" t="n">
-        <v>7780.5</v>
+        <v>7778.5</v>
       </c>
       <c r="F64" t="n">
-        <v>22692.5</v>
+        <v>22689</v>
       </c>
       <c r="G64" t="n">
-        <v>46181.1</v>
+        <v>46178.7</v>
       </c>
       <c r="H64" t="n">
-        <v>9965.799999999999</v>
+        <v>9963.799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>24768.8</v>
+        <v>24753.8</v>
       </c>
       <c r="J64" t="n">
-        <v>23682.7</v>
+        <v>23681.7</v>
       </c>
       <c r="K64" t="n">
-        <v>52923.6</v>
+        <v>52920.1</v>
       </c>
       <c r="L64" t="n">
-        <v>2508.55</v>
+        <v>2508.4</v>
       </c>
       <c r="M64" t="n">
-        <v>6506.25</v>
+        <v>6505.95</v>
       </c>
       <c r="N64" t="n">
-        <v>5573</v>
+        <v>5571.5</v>
       </c>
     </row>
     <row r="65">
@@ -2438,7 +2438,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B65" t="n">
-        <v>9274.799999999999</v>
+        <v>9272.4</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -2459,40 +2459,40 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.15097</v>
+        <v>1.15067</v>
       </c>
       <c r="D66" t="n">
-        <v>1.3264</v>
+        <v>1.32591</v>
       </c>
       <c r="E66" t="n">
-        <v>7646.4</v>
+        <v>7644.4</v>
       </c>
       <c r="F66" t="n">
-        <v>22101.1</v>
+        <v>22097.6</v>
       </c>
       <c r="G66" t="n">
-        <v>45061.5</v>
+        <v>45056.6</v>
       </c>
       <c r="H66" t="n">
-        <v>9895.299999999999</v>
+        <v>9893.299999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24627.5</v>
+        <v>24612.5</v>
       </c>
       <c r="J66" t="n">
-        <v>23069.6</v>
+        <v>23067.1</v>
       </c>
       <c r="K66" t="n">
-        <v>51137.7</v>
+        <v>51122.7</v>
       </c>
       <c r="L66" t="n">
-        <v>2443.2</v>
+        <v>2442.7</v>
       </c>
       <c r="M66" t="n">
-        <v>6355.25</v>
+        <v>6354.5</v>
       </c>
       <c r="N66" t="n">
-        <v>5455.22</v>
+        <v>5453.72</v>
       </c>
     </row>
     <row r="67">
@@ -2500,7 +2500,7 @@
         <v>46108.16666666666</v>
       </c>
       <c r="B67" t="n">
-        <v>9977.299999999999</v>
+        <v>9973.4</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -2521,40 +2521,40 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.148835</v>
+        <v>1.14879</v>
       </c>
       <c r="D68" t="n">
-        <v>1.323875</v>
+        <v>1.32377</v>
       </c>
       <c r="E68" t="n">
-        <v>7618.7</v>
+        <v>7616.7</v>
       </c>
       <c r="F68" t="n">
-        <v>22031.4</v>
+        <v>22027.9</v>
       </c>
       <c r="G68" t="n">
-        <v>44945.6</v>
+        <v>44943.2</v>
       </c>
       <c r="H68" t="n">
-        <v>9879.4</v>
+        <v>9877.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24593.4</v>
+        <v>24578.4</v>
       </c>
       <c r="J68" t="n">
-        <v>23027.2</v>
+        <v>23026.2</v>
       </c>
       <c r="K68" t="n">
-        <v>50609</v>
+        <v>50601.5</v>
       </c>
       <c r="L68" t="n">
-        <v>2430.85</v>
+        <v>2430.7</v>
       </c>
       <c r="M68" t="n">
-        <v>6340.21</v>
+        <v>6339.91</v>
       </c>
       <c r="N68" t="n">
-        <v>5435.4</v>
+        <v>5433.9</v>
       </c>
     </row>
     <row r="69">
@@ -2562,7 +2562,7 @@
         <v>46110.20833333334</v>
       </c>
       <c r="B69" t="n">
-        <v>9976.4</v>
+        <v>9974</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -2583,40 +2583,40 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1.145975</v>
+        <v>1.14593</v>
       </c>
       <c r="D70" t="n">
-        <v>1.317995</v>
+        <v>1.31792</v>
       </c>
       <c r="E70" t="n">
-        <v>7722.7</v>
+        <v>7720.7</v>
       </c>
       <c r="F70" t="n">
-        <v>22434.6</v>
+        <v>22431.1</v>
       </c>
       <c r="G70" t="n">
-        <v>45225.5</v>
+        <v>45223.1</v>
       </c>
       <c r="H70" t="n">
-        <v>10070.4</v>
+        <v>10068.4</v>
       </c>
       <c r="I70" t="n">
-        <v>24724.4</v>
+        <v>24709.4</v>
       </c>
       <c r="J70" t="n">
-        <v>22920.3</v>
+        <v>22919.3</v>
       </c>
       <c r="K70" t="n">
-        <v>51054.8</v>
+        <v>51047.3</v>
       </c>
       <c r="L70" t="n">
-        <v>2409.85</v>
+        <v>2409.7</v>
       </c>
       <c r="M70" t="n">
-        <v>6341.38</v>
+        <v>6341.08</v>
       </c>
       <c r="N70" t="n">
-        <v>5500.9</v>
+        <v>5499.4</v>
       </c>
     </row>
     <row r="71">
@@ -2624,7 +2624,7 @@
         <v>46111.20833333334</v>
       </c>
       <c r="B71" t="n">
-        <v>10068.9</v>
+        <v>10066.5</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -2645,40 +2645,40 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.155875</v>
+        <v>1.15583</v>
       </c>
       <c r="D72" t="n">
-        <v>1.323055</v>
+        <v>1.32294</v>
       </c>
       <c r="E72" t="n">
-        <v>7921.4</v>
+        <v>7919.4</v>
       </c>
       <c r="F72" t="n">
-        <v>23026.2</v>
+        <v>23022.7</v>
       </c>
       <c r="G72" t="n">
-        <v>46230.95</v>
+        <v>46229.5</v>
       </c>
       <c r="H72" t="n">
-        <v>10279.9</v>
+        <v>10277.9</v>
       </c>
       <c r="I72" t="n">
-        <v>25317.1</v>
+        <v>25302.1</v>
       </c>
       <c r="J72" t="n">
-        <v>23777.1</v>
+        <v>23776.1</v>
       </c>
       <c r="K72" t="n">
-        <v>53050.8</v>
+        <v>53043.3</v>
       </c>
       <c r="L72" t="n">
-        <v>2494.15</v>
+        <v>2494</v>
       </c>
       <c r="M72" t="n">
-        <v>6530.15</v>
+        <v>6529.85</v>
       </c>
       <c r="N72" t="n">
-        <v>5653.5</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="73">
@@ -2686,7 +2686,7 @@
         <v>46112.20833333334</v>
       </c>
       <c r="B73" t="n">
-        <v>9969.1</v>
+        <v>9966.700000000001</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -2707,40 +2707,40 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1.159095</v>
+        <v>1.15905</v>
       </c>
       <c r="D74" t="n">
-        <v>1.330625</v>
+        <v>1.33055</v>
       </c>
       <c r="E74" t="n">
-        <v>7976.6</v>
+        <v>7974.6</v>
       </c>
       <c r="F74" t="n">
-        <v>23289</v>
+        <v>23285.5</v>
       </c>
       <c r="G74" t="n">
-        <v>46561.8</v>
+        <v>46559.4</v>
       </c>
       <c r="H74" t="n">
-        <v>10416.2</v>
+        <v>10414.2</v>
       </c>
       <c r="I74" t="n">
-        <v>25315.3</v>
+        <v>25300.3</v>
       </c>
       <c r="J74" t="n">
-        <v>23996.1</v>
+        <v>23995.1</v>
       </c>
       <c r="K74" t="n">
-        <v>54233.9</v>
+        <v>54226.4</v>
       </c>
       <c r="L74" t="n">
-        <v>2510.15</v>
+        <v>2510</v>
       </c>
       <c r="M74" t="n">
-        <v>6572.13</v>
+        <v>6571.83</v>
       </c>
       <c r="N74" t="n">
-        <v>5720.9</v>
+        <v>5719.4</v>
       </c>
     </row>
     <row r="75">
@@ -2748,7 +2748,7 @@
         <v>46113.20833333334</v>
       </c>
       <c r="B75" t="n">
-        <v>10095.1</v>
+        <v>10092.7</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -2769,40 +2769,40 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1.154015</v>
+        <v>1.15397</v>
       </c>
       <c r="D76" t="n">
-        <v>1.322585</v>
+        <v>1.32248</v>
       </c>
       <c r="E76" t="n">
-        <v>7990.9</v>
+        <v>7988.9</v>
       </c>
       <c r="F76" t="n">
-        <v>23217.6</v>
+        <v>23214.1</v>
       </c>
       <c r="G76" t="n">
-        <v>46522.4</v>
+        <v>46520</v>
       </c>
       <c r="H76" t="n">
-        <v>10451.6</v>
+        <v>10449.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25270.4</v>
+        <v>25255.4</v>
       </c>
       <c r="J76" t="n">
-        <v>24030.5</v>
+        <v>24029.5</v>
       </c>
       <c r="K76" t="n">
-        <v>53247.5</v>
+        <v>53240</v>
       </c>
       <c r="L76" t="n">
-        <v>2530.55</v>
+        <v>2530.4</v>
       </c>
       <c r="M76" t="n">
-        <v>6583.360000000001</v>
+        <v>6583.06</v>
       </c>
       <c r="N76" t="n">
-        <v>5701.47</v>
+        <v>5699.97</v>
       </c>
     </row>
     <row r="77">
@@ -2810,7 +2810,7 @@
         <v>46114.20833333334</v>
       </c>
       <c r="B77" t="n">
-        <v>10581</v>
+        <v>10578.6</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -2831,40 +2831,40 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.15187</v>
+        <v>1.15154</v>
       </c>
       <c r="D78" t="n">
-        <v>1.320465</v>
+        <v>1.31987</v>
       </c>
       <c r="E78" t="n">
-        <v>7960.4</v>
+        <v>7958.4</v>
       </c>
       <c r="F78" t="n">
-        <v>23127.3</v>
+        <v>23123.8</v>
       </c>
       <c r="G78" t="n">
-        <v>46407.7</v>
+        <v>46405.9</v>
       </c>
       <c r="H78" t="n">
-        <v>10432</v>
+        <v>10430</v>
       </c>
       <c r="I78" t="n">
-        <v>25188.7</v>
+        <v>25173.7</v>
       </c>
       <c r="J78" t="n">
-        <v>23957.4</v>
+        <v>23956.4</v>
       </c>
       <c r="K78" t="n">
-        <v>53165.2</v>
+        <v>53150.2</v>
       </c>
       <c r="L78" t="n">
-        <v>2519.65</v>
+        <v>2519.5</v>
       </c>
       <c r="M78" t="n">
-        <v>6563.67</v>
+        <v>6563.37</v>
       </c>
       <c r="N78" t="n">
-        <v>5679.77</v>
+        <v>5678.27</v>
       </c>
     </row>
     <row r="79">
@@ -2875,34 +2875,34 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>7934.5</v>
+        <v>7932.5</v>
       </c>
       <c r="F79" t="n">
-        <v>23052.9</v>
+        <v>23049.4</v>
       </c>
       <c r="G79" t="n">
-        <v>46258.3</v>
+        <v>46255.9</v>
       </c>
       <c r="H79" t="n">
-        <v>10416.4</v>
+        <v>10414.4</v>
       </c>
       <c r="I79" t="n">
-        <v>25153.9</v>
+        <v>25138.9</v>
       </c>
       <c r="J79" t="n">
-        <v>23907.8</v>
+        <v>23906.8</v>
       </c>
       <c r="K79" t="n">
-        <v>52872.6</v>
+        <v>52865.1</v>
       </c>
       <c r="L79" t="n">
-        <v>2510.85</v>
+        <v>2510.7</v>
       </c>
       <c r="M79" t="n">
-        <v>6547.57</v>
+        <v>6547.27</v>
       </c>
       <c r="N79" t="n">
-        <v>5661.8</v>
+        <v>5660.3</v>
       </c>
     </row>
     <row r="80">
@@ -2910,7 +2910,7 @@
         <v>46117.20833333334</v>
       </c>
       <c r="B80" t="n">
-        <v>10420.3</v>
+        <v>10417.9</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -2931,40 +2931,40 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1.154265</v>
+        <v>1.15422</v>
       </c>
       <c r="D81" t="n">
-        <v>1.323355</v>
+        <v>1.32328</v>
       </c>
       <c r="E81" t="n">
-        <v>8026.1</v>
+        <v>8024.1</v>
       </c>
       <c r="F81" t="n">
-        <v>23295.1</v>
+        <v>23291.6</v>
       </c>
       <c r="G81" t="n">
-        <v>46709.5</v>
+        <v>46707.1</v>
       </c>
       <c r="H81" t="n">
-        <v>10477.6</v>
+        <v>10475.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25312</v>
+        <v>25297</v>
       </c>
       <c r="J81" t="n">
-        <v>24134.7</v>
+        <v>24133.7</v>
       </c>
       <c r="K81" t="n">
-        <v>53883.7</v>
+        <v>53876.2</v>
       </c>
       <c r="L81" t="n">
-        <v>2536.65</v>
+        <v>2536.5</v>
       </c>
       <c r="M81" t="n">
-        <v>6603.96</v>
+        <v>6603.66</v>
       </c>
       <c r="N81" t="n">
-        <v>5727.1</v>
+        <v>5725.6</v>
       </c>
     </row>
     <row r="82">
@@ -2972,7 +2972,7 @@
         <v>46118.20833333334</v>
       </c>
       <c r="B82" t="n">
-        <v>10675.7</v>
+        <v>10673.3</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -2993,40 +2993,40 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1.166825</v>
+        <v>1.16675</v>
       </c>
       <c r="D83" t="n">
-        <v>1.337355</v>
+        <v>1.33725</v>
       </c>
       <c r="E83" t="n">
-        <v>8193.700000000001</v>
+        <v>8191.7</v>
       </c>
       <c r="F83" t="n">
-        <v>23802.3</v>
+        <v>23798.8</v>
       </c>
       <c r="G83" t="n">
-        <v>47545.8</v>
+        <v>47543.4</v>
       </c>
       <c r="H83" t="n">
-        <v>10557.1</v>
+        <v>10555.1</v>
       </c>
       <c r="I83" t="n">
-        <v>25620.5</v>
+        <v>25605.5</v>
       </c>
       <c r="J83" t="n">
-        <v>24748.9</v>
+        <v>24747.9</v>
       </c>
       <c r="K83" t="n">
-        <v>55942.4</v>
+        <v>55934.9</v>
       </c>
       <c r="L83" t="n">
-        <v>2623.75</v>
+        <v>2623.6</v>
       </c>
       <c r="M83" t="n">
-        <v>6752.42</v>
+        <v>6752.12</v>
       </c>
       <c r="N83" t="n">
-        <v>5845.7</v>
+        <v>5844.2</v>
       </c>
     </row>
     <row r="84">
@@ -3034,7 +3034,7 @@
         <v>46119.20833333334</v>
       </c>
       <c r="B84" t="n">
-        <v>9110.700000000001</v>
+        <v>9108.299999999999</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -3055,40 +3055,40 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1.166275</v>
+        <v>1.16623</v>
       </c>
       <c r="D85" t="n">
-        <v>1.339785</v>
+        <v>1.33971</v>
       </c>
       <c r="E85" t="n">
-        <v>8274.200000000001</v>
+        <v>8272.200000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>24005.2</v>
+        <v>24001.7</v>
       </c>
       <c r="G85" t="n">
-        <v>47886.5</v>
+        <v>47884.1</v>
       </c>
       <c r="H85" t="n">
-        <v>10659.2</v>
+        <v>10657.2</v>
       </c>
       <c r="I85" t="n">
-        <v>25877.5</v>
+        <v>25862.5</v>
       </c>
       <c r="J85" t="n">
-        <v>24864</v>
+        <v>24863</v>
       </c>
       <c r="K85" t="n">
-        <v>56750.7</v>
+        <v>56743.2</v>
       </c>
       <c r="L85" t="n">
-        <v>2621.15</v>
+        <v>2621</v>
       </c>
       <c r="M85" t="n">
-        <v>6775.84</v>
+        <v>6775.54</v>
       </c>
       <c r="N85" t="n">
-        <v>5913.6</v>
+        <v>5912.1</v>
       </c>
     </row>
     <row r="86">
@@ -3096,7 +3096,7 @@
         <v>46120.20833333334</v>
       </c>
       <c r="B86" t="n">
-        <v>9245.299999999999</v>
+        <v>9242.9</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -3117,40 +3117,40 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.169405</v>
+        <v>1.16936</v>
       </c>
       <c r="D87" t="n">
-        <v>1.342805</v>
+        <v>1.34273</v>
       </c>
       <c r="E87" t="n">
-        <v>8252.299999999999</v>
+        <v>8250.299999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>23860.1</v>
+        <v>23856.6</v>
       </c>
       <c r="G87" t="n">
-        <v>48155.1</v>
+        <v>48152.7</v>
       </c>
       <c r="H87" t="n">
-        <v>10594.9</v>
+        <v>10592.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25916.1</v>
+        <v>25901.1</v>
       </c>
       <c r="J87" t="n">
-        <v>25042.9</v>
+        <v>25041.9</v>
       </c>
       <c r="K87" t="n">
-        <v>56487.1</v>
+        <v>56479.6</v>
       </c>
       <c r="L87" t="n">
-        <v>2635.65</v>
+        <v>2635.5</v>
       </c>
       <c r="M87" t="n">
-        <v>6816.9</v>
+        <v>6816.6</v>
       </c>
       <c r="N87" t="n">
-        <v>5900.9</v>
+        <v>5899.4</v>
       </c>
     </row>
     <row r="88">
@@ -3158,7 +3158,7 @@
         <v>46121.20833333334</v>
       </c>
       <c r="B88" t="n">
-        <v>9242.700000000001</v>
+        <v>9240.299999999999</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -3179,40 +3179,40 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.1726</v>
+        <v>1.17227</v>
       </c>
       <c r="D89" t="n">
-        <v>1.346235</v>
+        <v>1.34564</v>
       </c>
       <c r="E89" t="n">
-        <v>8266.799999999999</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>23823.9</v>
+        <v>23820.4</v>
       </c>
       <c r="G89" t="n">
-        <v>47972</v>
+        <v>47967.1</v>
       </c>
       <c r="H89" t="n">
-        <v>10605.1</v>
+        <v>10603.1</v>
       </c>
       <c r="I89" t="n">
-        <v>25948.9</v>
+        <v>25933.9</v>
       </c>
       <c r="J89" t="n">
-        <v>25164.7</v>
+        <v>25162.2</v>
       </c>
       <c r="K89" t="n">
-        <v>57406.8</v>
+        <v>57391.8</v>
       </c>
       <c r="L89" t="n">
-        <v>2636.3</v>
+        <v>2635.8</v>
       </c>
       <c r="M89" t="n">
-        <v>6825.55</v>
+        <v>6824.8</v>
       </c>
       <c r="N89" t="n">
-        <v>5928.91</v>
+        <v>5927.41</v>
       </c>
     </row>
     <row r="90">
@@ -3220,7 +3220,7 @@
         <v>46122.20833333334</v>
       </c>
       <c r="B90" t="n">
-        <v>9114.700000000001</v>
+        <v>9110.799999999999</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -3241,40 +3241,40 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.167255</v>
+        <v>1.16721</v>
       </c>
       <c r="D91" t="n">
-        <v>1.339455</v>
+        <v>1.33938</v>
       </c>
       <c r="E91" t="n">
-        <v>8130.9</v>
+        <v>8128.9</v>
       </c>
       <c r="F91" t="n">
-        <v>23438.1</v>
+        <v>23434.6</v>
       </c>
       <c r="G91" t="n">
-        <v>47403</v>
+        <v>47400.6</v>
       </c>
       <c r="H91" t="n">
-        <v>10523</v>
+        <v>10521</v>
       </c>
       <c r="I91" t="n">
-        <v>25770.2</v>
+        <v>25755.2</v>
       </c>
       <c r="J91" t="n">
-        <v>24791.8</v>
+        <v>24790.8</v>
       </c>
       <c r="K91" t="n">
-        <v>56085.5</v>
+        <v>56078</v>
       </c>
       <c r="L91" t="n">
-        <v>2587.85</v>
+        <v>2587.7</v>
       </c>
       <c r="M91" t="n">
-        <v>6740.55</v>
+        <v>6740.25</v>
       </c>
       <c r="N91" t="n">
-        <v>5831.8</v>
+        <v>5830.3</v>
       </c>
     </row>
     <row r="92">
@@ -3282,7 +3282,7 @@
         <v>46124.20833333334</v>
       </c>
       <c r="B92" t="n">
-        <v>9809.4</v>
+        <v>9807</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -3303,40 +3303,40 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.176135</v>
+        <v>1.17609</v>
       </c>
       <c r="D93" t="n">
-        <v>1.351065</v>
+        <v>1.35099</v>
       </c>
       <c r="E93" t="n">
-        <v>8268.299999999999</v>
+        <v>8266.299999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>23965.5</v>
+        <v>23962</v>
       </c>
       <c r="G93" t="n">
-        <v>48227.7</v>
+        <v>48225.3</v>
       </c>
       <c r="H93" t="n">
-        <v>10617.9</v>
+        <v>10615.9</v>
       </c>
       <c r="I93" t="n">
-        <v>25968.2</v>
+        <v>25953.2</v>
       </c>
       <c r="J93" t="n">
-        <v>25435.7</v>
+        <v>25434.7</v>
       </c>
       <c r="K93" t="n">
-        <v>57698.9</v>
+        <v>57691.4</v>
       </c>
       <c r="L93" t="n">
-        <v>2678.15</v>
+        <v>2678</v>
       </c>
       <c r="M93" t="n">
-        <v>6890.15</v>
+        <v>6889.85</v>
       </c>
       <c r="N93" t="n">
-        <v>5947.3</v>
+        <v>5945.8</v>
       </c>
     </row>
     <row r="94">
@@ -3344,7 +3344,7 @@
         <v>46125.20833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>9266.200000000001</v>
+        <v>9263.799999999999</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -3365,40 +3365,40 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.179485</v>
+        <v>1.17944</v>
       </c>
       <c r="D95" t="n">
-        <v>1.356875</v>
+        <v>1.3568</v>
       </c>
       <c r="E95" t="n">
-        <v>8326.9</v>
+        <v>8324.9</v>
       </c>
       <c r="F95" t="n">
-        <v>24054.9</v>
+        <v>24051.4</v>
       </c>
       <c r="G95" t="n">
-        <v>48537.7</v>
+        <v>48535.3</v>
       </c>
       <c r="H95" t="n">
-        <v>10624.6</v>
+        <v>10622.6</v>
       </c>
       <c r="I95" t="n">
-        <v>26212.7</v>
+        <v>26197.7</v>
       </c>
       <c r="J95" t="n">
-        <v>25830.8</v>
+        <v>25829.8</v>
       </c>
       <c r="K95" t="n">
-        <v>58706</v>
+        <v>58698.5</v>
       </c>
       <c r="L95" t="n">
-        <v>2705.55</v>
+        <v>2705.4</v>
       </c>
       <c r="M95" t="n">
-        <v>6967.77</v>
+        <v>6967.47</v>
       </c>
       <c r="N95" t="n">
-        <v>5986.4</v>
+        <v>5984.9</v>
       </c>
     </row>
     <row r="96">
@@ -3406,7 +3406,7 @@
         <v>46126.20833333334</v>
       </c>
       <c r="B96" t="n">
-        <v>8869</v>
+        <v>8866.6</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -3427,40 +3427,40 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.180235</v>
+        <v>1.18019</v>
       </c>
       <c r="D97" t="n">
-        <v>1.356785</v>
+        <v>1.35671</v>
       </c>
       <c r="E97" t="n">
-        <v>8264.799999999999</v>
+        <v>8262.799999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>24107.1</v>
+        <v>24103.6</v>
       </c>
       <c r="G97" t="n">
-        <v>48527.8</v>
+        <v>48525.4</v>
       </c>
       <c r="H97" t="n">
-        <v>10556.1</v>
+        <v>10554.1</v>
       </c>
       <c r="I97" t="n">
-        <v>26130.4</v>
+        <v>26115.4</v>
       </c>
       <c r="J97" t="n">
-        <v>26229.3</v>
+        <v>26228.3</v>
       </c>
       <c r="K97" t="n">
-        <v>58563.8</v>
+        <v>58556.3</v>
       </c>
       <c r="L97" t="n">
-        <v>2716.35</v>
+        <v>2716.2</v>
       </c>
       <c r="M97" t="n">
-        <v>7028.29</v>
+        <v>7027.99</v>
       </c>
       <c r="N97" t="n">
-        <v>5946.9</v>
+        <v>5945.4</v>
       </c>
     </row>
     <row r="98">
@@ -3468,7 +3468,7 @@
         <v>46127.20833333334</v>
       </c>
       <c r="B98" t="n">
-        <v>8868.4</v>
+        <v>8866</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -3489,40 +3489,40 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.178545</v>
+        <v>1.1785</v>
       </c>
       <c r="D99" t="n">
-        <v>1.353215</v>
+        <v>1.35314</v>
       </c>
       <c r="E99" t="n">
-        <v>8266.4</v>
+        <v>8264.4</v>
       </c>
       <c r="F99" t="n">
-        <v>24140.9</v>
+        <v>24137.4</v>
       </c>
       <c r="G99" t="n">
-        <v>48661.1</v>
+        <v>48658.7</v>
       </c>
       <c r="H99" t="n">
-        <v>10590.9</v>
+        <v>10588.9</v>
       </c>
       <c r="I99" t="n">
-        <v>26236.3</v>
+        <v>26221.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26321.7</v>
+        <v>26320.7</v>
       </c>
       <c r="K99" t="n">
-        <v>59430.4</v>
+        <v>59422.9</v>
       </c>
       <c r="L99" t="n">
-        <v>2725.15</v>
+        <v>2725</v>
       </c>
       <c r="M99" t="n">
-        <v>7046.74</v>
+        <v>7046.44</v>
       </c>
       <c r="N99" t="n">
-        <v>5920.67</v>
+        <v>5919.17</v>
       </c>
     </row>
     <row r="100">
@@ -3530,7 +3530,7 @@
         <v>46128.20833333334</v>
       </c>
       <c r="B100" t="n">
-        <v>9030.200000000001</v>
+        <v>9027.799999999999</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -3551,40 +3551,40 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.176345</v>
+        <v>1.17606</v>
       </c>
       <c r="D101" t="n">
-        <v>1.351615</v>
+        <v>1.35102</v>
       </c>
       <c r="E101" t="n">
-        <v>8407.9</v>
+        <v>8405.9</v>
       </c>
       <c r="F101" t="n">
-        <v>24651.9</v>
+        <v>24648.4</v>
       </c>
       <c r="G101" t="n">
-        <v>49453</v>
+        <v>49448.1</v>
       </c>
       <c r="H101" t="n">
-        <v>10697.9</v>
+        <v>10695.9</v>
       </c>
       <c r="I101" t="n">
-        <v>26504.1</v>
+        <v>26489.1</v>
       </c>
       <c r="J101" t="n">
-        <v>26684.1</v>
+        <v>26681.6</v>
       </c>
       <c r="K101" t="n">
-        <v>59693.4</v>
+        <v>59678.4</v>
       </c>
       <c r="L101" t="n">
-        <v>2777.8</v>
+        <v>2777.3</v>
       </c>
       <c r="M101" t="n">
-        <v>7126.42</v>
+        <v>7125.67</v>
       </c>
       <c r="N101" t="n">
-        <v>6036.51</v>
+        <v>6035.01</v>
       </c>
     </row>
     <row r="102">
@@ -3592,7 +3592,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B102" t="n">
-        <v>8417.5</v>
+        <v>8413.6</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -3613,23 +3613,23 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.173945</v>
+        <v>1.1739</v>
       </c>
       <c r="D103" t="n">
-        <v>1.348705</v>
+        <v>1.34863</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>10633.2</v>
+        <v>10631.2</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>7073.76</v>
+        <v>7073.46</v>
       </c>
       <c r="N103" t="inlineStr"/>
     </row>
@@ -3638,7 +3638,7 @@
         <v>46131.20833333334</v>
       </c>
       <c r="B104" t="n">
-        <v>8910.9</v>
+        <v>8908.5</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -3659,23 +3659,23 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.179005</v>
+        <v>1.17896</v>
       </c>
       <c r="D105" t="n">
-        <v>1.353895</v>
+        <v>1.35382</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>10627.6</v>
+        <v>10625.6</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>7121.9</v>
+        <v>7121.6</v>
       </c>
       <c r="N105" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>46132.20833333334</v>
       </c>
       <c r="B106" t="n">
-        <v>8670.9</v>
+        <v>8668.5</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -3705,23 +3705,23 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.173925</v>
+        <v>1.17388</v>
       </c>
       <c r="D107" t="n">
-        <v>1.350235</v>
+        <v>1.35016</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>10466.5</v>
+        <v>10464.5</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>7088.99</v>
+        <v>7088.69</v>
       </c>
       <c r="N107" t="inlineStr"/>
     </row>
@@ -3730,7 +3730,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B108" t="n">
-        <v>8926.9</v>
+        <v>8925.5</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -3751,23 +3751,23 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>1.170595</v>
+        <v>1.17055</v>
       </c>
       <c r="D109" t="n">
-        <v>1.350215</v>
+        <v>1.35014</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>10460.2</v>
+        <v>10458.2</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>7127.22</v>
+        <v>7126.92</v>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
@@ -3776,7 +3776,7 @@
         <v>46134.20833333334</v>
       </c>
       <c r="B110" t="n">
-        <v>9453.1</v>
+        <v>9450.700000000001</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1.168635</v>
+        <v>1.16859</v>
       </c>
       <c r="D111" t="n">
-        <v>1.346735</v>
+        <v>1.34666</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10417.5</v>
+        <v>10415.5</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>7114.23</v>
+        <v>7113.93</v>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
@@ -3822,7 +3822,7 @@
         <v>46135.20833333334</v>
       </c>
       <c r="B112" t="n">
-        <v>9661.1</v>
+        <v>9658.700000000001</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -3843,23 +3843,23 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1.171835</v>
+        <v>1.17154</v>
       </c>
       <c r="D113" t="n">
-        <v>1.353095</v>
+        <v>1.3525</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>10387.5</v>
+        <v>10385.5</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>7163.69</v>
+        <v>7162.94</v>
       </c>
       <c r="N113" t="inlineStr"/>
     </row>
@@ -3868,7 +3868,7 @@
         <v>46136.20833333334</v>
       </c>
       <c r="B114" t="n">
-        <v>9486.799999999999</v>
+        <v>9484.4</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1.170825</v>
+        <v>1.17078</v>
       </c>
       <c r="D115" t="n">
-        <v>1.351595</v>
+        <v>1.35149</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>10370.5</v>
+        <v>10368.5</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>7151.27</v>
+        <v>7150.97</v>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
@@ -3914,7 +3914,7 @@
         <v>46138.20833333334</v>
       </c>
       <c r="B116" t="n">
-        <v>9529.1</v>
+        <v>9527.700000000001</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -3935,23 +3935,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.17246</v>
+        <v>1.17243</v>
       </c>
       <c r="D117" t="n">
-        <v>1.353605</v>
+        <v>1.35356</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10337.9</v>
+        <v>10336.9</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7176.440000000001</v>
+        <v>7176.24</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -3960,7 +3960,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9605.1</v>
+        <v>9602.700000000001</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -7629,10 +7629,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.17877</v>
+        <v>1.178815</v>
       </c>
       <c r="D2" t="n">
-        <v>1.34943</v>
+        <v>1.349475</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -7643,7 +7643,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6878.66</v>
+        <v>6878.96</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -7652,7 +7652,7 @@
         <v>46071.20833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>6519.3</v>
+        <v>6521.200000000001</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -7673,40 +7673,40 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.17683</v>
+        <v>1.17686</v>
       </c>
       <c r="D4" t="n">
-        <v>1.34592</v>
+        <v>1.345965</v>
       </c>
       <c r="E4" t="n">
-        <v>8415.9</v>
+        <v>8417.9</v>
       </c>
       <c r="F4" t="n">
-        <v>25030.1</v>
+        <v>25033.6</v>
       </c>
       <c r="G4" t="n">
-        <v>49407.6</v>
+        <v>49410</v>
       </c>
       <c r="H4" t="n">
-        <v>10668.2</v>
+        <v>10670.2</v>
       </c>
       <c r="I4" t="n">
-        <v>26781.7</v>
+        <v>26796.7</v>
       </c>
       <c r="J4" t="n">
-        <v>24816.3</v>
+        <v>24817.3</v>
       </c>
       <c r="K4" t="n">
-        <v>57080.7</v>
+        <v>57084.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2661.8</v>
+        <v>2661.95</v>
       </c>
       <c r="M4" t="n">
-        <v>6865.54</v>
+        <v>6865.84</v>
       </c>
       <c r="N4" t="n">
-        <v>6063.9</v>
+        <v>6065.4</v>
       </c>
     </row>
     <row r="5">
@@ -7714,7 +7714,7 @@
         <v>46072.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>6670.8</v>
+        <v>6672.200000000001</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -7735,40 +7735,40 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.17797</v>
+        <v>1.17822</v>
       </c>
       <c r="D6" t="n">
-        <v>1.34765</v>
+        <v>1.348245</v>
       </c>
       <c r="E6" t="n">
-        <v>8533.4</v>
+        <v>8535.4</v>
       </c>
       <c r="F6" t="n">
-        <v>25233.1</v>
+        <v>25236.6</v>
       </c>
       <c r="G6" t="n">
-        <v>49619.9</v>
+        <v>49624.8</v>
       </c>
       <c r="H6" t="n">
-        <v>10718.4</v>
+        <v>10720.4</v>
       </c>
       <c r="I6" t="n">
-        <v>26848.4</v>
+        <v>26863.4</v>
       </c>
       <c r="J6" t="n">
-        <v>25013.7</v>
+        <v>25016.2</v>
       </c>
       <c r="K6" t="n">
-        <v>57073.3</v>
+        <v>57088.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2661.7</v>
+        <v>2662.2</v>
       </c>
       <c r="M6" t="n">
-        <v>6909.88</v>
+        <v>6910.63</v>
       </c>
       <c r="N6" t="n">
-        <v>6133.6</v>
+        <v>6135.1</v>
       </c>
     </row>
     <row r="7">
@@ -7776,7 +7776,7 @@
         <v>46073.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>6628.3</v>
+        <v>6630.200000000001</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -7797,40 +7797,40 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.18328</v>
+        <v>1.18331</v>
       </c>
       <c r="D8" t="n">
-        <v>1.35316</v>
+        <v>1.353205</v>
       </c>
       <c r="E8" t="n">
-        <v>8513.200000000001</v>
+        <v>8515.200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>25172.5</v>
+        <v>25176</v>
       </c>
       <c r="G8" t="n">
-        <v>49526</v>
+        <v>49528.4</v>
       </c>
       <c r="H8" t="n">
-        <v>10701.4</v>
+        <v>10703.4</v>
       </c>
       <c r="I8" t="n">
-        <v>26811.4</v>
+        <v>26826.4</v>
       </c>
       <c r="J8" t="n">
-        <v>24910.3</v>
+        <v>24911.3</v>
       </c>
       <c r="K8" t="n">
-        <v>56978.1</v>
+        <v>56981.6</v>
       </c>
       <c r="L8" t="n">
-        <v>2652.5</v>
+        <v>2652.65</v>
       </c>
       <c r="M8" t="n">
-        <v>6891.98</v>
+        <v>6892.28</v>
       </c>
       <c r="N8" t="n">
-        <v>6118.9</v>
+        <v>6120.4</v>
       </c>
     </row>
     <row r="9">
@@ -7838,7 +7838,7 @@
         <v>46075.20833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>6556.3</v>
+        <v>6557.700000000001</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -7859,40 +7859,40 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.17928</v>
+        <v>1.179325</v>
       </c>
       <c r="D10" t="n">
-        <v>1.34948</v>
+        <v>1.349555</v>
       </c>
       <c r="E10" t="n">
-        <v>8504.6</v>
+        <v>8506.6</v>
       </c>
       <c r="F10" t="n">
-        <v>24993</v>
+        <v>24996.5</v>
       </c>
       <c r="G10" t="n">
-        <v>48837.1</v>
+        <v>48839.5</v>
       </c>
       <c r="H10" t="n">
-        <v>10690.7</v>
+        <v>10692.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26876.9</v>
+        <v>26891.9</v>
       </c>
       <c r="J10" t="n">
-        <v>24734.3</v>
+        <v>24735.3</v>
       </c>
       <c r="K10" t="n">
-        <v>56662.3</v>
+        <v>56665.8</v>
       </c>
       <c r="L10" t="n">
-        <v>2621.3</v>
+        <v>2621.45</v>
       </c>
       <c r="M10" t="n">
-        <v>6844.01</v>
+        <v>6844.309999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6121.8</v>
+        <v>6123.3</v>
       </c>
     </row>
     <row r="11">
@@ -7900,7 +7900,7 @@
         <v>46076.20833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>6674.9</v>
+        <v>6676.299999999999</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -7921,40 +7921,40 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.1774</v>
+        <v>1.17743</v>
       </c>
       <c r="D12" t="n">
-        <v>1.34956</v>
+        <v>1.349605</v>
       </c>
       <c r="E12" t="n">
-        <v>8537.9</v>
+        <v>8539.9</v>
       </c>
       <c r="F12" t="n">
-        <v>25035.8</v>
+        <v>25039.3</v>
       </c>
       <c r="G12" t="n">
-        <v>49175.1</v>
+        <v>49177.5</v>
       </c>
       <c r="H12" t="n">
-        <v>10710.4</v>
+        <v>10712.4</v>
       </c>
       <c r="I12" t="n">
-        <v>26751.2</v>
+        <v>26766.2</v>
       </c>
       <c r="J12" t="n">
-        <v>24994.3</v>
+        <v>24995.3</v>
       </c>
       <c r="K12" t="n">
-        <v>57908.5</v>
+        <v>57912</v>
       </c>
       <c r="L12" t="n">
-        <v>2651.4</v>
+        <v>2651.55</v>
       </c>
       <c r="M12" t="n">
-        <v>6891.78</v>
+        <v>6892.08</v>
       </c>
       <c r="N12" t="n">
-        <v>6134.6</v>
+        <v>6136.1</v>
       </c>
     </row>
     <row r="13">
@@ -7962,7 +7962,7 @@
         <v>46077.20833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>6597.5</v>
+        <v>6598.9</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -7983,40 +7983,40 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.18151</v>
+        <v>1.18154</v>
       </c>
       <c r="D14" t="n">
-        <v>1.35576</v>
+        <v>1.355805</v>
       </c>
       <c r="E14" t="n">
-        <v>8567.6</v>
+        <v>8569.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25177.8</v>
+        <v>25181.3</v>
       </c>
       <c r="G14" t="n">
-        <v>49389.6</v>
+        <v>49392</v>
       </c>
       <c r="H14" t="n">
-        <v>10802.4</v>
+        <v>10804.4</v>
       </c>
       <c r="I14" t="n">
-        <v>26935</v>
+        <v>26950</v>
       </c>
       <c r="J14" t="n">
-        <v>25269</v>
+        <v>25270</v>
       </c>
       <c r="K14" t="n">
-        <v>59281.6</v>
+        <v>59285.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2660.5</v>
+        <v>2660.65</v>
       </c>
       <c r="M14" t="n">
-        <v>6937.36</v>
+        <v>6937.66</v>
       </c>
       <c r="N14" t="n">
-        <v>6174.2</v>
+        <v>6175.7</v>
       </c>
     </row>
     <row r="15">
@@ -8024,7 +8024,7 @@
         <v>46078.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>6555.2</v>
+        <v>6556.6</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -8045,40 +8045,40 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.18032</v>
+        <v>1.180365</v>
       </c>
       <c r="D16" t="n">
-        <v>1.34911</v>
+        <v>1.349155</v>
       </c>
       <c r="E16" t="n">
-        <v>8609.700000000001</v>
+        <v>8611.700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>25249.8</v>
+        <v>25253.3</v>
       </c>
       <c r="G16" t="n">
-        <v>49227.2</v>
+        <v>49229.6</v>
       </c>
       <c r="H16" t="n">
-        <v>10833.1</v>
+        <v>10835.1</v>
       </c>
       <c r="I16" t="n">
-        <v>26374.6</v>
+        <v>26389.6</v>
       </c>
       <c r="J16" t="n">
-        <v>24954.6</v>
+        <v>24955.6</v>
       </c>
       <c r="K16" t="n">
-        <v>58431.5</v>
+        <v>58435</v>
       </c>
       <c r="L16" t="n">
-        <v>2655.4</v>
+        <v>2655.55</v>
       </c>
       <c r="M16" t="n">
-        <v>6882.06</v>
+        <v>6882.360000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>6149.2</v>
+        <v>6150.7</v>
       </c>
     </row>
     <row r="17">
@@ -8086,7 +8086,7 @@
         <v>46079.20833333334</v>
       </c>
       <c r="B17" t="n">
-        <v>6530.4</v>
+        <v>6531.799999999999</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -8107,40 +8107,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.18146</v>
+        <v>1.18179</v>
       </c>
       <c r="D18" t="n">
-        <v>1.34768</v>
+        <v>1.34806</v>
       </c>
       <c r="E18" t="n">
-        <v>8528.6</v>
+        <v>8530.6</v>
       </c>
       <c r="F18" t="n">
-        <v>25140.2</v>
+        <v>25143.7</v>
       </c>
       <c r="G18" t="n">
-        <v>48853.6</v>
+        <v>48858.5</v>
       </c>
       <c r="H18" t="n">
-        <v>10860.7</v>
+        <v>10862.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26475.4</v>
+        <v>26490.4</v>
       </c>
       <c r="J18" t="n">
-        <v>24913.4</v>
+        <v>24914.4</v>
       </c>
       <c r="K18" t="n">
-        <v>58609.2</v>
+        <v>58612.7</v>
       </c>
       <c r="L18" t="n">
-        <v>2626.5</v>
+        <v>2626.65</v>
       </c>
       <c r="M18" t="n">
-        <v>6864.83</v>
+        <v>6865.58</v>
       </c>
       <c r="N18" t="n">
-        <v>6093.88</v>
+        <v>6095.38</v>
       </c>
     </row>
     <row r="19">
@@ -8148,7 +8148,7 @@
         <v>46080.20833333334</v>
       </c>
       <c r="B19" t="n">
-        <v>6724.1</v>
+        <v>6725.5</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -8169,40 +8169,40 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1.17591</v>
+        <v>1.17594</v>
       </c>
       <c r="D20" t="n">
-        <v>1.34048</v>
+        <v>1.340525</v>
       </c>
       <c r="E20" t="n">
-        <v>8464.4</v>
+        <v>8466.4</v>
       </c>
       <c r="F20" t="n">
-        <v>24942.8</v>
+        <v>24946.3</v>
       </c>
       <c r="G20" t="n">
-        <v>48366.4</v>
+        <v>48368.8</v>
       </c>
       <c r="H20" t="n">
-        <v>10809.6</v>
+        <v>10811.6</v>
       </c>
       <c r="I20" t="n">
-        <v>26335.6</v>
+        <v>26350.6</v>
       </c>
       <c r="J20" t="n">
-        <v>24695.7</v>
+        <v>24696.7</v>
       </c>
       <c r="K20" t="n">
-        <v>57484.6</v>
+        <v>57488.1</v>
       </c>
       <c r="L20" t="n">
-        <v>2591.1</v>
+        <v>2591.25</v>
       </c>
       <c r="M20" t="n">
-        <v>6805.65</v>
+        <v>6805.95</v>
       </c>
       <c r="N20" t="n">
-        <v>6048.08</v>
+        <v>6049.58</v>
       </c>
     </row>
     <row r="21">
@@ -8210,7 +8210,7 @@
         <v>46082.20833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>7098.9</v>
+        <v>7100.799999999999</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -8231,40 +8231,40 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.16939</v>
+        <v>1.169435</v>
       </c>
       <c r="D22" t="n">
-        <v>1.34077</v>
+        <v>1.340815</v>
       </c>
       <c r="E22" t="n">
-        <v>8385.700000000001</v>
+        <v>8387.700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>24578.7</v>
+        <v>24582.2</v>
       </c>
       <c r="G22" t="n">
-        <v>48821.2</v>
+        <v>48823.6</v>
       </c>
       <c r="H22" t="n">
-        <v>10787.5</v>
+        <v>10789.5</v>
       </c>
       <c r="I22" t="n">
-        <v>26141.8</v>
+        <v>26156.8</v>
       </c>
       <c r="J22" t="n">
-        <v>24934.3</v>
+        <v>24935.3</v>
       </c>
       <c r="K22" t="n">
-        <v>57709.6</v>
+        <v>57713.1</v>
       </c>
       <c r="L22" t="n">
-        <v>2650.7</v>
+        <v>2650.85</v>
       </c>
       <c r="M22" t="n">
-        <v>6867.64</v>
+        <v>6867.940000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>5980.7</v>
+        <v>5982.2</v>
       </c>
     </row>
     <row r="23">
@@ -8272,7 +8272,7 @@
         <v>46083.20833333334</v>
       </c>
       <c r="B23" t="n">
-        <v>7240.5</v>
+        <v>7242.4</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -8293,40 +8293,40 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1.16107</v>
+        <v>1.1611</v>
       </c>
       <c r="D24" t="n">
-        <v>1.33507</v>
+        <v>1.335115</v>
       </c>
       <c r="E24" t="n">
-        <v>8163.4</v>
+        <v>8165.4</v>
       </c>
       <c r="F24" t="n">
-        <v>23981.5</v>
+        <v>23985</v>
       </c>
       <c r="G24" t="n">
-        <v>48410.9</v>
+        <v>48413.3</v>
       </c>
       <c r="H24" t="n">
-        <v>10515.1</v>
+        <v>10517.1</v>
       </c>
       <c r="I24" t="n">
-        <v>25453.5</v>
+        <v>25468.5</v>
       </c>
       <c r="J24" t="n">
-        <v>24667</v>
+        <v>24668</v>
       </c>
       <c r="K24" t="n">
-        <v>54948.2</v>
+        <v>54951.7</v>
       </c>
       <c r="L24" t="n">
-        <v>2603.3</v>
+        <v>2603.45</v>
       </c>
       <c r="M24" t="n">
-        <v>6802.2</v>
+        <v>6802.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5811.8</v>
+        <v>5813.3</v>
       </c>
     </row>
     <row r="25">
@@ -8334,7 +8334,7 @@
         <v>46084.20833333334</v>
       </c>
       <c r="B25" t="n">
-        <v>7494.8</v>
+        <v>7496.700000000001</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -8355,40 +8355,40 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.16346</v>
+        <v>1.163505</v>
       </c>
       <c r="D26" t="n">
-        <v>1.33688</v>
+        <v>1.336925</v>
       </c>
       <c r="E26" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="F26" t="n">
-        <v>24298.7</v>
+        <v>24302.2</v>
       </c>
       <c r="G26" t="n">
-        <v>48750.8</v>
+        <v>48753.2</v>
       </c>
       <c r="H26" t="n">
-        <v>10624.8</v>
+        <v>10626.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25587.8</v>
+        <v>25602.8</v>
       </c>
       <c r="J26" t="n">
-        <v>25136.1</v>
+        <v>25137.1</v>
       </c>
       <c r="K26" t="n">
-        <v>56229.4</v>
+        <v>56232.9</v>
       </c>
       <c r="L26" t="n">
-        <v>2635.7</v>
+        <v>2635.85</v>
       </c>
       <c r="M26" t="n">
-        <v>6877.74</v>
+        <v>6878.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5900.4</v>
+        <v>5901.9</v>
       </c>
     </row>
     <row r="27">
@@ -8396,7 +8396,7 @@
         <v>46085.20833333334</v>
       </c>
       <c r="B27" t="n">
-        <v>7664.1</v>
+        <v>7666</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -8417,40 +8417,40 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.16064</v>
+        <v>1.16067</v>
       </c>
       <c r="D28" t="n">
-        <v>1.33552</v>
+        <v>1.335565</v>
       </c>
       <c r="E28" t="n">
-        <v>8057.2</v>
+        <v>8059.2</v>
       </c>
       <c r="F28" t="n">
-        <v>23862.7</v>
+        <v>23866.2</v>
       </c>
       <c r="G28" t="n">
-        <v>48031.6</v>
+        <v>48034</v>
       </c>
       <c r="H28" t="n">
-        <v>10405.9</v>
+        <v>10407.9</v>
       </c>
       <c r="I28" t="n">
-        <v>25187.5</v>
+        <v>25202.5</v>
       </c>
       <c r="J28" t="n">
-        <v>25030.4</v>
+        <v>25031.4</v>
       </c>
       <c r="K28" t="n">
-        <v>54559.7</v>
+        <v>54563.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2592.7</v>
+        <v>2592.85</v>
       </c>
       <c r="M28" t="n">
-        <v>6834.13</v>
+        <v>6834.43</v>
       </c>
       <c r="N28" t="n">
-        <v>5792.1</v>
+        <v>5793.6</v>
       </c>
     </row>
     <row r="29">
@@ -8458,7 +8458,7 @@
         <v>46086.20833333334</v>
       </c>
       <c r="B29" t="n">
-        <v>7885.6</v>
+        <v>7887.5</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -8479,40 +8479,40 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1.16139</v>
+        <v>1.161695</v>
       </c>
       <c r="D30" t="n">
-        <v>1.34039</v>
+        <v>1.340985</v>
       </c>
       <c r="E30" t="n">
-        <v>8015.2</v>
+        <v>8017.2</v>
       </c>
       <c r="F30" t="n">
-        <v>23636.8</v>
+        <v>23640.3</v>
       </c>
       <c r="G30" t="n">
-        <v>47429.3</v>
+        <v>47434.2</v>
       </c>
       <c r="H30" t="n">
-        <v>10316.8</v>
+        <v>10318.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25310.2</v>
+        <v>25325.2</v>
       </c>
       <c r="J30" t="n">
-        <v>24631.7</v>
+        <v>24634.2</v>
       </c>
       <c r="K30" t="n">
-        <v>54014.9</v>
+        <v>54029.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2521.5</v>
+        <v>2522</v>
       </c>
       <c r="M30" t="n">
-        <v>6732.48</v>
+        <v>6733.23</v>
       </c>
       <c r="N30" t="n">
-        <v>5721.53</v>
+        <v>5723.03</v>
       </c>
     </row>
     <row r="31">
@@ -8520,7 +8520,7 @@
         <v>46087.20833333334</v>
       </c>
       <c r="B31" t="n">
-        <v>8943.9</v>
+        <v>8947.799999999999</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -8541,40 +8541,40 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.15241</v>
+        <v>1.152455</v>
       </c>
       <c r="D32" t="n">
-        <v>1.33047</v>
+        <v>1.330515</v>
       </c>
       <c r="E32" t="n">
-        <v>7871</v>
+        <v>7873</v>
       </c>
       <c r="F32" t="n">
-        <v>23218.8</v>
+        <v>23222.3</v>
       </c>
       <c r="G32" t="n">
-        <v>46610.6</v>
+        <v>46613</v>
       </c>
       <c r="H32" t="n">
-        <v>10193.8</v>
+        <v>10195.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25027.2</v>
+        <v>25042.2</v>
       </c>
       <c r="J32" t="n">
-        <v>24186.4</v>
+        <v>24187.4</v>
       </c>
       <c r="K32" t="n">
-        <v>52213</v>
+        <v>52216.5</v>
       </c>
       <c r="L32" t="n">
-        <v>2433.2</v>
+        <v>2433.35</v>
       </c>
       <c r="M32" t="n">
-        <v>6622.15</v>
+        <v>6622.45</v>
       </c>
       <c r="N32" t="n">
-        <v>5614.4</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="33">
@@ -8582,7 +8582,7 @@
         <v>46089.20833333334</v>
       </c>
       <c r="B33" t="n">
-        <v>11224.7</v>
+        <v>11228.6</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -8603,40 +8603,40 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.16157</v>
+        <v>1.161615</v>
       </c>
       <c r="D34" t="n">
-        <v>1.3424</v>
+        <v>1.342445</v>
       </c>
       <c r="E34" t="n">
-        <v>7998.3</v>
+        <v>8000.3</v>
       </c>
       <c r="F34" t="n">
-        <v>23699.6</v>
+        <v>23703.1</v>
       </c>
       <c r="G34" t="n">
-        <v>47531.9</v>
+        <v>47534.3</v>
       </c>
       <c r="H34" t="n">
-        <v>10305.8</v>
+        <v>10307.8</v>
       </c>
       <c r="I34" t="n">
-        <v>25530.7</v>
+        <v>25545.7</v>
       </c>
       <c r="J34" t="n">
-        <v>24853.1</v>
+        <v>24854.1</v>
       </c>
       <c r="K34" t="n">
-        <v>54256.1</v>
+        <v>54259.6</v>
       </c>
       <c r="L34" t="n">
-        <v>2533.9</v>
+        <v>2534.05</v>
       </c>
       <c r="M34" t="n">
-        <v>6765.77</v>
+        <v>6766.07</v>
       </c>
       <c r="N34" t="n">
-        <v>5763.2</v>
+        <v>5764.7</v>
       </c>
     </row>
     <row r="35">
@@ -8644,7 +8644,7 @@
         <v>46090.16666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>8801.5</v>
+        <v>8805.4</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -8665,40 +8665,40 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.16115</v>
+        <v>1.161195</v>
       </c>
       <c r="D36" t="n">
-        <v>1.34194</v>
+        <v>1.341985</v>
       </c>
       <c r="E36" t="n">
-        <v>7994.9</v>
+        <v>7996.9</v>
       </c>
       <c r="F36" t="n">
-        <v>23805.6</v>
+        <v>23809.1</v>
       </c>
       <c r="G36" t="n">
-        <v>47742.1</v>
+        <v>47744.5</v>
       </c>
       <c r="H36" t="n">
-        <v>10383.1</v>
+        <v>10385.1</v>
       </c>
       <c r="I36" t="n">
-        <v>25930.2</v>
+        <v>25945.2</v>
       </c>
       <c r="J36" t="n">
-        <v>24989.4</v>
+        <v>24990.4</v>
       </c>
       <c r="K36" t="n">
-        <v>55063.4</v>
+        <v>55066.9</v>
       </c>
       <c r="L36" t="n">
-        <v>2551.9</v>
+        <v>2552.05</v>
       </c>
       <c r="M36" t="n">
-        <v>6790.95</v>
+        <v>6791.25</v>
       </c>
       <c r="N36" t="n">
-        <v>5785.4</v>
+        <v>5786.9</v>
       </c>
     </row>
     <row r="37">
@@ -8706,7 +8706,7 @@
         <v>46091.16666666666</v>
       </c>
       <c r="B37" t="n">
-        <v>8210.4</v>
+        <v>8214.299999999999</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -8727,40 +8727,40 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1.15422</v>
+        <v>1.154265</v>
       </c>
       <c r="D38" t="n">
-        <v>1.33821</v>
+        <v>1.338255</v>
       </c>
       <c r="E38" t="n">
-        <v>7974.9</v>
+        <v>7976.9</v>
       </c>
       <c r="F38" t="n">
-        <v>23461.7</v>
+        <v>23465.2</v>
       </c>
       <c r="G38" t="n">
-        <v>47027.9</v>
+        <v>47030.3</v>
       </c>
       <c r="H38" t="n">
-        <v>10270.4</v>
+        <v>10272.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25619.7</v>
+        <v>25634.7</v>
       </c>
       <c r="J38" t="n">
-        <v>24767.1</v>
+        <v>24768.1</v>
       </c>
       <c r="K38" t="n">
-        <v>54154.5</v>
+        <v>54158</v>
       </c>
       <c r="L38" t="n">
-        <v>2505.6</v>
+        <v>2505.75</v>
       </c>
       <c r="M38" t="n">
-        <v>6724.31</v>
+        <v>6724.610000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>5751.13</v>
+        <v>5752.63</v>
       </c>
     </row>
     <row r="39">
@@ -8768,7 +8768,7 @@
         <v>46092.16666666666</v>
       </c>
       <c r="B39" t="n">
-        <v>9363.9</v>
+        <v>9366.299999999999</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -8789,40 +8789,40 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1.15202</v>
+        <v>1.152065</v>
       </c>
       <c r="D40" t="n">
-        <v>1.33507</v>
+        <v>1.335115</v>
       </c>
       <c r="E40" t="n">
-        <v>7962.5</v>
+        <v>7964.5</v>
       </c>
       <c r="F40" t="n">
-        <v>23491.5</v>
+        <v>23495</v>
       </c>
       <c r="G40" t="n">
-        <v>46737.5</v>
+        <v>46739.9</v>
       </c>
       <c r="H40" t="n">
-        <v>10281.7</v>
+        <v>10283.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25438.6</v>
+        <v>25453.6</v>
       </c>
       <c r="J40" t="n">
-        <v>24513</v>
+        <v>24514</v>
       </c>
       <c r="K40" t="n">
-        <v>53458.7</v>
+        <v>53462.2</v>
       </c>
       <c r="L40" t="n">
-        <v>2490.8</v>
+        <v>2490.95</v>
       </c>
       <c r="M40" t="n">
-        <v>6675.71</v>
+        <v>6676.01</v>
       </c>
       <c r="N40" t="n">
-        <v>5723.8</v>
+        <v>5725.3</v>
       </c>
     </row>
     <row r="41">
@@ -8830,7 +8830,7 @@
         <v>46093.16666666666</v>
       </c>
       <c r="B41" t="n">
-        <v>9466</v>
+        <v>9468.4</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -8851,40 +8851,40 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.14162</v>
+        <v>1.141665</v>
       </c>
       <c r="D42" t="n">
-        <v>1.3218</v>
+        <v>1.32235</v>
       </c>
       <c r="E42" t="n">
-        <v>7874.6</v>
+        <v>7875.6</v>
       </c>
       <c r="F42" t="n">
-        <v>23327.9</v>
+        <v>23329.3</v>
       </c>
       <c r="G42" t="n">
-        <v>46470.2</v>
+        <v>46475.1</v>
       </c>
       <c r="H42" t="n">
-        <v>10238.1</v>
+        <v>10240.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25385.4</v>
+        <v>25400.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24318.7</v>
+        <v>24321.2</v>
       </c>
       <c r="K42" t="n">
-        <v>53135.3</v>
+        <v>53150.3</v>
       </c>
       <c r="L42" t="n">
-        <v>2474</v>
+        <v>2474.5</v>
       </c>
       <c r="M42" t="n">
-        <v>6620.29</v>
+        <v>6621.04</v>
       </c>
       <c r="N42" t="n">
-        <v>5688.61</v>
+        <v>5689.36</v>
       </c>
     </row>
     <row r="43">
@@ -8892,7 +8892,7 @@
         <v>46094.16666666666</v>
       </c>
       <c r="B43" t="n">
-        <v>9764</v>
+        <v>9766.4</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -8913,40 +8913,40 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1.14355</v>
+        <v>1.143595</v>
       </c>
       <c r="D44" t="n">
-        <v>1.3245</v>
+        <v>1.324575</v>
       </c>
       <c r="E44" t="n">
-        <v>7917.5</v>
+        <v>7919.5</v>
       </c>
       <c r="F44" t="n">
-        <v>23425.1</v>
+        <v>23428.6</v>
       </c>
       <c r="G44" t="n">
-        <v>46639.4</v>
+        <v>46641.8</v>
       </c>
       <c r="H44" t="n">
-        <v>10266.8</v>
+        <v>10268.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25435.7</v>
+        <v>25450.7</v>
       </c>
       <c r="J44" t="n">
-        <v>24423</v>
+        <v>24424</v>
       </c>
       <c r="K44" t="n">
-        <v>53648.4</v>
+        <v>53651.9</v>
       </c>
       <c r="L44" t="n">
-        <v>2489.3</v>
+        <v>2489.45</v>
       </c>
       <c r="M44" t="n">
-        <v>6645.18</v>
+        <v>6645.48</v>
       </c>
       <c r="N44" t="n">
-        <v>5712.4</v>
+        <v>5713.9</v>
       </c>
     </row>
     <row r="45">
@@ -8954,7 +8954,7 @@
         <v>46096.16666666666</v>
       </c>
       <c r="B45" t="n">
-        <v>9776.299999999999</v>
+        <v>9778.700000000001</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -8975,40 +8975,40 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1.14977</v>
+        <v>1.149815</v>
       </c>
       <c r="D46" t="n">
-        <v>1.33114</v>
+        <v>1.331215</v>
       </c>
       <c r="E46" t="n">
-        <v>7947</v>
+        <v>7949</v>
       </c>
       <c r="F46" t="n">
-        <v>23621.9</v>
+        <v>23625.4</v>
       </c>
       <c r="G46" t="n">
-        <v>46924.3</v>
+        <v>46926.7</v>
       </c>
       <c r="H46" t="n">
-        <v>10345</v>
+        <v>10347</v>
       </c>
       <c r="I46" t="n">
-        <v>25846.7</v>
+        <v>25861.7</v>
       </c>
       <c r="J46" t="n">
-        <v>24651</v>
+        <v>24652</v>
       </c>
       <c r="K46" t="n">
-        <v>54334.1</v>
+        <v>54337.6</v>
       </c>
       <c r="L46" t="n">
-        <v>2501.5</v>
+        <v>2501.65</v>
       </c>
       <c r="M46" t="n">
-        <v>6697.82</v>
+        <v>6698.12</v>
       </c>
       <c r="N46" t="n">
-        <v>5752.7</v>
+        <v>5754.2</v>
       </c>
     </row>
     <row r="47">
@@ -9016,7 +9016,7 @@
         <v>46097.16666666666</v>
       </c>
       <c r="B47" t="n">
-        <v>9525</v>
+        <v>9527.4</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -9037,40 +9037,40 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1.15383</v>
+        <v>1.153885</v>
       </c>
       <c r="D48" t="n">
-        <v>1.33558</v>
+        <v>1.33575</v>
       </c>
       <c r="E48" t="n">
-        <v>7954.2</v>
+        <v>7956.2</v>
       </c>
       <c r="F48" t="n">
-        <v>23667</v>
+        <v>23670.5</v>
       </c>
       <c r="G48" t="n">
-        <v>46942.2</v>
+        <v>46944.6</v>
       </c>
       <c r="H48" t="n">
-        <v>10360.5</v>
+        <v>10362.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25844.5</v>
+        <v>25859.5</v>
       </c>
       <c r="J48" t="n">
-        <v>24774.5</v>
+        <v>24775.5</v>
       </c>
       <c r="K48" t="n">
-        <v>54270.9</v>
+        <v>54274.4</v>
       </c>
       <c r="L48" t="n">
-        <v>2517.7</v>
+        <v>2517.85</v>
       </c>
       <c r="M48" t="n">
-        <v>6711.38</v>
+        <v>6711.68</v>
       </c>
       <c r="N48" t="n">
-        <v>5754.9</v>
+        <v>5756.4</v>
       </c>
     </row>
     <row r="49">
@@ -9078,7 +9078,7 @@
         <v>46098.16666666666</v>
       </c>
       <c r="B49" t="n">
-        <v>9247.700000000001</v>
+        <v>9250.1</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -9099,40 +9099,40 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.14628</v>
+        <v>1.146325</v>
       </c>
       <c r="D50" t="n">
-        <v>1.32638</v>
+        <v>1.326425</v>
       </c>
       <c r="E50" t="n">
-        <v>7895.7</v>
+        <v>7897.7</v>
       </c>
       <c r="F50" t="n">
-        <v>23166</v>
+        <v>23169.5</v>
       </c>
       <c r="G50" t="n">
-        <v>46154.6</v>
+        <v>46157</v>
       </c>
       <c r="H50" t="n">
-        <v>10219.1</v>
+        <v>10221.1</v>
       </c>
       <c r="I50" t="n">
-        <v>25401.9</v>
+        <v>25416.9</v>
       </c>
       <c r="J50" t="n">
-        <v>24394.2</v>
+        <v>24395.2</v>
       </c>
       <c r="K50" t="n">
-        <v>53596.1</v>
+        <v>53599.6</v>
       </c>
       <c r="L50" t="n">
-        <v>2474.3</v>
+        <v>2474.45</v>
       </c>
       <c r="M50" t="n">
-        <v>6698.79</v>
+        <v>6698.99</v>
       </c>
       <c r="N50" t="n">
-        <v>5654</v>
+        <v>5655.5</v>
       </c>
     </row>
     <row r="51">
@@ -9140,7 +9140,7 @@
         <v>46099.16666666666</v>
       </c>
       <c r="B51" t="n">
-        <v>9647.9</v>
+        <v>9650.299999999999</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -9161,38 +9161,38 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.15762</v>
+        <v>1.15765</v>
       </c>
       <c r="D52" t="n">
-        <v>1.34236</v>
+        <v>1.342435</v>
       </c>
       <c r="E52" t="n">
-        <v>7840.7</v>
+        <v>7842.7</v>
       </c>
       <c r="F52" t="n">
-        <v>23016.2</v>
+        <v>23019.7</v>
       </c>
       <c r="G52" t="n">
-        <v>46136.8</v>
+        <v>46139.2</v>
       </c>
       <c r="H52" t="n">
-        <v>10067.6</v>
+        <v>10069.6</v>
       </c>
       <c r="I52" t="n">
-        <v>25353.8</v>
+        <v>25368.8</v>
       </c>
       <c r="J52" t="n">
-        <v>24406.7</v>
+        <v>24407.7</v>
       </c>
       <c r="K52" t="n">
-        <v>53397.7</v>
+        <v>53401.2</v>
       </c>
       <c r="L52" t="n">
-        <v>2508.4</v>
+        <v>2508.55</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>5653.9</v>
+        <v>5655.4</v>
       </c>
     </row>
     <row r="53">
@@ -9200,7 +9200,7 @@
         <v>46100.16666666666</v>
       </c>
       <c r="B53" t="n">
-        <v>9384.4</v>
+        <v>9386.799999999999</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -9221,40 +9221,40 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.15679</v>
+        <v>1.15709</v>
       </c>
       <c r="D54" t="n">
-        <v>1.33356</v>
+        <v>1.33411</v>
       </c>
       <c r="E54" t="n">
-        <v>7611.8</v>
+        <v>7613.8</v>
       </c>
       <c r="F54" t="n">
-        <v>22210.8</v>
+        <v>22214.3</v>
       </c>
       <c r="G54" t="n">
-        <v>45798.2</v>
+        <v>45803.1</v>
       </c>
       <c r="H54" t="n">
-        <v>9837.299999999999</v>
+        <v>9839.299999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>24755.8</v>
+        <v>24770.8</v>
       </c>
       <c r="J54" t="n">
-        <v>23997.9</v>
+        <v>24000.4</v>
       </c>
       <c r="K54" t="n">
-        <v>51302.2</v>
+        <v>51317.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2451.6</v>
+        <v>2452.1</v>
       </c>
       <c r="M54" t="n">
-        <v>6536.37</v>
+        <v>6537.12</v>
       </c>
       <c r="N54" t="n">
-        <v>5473.45</v>
+        <v>5474.95</v>
       </c>
     </row>
     <row r="55">
@@ -9262,7 +9262,7 @@
         <v>46101.16666666666</v>
       </c>
       <c r="B55" t="n">
-        <v>9788.799999999999</v>
+        <v>9792.700000000001</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -9283,40 +9283,40 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.1562</v>
+        <v>1.156245</v>
       </c>
       <c r="D56" t="n">
-        <v>1.33332</v>
+        <v>1.333395</v>
       </c>
       <c r="E56" t="n">
-        <v>7538.6</v>
+        <v>7540.6</v>
       </c>
       <c r="F56" t="n">
-        <v>21972.1</v>
+        <v>21975.6</v>
       </c>
       <c r="G56" t="n">
-        <v>45536.2</v>
+        <v>45538.6</v>
       </c>
       <c r="H56" t="n">
-        <v>9792.1</v>
+        <v>9794.1</v>
       </c>
       <c r="I56" t="n">
-        <v>24644.3</v>
+        <v>24659.3</v>
       </c>
       <c r="J56" t="n">
-        <v>23793.4</v>
+        <v>23794.4</v>
       </c>
       <c r="K56" t="n">
-        <v>51177</v>
+        <v>51180.5</v>
       </c>
       <c r="L56" t="n">
-        <v>2432.5</v>
+        <v>2432.65</v>
       </c>
       <c r="M56" t="n">
-        <v>6488.2</v>
+        <v>6488.5</v>
       </c>
       <c r="N56" t="n">
-        <v>5418.1</v>
+        <v>5419.6</v>
       </c>
     </row>
     <row r="57">
@@ -9324,7 +9324,7 @@
         <v>46103.16666666666</v>
       </c>
       <c r="B57" t="n">
-        <v>9883.200000000001</v>
+        <v>9885.6</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -9345,40 +9345,40 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.16077</v>
+        <v>1.1608</v>
       </c>
       <c r="D58" t="n">
-        <v>1.34255</v>
+        <v>1.342625</v>
       </c>
       <c r="E58" t="n">
-        <v>7796.8</v>
+        <v>7798.8</v>
       </c>
       <c r="F58" t="n">
-        <v>22841.5</v>
+        <v>22845</v>
       </c>
       <c r="G58" t="n">
-        <v>46288.2</v>
+        <v>46290.6</v>
       </c>
       <c r="H58" t="n">
-        <v>9961.6</v>
+        <v>9963.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24967.7</v>
+        <v>24982.7</v>
       </c>
       <c r="J58" t="n">
-        <v>24240.8</v>
+        <v>24241.8</v>
       </c>
       <c r="K58" t="n">
-        <v>53014.7</v>
+        <v>53018.2</v>
       </c>
       <c r="L58" t="n">
-        <v>2500.4</v>
+        <v>2500.55</v>
       </c>
       <c r="M58" t="n">
-        <v>6593.77</v>
+        <v>6594.07</v>
       </c>
       <c r="N58" t="n">
-        <v>5616.2</v>
+        <v>5617.7</v>
       </c>
     </row>
     <row r="59">
@@ -9386,7 +9386,7 @@
         <v>46104.16666666666</v>
       </c>
       <c r="B59" t="n">
-        <v>9121</v>
+        <v>9123.4</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -9407,40 +9407,40 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.1613</v>
+        <v>1.161345</v>
       </c>
       <c r="D60" t="n">
-        <v>1.34141</v>
+        <v>1.341485</v>
       </c>
       <c r="E60" t="n">
-        <v>7813.7</v>
+        <v>7815.7</v>
       </c>
       <c r="F60" t="n">
-        <v>22887.5</v>
+        <v>22891</v>
       </c>
       <c r="G60" t="n">
-        <v>46445.6</v>
+        <v>46448</v>
       </c>
       <c r="H60" t="n">
-        <v>10013.3</v>
+        <v>10015.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25035.4</v>
+        <v>25050.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24204</v>
+        <v>24205</v>
       </c>
       <c r="K60" t="n">
-        <v>53497.1</v>
+        <v>53500.6</v>
       </c>
       <c r="L60" t="n">
-        <v>2535.6</v>
+        <v>2535.75</v>
       </c>
       <c r="M60" t="n">
-        <v>6599.67</v>
+        <v>6599.97</v>
       </c>
       <c r="N60" t="n">
-        <v>5644.18</v>
+        <v>5645.68</v>
       </c>
     </row>
     <row r="61">
@@ -9448,7 +9448,7 @@
         <v>46105.16666666666</v>
       </c>
       <c r="B61" t="n">
-        <v>8852.799999999999</v>
+        <v>8855.200000000001</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -9469,40 +9469,40 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.15614</v>
+        <v>1.156185</v>
       </c>
       <c r="D62" t="n">
-        <v>1.33631</v>
+        <v>1.336385</v>
       </c>
       <c r="E62" t="n">
-        <v>7813.5</v>
+        <v>7815.5</v>
       </c>
       <c r="F62" t="n">
-        <v>22866.6</v>
+        <v>22870.1</v>
       </c>
       <c r="G62" t="n">
-        <v>46357.1</v>
+        <v>46359.5</v>
       </c>
       <c r="H62" t="n">
-        <v>10083.7</v>
+        <v>10085.7</v>
       </c>
       <c r="I62" t="n">
-        <v>25244.3</v>
+        <v>25259.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24113.6</v>
+        <v>24114.6</v>
       </c>
       <c r="K62" t="n">
-        <v>53875</v>
+        <v>53878.5</v>
       </c>
       <c r="L62" t="n">
-        <v>2530.6</v>
+        <v>2530.75</v>
       </c>
       <c r="M62" t="n">
-        <v>6580.7</v>
+        <v>6581</v>
       </c>
       <c r="N62" t="n">
-        <v>5620.01</v>
+        <v>5621.51</v>
       </c>
     </row>
     <row r="63">
@@ -9510,7 +9510,7 @@
         <v>46106.16666666666</v>
       </c>
       <c r="B63" t="n">
-        <v>9115.299999999999</v>
+        <v>9117.700000000001</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -9531,40 +9531,40 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.15345</v>
+        <v>1.153495</v>
       </c>
       <c r="D64" t="n">
-        <v>1.33334</v>
+        <v>1.333415</v>
       </c>
       <c r="E64" t="n">
-        <v>7778.5</v>
+        <v>7780.5</v>
       </c>
       <c r="F64" t="n">
-        <v>22689</v>
+        <v>22692.5</v>
       </c>
       <c r="G64" t="n">
-        <v>46178.7</v>
+        <v>46181.1</v>
       </c>
       <c r="H64" t="n">
-        <v>9963.799999999999</v>
+        <v>9965.799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>24753.8</v>
+        <v>24768.8</v>
       </c>
       <c r="J64" t="n">
-        <v>23681.7</v>
+        <v>23682.7</v>
       </c>
       <c r="K64" t="n">
-        <v>52920.1</v>
+        <v>52923.6</v>
       </c>
       <c r="L64" t="n">
-        <v>2508.4</v>
+        <v>2508.55</v>
       </c>
       <c r="M64" t="n">
-        <v>6505.95</v>
+        <v>6506.25</v>
       </c>
       <c r="N64" t="n">
-        <v>5571.5</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="65">
@@ -9572,7 +9572,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B65" t="n">
-        <v>9272.4</v>
+        <v>9274.799999999999</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -9593,40 +9593,40 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.15067</v>
+        <v>1.15097</v>
       </c>
       <c r="D66" t="n">
-        <v>1.32591</v>
+        <v>1.3264</v>
       </c>
       <c r="E66" t="n">
-        <v>7644.4</v>
+        <v>7646.4</v>
       </c>
       <c r="F66" t="n">
-        <v>22097.6</v>
+        <v>22101.1</v>
       </c>
       <c r="G66" t="n">
-        <v>45056.6</v>
+        <v>45061.5</v>
       </c>
       <c r="H66" t="n">
-        <v>9893.299999999999</v>
+        <v>9895.299999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24612.5</v>
+        <v>24627.5</v>
       </c>
       <c r="J66" t="n">
-        <v>23067.1</v>
+        <v>23069.6</v>
       </c>
       <c r="K66" t="n">
-        <v>51122.7</v>
+        <v>51137.7</v>
       </c>
       <c r="L66" t="n">
-        <v>2442.7</v>
+        <v>2443.2</v>
       </c>
       <c r="M66" t="n">
-        <v>6354.5</v>
+        <v>6355.25</v>
       </c>
       <c r="N66" t="n">
-        <v>5453.72</v>
+        <v>5455.22</v>
       </c>
     </row>
     <row r="67">
@@ -9634,7 +9634,7 @@
         <v>46108.16666666666</v>
       </c>
       <c r="B67" t="n">
-        <v>9973.4</v>
+        <v>9977.299999999999</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -9655,40 +9655,40 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.14879</v>
+        <v>1.148835</v>
       </c>
       <c r="D68" t="n">
-        <v>1.32377</v>
+        <v>1.323875</v>
       </c>
       <c r="E68" t="n">
-        <v>7616.7</v>
+        <v>7618.7</v>
       </c>
       <c r="F68" t="n">
-        <v>22027.9</v>
+        <v>22031.4</v>
       </c>
       <c r="G68" t="n">
-        <v>44943.2</v>
+        <v>44945.6</v>
       </c>
       <c r="H68" t="n">
-        <v>9877.4</v>
+        <v>9879.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24578.4</v>
+        <v>24593.4</v>
       </c>
       <c r="J68" t="n">
-        <v>23026.2</v>
+        <v>23027.2</v>
       </c>
       <c r="K68" t="n">
-        <v>50601.5</v>
+        <v>50609</v>
       </c>
       <c r="L68" t="n">
-        <v>2430.7</v>
+        <v>2430.85</v>
       </c>
       <c r="M68" t="n">
-        <v>6339.91</v>
+        <v>6340.21</v>
       </c>
       <c r="N68" t="n">
-        <v>5433.9</v>
+        <v>5435.4</v>
       </c>
     </row>
     <row r="69">
@@ -9696,7 +9696,7 @@
         <v>46110.20833333334</v>
       </c>
       <c r="B69" t="n">
-        <v>9974</v>
+        <v>9976.4</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -9717,40 +9717,40 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1.14593</v>
+        <v>1.145975</v>
       </c>
       <c r="D70" t="n">
-        <v>1.31792</v>
+        <v>1.317995</v>
       </c>
       <c r="E70" t="n">
-        <v>7720.7</v>
+        <v>7722.7</v>
       </c>
       <c r="F70" t="n">
-        <v>22431.1</v>
+        <v>22434.6</v>
       </c>
       <c r="G70" t="n">
-        <v>45223.1</v>
+        <v>45225.5</v>
       </c>
       <c r="H70" t="n">
-        <v>10068.4</v>
+        <v>10070.4</v>
       </c>
       <c r="I70" t="n">
-        <v>24709.4</v>
+        <v>24724.4</v>
       </c>
       <c r="J70" t="n">
-        <v>22919.3</v>
+        <v>22920.3</v>
       </c>
       <c r="K70" t="n">
-        <v>51047.3</v>
+        <v>51054.8</v>
       </c>
       <c r="L70" t="n">
-        <v>2409.7</v>
+        <v>2409.85</v>
       </c>
       <c r="M70" t="n">
-        <v>6341.08</v>
+        <v>6341.38</v>
       </c>
       <c r="N70" t="n">
-        <v>5499.4</v>
+        <v>5500.9</v>
       </c>
     </row>
     <row r="71">
@@ -9758,7 +9758,7 @@
         <v>46111.20833333334</v>
       </c>
       <c r="B71" t="n">
-        <v>10066.5</v>
+        <v>10068.9</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -9779,40 +9779,40 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.15583</v>
+        <v>1.155875</v>
       </c>
       <c r="D72" t="n">
-        <v>1.32294</v>
+        <v>1.323055</v>
       </c>
       <c r="E72" t="n">
-        <v>7919.4</v>
+        <v>7921.4</v>
       </c>
       <c r="F72" t="n">
-        <v>23022.7</v>
+        <v>23026.2</v>
       </c>
       <c r="G72" t="n">
-        <v>46229.5</v>
+        <v>46230.95</v>
       </c>
       <c r="H72" t="n">
-        <v>10277.9</v>
+        <v>10279.9</v>
       </c>
       <c r="I72" t="n">
-        <v>25302.1</v>
+        <v>25317.1</v>
       </c>
       <c r="J72" t="n">
-        <v>23776.1</v>
+        <v>23777.1</v>
       </c>
       <c r="K72" t="n">
-        <v>53043.3</v>
+        <v>53050.8</v>
       </c>
       <c r="L72" t="n">
-        <v>2494</v>
+        <v>2494.15</v>
       </c>
       <c r="M72" t="n">
-        <v>6529.85</v>
+        <v>6530.15</v>
       </c>
       <c r="N72" t="n">
-        <v>5652</v>
+        <v>5653.5</v>
       </c>
     </row>
     <row r="73">
@@ -9820,7 +9820,7 @@
         <v>46112.20833333334</v>
       </c>
       <c r="B73" t="n">
-        <v>9966.700000000001</v>
+        <v>9969.1</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -9841,40 +9841,40 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1.15905</v>
+        <v>1.159095</v>
       </c>
       <c r="D74" t="n">
-        <v>1.33055</v>
+        <v>1.330625</v>
       </c>
       <c r="E74" t="n">
-        <v>7974.6</v>
+        <v>7976.6</v>
       </c>
       <c r="F74" t="n">
-        <v>23285.5</v>
+        <v>23289</v>
       </c>
       <c r="G74" t="n">
-        <v>46559.4</v>
+        <v>46561.8</v>
       </c>
       <c r="H74" t="n">
-        <v>10414.2</v>
+        <v>10416.2</v>
       </c>
       <c r="I74" t="n">
-        <v>25300.3</v>
+        <v>25315.3</v>
       </c>
       <c r="J74" t="n">
-        <v>23995.1</v>
+        <v>23996.1</v>
       </c>
       <c r="K74" t="n">
-        <v>54226.4</v>
+        <v>54233.9</v>
       </c>
       <c r="L74" t="n">
-        <v>2510</v>
+        <v>2510.15</v>
       </c>
       <c r="M74" t="n">
-        <v>6571.83</v>
+        <v>6572.13</v>
       </c>
       <c r="N74" t="n">
-        <v>5719.4</v>
+        <v>5720.9</v>
       </c>
     </row>
     <row r="75">
@@ -9882,7 +9882,7 @@
         <v>46113.20833333334</v>
       </c>
       <c r="B75" t="n">
-        <v>10092.7</v>
+        <v>10095.1</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -9903,40 +9903,40 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1.15397</v>
+        <v>1.154015</v>
       </c>
       <c r="D76" t="n">
-        <v>1.32248</v>
+        <v>1.322585</v>
       </c>
       <c r="E76" t="n">
-        <v>7988.9</v>
+        <v>7990.9</v>
       </c>
       <c r="F76" t="n">
-        <v>23214.1</v>
+        <v>23217.6</v>
       </c>
       <c r="G76" t="n">
-        <v>46520</v>
+        <v>46522.4</v>
       </c>
       <c r="H76" t="n">
-        <v>10449.6</v>
+        <v>10451.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25255.4</v>
+        <v>25270.4</v>
       </c>
       <c r="J76" t="n">
-        <v>24029.5</v>
+        <v>24030.5</v>
       </c>
       <c r="K76" t="n">
-        <v>53240</v>
+        <v>53247.5</v>
       </c>
       <c r="L76" t="n">
-        <v>2530.4</v>
+        <v>2530.55</v>
       </c>
       <c r="M76" t="n">
-        <v>6583.06</v>
+        <v>6583.360000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>5699.97</v>
+        <v>5701.47</v>
       </c>
     </row>
     <row r="77">
@@ -9944,7 +9944,7 @@
         <v>46114.20833333334</v>
       </c>
       <c r="B77" t="n">
-        <v>10578.6</v>
+        <v>10581</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -9965,40 +9965,40 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.15154</v>
+        <v>1.15187</v>
       </c>
       <c r="D78" t="n">
-        <v>1.31987</v>
+        <v>1.320465</v>
       </c>
       <c r="E78" t="n">
-        <v>7958.4</v>
+        <v>7960.4</v>
       </c>
       <c r="F78" t="n">
-        <v>23123.8</v>
+        <v>23127.3</v>
       </c>
       <c r="G78" t="n">
-        <v>46405.9</v>
+        <v>46407.7</v>
       </c>
       <c r="H78" t="n">
-        <v>10430</v>
+        <v>10432</v>
       </c>
       <c r="I78" t="n">
-        <v>25173.7</v>
+        <v>25188.7</v>
       </c>
       <c r="J78" t="n">
-        <v>23956.4</v>
+        <v>23957.4</v>
       </c>
       <c r="K78" t="n">
-        <v>53150.2</v>
+        <v>53165.2</v>
       </c>
       <c r="L78" t="n">
-        <v>2519.5</v>
+        <v>2519.65</v>
       </c>
       <c r="M78" t="n">
-        <v>6563.37</v>
+        <v>6563.67</v>
       </c>
       <c r="N78" t="n">
-        <v>5678.27</v>
+        <v>5679.77</v>
       </c>
     </row>
     <row r="79">
@@ -10009,34 +10009,34 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>7932.5</v>
+        <v>7934.5</v>
       </c>
       <c r="F79" t="n">
-        <v>23049.4</v>
+        <v>23052.9</v>
       </c>
       <c r="G79" t="n">
-        <v>46255.9</v>
+        <v>46258.3</v>
       </c>
       <c r="H79" t="n">
-        <v>10414.4</v>
+        <v>10416.4</v>
       </c>
       <c r="I79" t="n">
-        <v>25138.9</v>
+        <v>25153.9</v>
       </c>
       <c r="J79" t="n">
-        <v>23906.8</v>
+        <v>23907.8</v>
       </c>
       <c r="K79" t="n">
-        <v>52865.1</v>
+        <v>52872.6</v>
       </c>
       <c r="L79" t="n">
-        <v>2510.7</v>
+        <v>2510.85</v>
       </c>
       <c r="M79" t="n">
-        <v>6547.27</v>
+        <v>6547.57</v>
       </c>
       <c r="N79" t="n">
-        <v>5660.3</v>
+        <v>5661.8</v>
       </c>
     </row>
     <row r="80">
@@ -10044,7 +10044,7 @@
         <v>46117.20833333334</v>
       </c>
       <c r="B80" t="n">
-        <v>10417.9</v>
+        <v>10420.3</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -10065,40 +10065,40 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1.15422</v>
+        <v>1.154265</v>
       </c>
       <c r="D81" t="n">
-        <v>1.32328</v>
+        <v>1.323355</v>
       </c>
       <c r="E81" t="n">
-        <v>8024.1</v>
+        <v>8026.1</v>
       </c>
       <c r="F81" t="n">
-        <v>23291.6</v>
+        <v>23295.1</v>
       </c>
       <c r="G81" t="n">
-        <v>46707.1</v>
+        <v>46709.5</v>
       </c>
       <c r="H81" t="n">
-        <v>10475.6</v>
+        <v>10477.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25297</v>
+        <v>25312</v>
       </c>
       <c r="J81" t="n">
-        <v>24133.7</v>
+        <v>24134.7</v>
       </c>
       <c r="K81" t="n">
-        <v>53876.2</v>
+        <v>53883.7</v>
       </c>
       <c r="L81" t="n">
-        <v>2536.5</v>
+        <v>2536.65</v>
       </c>
       <c r="M81" t="n">
-        <v>6603.66</v>
+        <v>6603.96</v>
       </c>
       <c r="N81" t="n">
-        <v>5725.6</v>
+        <v>5727.1</v>
       </c>
     </row>
     <row r="82">
@@ -10106,7 +10106,7 @@
         <v>46118.20833333334</v>
       </c>
       <c r="B82" t="n">
-        <v>10673.3</v>
+        <v>10675.7</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -10127,40 +10127,40 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1.16675</v>
+        <v>1.166825</v>
       </c>
       <c r="D83" t="n">
-        <v>1.33725</v>
+        <v>1.337355</v>
       </c>
       <c r="E83" t="n">
-        <v>8191.7</v>
+        <v>8193.700000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>23798.8</v>
+        <v>23802.3</v>
       </c>
       <c r="G83" t="n">
-        <v>47543.4</v>
+        <v>47545.8</v>
       </c>
       <c r="H83" t="n">
-        <v>10555.1</v>
+        <v>10557.1</v>
       </c>
       <c r="I83" t="n">
-        <v>25605.5</v>
+        <v>25620.5</v>
       </c>
       <c r="J83" t="n">
-        <v>24747.9</v>
+        <v>24748.9</v>
       </c>
       <c r="K83" t="n">
-        <v>55934.9</v>
+        <v>55942.4</v>
       </c>
       <c r="L83" t="n">
-        <v>2623.6</v>
+        <v>2623.75</v>
       </c>
       <c r="M83" t="n">
-        <v>6752.12</v>
+        <v>6752.42</v>
       </c>
       <c r="N83" t="n">
-        <v>5844.2</v>
+        <v>5845.7</v>
       </c>
     </row>
     <row r="84">
@@ -10168,7 +10168,7 @@
         <v>46119.20833333334</v>
       </c>
       <c r="B84" t="n">
-        <v>9108.299999999999</v>
+        <v>9110.700000000001</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -10189,40 +10189,40 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1.16623</v>
+        <v>1.166275</v>
       </c>
       <c r="D85" t="n">
-        <v>1.33971</v>
+        <v>1.339785</v>
       </c>
       <c r="E85" t="n">
-        <v>8272.200000000001</v>
+        <v>8274.200000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>24001.7</v>
+        <v>24005.2</v>
       </c>
       <c r="G85" t="n">
-        <v>47884.1</v>
+        <v>47886.5</v>
       </c>
       <c r="H85" t="n">
-        <v>10657.2</v>
+        <v>10659.2</v>
       </c>
       <c r="I85" t="n">
-        <v>25862.5</v>
+        <v>25877.5</v>
       </c>
       <c r="J85" t="n">
-        <v>24863</v>
+        <v>24864</v>
       </c>
       <c r="K85" t="n">
-        <v>56743.2</v>
+        <v>56750.7</v>
       </c>
       <c r="L85" t="n">
-        <v>2621</v>
+        <v>2621.15</v>
       </c>
       <c r="M85" t="n">
-        <v>6775.54</v>
+        <v>6775.84</v>
       </c>
       <c r="N85" t="n">
-        <v>5912.1</v>
+        <v>5913.6</v>
       </c>
     </row>
     <row r="86">
@@ -10230,7 +10230,7 @@
         <v>46120.20833333334</v>
       </c>
       <c r="B86" t="n">
-        <v>9242.9</v>
+        <v>9245.299999999999</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -10251,40 +10251,40 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.16936</v>
+        <v>1.169405</v>
       </c>
       <c r="D87" t="n">
-        <v>1.34273</v>
+        <v>1.342805</v>
       </c>
       <c r="E87" t="n">
-        <v>8250.299999999999</v>
+        <v>8252.299999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>23856.6</v>
+        <v>23860.1</v>
       </c>
       <c r="G87" t="n">
-        <v>48152.7</v>
+        <v>48155.1</v>
       </c>
       <c r="H87" t="n">
-        <v>10592.9</v>
+        <v>10594.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25901.1</v>
+        <v>25916.1</v>
       </c>
       <c r="J87" t="n">
-        <v>25041.9</v>
+        <v>25042.9</v>
       </c>
       <c r="K87" t="n">
-        <v>56479.6</v>
+        <v>56487.1</v>
       </c>
       <c r="L87" t="n">
-        <v>2635.5</v>
+        <v>2635.65</v>
       </c>
       <c r="M87" t="n">
-        <v>6816.6</v>
+        <v>6816.9</v>
       </c>
       <c r="N87" t="n">
-        <v>5899.4</v>
+        <v>5900.9</v>
       </c>
     </row>
     <row r="88">
@@ -10292,7 +10292,7 @@
         <v>46121.20833333334</v>
       </c>
       <c r="B88" t="n">
-        <v>9240.299999999999</v>
+        <v>9242.700000000001</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -10313,40 +10313,40 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.17227</v>
+        <v>1.1726</v>
       </c>
       <c r="D89" t="n">
-        <v>1.34564</v>
+        <v>1.346235</v>
       </c>
       <c r="E89" t="n">
-        <v>8264.799999999999</v>
+        <v>8266.799999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>23820.4</v>
+        <v>23823.9</v>
       </c>
       <c r="G89" t="n">
-        <v>47967.1</v>
+        <v>47972</v>
       </c>
       <c r="H89" t="n">
-        <v>10603.1</v>
+        <v>10605.1</v>
       </c>
       <c r="I89" t="n">
-        <v>25933.9</v>
+        <v>25948.9</v>
       </c>
       <c r="J89" t="n">
-        <v>25162.2</v>
+        <v>25164.7</v>
       </c>
       <c r="K89" t="n">
-        <v>57391.8</v>
+        <v>57406.8</v>
       </c>
       <c r="L89" t="n">
-        <v>2635.8</v>
+        <v>2636.3</v>
       </c>
       <c r="M89" t="n">
-        <v>6824.8</v>
+        <v>6825.55</v>
       </c>
       <c r="N89" t="n">
-        <v>5927.41</v>
+        <v>5928.91</v>
       </c>
     </row>
     <row r="90">
@@ -10354,7 +10354,7 @@
         <v>46122.20833333334</v>
       </c>
       <c r="B90" t="n">
-        <v>9110.799999999999</v>
+        <v>9114.700000000001</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -10375,40 +10375,40 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.16721</v>
+        <v>1.167255</v>
       </c>
       <c r="D91" t="n">
-        <v>1.33938</v>
+        <v>1.339455</v>
       </c>
       <c r="E91" t="n">
-        <v>8128.9</v>
+        <v>8130.9</v>
       </c>
       <c r="F91" t="n">
-        <v>23434.6</v>
+        <v>23438.1</v>
       </c>
       <c r="G91" t="n">
-        <v>47400.6</v>
+        <v>47403</v>
       </c>
       <c r="H91" t="n">
-        <v>10521</v>
+        <v>10523</v>
       </c>
       <c r="I91" t="n">
-        <v>25755.2</v>
+        <v>25770.2</v>
       </c>
       <c r="J91" t="n">
-        <v>24790.8</v>
+        <v>24791.8</v>
       </c>
       <c r="K91" t="n">
-        <v>56078</v>
+        <v>56085.5</v>
       </c>
       <c r="L91" t="n">
-        <v>2587.7</v>
+        <v>2587.85</v>
       </c>
       <c r="M91" t="n">
-        <v>6740.25</v>
+        <v>6740.55</v>
       </c>
       <c r="N91" t="n">
-        <v>5830.3</v>
+        <v>5831.8</v>
       </c>
     </row>
     <row r="92">
@@ -10416,7 +10416,7 @@
         <v>46124.20833333334</v>
       </c>
       <c r="B92" t="n">
-        <v>9807</v>
+        <v>9809.4</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -10437,40 +10437,40 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.17609</v>
+        <v>1.176135</v>
       </c>
       <c r="D93" t="n">
-        <v>1.35099</v>
+        <v>1.351065</v>
       </c>
       <c r="E93" t="n">
-        <v>8266.299999999999</v>
+        <v>8268.299999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>23962</v>
+        <v>23965.5</v>
       </c>
       <c r="G93" t="n">
-        <v>48225.3</v>
+        <v>48227.7</v>
       </c>
       <c r="H93" t="n">
-        <v>10615.9</v>
+        <v>10617.9</v>
       </c>
       <c r="I93" t="n">
-        <v>25953.2</v>
+        <v>25968.2</v>
       </c>
       <c r="J93" t="n">
-        <v>25434.7</v>
+        <v>25435.7</v>
       </c>
       <c r="K93" t="n">
-        <v>57691.4</v>
+        <v>57698.9</v>
       </c>
       <c r="L93" t="n">
-        <v>2678</v>
+        <v>2678.15</v>
       </c>
       <c r="M93" t="n">
-        <v>6889.85</v>
+        <v>6890.15</v>
       </c>
       <c r="N93" t="n">
-        <v>5945.8</v>
+        <v>5947.3</v>
       </c>
     </row>
     <row r="94">
@@ -10478,7 +10478,7 @@
         <v>46125.20833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>9263.799999999999</v>
+        <v>9266.200000000001</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -10499,40 +10499,40 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.17944</v>
+        <v>1.179485</v>
       </c>
       <c r="D95" t="n">
-        <v>1.3568</v>
+        <v>1.356875</v>
       </c>
       <c r="E95" t="n">
-        <v>8324.9</v>
+        <v>8326.9</v>
       </c>
       <c r="F95" t="n">
-        <v>24051.4</v>
+        <v>24054.9</v>
       </c>
       <c r="G95" t="n">
-        <v>48535.3</v>
+        <v>48537.7</v>
       </c>
       <c r="H95" t="n">
-        <v>10622.6</v>
+        <v>10624.6</v>
       </c>
       <c r="I95" t="n">
-        <v>26197.7</v>
+        <v>26212.7</v>
       </c>
       <c r="J95" t="n">
-        <v>25829.8</v>
+        <v>25830.8</v>
       </c>
       <c r="K95" t="n">
-        <v>58698.5</v>
+        <v>58706</v>
       </c>
       <c r="L95" t="n">
-        <v>2705.4</v>
+        <v>2705.55</v>
       </c>
       <c r="M95" t="n">
-        <v>6967.47</v>
+        <v>6967.77</v>
       </c>
       <c r="N95" t="n">
-        <v>5984.9</v>
+        <v>5986.4</v>
       </c>
     </row>
     <row r="96">
@@ -10540,7 +10540,7 @@
         <v>46126.20833333334</v>
       </c>
       <c r="B96" t="n">
-        <v>8866.6</v>
+        <v>8869</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -10561,40 +10561,40 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.18019</v>
+        <v>1.180235</v>
       </c>
       <c r="D97" t="n">
-        <v>1.35671</v>
+        <v>1.356785</v>
       </c>
       <c r="E97" t="n">
-        <v>8262.799999999999</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>24103.6</v>
+        <v>24107.1</v>
       </c>
       <c r="G97" t="n">
-        <v>48525.4</v>
+        <v>48527.8</v>
       </c>
       <c r="H97" t="n">
-        <v>10554.1</v>
+        <v>10556.1</v>
       </c>
       <c r="I97" t="n">
-        <v>26115.4</v>
+        <v>26130.4</v>
       </c>
       <c r="J97" t="n">
-        <v>26228.3</v>
+        <v>26229.3</v>
       </c>
       <c r="K97" t="n">
-        <v>58556.3</v>
+        <v>58563.8</v>
       </c>
       <c r="L97" t="n">
-        <v>2716.2</v>
+        <v>2716.35</v>
       </c>
       <c r="M97" t="n">
-        <v>7027.99</v>
+        <v>7028.29</v>
       </c>
       <c r="N97" t="n">
-        <v>5945.4</v>
+        <v>5946.9</v>
       </c>
     </row>
     <row r="98">
@@ -10602,7 +10602,7 @@
         <v>46127.20833333334</v>
       </c>
       <c r="B98" t="n">
-        <v>8866</v>
+        <v>8868.4</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -10623,40 +10623,40 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.1785</v>
+        <v>1.178545</v>
       </c>
       <c r="D99" t="n">
-        <v>1.35314</v>
+        <v>1.353215</v>
       </c>
       <c r="E99" t="n">
-        <v>8264.4</v>
+        <v>8266.4</v>
       </c>
       <c r="F99" t="n">
-        <v>24137.4</v>
+        <v>24140.9</v>
       </c>
       <c r="G99" t="n">
-        <v>48658.7</v>
+        <v>48661.1</v>
       </c>
       <c r="H99" t="n">
-        <v>10588.9</v>
+        <v>10590.9</v>
       </c>
       <c r="I99" t="n">
-        <v>26221.3</v>
+        <v>26236.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26320.7</v>
+        <v>26321.7</v>
       </c>
       <c r="K99" t="n">
-        <v>59422.9</v>
+        <v>59430.4</v>
       </c>
       <c r="L99" t="n">
-        <v>2725</v>
+        <v>2725.15</v>
       </c>
       <c r="M99" t="n">
-        <v>7046.44</v>
+        <v>7046.74</v>
       </c>
       <c r="N99" t="n">
-        <v>5919.17</v>
+        <v>5920.67</v>
       </c>
     </row>
     <row r="100">
@@ -10664,7 +10664,7 @@
         <v>46128.20833333334</v>
       </c>
       <c r="B100" t="n">
-        <v>9027.799999999999</v>
+        <v>9030.200000000001</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -10685,40 +10685,40 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.17606</v>
+        <v>1.176345</v>
       </c>
       <c r="D101" t="n">
-        <v>1.35102</v>
+        <v>1.351615</v>
       </c>
       <c r="E101" t="n">
-        <v>8405.9</v>
+        <v>8407.9</v>
       </c>
       <c r="F101" t="n">
-        <v>24648.4</v>
+        <v>24651.9</v>
       </c>
       <c r="G101" t="n">
-        <v>49448.1</v>
+        <v>49453</v>
       </c>
       <c r="H101" t="n">
-        <v>10695.9</v>
+        <v>10697.9</v>
       </c>
       <c r="I101" t="n">
-        <v>26489.1</v>
+        <v>26504.1</v>
       </c>
       <c r="J101" t="n">
-        <v>26681.6</v>
+        <v>26684.1</v>
       </c>
       <c r="K101" t="n">
-        <v>59678.4</v>
+        <v>59693.4</v>
       </c>
       <c r="L101" t="n">
-        <v>2777.3</v>
+        <v>2777.8</v>
       </c>
       <c r="M101" t="n">
-        <v>7125.67</v>
+        <v>7126.42</v>
       </c>
       <c r="N101" t="n">
-        <v>6035.01</v>
+        <v>6036.51</v>
       </c>
     </row>
     <row r="102">
@@ -10726,7 +10726,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B102" t="n">
-        <v>8413.6</v>
+        <v>8417.5</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -10747,23 +10747,23 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.1739</v>
+        <v>1.173945</v>
       </c>
       <c r="D103" t="n">
-        <v>1.34863</v>
+        <v>1.348705</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>10631.2</v>
+        <v>10633.2</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>7073.46</v>
+        <v>7073.76</v>
       </c>
       <c r="N103" t="inlineStr"/>
     </row>
@@ -10772,7 +10772,7 @@
         <v>46131.20833333334</v>
       </c>
       <c r="B104" t="n">
-        <v>8908.5</v>
+        <v>8910.9</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -10793,23 +10793,23 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.17896</v>
+        <v>1.179005</v>
       </c>
       <c r="D105" t="n">
-        <v>1.35382</v>
+        <v>1.353895</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>10625.6</v>
+        <v>10627.6</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>7121.6</v>
+        <v>7121.9</v>
       </c>
       <c r="N105" t="inlineStr"/>
     </row>
@@ -10818,7 +10818,7 @@
         <v>46132.20833333334</v>
       </c>
       <c r="B106" t="n">
-        <v>8668.5</v>
+        <v>8670.9</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -10839,23 +10839,23 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.17388</v>
+        <v>1.173925</v>
       </c>
       <c r="D107" t="n">
-        <v>1.35016</v>
+        <v>1.350235</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>10464.5</v>
+        <v>10466.5</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>7088.69</v>
+        <v>7088.99</v>
       </c>
       <c r="N107" t="inlineStr"/>
     </row>
@@ -10864,7 +10864,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B108" t="n">
-        <v>8925.5</v>
+        <v>8926.9</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -10885,23 +10885,23 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>1.17055</v>
+        <v>1.170595</v>
       </c>
       <c r="D109" t="n">
-        <v>1.35014</v>
+        <v>1.350215</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>10458.2</v>
+        <v>10460.2</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>7126.92</v>
+        <v>7127.22</v>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
@@ -10910,7 +10910,7 @@
         <v>46134.20833333334</v>
       </c>
       <c r="B110" t="n">
-        <v>9450.700000000001</v>
+        <v>9453.1</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -10931,23 +10931,23 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1.16859</v>
+        <v>1.168635</v>
       </c>
       <c r="D111" t="n">
-        <v>1.34666</v>
+        <v>1.346735</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10415.5</v>
+        <v>10417.5</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>7113.93</v>
+        <v>7114.23</v>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
@@ -10956,7 +10956,7 @@
         <v>46135.20833333334</v>
       </c>
       <c r="B112" t="n">
-        <v>9658.700000000001</v>
+        <v>9661.1</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -10977,23 +10977,23 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1.17154</v>
+        <v>1.171835</v>
       </c>
       <c r="D113" t="n">
-        <v>1.3525</v>
+        <v>1.353095</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>10385.5</v>
+        <v>10387.5</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>7162.94</v>
+        <v>7163.69</v>
       </c>
       <c r="N113" t="inlineStr"/>
     </row>
@@ -11002,7 +11002,7 @@
         <v>46136.20833333334</v>
       </c>
       <c r="B114" t="n">
-        <v>9484.4</v>
+        <v>9486.799999999999</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -11023,23 +11023,23 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1.17078</v>
+        <v>1.170825</v>
       </c>
       <c r="D115" t="n">
-        <v>1.35149</v>
+        <v>1.351595</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>10368.5</v>
+        <v>10370.5</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>7150.97</v>
+        <v>7151.27</v>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
@@ -11048,7 +11048,7 @@
         <v>46138.20833333334</v>
       </c>
       <c r="B116" t="n">
-        <v>9527.700000000001</v>
+        <v>9529.1</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -11069,23 +11069,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.17243</v>
+        <v>1.17246</v>
       </c>
       <c r="D117" t="n">
-        <v>1.35356</v>
+        <v>1.353605</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10336.9</v>
+        <v>10337.9</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7176.24</v>
+        <v>7176.440000000001</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -11094,7 +11094,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9602.700000000001</v>
+        <v>9605.1</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>

--- a/data/input/universe_series.xlsx
+++ b/data/input/universe_series.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="bid_close" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mid_open" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mid_close" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="mid_close" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="mid_open" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3935,23 +3935,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.17243</v>
+        <v>1.17216</v>
       </c>
       <c r="D117" t="n">
-        <v>1.35356</v>
+        <v>1.3535</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10336.9</v>
+        <v>10330.5</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7176.24</v>
+        <v>7185.65</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -3960,7 +3960,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9602.700000000001</v>
+        <v>9759.5</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -3975,6 +3975,190 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>1.17154</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.35207</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>10309.6</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>7145.07</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46140.20833333334</v>
+      </c>
+      <c r="B120" t="n">
+        <v>9928.700000000001</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>1.16778</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.34793</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>10205.5</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>7154.52</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46141.20833333334</v>
+      </c>
+      <c r="B122" t="n">
+        <v>10909.4</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>1.17314</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.36038</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>10361.4</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>7220.22</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46142.20833333334</v>
+      </c>
+      <c r="B124" t="n">
+        <v>10549</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>1.17168</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>10349</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>7218.63</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46143.20833333334</v>
+      </c>
+      <c r="B126" t="n">
+        <v>10257</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3986,7 +4170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4062,10 +4246,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.18506</v>
+        <v>1.178815</v>
       </c>
       <c r="D2" t="n">
-        <v>1.356285</v>
+        <v>1.349475</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -4076,7 +4260,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6834.59</v>
+        <v>6878.96</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -4085,7 +4269,7 @@
         <v>46071.20833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>6248.200000000001</v>
+        <v>6521.200000000001</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -4106,40 +4290,40 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.178825</v>
+        <v>1.17686</v>
       </c>
       <c r="D4" t="n">
-        <v>1.349495</v>
+        <v>1.345965</v>
       </c>
       <c r="E4" t="n">
-        <v>8424.9</v>
+        <v>8417.9</v>
       </c>
       <c r="F4" t="n">
-        <v>25234.3</v>
+        <v>25033.6</v>
       </c>
       <c r="G4" t="n">
-        <v>49646.3</v>
+        <v>49410</v>
       </c>
       <c r="H4" t="n">
-        <v>10679.1</v>
+        <v>10670.2</v>
       </c>
       <c r="I4" t="n">
-        <v>26847.6</v>
+        <v>26796.7</v>
       </c>
       <c r="J4" t="n">
-        <v>24896.8</v>
+        <v>24817.3</v>
       </c>
       <c r="K4" t="n">
-        <v>57517.5</v>
+        <v>57084.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2656.25</v>
+        <v>2661.95</v>
       </c>
       <c r="M4" t="n">
-        <v>6879.21</v>
+        <v>6865.84</v>
       </c>
       <c r="N4" t="n">
-        <v>6097.6</v>
+        <v>6065.4</v>
       </c>
     </row>
     <row r="5">
@@ -4147,7 +4331,7 @@
         <v>46072.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>6522.200000000001</v>
+        <v>6672.200000000001</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -4168,40 +4352,40 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.17689</v>
+        <v>1.17822</v>
       </c>
       <c r="D6" t="n">
-        <v>1.345955</v>
+        <v>1.348245</v>
       </c>
       <c r="E6" t="n">
-        <v>8418.1</v>
+        <v>8535.4</v>
       </c>
       <c r="F6" t="n">
-        <v>25034.1</v>
+        <v>25236.6</v>
       </c>
       <c r="G6" t="n">
-        <v>49410.5</v>
+        <v>49624.8</v>
       </c>
       <c r="H6" t="n">
-        <v>10670.3</v>
+        <v>10720.4</v>
       </c>
       <c r="I6" t="n">
-        <v>26796.9</v>
+        <v>26863.4</v>
       </c>
       <c r="J6" t="n">
-        <v>24817.5</v>
+        <v>25016.2</v>
       </c>
       <c r="K6" t="n">
-        <v>57086.7</v>
+        <v>57088.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2662.05</v>
+        <v>2662.2</v>
       </c>
       <c r="M6" t="n">
-        <v>6865.97</v>
+        <v>6910.63</v>
       </c>
       <c r="N6" t="n">
-        <v>6065.5</v>
+        <v>6135.1</v>
       </c>
     </row>
     <row r="7">
@@ -4209,7 +4393,7 @@
         <v>46073.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>6672.200000000001</v>
+        <v>6630.200000000001</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -4230,40 +4414,40 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.179725</v>
+        <v>1.18331</v>
       </c>
       <c r="D8" t="n">
-        <v>1.349105</v>
+        <v>1.353205</v>
       </c>
       <c r="E8" t="n">
-        <v>8526.200000000001</v>
+        <v>8515.200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>25208.9</v>
+        <v>25176</v>
       </c>
       <c r="G8" t="n">
-        <v>49576.3</v>
+        <v>49528.4</v>
       </c>
       <c r="H8" t="n">
-        <v>10712.6</v>
+        <v>10703.4</v>
       </c>
       <c r="I8" t="n">
-        <v>26846.7</v>
+        <v>26826.4</v>
       </c>
       <c r="J8" t="n">
-        <v>24973.5</v>
+        <v>24911.3</v>
       </c>
       <c r="K8" t="n">
-        <v>57079</v>
+        <v>56981.6</v>
       </c>
       <c r="L8" t="n">
-        <v>2656.55</v>
+        <v>2652.65</v>
       </c>
       <c r="M8" t="n">
-        <v>6903.7</v>
+        <v>6892.28</v>
       </c>
       <c r="N8" t="n">
-        <v>6128.4</v>
+        <v>6120.4</v>
       </c>
     </row>
     <row r="9">
@@ -4271,7 +4455,7 @@
         <v>46075.20833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>6573.9</v>
+        <v>6557.700000000001</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4292,40 +4476,40 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.1833</v>
+        <v>1.179325</v>
       </c>
       <c r="D10" t="n">
-        <v>1.353215</v>
+        <v>1.349555</v>
       </c>
       <c r="E10" t="n">
-        <v>8515.1</v>
+        <v>8506.6</v>
       </c>
       <c r="F10" t="n">
-        <v>25175.6</v>
+        <v>24996.5</v>
       </c>
       <c r="G10" t="n">
-        <v>49528.9</v>
+        <v>48839.5</v>
       </c>
       <c r="H10" t="n">
-        <v>10703.3</v>
+        <v>10692.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26826.2</v>
+        <v>26891.9</v>
       </c>
       <c r="J10" t="n">
-        <v>24910.7</v>
+        <v>24735.3</v>
       </c>
       <c r="K10" t="n">
-        <v>56979.1</v>
+        <v>56665.8</v>
       </c>
       <c r="L10" t="n">
-        <v>2652.45</v>
+        <v>2621.45</v>
       </c>
       <c r="M10" t="n">
-        <v>6892.15</v>
+        <v>6844.309999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6120.3</v>
+        <v>6123.3</v>
       </c>
     </row>
     <row r="11">
@@ -4333,7 +4517,7 @@
         <v>46076.20833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>6557.799999999999</v>
+        <v>6676.299999999999</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4354,40 +4538,40 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.179315</v>
+        <v>1.17743</v>
       </c>
       <c r="D12" t="n">
-        <v>1.349545</v>
+        <v>1.349605</v>
       </c>
       <c r="E12" t="n">
-        <v>8506.5</v>
+        <v>8539.9</v>
       </c>
       <c r="F12" t="n">
-        <v>24996.1</v>
+        <v>25039.3</v>
       </c>
       <c r="G12" t="n">
-        <v>48840</v>
+        <v>49177.5</v>
       </c>
       <c r="H12" t="n">
-        <v>10692.6</v>
+        <v>10712.4</v>
       </c>
       <c r="I12" t="n">
-        <v>26891.6</v>
+        <v>26766.2</v>
       </c>
       <c r="J12" t="n">
-        <v>24735.1</v>
+        <v>24995.3</v>
       </c>
       <c r="K12" t="n">
-        <v>56693.3</v>
+        <v>57912</v>
       </c>
       <c r="L12" t="n">
-        <v>2621.75</v>
+        <v>2651.55</v>
       </c>
       <c r="M12" t="n">
-        <v>6844.559999999999</v>
+        <v>6892.08</v>
       </c>
       <c r="N12" t="n">
-        <v>6123.2</v>
+        <v>6136.1</v>
       </c>
     </row>
     <row r="13">
@@ -4395,7 +4579,7 @@
         <v>46077.20833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>6675.299999999999</v>
+        <v>6598.9</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4416,40 +4600,40 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.17746</v>
+        <v>1.18154</v>
       </c>
       <c r="D14" t="n">
-        <v>1.349615</v>
+        <v>1.355805</v>
       </c>
       <c r="E14" t="n">
-        <v>8539.799999999999</v>
+        <v>8569.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25038.9</v>
+        <v>25181.3</v>
       </c>
       <c r="G14" t="n">
-        <v>49176.5</v>
+        <v>49392</v>
       </c>
       <c r="H14" t="n">
-        <v>10712.3</v>
+        <v>10804.4</v>
       </c>
       <c r="I14" t="n">
-        <v>26766</v>
+        <v>26950</v>
       </c>
       <c r="J14" t="n">
-        <v>24995</v>
+        <v>25270</v>
       </c>
       <c r="K14" t="n">
-        <v>57919.5</v>
+        <v>59285.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2651.45</v>
+        <v>2660.65</v>
       </c>
       <c r="M14" t="n">
-        <v>6891.95</v>
+        <v>6937.66</v>
       </c>
       <c r="N14" t="n">
-        <v>6136</v>
+        <v>6175.7</v>
       </c>
     </row>
     <row r="15">
@@ -4457,7 +4641,7 @@
         <v>46078.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>6599.1</v>
+        <v>6556.6</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -4478,40 +4662,40 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.18153</v>
+        <v>1.180365</v>
       </c>
       <c r="D16" t="n">
-        <v>1.355835</v>
+        <v>1.349155</v>
       </c>
       <c r="E16" t="n">
-        <v>8569.5</v>
+        <v>8611.700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>25180.7</v>
+        <v>25253.3</v>
       </c>
       <c r="G16" t="n">
-        <v>49392.5</v>
+        <v>49229.6</v>
       </c>
       <c r="H16" t="n">
-        <v>10804.3</v>
+        <v>10835.1</v>
       </c>
       <c r="I16" t="n">
-        <v>26949.5</v>
+        <v>26389.6</v>
       </c>
       <c r="J16" t="n">
-        <v>25270.1</v>
+        <v>24955.6</v>
       </c>
       <c r="K16" t="n">
-        <v>59282.6</v>
+        <v>58435</v>
       </c>
       <c r="L16" t="n">
-        <v>2660.95</v>
+        <v>2655.55</v>
       </c>
       <c r="M16" t="n">
-        <v>6937.41</v>
+        <v>6882.360000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>6175.6</v>
+        <v>6150.7</v>
       </c>
     </row>
     <row r="17">
@@ -4519,7 +4703,7 @@
         <v>46079.20833333334</v>
       </c>
       <c r="B17" t="n">
-        <v>6556.700000000001</v>
+        <v>6531.799999999999</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -4540,40 +4724,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.180345</v>
+        <v>1.18179</v>
       </c>
       <c r="D18" t="n">
-        <v>1.349145</v>
+        <v>1.34806</v>
       </c>
       <c r="E18" t="n">
-        <v>8611.299999999999</v>
+        <v>8530.6</v>
       </c>
       <c r="F18" t="n">
-        <v>25252.1</v>
+        <v>25143.7</v>
       </c>
       <c r="G18" t="n">
-        <v>49229.1</v>
+        <v>48858.5</v>
       </c>
       <c r="H18" t="n">
-        <v>10834.9</v>
+        <v>10862.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26389</v>
+        <v>26490.4</v>
       </c>
       <c r="J18" t="n">
-        <v>24955.4</v>
+        <v>24914.4</v>
       </c>
       <c r="K18" t="n">
-        <v>58385</v>
+        <v>58612.7</v>
       </c>
       <c r="L18" t="n">
-        <v>2655.45</v>
+        <v>2626.65</v>
       </c>
       <c r="M18" t="n">
-        <v>6881.99</v>
+        <v>6865.58</v>
       </c>
       <c r="N18" t="n">
-        <v>6150.4</v>
+        <v>6095.38</v>
       </c>
     </row>
     <row r="19">
@@ -4581,7 +4765,7 @@
         <v>46080.20833333334</v>
       </c>
       <c r="B19" t="n">
-        <v>6531.700000000001</v>
+        <v>6725.5</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -4602,40 +4786,40 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1.176735</v>
+        <v>1.17594</v>
       </c>
       <c r="D20" t="n">
-        <v>1.34183</v>
+        <v>1.340525</v>
       </c>
       <c r="E20" t="n">
-        <v>8470.9</v>
+        <v>8466.4</v>
       </c>
       <c r="F20" t="n">
-        <v>24967.8</v>
+        <v>24946.3</v>
       </c>
       <c r="G20" t="n">
-        <v>48514.6</v>
+        <v>48368.8</v>
       </c>
       <c r="H20" t="n">
-        <v>10810.3</v>
+        <v>10811.6</v>
       </c>
       <c r="I20" t="n">
-        <v>26383</v>
+        <v>26350.6</v>
       </c>
       <c r="J20" t="n">
-        <v>24680.4</v>
+        <v>24696.7</v>
       </c>
       <c r="K20" t="n">
-        <v>57705.8</v>
+        <v>57488.1</v>
       </c>
       <c r="L20" t="n">
-        <v>2605.05</v>
+        <v>2591.25</v>
       </c>
       <c r="M20" t="n">
-        <v>6817.17</v>
+        <v>6805.95</v>
       </c>
       <c r="N20" t="n">
-        <v>6052.78</v>
+        <v>6049.58</v>
       </c>
     </row>
     <row r="21">
@@ -4643,7 +4827,7 @@
         <v>46082.20833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>7359.799999999999</v>
+        <v>7100.799999999999</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -4664,40 +4848,40 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.17591</v>
+        <v>1.169435</v>
       </c>
       <c r="D22" t="n">
-        <v>1.340465</v>
+        <v>1.340815</v>
       </c>
       <c r="E22" t="n">
-        <v>8466.6</v>
+        <v>8387.700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>24947.2</v>
+        <v>24582.2</v>
       </c>
       <c r="G22" t="n">
-        <v>48369.8</v>
+        <v>48823.6</v>
       </c>
       <c r="H22" t="n">
-        <v>10811.7</v>
+        <v>10789.5</v>
       </c>
       <c r="I22" t="n">
-        <v>26351.1</v>
+        <v>26156.8</v>
       </c>
       <c r="J22" t="n">
-        <v>24696.9</v>
+        <v>24935.3</v>
       </c>
       <c r="K22" t="n">
-        <v>57483.1</v>
+        <v>57713.1</v>
       </c>
       <c r="L22" t="n">
-        <v>2591.15</v>
+        <v>2650.85</v>
       </c>
       <c r="M22" t="n">
-        <v>6806.2</v>
+        <v>6867.940000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>6049.78</v>
+        <v>5982.2</v>
       </c>
     </row>
     <row r="23">
@@ -4705,7 +4889,7 @@
         <v>46083.20833333334</v>
       </c>
       <c r="B23" t="n">
-        <v>7101.6</v>
+        <v>7242.4</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -4726,40 +4910,40 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1.169445</v>
+        <v>1.1611</v>
       </c>
       <c r="D24" t="n">
-        <v>1.340805</v>
+        <v>1.335115</v>
       </c>
       <c r="E24" t="n">
-        <v>8388</v>
+        <v>8165.4</v>
       </c>
       <c r="F24" t="n">
-        <v>24583</v>
+        <v>23985</v>
       </c>
       <c r="G24" t="n">
-        <v>48825.6</v>
+        <v>48413.3</v>
       </c>
       <c r="H24" t="n">
-        <v>10789.6</v>
+        <v>10517.1</v>
       </c>
       <c r="I24" t="n">
-        <v>26157.2</v>
+        <v>25468.5</v>
       </c>
       <c r="J24" t="n">
-        <v>24937</v>
+        <v>24668</v>
       </c>
       <c r="K24" t="n">
-        <v>57710.6</v>
+        <v>54951.7</v>
       </c>
       <c r="L24" t="n">
-        <v>2651.05</v>
+        <v>2603.45</v>
       </c>
       <c r="M24" t="n">
-        <v>6868.190000000001</v>
+        <v>6802.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5982.4</v>
+        <v>5813.3</v>
       </c>
     </row>
     <row r="25">
@@ -4767,7 +4951,7 @@
         <v>46084.20833333334</v>
       </c>
       <c r="B25" t="n">
-        <v>7242.6</v>
+        <v>7496.700000000001</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -4788,40 +4972,40 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.16112</v>
+        <v>1.163505</v>
       </c>
       <c r="D26" t="n">
-        <v>1.335135</v>
+        <v>1.336925</v>
       </c>
       <c r="E26" t="n">
-        <v>8166.5</v>
+        <v>8204</v>
       </c>
       <c r="F26" t="n">
-        <v>23985.8</v>
+        <v>24302.2</v>
       </c>
       <c r="G26" t="n">
-        <v>48412.8</v>
+        <v>48753.2</v>
       </c>
       <c r="H26" t="n">
-        <v>10517.2</v>
+        <v>10626.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25468.9</v>
+        <v>25602.8</v>
       </c>
       <c r="J26" t="n">
-        <v>24667.6</v>
+        <v>25137.1</v>
       </c>
       <c r="K26" t="n">
-        <v>54976.7</v>
+        <v>56232.9</v>
       </c>
       <c r="L26" t="n">
-        <v>2603.55</v>
+        <v>2635.85</v>
       </c>
       <c r="M26" t="n">
-        <v>6802.75</v>
+        <v>6878.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5813.5</v>
+        <v>5901.9</v>
       </c>
     </row>
     <row r="27">
@@ -4829,7 +5013,7 @@
         <v>46085.20833333334</v>
       </c>
       <c r="B27" t="n">
-        <v>7498.5</v>
+        <v>7666</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -4850,40 +5034,40 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.163485</v>
+        <v>1.16067</v>
       </c>
       <c r="D28" t="n">
-        <v>1.336905</v>
+        <v>1.335565</v>
       </c>
       <c r="E28" t="n">
-        <v>8203.9</v>
+        <v>8059.2</v>
       </c>
       <c r="F28" t="n">
-        <v>24301.8</v>
+        <v>23866.2</v>
       </c>
       <c r="G28" t="n">
-        <v>48752.7</v>
+        <v>48034</v>
       </c>
       <c r="H28" t="n">
-        <v>10626.7</v>
+        <v>10407.9</v>
       </c>
       <c r="I28" t="n">
-        <v>25602.6</v>
+        <v>25202.5</v>
       </c>
       <c r="J28" t="n">
-        <v>25137</v>
+        <v>25031.4</v>
       </c>
       <c r="K28" t="n">
-        <v>56215.4</v>
+        <v>54563.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2635.75</v>
+        <v>2592.85</v>
       </c>
       <c r="M28" t="n">
-        <v>6877.92</v>
+        <v>6834.43</v>
       </c>
       <c r="N28" t="n">
-        <v>5901.8</v>
+        <v>5793.6</v>
       </c>
     </row>
     <row r="29">
@@ -4891,7 +5075,7 @@
         <v>46086.20833333334</v>
       </c>
       <c r="B29" t="n">
-        <v>7665.700000000001</v>
+        <v>7887.5</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -4912,40 +5096,40 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1.16068</v>
+        <v>1.161695</v>
       </c>
       <c r="D30" t="n">
-        <v>1.335575</v>
+        <v>1.340985</v>
       </c>
       <c r="E30" t="n">
-        <v>8059.4</v>
+        <v>8017.2</v>
       </c>
       <c r="F30" t="n">
-        <v>23867</v>
+        <v>23640.3</v>
       </c>
       <c r="G30" t="n">
-        <v>48032.8</v>
+        <v>47434.2</v>
       </c>
       <c r="H30" t="n">
-        <v>10408</v>
+        <v>10318.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25202.9</v>
+        <v>25325.2</v>
       </c>
       <c r="J30" t="n">
-        <v>25032.3</v>
+        <v>24634.2</v>
       </c>
       <c r="K30" t="n">
-        <v>54575.7</v>
+        <v>54029.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2592.75</v>
+        <v>2522</v>
       </c>
       <c r="M30" t="n">
-        <v>6834.68</v>
+        <v>6733.23</v>
       </c>
       <c r="N30" t="n">
-        <v>5793.8</v>
+        <v>5723.03</v>
       </c>
     </row>
     <row r="31">
@@ -4953,7 +5137,7 @@
         <v>46087.20833333334</v>
       </c>
       <c r="B31" t="n">
-        <v>7886.9</v>
+        <v>8947.799999999999</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -4974,40 +5158,40 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.154965</v>
+        <v>1.152455</v>
       </c>
       <c r="D32" t="n">
-        <v>1.33393</v>
+        <v>1.330515</v>
       </c>
       <c r="E32" t="n">
-        <v>7921.2</v>
+        <v>7873</v>
       </c>
       <c r="F32" t="n">
-        <v>23357.4</v>
+        <v>23222.3</v>
       </c>
       <c r="G32" t="n">
-        <v>46831</v>
+        <v>46613</v>
       </c>
       <c r="H32" t="n">
-        <v>10244.7</v>
+        <v>10195.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25160.3</v>
+        <v>25042.2</v>
       </c>
       <c r="J32" t="n">
-        <v>24403</v>
+        <v>24187.4</v>
       </c>
       <c r="K32" t="n">
-        <v>53227.3</v>
+        <v>52216.5</v>
       </c>
       <c r="L32" t="n">
-        <v>2493.15</v>
+        <v>2433.35</v>
       </c>
       <c r="M32" t="n">
-        <v>6678.34</v>
+        <v>6622.45</v>
       </c>
       <c r="N32" t="n">
-        <v>5654.6</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="33">
@@ -5015,7 +5199,7 @@
         <v>46089.20833333334</v>
       </c>
       <c r="B33" t="n">
-        <v>9555</v>
+        <v>11228.6</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -5036,40 +5220,40 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.1524</v>
+        <v>1.161615</v>
       </c>
       <c r="D34" t="n">
-        <v>1.330495</v>
+        <v>1.342445</v>
       </c>
       <c r="E34" t="n">
-        <v>7872.9</v>
+        <v>8000.3</v>
       </c>
       <c r="F34" t="n">
-        <v>23221.9</v>
+        <v>23703.1</v>
       </c>
       <c r="G34" t="n">
-        <v>46616</v>
+        <v>47534.3</v>
       </c>
       <c r="H34" t="n">
-        <v>10195.7</v>
+        <v>10307.8</v>
       </c>
       <c r="I34" t="n">
-        <v>25042</v>
+        <v>25545.7</v>
       </c>
       <c r="J34" t="n">
-        <v>24187.3</v>
+        <v>24854.1</v>
       </c>
       <c r="K34" t="n">
-        <v>52231.5</v>
+        <v>54259.6</v>
       </c>
       <c r="L34" t="n">
-        <v>2433.75</v>
+        <v>2534.05</v>
       </c>
       <c r="M34" t="n">
-        <v>6623.07</v>
+        <v>6766.07</v>
       </c>
       <c r="N34" t="n">
-        <v>5615.8</v>
+        <v>5764.7</v>
       </c>
     </row>
     <row r="35">
@@ -5077,7 +5261,7 @@
         <v>46090.16666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>11229.7</v>
+        <v>8805.4</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -5098,40 +5282,40 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.161575</v>
+        <v>1.161195</v>
       </c>
       <c r="D36" t="n">
-        <v>1.342415</v>
+        <v>1.341985</v>
       </c>
       <c r="E36" t="n">
-        <v>8000.2</v>
+        <v>7996.9</v>
       </c>
       <c r="F36" t="n">
-        <v>23702.6</v>
+        <v>23809.1</v>
       </c>
       <c r="G36" t="n">
-        <v>47534.8</v>
+        <v>47744.5</v>
       </c>
       <c r="H36" t="n">
-        <v>10307.7</v>
+        <v>10385.1</v>
       </c>
       <c r="I36" t="n">
-        <v>25545.5</v>
+        <v>25945.2</v>
       </c>
       <c r="J36" t="n">
-        <v>24854</v>
+        <v>24990.4</v>
       </c>
       <c r="K36" t="n">
-        <v>54251.3</v>
+        <v>55066.9</v>
       </c>
       <c r="L36" t="n">
-        <v>2534.15</v>
+        <v>2552.05</v>
       </c>
       <c r="M36" t="n">
-        <v>6765.95</v>
+        <v>6791.25</v>
       </c>
       <c r="N36" t="n">
-        <v>5764.6</v>
+        <v>5786.9</v>
       </c>
     </row>
     <row r="37">
@@ -5139,7 +5323,7 @@
         <v>46091.16666666666</v>
       </c>
       <c r="B37" t="n">
-        <v>8805.6</v>
+        <v>8214.299999999999</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -5160,40 +5344,40 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1.161165</v>
+        <v>1.154265</v>
       </c>
       <c r="D38" t="n">
-        <v>1.341995</v>
+        <v>1.338255</v>
       </c>
       <c r="E38" t="n">
-        <v>7998.1</v>
+        <v>7976.9</v>
       </c>
       <c r="F38" t="n">
-        <v>23812.8</v>
+        <v>23465.2</v>
       </c>
       <c r="G38" t="n">
-        <v>47746.5</v>
+        <v>47030.3</v>
       </c>
       <c r="H38" t="n">
-        <v>10385.4</v>
+        <v>10272.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25946.7</v>
+        <v>25634.7</v>
       </c>
       <c r="J38" t="n">
-        <v>24991.9</v>
+        <v>24768.1</v>
       </c>
       <c r="K38" t="n">
-        <v>55064.4</v>
+        <v>54158</v>
       </c>
       <c r="L38" t="n">
-        <v>2552.65</v>
+        <v>2505.75</v>
       </c>
       <c r="M38" t="n">
-        <v>6792.13</v>
+        <v>6724.610000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>5787.8</v>
+        <v>5752.63</v>
       </c>
     </row>
     <row r="39">
@@ -5201,7 +5385,7 @@
         <v>46092.16666666666</v>
       </c>
       <c r="B39" t="n">
-        <v>8214</v>
+        <v>9366.299999999999</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -5222,40 +5406,40 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1.154255</v>
+        <v>1.152065</v>
       </c>
       <c r="D40" t="n">
-        <v>1.338185</v>
+        <v>1.335115</v>
       </c>
       <c r="E40" t="n">
-        <v>7977.3</v>
+        <v>7964.5</v>
       </c>
       <c r="F40" t="n">
-        <v>23466.3</v>
+        <v>23495</v>
       </c>
       <c r="G40" t="n">
-        <v>47199.39999999999</v>
+        <v>46739.9</v>
       </c>
       <c r="H40" t="n">
-        <v>10272.5</v>
+        <v>10283.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25635.2</v>
+        <v>25453.6</v>
       </c>
       <c r="J40" t="n">
-        <v>24768</v>
+        <v>24514</v>
       </c>
       <c r="K40" t="n">
-        <v>54153</v>
+        <v>53462.2</v>
       </c>
       <c r="L40" t="n">
-        <v>2506.45</v>
+        <v>2490.95</v>
       </c>
       <c r="M40" t="n">
-        <v>6724.49</v>
+        <v>6676.01</v>
       </c>
       <c r="N40" t="n">
-        <v>5752.93</v>
+        <v>5725.3</v>
       </c>
     </row>
     <row r="41">
@@ -5263,7 +5447,7 @@
         <v>46093.16666666666</v>
       </c>
       <c r="B41" t="n">
-        <v>9365.799999999999</v>
+        <v>9468.4</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -5284,40 +5468,40 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.152075</v>
+        <v>1.141665</v>
       </c>
       <c r="D42" t="n">
-        <v>1.335135</v>
+        <v>1.32235</v>
       </c>
       <c r="E42" t="n">
-        <v>7964.1</v>
+        <v>7875.6</v>
       </c>
       <c r="F42" t="n">
-        <v>23493.9</v>
+        <v>23329.3</v>
       </c>
       <c r="G42" t="n">
-        <v>46740.4</v>
+        <v>46475.1</v>
       </c>
       <c r="H42" t="n">
-        <v>10283.6</v>
+        <v>10240.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25453.2</v>
+        <v>25400.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24514.1</v>
+        <v>24321.2</v>
       </c>
       <c r="K42" t="n">
-        <v>53442.2</v>
+        <v>53150.3</v>
       </c>
       <c r="L42" t="n">
-        <v>2490.75</v>
+        <v>2474.5</v>
       </c>
       <c r="M42" t="n">
-        <v>6675.76</v>
+        <v>6621.04</v>
       </c>
       <c r="N42" t="n">
-        <v>5725</v>
+        <v>5689.36</v>
       </c>
     </row>
     <row r="43">
@@ -5325,7 +5509,7 @@
         <v>46094.16666666666</v>
       </c>
       <c r="B43" t="n">
-        <v>9467.6</v>
+        <v>9766.4</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -5346,40 +5530,40 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1.14245</v>
+        <v>1.143595</v>
       </c>
       <c r="D44" t="n">
-        <v>1.32235</v>
+        <v>1.324575</v>
       </c>
       <c r="E44" t="n">
-        <v>7899.3</v>
+        <v>7919.5</v>
       </c>
       <c r="F44" t="n">
-        <v>23369.4</v>
+        <v>23428.6</v>
       </c>
       <c r="G44" t="n">
-        <v>46472</v>
+        <v>46641.8</v>
       </c>
       <c r="H44" t="n">
-        <v>10252.1</v>
+        <v>10268.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25421.2</v>
+        <v>25450.7</v>
       </c>
       <c r="J44" t="n">
-        <v>24304.8</v>
+        <v>24424</v>
       </c>
       <c r="K44" t="n">
-        <v>52934.6</v>
+        <v>53651.9</v>
       </c>
       <c r="L44" t="n">
-        <v>2472.65</v>
+        <v>2489.45</v>
       </c>
       <c r="M44" t="n">
-        <v>6618.15</v>
+        <v>6645.48</v>
       </c>
       <c r="N44" t="n">
-        <v>5699.4</v>
+        <v>5713.9</v>
       </c>
     </row>
     <row r="45">
@@ -5387,7 +5571,7 @@
         <v>46096.16666666666</v>
       </c>
       <c r="B45" t="n">
-        <v>9994.9</v>
+        <v>9778.700000000001</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -5408,40 +5592,40 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1.143575</v>
+        <v>1.149815</v>
       </c>
       <c r="D46" t="n">
-        <v>1.324585</v>
+        <v>1.331215</v>
       </c>
       <c r="E46" t="n">
-        <v>7919.2</v>
+        <v>7949</v>
       </c>
       <c r="F46" t="n">
-        <v>23429.7</v>
+        <v>23625.4</v>
       </c>
       <c r="G46" t="n">
-        <v>46642.3</v>
+        <v>46926.7</v>
       </c>
       <c r="H46" t="n">
-        <v>10268.7</v>
+        <v>10347</v>
       </c>
       <c r="I46" t="n">
-        <v>25450.6</v>
+        <v>25861.7</v>
       </c>
       <c r="J46" t="n">
-        <v>24424.7</v>
+        <v>24652</v>
       </c>
       <c r="K46" t="n">
-        <v>53659.4</v>
+        <v>54337.6</v>
       </c>
       <c r="L46" t="n">
-        <v>2489.55</v>
+        <v>2501.65</v>
       </c>
       <c r="M46" t="n">
-        <v>6645.73</v>
+        <v>6698.12</v>
       </c>
       <c r="N46" t="n">
-        <v>5714.1</v>
+        <v>5754.2</v>
       </c>
     </row>
     <row r="47">
@@ -5449,7 +5633,7 @@
         <v>46097.16666666666</v>
       </c>
       <c r="B47" t="n">
-        <v>9779.1</v>
+        <v>9527.4</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -5470,40 +5654,40 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1.149825</v>
+        <v>1.153885</v>
       </c>
       <c r="D48" t="n">
-        <v>1.331205</v>
+        <v>1.33575</v>
       </c>
       <c r="E48" t="n">
-        <v>7949.3</v>
+        <v>7956.2</v>
       </c>
       <c r="F48" t="n">
-        <v>23624.3</v>
+        <v>23670.5</v>
       </c>
       <c r="G48" t="n">
-        <v>46926.2</v>
+        <v>46944.6</v>
       </c>
       <c r="H48" t="n">
-        <v>10347.1</v>
+        <v>10362.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25861.8</v>
+        <v>25859.5</v>
       </c>
       <c r="J48" t="n">
-        <v>24651.7</v>
+        <v>24775.5</v>
       </c>
       <c r="K48" t="n">
-        <v>54340.1</v>
+        <v>54274.4</v>
       </c>
       <c r="L48" t="n">
-        <v>2501.55</v>
+        <v>2517.85</v>
       </c>
       <c r="M48" t="n">
-        <v>6697.87</v>
+        <v>6711.68</v>
       </c>
       <c r="N48" t="n">
-        <v>5754</v>
+        <v>5756.4</v>
       </c>
     </row>
     <row r="49">
@@ -5511,7 +5695,7 @@
         <v>46098.16666666666</v>
       </c>
       <c r="B49" t="n">
-        <v>9527.5</v>
+        <v>9250.1</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -5532,40 +5716,40 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.153925</v>
+        <v>1.146325</v>
       </c>
       <c r="D50" t="n">
-        <v>1.33579</v>
+        <v>1.326425</v>
       </c>
       <c r="E50" t="n">
-        <v>7955.8</v>
+        <v>7897.7</v>
       </c>
       <c r="F50" t="n">
-        <v>23669.4</v>
+        <v>23169.5</v>
       </c>
       <c r="G50" t="n">
-        <v>46944.1</v>
+        <v>46157</v>
       </c>
       <c r="H50" t="n">
-        <v>10362.4</v>
+        <v>10221.1</v>
       </c>
       <c r="I50" t="n">
-        <v>25859.1</v>
+        <v>25416.9</v>
       </c>
       <c r="J50" t="n">
-        <v>24776</v>
+        <v>24395.2</v>
       </c>
       <c r="K50" t="n">
-        <v>54291.9</v>
+        <v>53599.6</v>
       </c>
       <c r="L50" t="n">
-        <v>2517.65</v>
+        <v>2474.45</v>
       </c>
       <c r="M50" t="n">
-        <v>6711.43</v>
+        <v>6698.99</v>
       </c>
       <c r="N50" t="n">
-        <v>5756.1</v>
+        <v>5655.5</v>
       </c>
     </row>
     <row r="51">
@@ -5573,7 +5757,7 @@
         <v>46099.16666666666</v>
       </c>
       <c r="B51" t="n">
-        <v>9251.700000000001</v>
+        <v>9650.299999999999</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -5594,38 +5778,38 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.146285</v>
+        <v>1.15765</v>
       </c>
       <c r="D52" t="n">
-        <v>1.326415</v>
+        <v>1.342435</v>
       </c>
       <c r="E52" t="n">
-        <v>7898.5</v>
+        <v>7842.7</v>
       </c>
       <c r="F52" t="n">
-        <v>23171.8</v>
+        <v>23019.7</v>
       </c>
       <c r="G52" t="n">
-        <v>46158</v>
+        <v>46139.2</v>
       </c>
       <c r="H52" t="n">
-        <v>10221.2</v>
+        <v>10069.6</v>
       </c>
       <c r="I52" t="n">
-        <v>25417.7</v>
+        <v>25368.8</v>
       </c>
       <c r="J52" t="n">
-        <v>24394.9</v>
+        <v>24407.7</v>
       </c>
       <c r="K52" t="n">
-        <v>53624.6</v>
+        <v>53401.2</v>
       </c>
       <c r="L52" t="n">
-        <v>2474.35</v>
+        <v>2508.55</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>5656.1</v>
+        <v>5655.4</v>
       </c>
     </row>
     <row r="53">
@@ -5633,7 +5817,7 @@
         <v>46100.16666666666</v>
       </c>
       <c r="B53" t="n">
-        <v>9653.200000000001</v>
+        <v>9386.799999999999</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -5654,40 +5838,40 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.15766</v>
+        <v>1.15709</v>
       </c>
       <c r="D54" t="n">
-        <v>1.342445</v>
+        <v>1.33411</v>
       </c>
       <c r="E54" t="n">
-        <v>7843</v>
+        <v>7613.8</v>
       </c>
       <c r="F54" t="n">
-        <v>23020.2</v>
+        <v>22214.3</v>
       </c>
       <c r="G54" t="n">
-        <v>46139.7</v>
+        <v>45803.1</v>
       </c>
       <c r="H54" t="n">
-        <v>10069.7</v>
+        <v>9839.299999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>25369.1</v>
+        <v>24770.8</v>
       </c>
       <c r="J54" t="n">
-        <v>24407.8</v>
+        <v>24000.4</v>
       </c>
       <c r="K54" t="n">
-        <v>53403.2</v>
+        <v>51317.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2508.75</v>
+        <v>2452.1</v>
       </c>
       <c r="M54" t="n">
-        <v>6619.34</v>
+        <v>6537.12</v>
       </c>
       <c r="N54" t="n">
-        <v>5655.6</v>
+        <v>5474.95</v>
       </c>
     </row>
     <row r="55">
@@ -5695,7 +5879,7 @@
         <v>46101.16666666666</v>
       </c>
       <c r="B55" t="n">
-        <v>9387.1</v>
+        <v>9792.700000000001</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -5716,40 +5900,40 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.153725</v>
+        <v>1.156245</v>
       </c>
       <c r="D56" t="n">
-        <v>1.33387</v>
+        <v>1.333395</v>
       </c>
       <c r="E56" t="n">
-        <v>7513</v>
+        <v>7540.6</v>
       </c>
       <c r="F56" t="n">
-        <v>21912.6</v>
+        <v>21975.6</v>
       </c>
       <c r="G56" t="n">
-        <v>45343.8</v>
+        <v>45538.6</v>
       </c>
       <c r="H56" t="n">
-        <v>9776</v>
+        <v>9794.1</v>
       </c>
       <c r="I56" t="n">
-        <v>24609.8</v>
+        <v>24659.3</v>
       </c>
       <c r="J56" t="n">
-        <v>23718.3</v>
+        <v>23794.4</v>
       </c>
       <c r="K56" t="n">
-        <v>50808.8</v>
+        <v>51180.5</v>
       </c>
       <c r="L56" t="n">
-        <v>2420.35</v>
+        <v>2432.65</v>
       </c>
       <c r="M56" t="n">
-        <v>6460.09</v>
+        <v>6488.5</v>
       </c>
       <c r="N56" t="n">
-        <v>5402.6</v>
+        <v>5419.6</v>
       </c>
     </row>
     <row r="57">
@@ -5757,7 +5941,7 @@
         <v>46103.16666666666</v>
       </c>
       <c r="B57" t="n">
-        <v>10008.4</v>
+        <v>9885.6</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -5778,40 +5962,40 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.156255</v>
+        <v>1.1608</v>
       </c>
       <c r="D58" t="n">
-        <v>1.333485</v>
+        <v>1.342625</v>
       </c>
       <c r="E58" t="n">
-        <v>7541.9</v>
+        <v>7798.8</v>
       </c>
       <c r="F58" t="n">
-        <v>21979.4</v>
+        <v>22845</v>
       </c>
       <c r="G58" t="n">
-        <v>45541.6</v>
+        <v>46290.6</v>
       </c>
       <c r="H58" t="n">
-        <v>9794.299999999999</v>
+        <v>9963.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24660.8</v>
+        <v>24982.7</v>
       </c>
       <c r="J58" t="n">
-        <v>23797.5</v>
+        <v>24241.8</v>
       </c>
       <c r="K58" t="n">
-        <v>51188</v>
+        <v>53018.2</v>
       </c>
       <c r="L58" t="n">
-        <v>2433.15</v>
+        <v>2500.55</v>
       </c>
       <c r="M58" t="n">
-        <v>6488.75</v>
+        <v>6594.07</v>
       </c>
       <c r="N58" t="n">
-        <v>5420.5</v>
+        <v>5617.7</v>
       </c>
     </row>
     <row r="59">
@@ -5819,7 +6003,7 @@
         <v>46104.16666666666</v>
       </c>
       <c r="B59" t="n">
-        <v>9884.4</v>
+        <v>9123.4</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -5840,40 +6024,40 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.16081</v>
+        <v>1.161345</v>
       </c>
       <c r="D60" t="n">
-        <v>1.342665</v>
+        <v>1.341485</v>
       </c>
       <c r="E60" t="n">
-        <v>7798.6</v>
+        <v>7815.7</v>
       </c>
       <c r="F60" t="n">
-        <v>22844.5</v>
+        <v>22891</v>
       </c>
       <c r="G60" t="n">
-        <v>46286.1</v>
+        <v>46448</v>
       </c>
       <c r="H60" t="n">
-        <v>9963.5</v>
+        <v>10015.3</v>
       </c>
       <c r="I60" t="n">
-        <v>24982.4</v>
+        <v>25050.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24241.5</v>
+        <v>24205</v>
       </c>
       <c r="K60" t="n">
-        <v>52995.7</v>
+        <v>53500.6</v>
       </c>
       <c r="L60" t="n">
-        <v>2500.15</v>
+        <v>2535.75</v>
       </c>
       <c r="M60" t="n">
-        <v>6593.95</v>
+        <v>6599.97</v>
       </c>
       <c r="N60" t="n">
-        <v>5617.6</v>
+        <v>5645.68</v>
       </c>
     </row>
     <row r="61">
@@ -5881,7 +6065,7 @@
         <v>46105.16666666666</v>
       </c>
       <c r="B61" t="n">
-        <v>9123.700000000001</v>
+        <v>8855.200000000001</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -5902,40 +6086,40 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.161335</v>
+        <v>1.156185</v>
       </c>
       <c r="D62" t="n">
-        <v>1.341465</v>
+        <v>1.336385</v>
       </c>
       <c r="E62" t="n">
-        <v>7815.3</v>
+        <v>7815.5</v>
       </c>
       <c r="F62" t="n">
-        <v>22889.8</v>
+        <v>22870.1</v>
       </c>
       <c r="G62" t="n">
-        <v>46448.5</v>
+        <v>46359.5</v>
       </c>
       <c r="H62" t="n">
-        <v>10015.1</v>
+        <v>10085.7</v>
       </c>
       <c r="I62" t="n">
-        <v>25050</v>
+        <v>25259.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24204.9</v>
+        <v>24114.6</v>
       </c>
       <c r="K62" t="n">
-        <v>53498.1</v>
+        <v>53878.5</v>
       </c>
       <c r="L62" t="n">
-        <v>2535.85</v>
+        <v>2530.75</v>
       </c>
       <c r="M62" t="n">
-        <v>6599.72</v>
+        <v>6581</v>
       </c>
       <c r="N62" t="n">
-        <v>5645.38</v>
+        <v>5621.51</v>
       </c>
     </row>
     <row r="63">
@@ -5943,7 +6127,7 @@
         <v>46106.16666666666</v>
       </c>
       <c r="B63" t="n">
-        <v>8856.6</v>
+        <v>9117.700000000001</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -5964,40 +6148,40 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.156175</v>
+        <v>1.153495</v>
       </c>
       <c r="D64" t="n">
-        <v>1.336365</v>
+        <v>1.333415</v>
       </c>
       <c r="E64" t="n">
-        <v>7815.9</v>
+        <v>7780.5</v>
       </c>
       <c r="F64" t="n">
-        <v>22871.3</v>
+        <v>22692.5</v>
       </c>
       <c r="G64" t="n">
-        <v>46358.7</v>
+        <v>46181.1</v>
       </c>
       <c r="H64" t="n">
-        <v>10085.8</v>
+        <v>9965.799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>25259.7</v>
+        <v>24768.8</v>
       </c>
       <c r="J64" t="n">
-        <v>24114.4</v>
+        <v>23682.7</v>
       </c>
       <c r="K64" t="n">
-        <v>53886</v>
+        <v>52923.6</v>
       </c>
       <c r="L64" t="n">
-        <v>2530.85</v>
+        <v>2508.55</v>
       </c>
       <c r="M64" t="n">
-        <v>6581.25</v>
+        <v>6506.25</v>
       </c>
       <c r="N64" t="n">
-        <v>5621.81</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="65">
@@ -6005,7 +6189,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B65" t="n">
-        <v>9118.1</v>
+        <v>9274.799999999999</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -6026,40 +6210,40 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.15342</v>
+        <v>1.15097</v>
       </c>
       <c r="D66" t="n">
-        <v>1.333305</v>
+        <v>1.3264</v>
       </c>
       <c r="E66" t="n">
-        <v>7780.9</v>
+        <v>7646.4</v>
       </c>
       <c r="F66" t="n">
-        <v>22693.7</v>
+        <v>22101.1</v>
       </c>
       <c r="G66" t="n">
-        <v>46185</v>
+        <v>45061.5</v>
       </c>
       <c r="H66" t="n">
-        <v>9966</v>
+        <v>9895.299999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24769.2</v>
+        <v>24627.5</v>
       </c>
       <c r="J66" t="n">
-        <v>23682.9</v>
+        <v>23069.6</v>
       </c>
       <c r="K66" t="n">
-        <v>52941.1</v>
+        <v>51137.7</v>
       </c>
       <c r="L66" t="n">
-        <v>2508.75</v>
+        <v>2443.2</v>
       </c>
       <c r="M66" t="n">
-        <v>6506.5</v>
+        <v>6355.25</v>
       </c>
       <c r="N66" t="n">
-        <v>5573.3</v>
+        <v>5455.22</v>
       </c>
     </row>
     <row r="67">
@@ -6067,7 +6251,7 @@
         <v>46108.16666666666</v>
       </c>
       <c r="B67" t="n">
-        <v>9273.9</v>
+        <v>9977.299999999999</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -6088,40 +6272,40 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.15081</v>
+        <v>1.148835</v>
       </c>
       <c r="D68" t="n">
-        <v>1.32634</v>
+        <v>1.323875</v>
       </c>
       <c r="E68" t="n">
-        <v>7623.5</v>
+        <v>7618.7</v>
       </c>
       <c r="F68" t="n">
-        <v>22033.7</v>
+        <v>22031.4</v>
       </c>
       <c r="G68" t="n">
-        <v>44942.8</v>
+        <v>44945.6</v>
       </c>
       <c r="H68" t="n">
-        <v>9881.700000000001</v>
+        <v>9879.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24599.6</v>
+        <v>24593.4</v>
       </c>
       <c r="J68" t="n">
-        <v>23006</v>
+        <v>23027.2</v>
       </c>
       <c r="K68" t="n">
-        <v>50871.5</v>
+        <v>50609</v>
       </c>
       <c r="L68" t="n">
-        <v>2435.15</v>
+        <v>2430.85</v>
       </c>
       <c r="M68" t="n">
-        <v>6337.22</v>
+        <v>6340.21</v>
       </c>
       <c r="N68" t="n">
-        <v>5438.9</v>
+        <v>5435.4</v>
       </c>
     </row>
     <row r="69">
@@ -6129,7 +6313,7 @@
         <v>46110.20833333334</v>
       </c>
       <c r="B69" t="n">
-        <v>10049.7</v>
+        <v>9976.4</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -6150,40 +6334,40 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1.148845</v>
+        <v>1.145975</v>
       </c>
       <c r="D70" t="n">
-        <v>1.323865</v>
+        <v>1.317995</v>
       </c>
       <c r="E70" t="n">
-        <v>7618.6</v>
+        <v>7722.7</v>
       </c>
       <c r="F70" t="n">
-        <v>22030.8</v>
+        <v>22434.6</v>
       </c>
       <c r="G70" t="n">
-        <v>44943.2</v>
+        <v>45225.5</v>
       </c>
       <c r="H70" t="n">
-        <v>9879.299999999999</v>
+        <v>10070.4</v>
       </c>
       <c r="I70" t="n">
-        <v>24593.1</v>
+        <v>24724.4</v>
       </c>
       <c r="J70" t="n">
-        <v>23027</v>
+        <v>22920.3</v>
       </c>
       <c r="K70" t="n">
-        <v>50611.5</v>
+        <v>51054.8</v>
       </c>
       <c r="L70" t="n">
-        <v>2430.65</v>
+        <v>2409.85</v>
       </c>
       <c r="M70" t="n">
-        <v>6340.08</v>
+        <v>6341.38</v>
       </c>
       <c r="N70" t="n">
-        <v>5435.2</v>
+        <v>5500.9</v>
       </c>
     </row>
     <row r="71">
@@ -6191,7 +6375,7 @@
         <v>46111.20833333334</v>
       </c>
       <c r="B71" t="n">
-        <v>9975.9</v>
+        <v>10068.9</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -6212,40 +6396,40 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.145925</v>
+        <v>1.155875</v>
       </c>
       <c r="D72" t="n">
-        <v>1.317965</v>
+        <v>1.323055</v>
       </c>
       <c r="E72" t="n">
-        <v>7722.4</v>
+        <v>7921.4</v>
       </c>
       <c r="F72" t="n">
-        <v>22434.1</v>
+        <v>23026.2</v>
       </c>
       <c r="G72" t="n">
-        <v>45226</v>
+        <v>46230.95</v>
       </c>
       <c r="H72" t="n">
-        <v>10070.3</v>
+        <v>10279.9</v>
       </c>
       <c r="I72" t="n">
-        <v>24724.2</v>
+        <v>25317.1</v>
       </c>
       <c r="J72" t="n">
-        <v>22920</v>
+        <v>23777.1</v>
       </c>
       <c r="K72" t="n">
-        <v>51049.8</v>
+        <v>53050.8</v>
       </c>
       <c r="L72" t="n">
-        <v>2409.75</v>
+        <v>2494.15</v>
       </c>
       <c r="M72" t="n">
-        <v>6341.26</v>
+        <v>6530.15</v>
       </c>
       <c r="N72" t="n">
-        <v>5500.7</v>
+        <v>5653.5</v>
       </c>
     </row>
     <row r="73">
@@ -6253,7 +6437,7 @@
         <v>46112.20833333334</v>
       </c>
       <c r="B73" t="n">
-        <v>10068.6</v>
+        <v>9969.1</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -6274,40 +6458,40 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1.155885</v>
+        <v>1.159095</v>
       </c>
       <c r="D74" t="n">
-        <v>1.32306</v>
+        <v>1.330625</v>
       </c>
       <c r="E74" t="n">
-        <v>7921</v>
+        <v>7976.6</v>
       </c>
       <c r="F74" t="n">
-        <v>23025</v>
+        <v>23289</v>
       </c>
       <c r="G74" t="n">
-        <v>46313.4</v>
+        <v>46561.8</v>
       </c>
       <c r="H74" t="n">
-        <v>10279.8</v>
+        <v>10416.2</v>
       </c>
       <c r="I74" t="n">
-        <v>25316.6</v>
+        <v>25315.3</v>
       </c>
       <c r="J74" t="n">
-        <v>23775.3</v>
+        <v>23996.1</v>
       </c>
       <c r="K74" t="n">
-        <v>53025.8</v>
+        <v>54233.9</v>
       </c>
       <c r="L74" t="n">
-        <v>2494.05</v>
+        <v>2510.15</v>
       </c>
       <c r="M74" t="n">
-        <v>6529.9</v>
+        <v>6572.13</v>
       </c>
       <c r="N74" t="n">
-        <v>5653.2</v>
+        <v>5720.9</v>
       </c>
     </row>
     <row r="75">
@@ -6315,7 +6499,7 @@
         <v>46113.20833333334</v>
       </c>
       <c r="B75" t="n">
-        <v>9968.9</v>
+        <v>10095.1</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -6336,40 +6520,40 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1.159125</v>
+        <v>1.154015</v>
       </c>
       <c r="D76" t="n">
-        <v>1.33069</v>
+        <v>1.322585</v>
       </c>
       <c r="E76" t="n">
-        <v>7977.1</v>
+        <v>7990.9</v>
       </c>
       <c r="F76" t="n">
-        <v>23290.2</v>
+        <v>23217.6</v>
       </c>
       <c r="G76" t="n">
-        <v>46564.3</v>
+        <v>46522.4</v>
       </c>
       <c r="H76" t="n">
-        <v>10416.3</v>
+        <v>10451.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25315.7</v>
+        <v>25270.4</v>
       </c>
       <c r="J76" t="n">
-        <v>23997.5</v>
+        <v>24030.5</v>
       </c>
       <c r="K76" t="n">
-        <v>54235.3</v>
+        <v>53247.5</v>
       </c>
       <c r="L76" t="n">
-        <v>2510.35</v>
+        <v>2530.55</v>
       </c>
       <c r="M76" t="n">
-        <v>6572.38</v>
+        <v>6583.360000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>5721.2</v>
+        <v>5701.47</v>
       </c>
     </row>
     <row r="77">
@@ -6377,7 +6561,7 @@
         <v>46114.20833333334</v>
       </c>
       <c r="B77" t="n">
-        <v>10094.8</v>
+        <v>10581</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -6398,40 +6582,40 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.154005</v>
+        <v>1.15187</v>
       </c>
       <c r="D78" t="n">
-        <v>1.322595</v>
+        <v>1.320465</v>
       </c>
       <c r="E78" t="n">
-        <v>7991</v>
+        <v>7960.4</v>
       </c>
       <c r="F78" t="n">
-        <v>23218.1</v>
+        <v>23127.3</v>
       </c>
       <c r="G78" t="n">
-        <v>46522.1</v>
+        <v>46407.7</v>
       </c>
       <c r="H78" t="n">
-        <v>10451.7</v>
+        <v>10432</v>
       </c>
       <c r="I78" t="n">
-        <v>25270.6</v>
+        <v>25188.7</v>
       </c>
       <c r="J78" t="n">
-        <v>24030.1</v>
+        <v>23957.4</v>
       </c>
       <c r="K78" t="n">
-        <v>53243.7</v>
+        <v>53165.2</v>
       </c>
       <c r="L78" t="n">
-        <v>2530.45</v>
+        <v>2519.65</v>
       </c>
       <c r="M78" t="n">
-        <v>6583.43</v>
+        <v>6563.67</v>
       </c>
       <c r="N78" t="n">
-        <v>5701.57</v>
+        <v>5679.77</v>
       </c>
     </row>
     <row r="79">
@@ -6442,34 +6626,34 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>7931.5</v>
+        <v>7934.5</v>
       </c>
       <c r="F79" t="n">
-        <v>23043.8</v>
+        <v>23052.9</v>
       </c>
       <c r="G79" t="n">
-        <v>46240.7</v>
+        <v>46258.3</v>
       </c>
       <c r="H79" t="n">
-        <v>10414.5</v>
+        <v>10416.4</v>
       </c>
       <c r="I79" t="n">
-        <v>25149.7</v>
+        <v>25153.9</v>
       </c>
       <c r="J79" t="n">
-        <v>23893</v>
+        <v>23907.8</v>
       </c>
       <c r="K79" t="n">
-        <v>53059.2</v>
+        <v>52872.6</v>
       </c>
       <c r="L79" t="n">
-        <v>2508.95</v>
+        <v>2510.85</v>
       </c>
       <c r="M79" t="n">
-        <v>6541.72</v>
+        <v>6547.57</v>
       </c>
       <c r="N79" t="n">
-        <v>5659.6</v>
+        <v>5661.8</v>
       </c>
     </row>
     <row r="80">
@@ -6477,7 +6661,7 @@
         <v>46117.20833333334</v>
       </c>
       <c r="B80" t="n">
-        <v>10542.1</v>
+        <v>10420.3</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -6498,40 +6682,40 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1.151625</v>
+        <v>1.154265</v>
       </c>
       <c r="D81" t="n">
-        <v>1.319585</v>
+        <v>1.323355</v>
       </c>
       <c r="E81" t="n">
-        <v>7934.6</v>
+        <v>8026.1</v>
       </c>
       <c r="F81" t="n">
-        <v>23053.5</v>
+        <v>23295.1</v>
       </c>
       <c r="G81" t="n">
-        <v>46257.8</v>
+        <v>46709.5</v>
       </c>
       <c r="H81" t="n">
-        <v>10416.5</v>
+        <v>10477.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25154.1</v>
+        <v>25312</v>
       </c>
       <c r="J81" t="n">
-        <v>23908.4</v>
+        <v>24134.7</v>
       </c>
       <c r="K81" t="n">
-        <v>52875.1</v>
+        <v>53883.7</v>
       </c>
       <c r="L81" t="n">
-        <v>2510.95</v>
+        <v>2536.65</v>
       </c>
       <c r="M81" t="n">
-        <v>6547.7</v>
+        <v>6603.96</v>
       </c>
       <c r="N81" t="n">
-        <v>5662</v>
+        <v>5727.1</v>
       </c>
     </row>
     <row r="82">
@@ -6539,7 +6723,7 @@
         <v>46118.20833333334</v>
       </c>
       <c r="B82" t="n">
-        <v>10421</v>
+        <v>10675.7</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -6560,40 +6744,40 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1.154235</v>
+        <v>1.166825</v>
       </c>
       <c r="D83" t="n">
-        <v>1.323335</v>
+        <v>1.337355</v>
       </c>
       <c r="E83" t="n">
-        <v>8026.3</v>
+        <v>8193.700000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>23295.6</v>
+        <v>23802.3</v>
       </c>
       <c r="G83" t="n">
-        <v>46712</v>
+        <v>47545.8</v>
       </c>
       <c r="H83" t="n">
-        <v>10477.7</v>
+        <v>10557.1</v>
       </c>
       <c r="I83" t="n">
-        <v>25312.2</v>
+        <v>25620.5</v>
       </c>
       <c r="J83" t="n">
-        <v>24134.8</v>
+        <v>24748.9</v>
       </c>
       <c r="K83" t="n">
-        <v>53882.5</v>
+        <v>55942.4</v>
       </c>
       <c r="L83" t="n">
-        <v>2536.45</v>
+        <v>2623.75</v>
       </c>
       <c r="M83" t="n">
-        <v>6604.09</v>
+        <v>6752.42</v>
       </c>
       <c r="N83" t="n">
-        <v>5727.2</v>
+        <v>5845.7</v>
       </c>
     </row>
     <row r="84">
@@ -6601,7 +6785,7 @@
         <v>46119.20833333334</v>
       </c>
       <c r="B84" t="n">
-        <v>10675.9</v>
+        <v>9110.700000000001</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -6622,40 +6806,40 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1.16686</v>
+        <v>1.166275</v>
       </c>
       <c r="D85" t="n">
-        <v>1.337415</v>
+        <v>1.339785</v>
       </c>
       <c r="E85" t="n">
-        <v>8193.6</v>
+        <v>8274.200000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>23801.8</v>
+        <v>24005.2</v>
       </c>
       <c r="G85" t="n">
-        <v>47546.3</v>
+        <v>47886.5</v>
       </c>
       <c r="H85" t="n">
-        <v>10557</v>
+        <v>10659.2</v>
       </c>
       <c r="I85" t="n">
-        <v>25620.3</v>
+        <v>25877.5</v>
       </c>
       <c r="J85" t="n">
-        <v>24748.8</v>
+        <v>24864</v>
       </c>
       <c r="K85" t="n">
-        <v>55944</v>
+        <v>56750.7</v>
       </c>
       <c r="L85" t="n">
-        <v>2623.35</v>
+        <v>2621.15</v>
       </c>
       <c r="M85" t="n">
-        <v>6752.54</v>
+        <v>6775.84</v>
       </c>
       <c r="N85" t="n">
-        <v>5845.6</v>
+        <v>5913.6</v>
       </c>
     </row>
     <row r="86">
@@ -6663,7 +6847,7 @@
         <v>46120.20833333334</v>
       </c>
       <c r="B86" t="n">
-        <v>9110.5</v>
+        <v>9245.299999999999</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -6684,40 +6868,40 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.166245</v>
+        <v>1.169405</v>
       </c>
       <c r="D87" t="n">
-        <v>1.339775</v>
+        <v>1.342805</v>
       </c>
       <c r="E87" t="n">
-        <v>8273.9</v>
+        <v>8252.299999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>24005.1</v>
+        <v>23860.1</v>
       </c>
       <c r="G87" t="n">
-        <v>47885.9</v>
+        <v>48155.1</v>
       </c>
       <c r="H87" t="n">
-        <v>10659</v>
+        <v>10594.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25877.4</v>
+        <v>25916.1</v>
       </c>
       <c r="J87" t="n">
-        <v>24863.4</v>
+        <v>25042.9</v>
       </c>
       <c r="K87" t="n">
-        <v>56735.7</v>
+        <v>56487.1</v>
       </c>
       <c r="L87" t="n">
-        <v>2621.05</v>
+        <v>2635.65</v>
       </c>
       <c r="M87" t="n">
-        <v>6775.83</v>
+        <v>6816.9</v>
       </c>
       <c r="N87" t="n">
-        <v>5913.4</v>
+        <v>5900.9</v>
       </c>
     </row>
     <row r="88">
@@ -6725,7 +6909,7 @@
         <v>46121.20833333334</v>
       </c>
       <c r="B88" t="n">
-        <v>9244.799999999999</v>
+        <v>9242.700000000001</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -6746,40 +6930,40 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.169385</v>
+        <v>1.1726</v>
       </c>
       <c r="D89" t="n">
-        <v>1.342795</v>
+        <v>1.346235</v>
       </c>
       <c r="E89" t="n">
-        <v>8252.5</v>
+        <v>8266.799999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>23860.6</v>
+        <v>23823.9</v>
       </c>
       <c r="G89" t="n">
-        <v>48155.6</v>
+        <v>47972</v>
       </c>
       <c r="H89" t="n">
-        <v>10595</v>
+        <v>10605.1</v>
       </c>
       <c r="I89" t="n">
-        <v>25916.3</v>
+        <v>25948.9</v>
       </c>
       <c r="J89" t="n">
-        <v>25043.1</v>
+        <v>25164.7</v>
       </c>
       <c r="K89" t="n">
-        <v>56495.2</v>
+        <v>57406.8</v>
       </c>
       <c r="L89" t="n">
-        <v>2635.55</v>
+        <v>2636.3</v>
       </c>
       <c r="M89" t="n">
-        <v>6817.02</v>
+        <v>6825.55</v>
       </c>
       <c r="N89" t="n">
-        <v>5901</v>
+        <v>5928.91</v>
       </c>
     </row>
     <row r="90">
@@ -6787,7 +6971,7 @@
         <v>46122.20833333334</v>
       </c>
       <c r="B90" t="n">
-        <v>9243</v>
+        <v>9114.700000000001</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -6808,40 +6992,40 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.1676</v>
+        <v>1.167255</v>
       </c>
       <c r="D91" t="n">
-        <v>1.34652</v>
+        <v>1.339455</v>
       </c>
       <c r="E91" t="n">
-        <v>8147</v>
+        <v>8130.9</v>
       </c>
       <c r="F91" t="n">
-        <v>23474</v>
+        <v>23438.1</v>
       </c>
       <c r="G91" t="n">
-        <v>47455.9</v>
+        <v>47403</v>
       </c>
       <c r="H91" t="n">
-        <v>10530.4</v>
+        <v>10523</v>
       </c>
       <c r="I91" t="n">
-        <v>25787.6</v>
+        <v>25770.2</v>
       </c>
       <c r="J91" t="n">
-        <v>24777</v>
+        <v>24791.8</v>
       </c>
       <c r="K91" t="n">
-        <v>56086.6</v>
+        <v>56085.5</v>
       </c>
       <c r="L91" t="n">
-        <v>2592.45</v>
+        <v>2587.85</v>
       </c>
       <c r="M91" t="n">
-        <v>6743.52</v>
+        <v>6740.55</v>
       </c>
       <c r="N91" t="n">
-        <v>5843.5</v>
+        <v>5831.8</v>
       </c>
     </row>
     <row r="92">
@@ -6849,7 +7033,7 @@
         <v>46124.20833333334</v>
       </c>
       <c r="B92" t="n">
-        <v>9660.4</v>
+        <v>9809.4</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -6870,40 +7054,40 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.167225</v>
+        <v>1.176135</v>
       </c>
       <c r="D93" t="n">
-        <v>1.339425</v>
+        <v>1.351065</v>
       </c>
       <c r="E93" t="n">
-        <v>8130.6</v>
+        <v>8268.299999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>23437.6</v>
+        <v>23965.5</v>
       </c>
       <c r="G93" t="n">
-        <v>47402.5</v>
+        <v>48227.7</v>
       </c>
       <c r="H93" t="n">
-        <v>10522.9</v>
+        <v>10617.9</v>
       </c>
       <c r="I93" t="n">
-        <v>25770</v>
+        <v>25968.2</v>
       </c>
       <c r="J93" t="n">
-        <v>24791.7</v>
+        <v>25435.7</v>
       </c>
       <c r="K93" t="n">
-        <v>56100.3</v>
+        <v>57698.9</v>
       </c>
       <c r="L93" t="n">
-        <v>2587.75</v>
+        <v>2678.15</v>
       </c>
       <c r="M93" t="n">
-        <v>6740.42</v>
+        <v>6890.15</v>
       </c>
       <c r="N93" t="n">
-        <v>5831.6</v>
+        <v>5947.3</v>
       </c>
     </row>
     <row r="94">
@@ -6911,7 +7095,7 @@
         <v>46125.20833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>9809.9</v>
+        <v>9266.200000000001</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -6932,40 +7116,40 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.176105</v>
+        <v>1.179485</v>
       </c>
       <c r="D95" t="n">
-        <v>1.351055</v>
+        <v>1.356875</v>
       </c>
       <c r="E95" t="n">
-        <v>8268.4</v>
+        <v>8326.9</v>
       </c>
       <c r="F95" t="n">
-        <v>23966.1</v>
+        <v>24054.9</v>
       </c>
       <c r="G95" t="n">
-        <v>48228.3</v>
+        <v>48537.7</v>
       </c>
       <c r="H95" t="n">
-        <v>10618</v>
+        <v>10624.6</v>
       </c>
       <c r="I95" t="n">
-        <v>25968.4</v>
+        <v>26212.7</v>
       </c>
       <c r="J95" t="n">
-        <v>25435.8</v>
+        <v>25830.8</v>
       </c>
       <c r="K95" t="n">
-        <v>57701.4</v>
+        <v>58706</v>
       </c>
       <c r="L95" t="n">
-        <v>2678.25</v>
+        <v>2705.55</v>
       </c>
       <c r="M95" t="n">
-        <v>6890.22</v>
+        <v>6967.77</v>
       </c>
       <c r="N95" t="n">
-        <v>5947.4</v>
+        <v>5986.4</v>
       </c>
     </row>
     <row r="96">
@@ -6973,7 +7157,7 @@
         <v>46126.20833333334</v>
       </c>
       <c r="B96" t="n">
-        <v>9266.6</v>
+        <v>8869</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -6994,40 +7178,40 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.179485</v>
+        <v>1.180235</v>
       </c>
       <c r="D97" t="n">
-        <v>1.356865</v>
+        <v>1.356785</v>
       </c>
       <c r="E97" t="n">
-        <v>8327</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>24055.4</v>
+        <v>24107.1</v>
       </c>
       <c r="G97" t="n">
-        <v>48538.2</v>
+        <v>48527.8</v>
       </c>
       <c r="H97" t="n">
-        <v>10624.7</v>
+        <v>10556.1</v>
       </c>
       <c r="I97" t="n">
-        <v>26212.9</v>
+        <v>26130.4</v>
       </c>
       <c r="J97" t="n">
-        <v>25830.9</v>
+        <v>26229.3</v>
       </c>
       <c r="K97" t="n">
-        <v>58703.5</v>
+        <v>58563.8</v>
       </c>
       <c r="L97" t="n">
-        <v>2705.65</v>
+        <v>2716.35</v>
       </c>
       <c r="M97" t="n">
-        <v>6967.84</v>
+        <v>7028.29</v>
       </c>
       <c r="N97" t="n">
-        <v>5986.5</v>
+        <v>5946.9</v>
       </c>
     </row>
     <row r="98">
@@ -7035,7 +7219,7 @@
         <v>46127.20833333334</v>
       </c>
       <c r="B98" t="n">
-        <v>8869.299999999999</v>
+        <v>8868.4</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -7056,40 +7240,40 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.180245</v>
+        <v>1.178545</v>
       </c>
       <c r="D99" t="n">
-        <v>1.356845</v>
+        <v>1.353215</v>
       </c>
       <c r="E99" t="n">
-        <v>8264.700000000001</v>
+        <v>8266.4</v>
       </c>
       <c r="F99" t="n">
-        <v>24107.7</v>
+        <v>24140.9</v>
       </c>
       <c r="G99" t="n">
-        <v>48526.8</v>
+        <v>48661.1</v>
       </c>
       <c r="H99" t="n">
-        <v>10556</v>
+        <v>10590.9</v>
       </c>
       <c r="I99" t="n">
-        <v>26130.7</v>
+        <v>26236.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26229.9</v>
+        <v>26321.7</v>
       </c>
       <c r="K99" t="n">
-        <v>58576.3</v>
+        <v>59430.4</v>
       </c>
       <c r="L99" t="n">
-        <v>2716.45</v>
+        <v>2725.15</v>
       </c>
       <c r="M99" t="n">
-        <v>7028.42</v>
+        <v>7046.74</v>
       </c>
       <c r="N99" t="n">
-        <v>5947.1</v>
+        <v>5920.67</v>
       </c>
     </row>
     <row r="100">
@@ -7097,7 +7281,7 @@
         <v>46128.20833333334</v>
       </c>
       <c r="B100" t="n">
-        <v>8868.1</v>
+        <v>9030.200000000001</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -7118,40 +7302,40 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.178535</v>
+        <v>1.176345</v>
       </c>
       <c r="D101" t="n">
-        <v>1.353225</v>
+        <v>1.351615</v>
       </c>
       <c r="E101" t="n">
-        <v>8266.200000000001</v>
+        <v>8407.9</v>
       </c>
       <c r="F101" t="n">
-        <v>24139.8</v>
+        <v>24651.9</v>
       </c>
       <c r="G101" t="n">
-        <v>48661.6</v>
+        <v>49453</v>
       </c>
       <c r="H101" t="n">
-        <v>10590.7</v>
+        <v>10697.9</v>
       </c>
       <c r="I101" t="n">
-        <v>26235.9</v>
+        <v>26504.1</v>
       </c>
       <c r="J101" t="n">
-        <v>26321.6</v>
+        <v>26684.1</v>
       </c>
       <c r="K101" t="n">
-        <v>59431</v>
+        <v>59693.4</v>
       </c>
       <c r="L101" t="n">
-        <v>2725.05</v>
+        <v>2777.8</v>
       </c>
       <c r="M101" t="n">
-        <v>7046.58</v>
+        <v>7126.42</v>
       </c>
       <c r="N101" t="n">
-        <v>5920.47</v>
+        <v>6036.51</v>
       </c>
     </row>
     <row r="102">
@@ -7159,7 +7343,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B102" t="n">
-        <v>9031.1</v>
+        <v>8417.5</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -7180,23 +7364,23 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.17366</v>
+        <v>1.173945</v>
       </c>
       <c r="D103" t="n">
-        <v>1.35162</v>
+        <v>1.348705</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>10619.4</v>
+        <v>10633.2</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>7062.22</v>
+        <v>7073.76</v>
       </c>
       <c r="N103" t="inlineStr"/>
     </row>
@@ -7205,7 +7389,7 @@
         <v>46131.20833333334</v>
       </c>
       <c r="B104" t="n">
-        <v>9006.299999999999</v>
+        <v>8910.9</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -7226,23 +7410,23 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.173945</v>
+        <v>1.179005</v>
       </c>
       <c r="D105" t="n">
-        <v>1.348665</v>
+        <v>1.353895</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>10633.3</v>
+        <v>10627.6</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>7073.88</v>
+        <v>7121.9</v>
       </c>
       <c r="N105" t="inlineStr"/>
     </row>
@@ -7251,7 +7435,7 @@
         <v>46132.20833333334</v>
       </c>
       <c r="B106" t="n">
-        <v>8910.4</v>
+        <v>8670.9</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -7272,23 +7456,23 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.179025</v>
+        <v>1.173925</v>
       </c>
       <c r="D107" t="n">
-        <v>1.353905</v>
+        <v>1.350235</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>10627.5</v>
+        <v>10466.5</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>7121.77</v>
+        <v>7088.99</v>
       </c>
       <c r="N107" t="inlineStr"/>
     </row>
@@ -7297,7 +7481,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B108" t="n">
-        <v>8669.9</v>
+        <v>8926.9</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -7318,23 +7502,23 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>1.173935</v>
+        <v>1.170595</v>
       </c>
       <c r="D109" t="n">
-        <v>1.350255</v>
+        <v>1.350215</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>10466.6</v>
+        <v>10460.2</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>7089.07</v>
+        <v>7127.22</v>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
@@ -7343,7 +7527,7 @@
         <v>46134.20833333334</v>
       </c>
       <c r="B110" t="n">
-        <v>8926.9</v>
+        <v>9453.1</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -7364,23 +7548,23 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1.170605</v>
+        <v>1.168635</v>
       </c>
       <c r="D111" t="n">
-        <v>1.350245</v>
+        <v>1.346735</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10460.3</v>
+        <v>10417.5</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>7127.34</v>
+        <v>7114.23</v>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
@@ -7389,7 +7573,7 @@
         <v>46135.20833333334</v>
       </c>
       <c r="B112" t="n">
-        <v>9453.6</v>
+        <v>9661.1</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -7410,23 +7594,23 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1.168645</v>
+        <v>1.171835</v>
       </c>
       <c r="D113" t="n">
-        <v>1.346725</v>
+        <v>1.353095</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>10417.3</v>
+        <v>10387.5</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>7114.110000000001</v>
+        <v>7163.69</v>
       </c>
       <c r="N113" t="inlineStr"/>
     </row>
@@ -7435,7 +7619,7 @@
         <v>46136.20833333334</v>
       </c>
       <c r="B114" t="n">
-        <v>9660.1</v>
+        <v>9486.799999999999</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -7456,23 +7640,23 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1.17021</v>
+        <v>1.170825</v>
       </c>
       <c r="D115" t="n">
-        <v>1.35339</v>
+        <v>1.351595</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>10372.1</v>
+        <v>10370.5</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>7156.71</v>
+        <v>7151.27</v>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
@@ -7481,7 +7665,7 @@
         <v>46138.20833333334</v>
       </c>
       <c r="B116" t="n">
-        <v>9544.4</v>
+        <v>9529.1</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -7502,23 +7686,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.170835</v>
+        <v>1.172205</v>
       </c>
       <c r="D117" t="n">
-        <v>1.351595</v>
+        <v>1.353575</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10370.6</v>
+        <v>10332.5</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7151.34</v>
+        <v>7185.95</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -7527,7 +7711,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9530.299999999999</v>
+        <v>9761.9</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -7542,6 +7726,190 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>1.171585</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.352145</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>10311.6</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>7145.37</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46140.20833333334</v>
+      </c>
+      <c r="B120" t="n">
+        <v>9931.1</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>1.167825</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.348005</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>10207.5</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>7154.82</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46141.20833333334</v>
+      </c>
+      <c r="B122" t="n">
+        <v>10911.8</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>1.173185</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.360455</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>10363.4</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>7220.52</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46142.20833333334</v>
+      </c>
+      <c r="B124" t="n">
+        <v>10551.4</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>1.171725</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.357075</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>10351</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>7218.93</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46143.20833333334</v>
+      </c>
+      <c r="B126" t="n">
+        <v>10259.4</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7553,7 +7921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7629,10 +7997,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.178815</v>
+        <v>1.18506</v>
       </c>
       <c r="D2" t="n">
-        <v>1.349475</v>
+        <v>1.356285</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -7643,7 +8011,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6878.96</v>
+        <v>6834.59</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -7652,7 +8020,7 @@
         <v>46071.20833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>6521.200000000001</v>
+        <v>6248.200000000001</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -7673,40 +8041,40 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.17686</v>
+        <v>1.178825</v>
       </c>
       <c r="D4" t="n">
-        <v>1.345965</v>
+        <v>1.349495</v>
       </c>
       <c r="E4" t="n">
-        <v>8417.9</v>
+        <v>8424.9</v>
       </c>
       <c r="F4" t="n">
-        <v>25033.6</v>
+        <v>25234.3</v>
       </c>
       <c r="G4" t="n">
-        <v>49410</v>
+        <v>49646.3</v>
       </c>
       <c r="H4" t="n">
-        <v>10670.2</v>
+        <v>10679.1</v>
       </c>
       <c r="I4" t="n">
-        <v>26796.7</v>
+        <v>26847.6</v>
       </c>
       <c r="J4" t="n">
-        <v>24817.3</v>
+        <v>24896.8</v>
       </c>
       <c r="K4" t="n">
-        <v>57084.2</v>
+        <v>57517.5</v>
       </c>
       <c r="L4" t="n">
-        <v>2661.95</v>
+        <v>2656.25</v>
       </c>
       <c r="M4" t="n">
-        <v>6865.84</v>
+        <v>6879.21</v>
       </c>
       <c r="N4" t="n">
-        <v>6065.4</v>
+        <v>6097.6</v>
       </c>
     </row>
     <row r="5">
@@ -7714,7 +8082,7 @@
         <v>46072.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>6672.200000000001</v>
+        <v>6522.200000000001</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -7735,40 +8103,40 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.17822</v>
+        <v>1.17689</v>
       </c>
       <c r="D6" t="n">
-        <v>1.348245</v>
+        <v>1.345955</v>
       </c>
       <c r="E6" t="n">
-        <v>8535.4</v>
+        <v>8418.1</v>
       </c>
       <c r="F6" t="n">
-        <v>25236.6</v>
+        <v>25034.1</v>
       </c>
       <c r="G6" t="n">
-        <v>49624.8</v>
+        <v>49410.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10720.4</v>
+        <v>10670.3</v>
       </c>
       <c r="I6" t="n">
-        <v>26863.4</v>
+        <v>26796.9</v>
       </c>
       <c r="J6" t="n">
-        <v>25016.2</v>
+        <v>24817.5</v>
       </c>
       <c r="K6" t="n">
-        <v>57088.3</v>
+        <v>57086.7</v>
       </c>
       <c r="L6" t="n">
-        <v>2662.2</v>
+        <v>2662.05</v>
       </c>
       <c r="M6" t="n">
-        <v>6910.63</v>
+        <v>6865.97</v>
       </c>
       <c r="N6" t="n">
-        <v>6135.1</v>
+        <v>6065.5</v>
       </c>
     </row>
     <row r="7">
@@ -7776,7 +8144,7 @@
         <v>46073.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>6630.200000000001</v>
+        <v>6672.200000000001</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -7797,40 +8165,40 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.18331</v>
+        <v>1.179725</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353205</v>
+        <v>1.349105</v>
       </c>
       <c r="E8" t="n">
-        <v>8515.200000000001</v>
+        <v>8526.200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>25176</v>
+        <v>25208.9</v>
       </c>
       <c r="G8" t="n">
-        <v>49528.4</v>
+        <v>49576.3</v>
       </c>
       <c r="H8" t="n">
-        <v>10703.4</v>
+        <v>10712.6</v>
       </c>
       <c r="I8" t="n">
-        <v>26826.4</v>
+        <v>26846.7</v>
       </c>
       <c r="J8" t="n">
-        <v>24911.3</v>
+        <v>24973.5</v>
       </c>
       <c r="K8" t="n">
-        <v>56981.6</v>
+        <v>57079</v>
       </c>
       <c r="L8" t="n">
-        <v>2652.65</v>
+        <v>2656.55</v>
       </c>
       <c r="M8" t="n">
-        <v>6892.28</v>
+        <v>6903.7</v>
       </c>
       <c r="N8" t="n">
-        <v>6120.4</v>
+        <v>6128.4</v>
       </c>
     </row>
     <row r="9">
@@ -7838,7 +8206,7 @@
         <v>46075.20833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>6557.700000000001</v>
+        <v>6573.9</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -7859,40 +8227,40 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.179325</v>
+        <v>1.1833</v>
       </c>
       <c r="D10" t="n">
-        <v>1.349555</v>
+        <v>1.353215</v>
       </c>
       <c r="E10" t="n">
-        <v>8506.6</v>
+        <v>8515.1</v>
       </c>
       <c r="F10" t="n">
-        <v>24996.5</v>
+        <v>25175.6</v>
       </c>
       <c r="G10" t="n">
-        <v>48839.5</v>
+        <v>49528.9</v>
       </c>
       <c r="H10" t="n">
-        <v>10692.7</v>
+        <v>10703.3</v>
       </c>
       <c r="I10" t="n">
-        <v>26891.9</v>
+        <v>26826.2</v>
       </c>
       <c r="J10" t="n">
-        <v>24735.3</v>
+        <v>24910.7</v>
       </c>
       <c r="K10" t="n">
-        <v>56665.8</v>
+        <v>56979.1</v>
       </c>
       <c r="L10" t="n">
-        <v>2621.45</v>
+        <v>2652.45</v>
       </c>
       <c r="M10" t="n">
-        <v>6844.309999999999</v>
+        <v>6892.15</v>
       </c>
       <c r="N10" t="n">
-        <v>6123.3</v>
+        <v>6120.3</v>
       </c>
     </row>
     <row r="11">
@@ -7900,7 +8268,7 @@
         <v>46076.20833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>6676.299999999999</v>
+        <v>6557.799999999999</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -7921,40 +8289,40 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.17743</v>
+        <v>1.179315</v>
       </c>
       <c r="D12" t="n">
-        <v>1.349605</v>
+        <v>1.349545</v>
       </c>
       <c r="E12" t="n">
-        <v>8539.9</v>
+        <v>8506.5</v>
       </c>
       <c r="F12" t="n">
-        <v>25039.3</v>
+        <v>24996.1</v>
       </c>
       <c r="G12" t="n">
-        <v>49177.5</v>
+        <v>48840</v>
       </c>
       <c r="H12" t="n">
-        <v>10712.4</v>
+        <v>10692.6</v>
       </c>
       <c r="I12" t="n">
-        <v>26766.2</v>
+        <v>26891.6</v>
       </c>
       <c r="J12" t="n">
-        <v>24995.3</v>
+        <v>24735.1</v>
       </c>
       <c r="K12" t="n">
-        <v>57912</v>
+        <v>56693.3</v>
       </c>
       <c r="L12" t="n">
-        <v>2651.55</v>
+        <v>2621.75</v>
       </c>
       <c r="M12" t="n">
-        <v>6892.08</v>
+        <v>6844.559999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>6136.1</v>
+        <v>6123.2</v>
       </c>
     </row>
     <row r="13">
@@ -7962,7 +8330,7 @@
         <v>46077.20833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>6598.9</v>
+        <v>6675.299999999999</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -7983,40 +8351,40 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.18154</v>
+        <v>1.17746</v>
       </c>
       <c r="D14" t="n">
-        <v>1.355805</v>
+        <v>1.349615</v>
       </c>
       <c r="E14" t="n">
-        <v>8569.6</v>
+        <v>8539.799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>25181.3</v>
+        <v>25038.9</v>
       </c>
       <c r="G14" t="n">
-        <v>49392</v>
+        <v>49176.5</v>
       </c>
       <c r="H14" t="n">
-        <v>10804.4</v>
+        <v>10712.3</v>
       </c>
       <c r="I14" t="n">
-        <v>26950</v>
+        <v>26766</v>
       </c>
       <c r="J14" t="n">
-        <v>25270</v>
+        <v>24995</v>
       </c>
       <c r="K14" t="n">
-        <v>59285.1</v>
+        <v>57919.5</v>
       </c>
       <c r="L14" t="n">
-        <v>2660.65</v>
+        <v>2651.45</v>
       </c>
       <c r="M14" t="n">
-        <v>6937.66</v>
+        <v>6891.95</v>
       </c>
       <c r="N14" t="n">
-        <v>6175.7</v>
+        <v>6136</v>
       </c>
     </row>
     <row r="15">
@@ -8024,7 +8392,7 @@
         <v>46078.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>6556.6</v>
+        <v>6599.1</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -8045,40 +8413,40 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.180365</v>
+        <v>1.18153</v>
       </c>
       <c r="D16" t="n">
-        <v>1.349155</v>
+        <v>1.355835</v>
       </c>
       <c r="E16" t="n">
-        <v>8611.700000000001</v>
+        <v>8569.5</v>
       </c>
       <c r="F16" t="n">
-        <v>25253.3</v>
+        <v>25180.7</v>
       </c>
       <c r="G16" t="n">
-        <v>49229.6</v>
+        <v>49392.5</v>
       </c>
       <c r="H16" t="n">
-        <v>10835.1</v>
+        <v>10804.3</v>
       </c>
       <c r="I16" t="n">
-        <v>26389.6</v>
+        <v>26949.5</v>
       </c>
       <c r="J16" t="n">
-        <v>24955.6</v>
+        <v>25270.1</v>
       </c>
       <c r="K16" t="n">
-        <v>58435</v>
+        <v>59282.6</v>
       </c>
       <c r="L16" t="n">
-        <v>2655.55</v>
+        <v>2660.95</v>
       </c>
       <c r="M16" t="n">
-        <v>6882.360000000001</v>
+        <v>6937.41</v>
       </c>
       <c r="N16" t="n">
-        <v>6150.7</v>
+        <v>6175.6</v>
       </c>
     </row>
     <row r="17">
@@ -8086,7 +8454,7 @@
         <v>46079.20833333334</v>
       </c>
       <c r="B17" t="n">
-        <v>6531.799999999999</v>
+        <v>6556.700000000001</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -8107,40 +8475,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.18179</v>
+        <v>1.180345</v>
       </c>
       <c r="D18" t="n">
-        <v>1.34806</v>
+        <v>1.349145</v>
       </c>
       <c r="E18" t="n">
-        <v>8530.6</v>
+        <v>8611.299999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>25143.7</v>
+        <v>25252.1</v>
       </c>
       <c r="G18" t="n">
-        <v>48858.5</v>
+        <v>49229.1</v>
       </c>
       <c r="H18" t="n">
-        <v>10862.7</v>
+        <v>10834.9</v>
       </c>
       <c r="I18" t="n">
-        <v>26490.4</v>
+        <v>26389</v>
       </c>
       <c r="J18" t="n">
-        <v>24914.4</v>
+        <v>24955.4</v>
       </c>
       <c r="K18" t="n">
-        <v>58612.7</v>
+        <v>58385</v>
       </c>
       <c r="L18" t="n">
-        <v>2626.65</v>
+        <v>2655.45</v>
       </c>
       <c r="M18" t="n">
-        <v>6865.58</v>
+        <v>6881.99</v>
       </c>
       <c r="N18" t="n">
-        <v>6095.38</v>
+        <v>6150.4</v>
       </c>
     </row>
     <row r="19">
@@ -8148,7 +8516,7 @@
         <v>46080.20833333334</v>
       </c>
       <c r="B19" t="n">
-        <v>6725.5</v>
+        <v>6531.700000000001</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -8169,40 +8537,40 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1.17594</v>
+        <v>1.176735</v>
       </c>
       <c r="D20" t="n">
-        <v>1.340525</v>
+        <v>1.34183</v>
       </c>
       <c r="E20" t="n">
-        <v>8466.4</v>
+        <v>8470.9</v>
       </c>
       <c r="F20" t="n">
-        <v>24946.3</v>
+        <v>24967.8</v>
       </c>
       <c r="G20" t="n">
-        <v>48368.8</v>
+        <v>48514.6</v>
       </c>
       <c r="H20" t="n">
-        <v>10811.6</v>
+        <v>10810.3</v>
       </c>
       <c r="I20" t="n">
-        <v>26350.6</v>
+        <v>26383</v>
       </c>
       <c r="J20" t="n">
-        <v>24696.7</v>
+        <v>24680.4</v>
       </c>
       <c r="K20" t="n">
-        <v>57488.1</v>
+        <v>57705.8</v>
       </c>
       <c r="L20" t="n">
-        <v>2591.25</v>
+        <v>2605.05</v>
       </c>
       <c r="M20" t="n">
-        <v>6805.95</v>
+        <v>6817.17</v>
       </c>
       <c r="N20" t="n">
-        <v>6049.58</v>
+        <v>6052.78</v>
       </c>
     </row>
     <row r="21">
@@ -8210,7 +8578,7 @@
         <v>46082.20833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>7100.799999999999</v>
+        <v>7359.799999999999</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -8231,40 +8599,40 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.169435</v>
+        <v>1.17591</v>
       </c>
       <c r="D22" t="n">
-        <v>1.340815</v>
+        <v>1.340465</v>
       </c>
       <c r="E22" t="n">
-        <v>8387.700000000001</v>
+        <v>8466.6</v>
       </c>
       <c r="F22" t="n">
-        <v>24582.2</v>
+        <v>24947.2</v>
       </c>
       <c r="G22" t="n">
-        <v>48823.6</v>
+        <v>48369.8</v>
       </c>
       <c r="H22" t="n">
-        <v>10789.5</v>
+        <v>10811.7</v>
       </c>
       <c r="I22" t="n">
-        <v>26156.8</v>
+        <v>26351.1</v>
       </c>
       <c r="J22" t="n">
-        <v>24935.3</v>
+        <v>24696.9</v>
       </c>
       <c r="K22" t="n">
-        <v>57713.1</v>
+        <v>57483.1</v>
       </c>
       <c r="L22" t="n">
-        <v>2650.85</v>
+        <v>2591.15</v>
       </c>
       <c r="M22" t="n">
-        <v>6867.940000000001</v>
+        <v>6806.2</v>
       </c>
       <c r="N22" t="n">
-        <v>5982.2</v>
+        <v>6049.78</v>
       </c>
     </row>
     <row r="23">
@@ -8272,7 +8640,7 @@
         <v>46083.20833333334</v>
       </c>
       <c r="B23" t="n">
-        <v>7242.4</v>
+        <v>7101.6</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -8293,40 +8661,40 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1.1611</v>
+        <v>1.169445</v>
       </c>
       <c r="D24" t="n">
-        <v>1.335115</v>
+        <v>1.340805</v>
       </c>
       <c r="E24" t="n">
-        <v>8165.4</v>
+        <v>8388</v>
       </c>
       <c r="F24" t="n">
-        <v>23985</v>
+        <v>24583</v>
       </c>
       <c r="G24" t="n">
-        <v>48413.3</v>
+        <v>48825.6</v>
       </c>
       <c r="H24" t="n">
-        <v>10517.1</v>
+        <v>10789.6</v>
       </c>
       <c r="I24" t="n">
-        <v>25468.5</v>
+        <v>26157.2</v>
       </c>
       <c r="J24" t="n">
-        <v>24668</v>
+        <v>24937</v>
       </c>
       <c r="K24" t="n">
-        <v>54951.7</v>
+        <v>57710.6</v>
       </c>
       <c r="L24" t="n">
-        <v>2603.45</v>
+        <v>2651.05</v>
       </c>
       <c r="M24" t="n">
-        <v>6802.5</v>
+        <v>6868.190000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>5813.3</v>
+        <v>5982.4</v>
       </c>
     </row>
     <row r="25">
@@ -8334,7 +8702,7 @@
         <v>46084.20833333334</v>
       </c>
       <c r="B25" t="n">
-        <v>7496.700000000001</v>
+        <v>7242.6</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -8355,40 +8723,40 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.163505</v>
+        <v>1.16112</v>
       </c>
       <c r="D26" t="n">
-        <v>1.336925</v>
+        <v>1.335135</v>
       </c>
       <c r="E26" t="n">
-        <v>8204</v>
+        <v>8166.5</v>
       </c>
       <c r="F26" t="n">
-        <v>24302.2</v>
+        <v>23985.8</v>
       </c>
       <c r="G26" t="n">
-        <v>48753.2</v>
+        <v>48412.8</v>
       </c>
       <c r="H26" t="n">
-        <v>10626.8</v>
+        <v>10517.2</v>
       </c>
       <c r="I26" t="n">
-        <v>25602.8</v>
+        <v>25468.9</v>
       </c>
       <c r="J26" t="n">
-        <v>25137.1</v>
+        <v>24667.6</v>
       </c>
       <c r="K26" t="n">
-        <v>56232.9</v>
+        <v>54976.7</v>
       </c>
       <c r="L26" t="n">
-        <v>2635.85</v>
+        <v>2603.55</v>
       </c>
       <c r="M26" t="n">
-        <v>6878.04</v>
+        <v>6802.75</v>
       </c>
       <c r="N26" t="n">
-        <v>5901.9</v>
+        <v>5813.5</v>
       </c>
     </row>
     <row r="27">
@@ -8396,7 +8764,7 @@
         <v>46085.20833333334</v>
       </c>
       <c r="B27" t="n">
-        <v>7666</v>
+        <v>7498.5</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -8417,40 +8785,40 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.16067</v>
+        <v>1.163485</v>
       </c>
       <c r="D28" t="n">
-        <v>1.335565</v>
+        <v>1.336905</v>
       </c>
       <c r="E28" t="n">
-        <v>8059.2</v>
+        <v>8203.9</v>
       </c>
       <c r="F28" t="n">
-        <v>23866.2</v>
+        <v>24301.8</v>
       </c>
       <c r="G28" t="n">
-        <v>48034</v>
+        <v>48752.7</v>
       </c>
       <c r="H28" t="n">
-        <v>10407.9</v>
+        <v>10626.7</v>
       </c>
       <c r="I28" t="n">
-        <v>25202.5</v>
+        <v>25602.6</v>
       </c>
       <c r="J28" t="n">
-        <v>25031.4</v>
+        <v>25137</v>
       </c>
       <c r="K28" t="n">
-        <v>54563.2</v>
+        <v>56215.4</v>
       </c>
       <c r="L28" t="n">
-        <v>2592.85</v>
+        <v>2635.75</v>
       </c>
       <c r="M28" t="n">
-        <v>6834.43</v>
+        <v>6877.92</v>
       </c>
       <c r="N28" t="n">
-        <v>5793.6</v>
+        <v>5901.8</v>
       </c>
     </row>
     <row r="29">
@@ -8458,7 +8826,7 @@
         <v>46086.20833333334</v>
       </c>
       <c r="B29" t="n">
-        <v>7887.5</v>
+        <v>7665.700000000001</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -8479,40 +8847,40 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1.161695</v>
+        <v>1.16068</v>
       </c>
       <c r="D30" t="n">
-        <v>1.340985</v>
+        <v>1.335575</v>
       </c>
       <c r="E30" t="n">
-        <v>8017.2</v>
+        <v>8059.4</v>
       </c>
       <c r="F30" t="n">
-        <v>23640.3</v>
+        <v>23867</v>
       </c>
       <c r="G30" t="n">
-        <v>47434.2</v>
+        <v>48032.8</v>
       </c>
       <c r="H30" t="n">
-        <v>10318.8</v>
+        <v>10408</v>
       </c>
       <c r="I30" t="n">
-        <v>25325.2</v>
+        <v>25202.9</v>
       </c>
       <c r="J30" t="n">
-        <v>24634.2</v>
+        <v>25032.3</v>
       </c>
       <c r="K30" t="n">
-        <v>54029.9</v>
+        <v>54575.7</v>
       </c>
       <c r="L30" t="n">
-        <v>2522</v>
+        <v>2592.75</v>
       </c>
       <c r="M30" t="n">
-        <v>6733.23</v>
+        <v>6834.68</v>
       </c>
       <c r="N30" t="n">
-        <v>5723.03</v>
+        <v>5793.8</v>
       </c>
     </row>
     <row r="31">
@@ -8520,7 +8888,7 @@
         <v>46087.20833333334</v>
       </c>
       <c r="B31" t="n">
-        <v>8947.799999999999</v>
+        <v>7886.9</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -8541,40 +8909,40 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.152455</v>
+        <v>1.154965</v>
       </c>
       <c r="D32" t="n">
-        <v>1.330515</v>
+        <v>1.33393</v>
       </c>
       <c r="E32" t="n">
-        <v>7873</v>
+        <v>7921.2</v>
       </c>
       <c r="F32" t="n">
-        <v>23222.3</v>
+        <v>23357.4</v>
       </c>
       <c r="G32" t="n">
-        <v>46613</v>
+        <v>46831</v>
       </c>
       <c r="H32" t="n">
-        <v>10195.8</v>
+        <v>10244.7</v>
       </c>
       <c r="I32" t="n">
-        <v>25042.2</v>
+        <v>25160.3</v>
       </c>
       <c r="J32" t="n">
-        <v>24187.4</v>
+        <v>24403</v>
       </c>
       <c r="K32" t="n">
-        <v>52216.5</v>
+        <v>53227.3</v>
       </c>
       <c r="L32" t="n">
-        <v>2433.35</v>
+        <v>2493.15</v>
       </c>
       <c r="M32" t="n">
-        <v>6622.45</v>
+        <v>6678.34</v>
       </c>
       <c r="N32" t="n">
-        <v>5615.9</v>
+        <v>5654.6</v>
       </c>
     </row>
     <row r="33">
@@ -8582,7 +8950,7 @@
         <v>46089.20833333334</v>
       </c>
       <c r="B33" t="n">
-        <v>11228.6</v>
+        <v>9555</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -8603,40 +8971,40 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.161615</v>
+        <v>1.1524</v>
       </c>
       <c r="D34" t="n">
-        <v>1.342445</v>
+        <v>1.330495</v>
       </c>
       <c r="E34" t="n">
-        <v>8000.3</v>
+        <v>7872.9</v>
       </c>
       <c r="F34" t="n">
-        <v>23703.1</v>
+        <v>23221.9</v>
       </c>
       <c r="G34" t="n">
-        <v>47534.3</v>
+        <v>46616</v>
       </c>
       <c r="H34" t="n">
-        <v>10307.8</v>
+        <v>10195.7</v>
       </c>
       <c r="I34" t="n">
-        <v>25545.7</v>
+        <v>25042</v>
       </c>
       <c r="J34" t="n">
-        <v>24854.1</v>
+        <v>24187.3</v>
       </c>
       <c r="K34" t="n">
-        <v>54259.6</v>
+        <v>52231.5</v>
       </c>
       <c r="L34" t="n">
-        <v>2534.05</v>
+        <v>2433.75</v>
       </c>
       <c r="M34" t="n">
-        <v>6766.07</v>
+        <v>6623.07</v>
       </c>
       <c r="N34" t="n">
-        <v>5764.7</v>
+        <v>5615.8</v>
       </c>
     </row>
     <row r="35">
@@ -8644,7 +9012,7 @@
         <v>46090.16666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>8805.4</v>
+        <v>11229.7</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -8665,40 +9033,40 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.161195</v>
+        <v>1.161575</v>
       </c>
       <c r="D36" t="n">
-        <v>1.341985</v>
+        <v>1.342415</v>
       </c>
       <c r="E36" t="n">
-        <v>7996.9</v>
+        <v>8000.2</v>
       </c>
       <c r="F36" t="n">
-        <v>23809.1</v>
+        <v>23702.6</v>
       </c>
       <c r="G36" t="n">
-        <v>47744.5</v>
+        <v>47534.8</v>
       </c>
       <c r="H36" t="n">
-        <v>10385.1</v>
+        <v>10307.7</v>
       </c>
       <c r="I36" t="n">
-        <v>25945.2</v>
+        <v>25545.5</v>
       </c>
       <c r="J36" t="n">
-        <v>24990.4</v>
+        <v>24854</v>
       </c>
       <c r="K36" t="n">
-        <v>55066.9</v>
+        <v>54251.3</v>
       </c>
       <c r="L36" t="n">
-        <v>2552.05</v>
+        <v>2534.15</v>
       </c>
       <c r="M36" t="n">
-        <v>6791.25</v>
+        <v>6765.95</v>
       </c>
       <c r="N36" t="n">
-        <v>5786.9</v>
+        <v>5764.6</v>
       </c>
     </row>
     <row r="37">
@@ -8706,7 +9074,7 @@
         <v>46091.16666666666</v>
       </c>
       <c r="B37" t="n">
-        <v>8214.299999999999</v>
+        <v>8805.6</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -8727,40 +9095,40 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1.154265</v>
+        <v>1.161165</v>
       </c>
       <c r="D38" t="n">
-        <v>1.338255</v>
+        <v>1.341995</v>
       </c>
       <c r="E38" t="n">
-        <v>7976.9</v>
+        <v>7998.1</v>
       </c>
       <c r="F38" t="n">
-        <v>23465.2</v>
+        <v>23812.8</v>
       </c>
       <c r="G38" t="n">
-        <v>47030.3</v>
+        <v>47746.5</v>
       </c>
       <c r="H38" t="n">
-        <v>10272.4</v>
+        <v>10385.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25634.7</v>
+        <v>25946.7</v>
       </c>
       <c r="J38" t="n">
-        <v>24768.1</v>
+        <v>24991.9</v>
       </c>
       <c r="K38" t="n">
-        <v>54158</v>
+        <v>55064.4</v>
       </c>
       <c r="L38" t="n">
-        <v>2505.75</v>
+        <v>2552.65</v>
       </c>
       <c r="M38" t="n">
-        <v>6724.610000000001</v>
+        <v>6792.13</v>
       </c>
       <c r="N38" t="n">
-        <v>5752.63</v>
+        <v>5787.8</v>
       </c>
     </row>
     <row r="39">
@@ -8768,7 +9136,7 @@
         <v>46092.16666666666</v>
       </c>
       <c r="B39" t="n">
-        <v>9366.299999999999</v>
+        <v>8214</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -8789,40 +9157,40 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1.152065</v>
+        <v>1.154255</v>
       </c>
       <c r="D40" t="n">
-        <v>1.335115</v>
+        <v>1.338185</v>
       </c>
       <c r="E40" t="n">
-        <v>7964.5</v>
+        <v>7977.3</v>
       </c>
       <c r="F40" t="n">
-        <v>23495</v>
+        <v>23466.3</v>
       </c>
       <c r="G40" t="n">
-        <v>46739.9</v>
+        <v>47199.39999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>10283.7</v>
+        <v>10272.5</v>
       </c>
       <c r="I40" t="n">
-        <v>25453.6</v>
+        <v>25635.2</v>
       </c>
       <c r="J40" t="n">
-        <v>24514</v>
+        <v>24768</v>
       </c>
       <c r="K40" t="n">
-        <v>53462.2</v>
+        <v>54153</v>
       </c>
       <c r="L40" t="n">
-        <v>2490.95</v>
+        <v>2506.45</v>
       </c>
       <c r="M40" t="n">
-        <v>6676.01</v>
+        <v>6724.49</v>
       </c>
       <c r="N40" t="n">
-        <v>5725.3</v>
+        <v>5752.93</v>
       </c>
     </row>
     <row r="41">
@@ -8830,7 +9198,7 @@
         <v>46093.16666666666</v>
       </c>
       <c r="B41" t="n">
-        <v>9468.4</v>
+        <v>9365.799999999999</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -8851,40 +9219,40 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.141665</v>
+        <v>1.152075</v>
       </c>
       <c r="D42" t="n">
-        <v>1.32235</v>
+        <v>1.335135</v>
       </c>
       <c r="E42" t="n">
-        <v>7875.6</v>
+        <v>7964.1</v>
       </c>
       <c r="F42" t="n">
-        <v>23329.3</v>
+        <v>23493.9</v>
       </c>
       <c r="G42" t="n">
-        <v>46475.1</v>
+        <v>46740.4</v>
       </c>
       <c r="H42" t="n">
-        <v>10240.1</v>
+        <v>10283.6</v>
       </c>
       <c r="I42" t="n">
-        <v>25400.4</v>
+        <v>25453.2</v>
       </c>
       <c r="J42" t="n">
-        <v>24321.2</v>
+        <v>24514.1</v>
       </c>
       <c r="K42" t="n">
-        <v>53150.3</v>
+        <v>53442.2</v>
       </c>
       <c r="L42" t="n">
-        <v>2474.5</v>
+        <v>2490.75</v>
       </c>
       <c r="M42" t="n">
-        <v>6621.04</v>
+        <v>6675.76</v>
       </c>
       <c r="N42" t="n">
-        <v>5689.36</v>
+        <v>5725</v>
       </c>
     </row>
     <row r="43">
@@ -8892,7 +9260,7 @@
         <v>46094.16666666666</v>
       </c>
       <c r="B43" t="n">
-        <v>9766.4</v>
+        <v>9467.6</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -8913,40 +9281,40 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1.143595</v>
+        <v>1.14245</v>
       </c>
       <c r="D44" t="n">
-        <v>1.324575</v>
+        <v>1.32235</v>
       </c>
       <c r="E44" t="n">
-        <v>7919.5</v>
+        <v>7899.3</v>
       </c>
       <c r="F44" t="n">
-        <v>23428.6</v>
+        <v>23369.4</v>
       </c>
       <c r="G44" t="n">
-        <v>46641.8</v>
+        <v>46472</v>
       </c>
       <c r="H44" t="n">
-        <v>10268.8</v>
+        <v>10252.1</v>
       </c>
       <c r="I44" t="n">
-        <v>25450.7</v>
+        <v>25421.2</v>
       </c>
       <c r="J44" t="n">
-        <v>24424</v>
+        <v>24304.8</v>
       </c>
       <c r="K44" t="n">
-        <v>53651.9</v>
+        <v>52934.6</v>
       </c>
       <c r="L44" t="n">
-        <v>2489.45</v>
+        <v>2472.65</v>
       </c>
       <c r="M44" t="n">
-        <v>6645.48</v>
+        <v>6618.15</v>
       </c>
       <c r="N44" t="n">
-        <v>5713.9</v>
+        <v>5699.4</v>
       </c>
     </row>
     <row r="45">
@@ -8954,7 +9322,7 @@
         <v>46096.16666666666</v>
       </c>
       <c r="B45" t="n">
-        <v>9778.700000000001</v>
+        <v>9994.9</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -8975,40 +9343,40 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1.149815</v>
+        <v>1.143575</v>
       </c>
       <c r="D46" t="n">
-        <v>1.331215</v>
+        <v>1.324585</v>
       </c>
       <c r="E46" t="n">
-        <v>7949</v>
+        <v>7919.2</v>
       </c>
       <c r="F46" t="n">
-        <v>23625.4</v>
+        <v>23429.7</v>
       </c>
       <c r="G46" t="n">
-        <v>46926.7</v>
+        <v>46642.3</v>
       </c>
       <c r="H46" t="n">
-        <v>10347</v>
+        <v>10268.7</v>
       </c>
       <c r="I46" t="n">
-        <v>25861.7</v>
+        <v>25450.6</v>
       </c>
       <c r="J46" t="n">
-        <v>24652</v>
+        <v>24424.7</v>
       </c>
       <c r="K46" t="n">
-        <v>54337.6</v>
+        <v>53659.4</v>
       </c>
       <c r="L46" t="n">
-        <v>2501.65</v>
+        <v>2489.55</v>
       </c>
       <c r="M46" t="n">
-        <v>6698.12</v>
+        <v>6645.73</v>
       </c>
       <c r="N46" t="n">
-        <v>5754.2</v>
+        <v>5714.1</v>
       </c>
     </row>
     <row r="47">
@@ -9016,7 +9384,7 @@
         <v>46097.16666666666</v>
       </c>
       <c r="B47" t="n">
-        <v>9527.4</v>
+        <v>9779.1</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -9037,40 +9405,40 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1.153885</v>
+        <v>1.149825</v>
       </c>
       <c r="D48" t="n">
-        <v>1.33575</v>
+        <v>1.331205</v>
       </c>
       <c r="E48" t="n">
-        <v>7956.2</v>
+        <v>7949.3</v>
       </c>
       <c r="F48" t="n">
-        <v>23670.5</v>
+        <v>23624.3</v>
       </c>
       <c r="G48" t="n">
-        <v>46944.6</v>
+        <v>46926.2</v>
       </c>
       <c r="H48" t="n">
-        <v>10362.5</v>
+        <v>10347.1</v>
       </c>
       <c r="I48" t="n">
-        <v>25859.5</v>
+        <v>25861.8</v>
       </c>
       <c r="J48" t="n">
-        <v>24775.5</v>
+        <v>24651.7</v>
       </c>
       <c r="K48" t="n">
-        <v>54274.4</v>
+        <v>54340.1</v>
       </c>
       <c r="L48" t="n">
-        <v>2517.85</v>
+        <v>2501.55</v>
       </c>
       <c r="M48" t="n">
-        <v>6711.68</v>
+        <v>6697.87</v>
       </c>
       <c r="N48" t="n">
-        <v>5756.4</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="49">
@@ -9078,7 +9446,7 @@
         <v>46098.16666666666</v>
       </c>
       <c r="B49" t="n">
-        <v>9250.1</v>
+        <v>9527.5</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -9099,40 +9467,40 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.146325</v>
+        <v>1.153925</v>
       </c>
       <c r="D50" t="n">
-        <v>1.326425</v>
+        <v>1.33579</v>
       </c>
       <c r="E50" t="n">
-        <v>7897.7</v>
+        <v>7955.8</v>
       </c>
       <c r="F50" t="n">
-        <v>23169.5</v>
+        <v>23669.4</v>
       </c>
       <c r="G50" t="n">
-        <v>46157</v>
+        <v>46944.1</v>
       </c>
       <c r="H50" t="n">
-        <v>10221.1</v>
+        <v>10362.4</v>
       </c>
       <c r="I50" t="n">
-        <v>25416.9</v>
+        <v>25859.1</v>
       </c>
       <c r="J50" t="n">
-        <v>24395.2</v>
+        <v>24776</v>
       </c>
       <c r="K50" t="n">
-        <v>53599.6</v>
+        <v>54291.9</v>
       </c>
       <c r="L50" t="n">
-        <v>2474.45</v>
+        <v>2517.65</v>
       </c>
       <c r="M50" t="n">
-        <v>6698.99</v>
+        <v>6711.43</v>
       </c>
       <c r="N50" t="n">
-        <v>5655.5</v>
+        <v>5756.1</v>
       </c>
     </row>
     <row r="51">
@@ -9140,7 +9508,7 @@
         <v>46099.16666666666</v>
       </c>
       <c r="B51" t="n">
-        <v>9650.299999999999</v>
+        <v>9251.700000000001</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -9161,38 +9529,38 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.15765</v>
+        <v>1.146285</v>
       </c>
       <c r="D52" t="n">
-        <v>1.342435</v>
+        <v>1.326415</v>
       </c>
       <c r="E52" t="n">
-        <v>7842.7</v>
+        <v>7898.5</v>
       </c>
       <c r="F52" t="n">
-        <v>23019.7</v>
+        <v>23171.8</v>
       </c>
       <c r="G52" t="n">
-        <v>46139.2</v>
+        <v>46158</v>
       </c>
       <c r="H52" t="n">
-        <v>10069.6</v>
+        <v>10221.2</v>
       </c>
       <c r="I52" t="n">
-        <v>25368.8</v>
+        <v>25417.7</v>
       </c>
       <c r="J52" t="n">
-        <v>24407.7</v>
+        <v>24394.9</v>
       </c>
       <c r="K52" t="n">
-        <v>53401.2</v>
+        <v>53624.6</v>
       </c>
       <c r="L52" t="n">
-        <v>2508.55</v>
+        <v>2474.35</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>5655.4</v>
+        <v>5656.1</v>
       </c>
     </row>
     <row r="53">
@@ -9200,7 +9568,7 @@
         <v>46100.16666666666</v>
       </c>
       <c r="B53" t="n">
-        <v>9386.799999999999</v>
+        <v>9653.200000000001</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -9221,40 +9589,40 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.15709</v>
+        <v>1.15766</v>
       </c>
       <c r="D54" t="n">
-        <v>1.33411</v>
+        <v>1.342445</v>
       </c>
       <c r="E54" t="n">
-        <v>7613.8</v>
+        <v>7843</v>
       </c>
       <c r="F54" t="n">
-        <v>22214.3</v>
+        <v>23020.2</v>
       </c>
       <c r="G54" t="n">
-        <v>45803.1</v>
+        <v>46139.7</v>
       </c>
       <c r="H54" t="n">
-        <v>9839.299999999999</v>
+        <v>10069.7</v>
       </c>
       <c r="I54" t="n">
-        <v>24770.8</v>
+        <v>25369.1</v>
       </c>
       <c r="J54" t="n">
-        <v>24000.4</v>
+        <v>24407.8</v>
       </c>
       <c r="K54" t="n">
-        <v>51317.2</v>
+        <v>53403.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2452.1</v>
+        <v>2508.75</v>
       </c>
       <c r="M54" t="n">
-        <v>6537.12</v>
+        <v>6619.34</v>
       </c>
       <c r="N54" t="n">
-        <v>5474.95</v>
+        <v>5655.6</v>
       </c>
     </row>
     <row r="55">
@@ -9262,7 +9630,7 @@
         <v>46101.16666666666</v>
       </c>
       <c r="B55" t="n">
-        <v>9792.700000000001</v>
+        <v>9387.1</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -9283,40 +9651,40 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.156245</v>
+        <v>1.153725</v>
       </c>
       <c r="D56" t="n">
-        <v>1.333395</v>
+        <v>1.33387</v>
       </c>
       <c r="E56" t="n">
-        <v>7540.6</v>
+        <v>7513</v>
       </c>
       <c r="F56" t="n">
-        <v>21975.6</v>
+        <v>21912.6</v>
       </c>
       <c r="G56" t="n">
-        <v>45538.6</v>
+        <v>45343.8</v>
       </c>
       <c r="H56" t="n">
-        <v>9794.1</v>
+        <v>9776</v>
       </c>
       <c r="I56" t="n">
-        <v>24659.3</v>
+        <v>24609.8</v>
       </c>
       <c r="J56" t="n">
-        <v>23794.4</v>
+        <v>23718.3</v>
       </c>
       <c r="K56" t="n">
-        <v>51180.5</v>
+        <v>50808.8</v>
       </c>
       <c r="L56" t="n">
-        <v>2432.65</v>
+        <v>2420.35</v>
       </c>
       <c r="M56" t="n">
-        <v>6488.5</v>
+        <v>6460.09</v>
       </c>
       <c r="N56" t="n">
-        <v>5419.6</v>
+        <v>5402.6</v>
       </c>
     </row>
     <row r="57">
@@ -9324,7 +9692,7 @@
         <v>46103.16666666666</v>
       </c>
       <c r="B57" t="n">
-        <v>9885.6</v>
+        <v>10008.4</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -9345,40 +9713,40 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.1608</v>
+        <v>1.156255</v>
       </c>
       <c r="D58" t="n">
-        <v>1.342625</v>
+        <v>1.333485</v>
       </c>
       <c r="E58" t="n">
-        <v>7798.8</v>
+        <v>7541.9</v>
       </c>
       <c r="F58" t="n">
-        <v>22845</v>
+        <v>21979.4</v>
       </c>
       <c r="G58" t="n">
-        <v>46290.6</v>
+        <v>45541.6</v>
       </c>
       <c r="H58" t="n">
-        <v>9963.6</v>
+        <v>9794.299999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>24982.7</v>
+        <v>24660.8</v>
       </c>
       <c r="J58" t="n">
-        <v>24241.8</v>
+        <v>23797.5</v>
       </c>
       <c r="K58" t="n">
-        <v>53018.2</v>
+        <v>51188</v>
       </c>
       <c r="L58" t="n">
-        <v>2500.55</v>
+        <v>2433.15</v>
       </c>
       <c r="M58" t="n">
-        <v>6594.07</v>
+        <v>6488.75</v>
       </c>
       <c r="N58" t="n">
-        <v>5617.7</v>
+        <v>5420.5</v>
       </c>
     </row>
     <row r="59">
@@ -9386,7 +9754,7 @@
         <v>46104.16666666666</v>
       </c>
       <c r="B59" t="n">
-        <v>9123.4</v>
+        <v>9884.4</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -9407,40 +9775,40 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.161345</v>
+        <v>1.16081</v>
       </c>
       <c r="D60" t="n">
-        <v>1.341485</v>
+        <v>1.342665</v>
       </c>
       <c r="E60" t="n">
-        <v>7815.7</v>
+        <v>7798.6</v>
       </c>
       <c r="F60" t="n">
-        <v>22891</v>
+        <v>22844.5</v>
       </c>
       <c r="G60" t="n">
-        <v>46448</v>
+        <v>46286.1</v>
       </c>
       <c r="H60" t="n">
-        <v>10015.3</v>
+        <v>9963.5</v>
       </c>
       <c r="I60" t="n">
-        <v>25050.4</v>
+        <v>24982.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24205</v>
+        <v>24241.5</v>
       </c>
       <c r="K60" t="n">
-        <v>53500.6</v>
+        <v>52995.7</v>
       </c>
       <c r="L60" t="n">
-        <v>2535.75</v>
+        <v>2500.15</v>
       </c>
       <c r="M60" t="n">
-        <v>6599.97</v>
+        <v>6593.95</v>
       </c>
       <c r="N60" t="n">
-        <v>5645.68</v>
+        <v>5617.6</v>
       </c>
     </row>
     <row r="61">
@@ -9448,7 +9816,7 @@
         <v>46105.16666666666</v>
       </c>
       <c r="B61" t="n">
-        <v>8855.200000000001</v>
+        <v>9123.700000000001</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -9469,40 +9837,40 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.156185</v>
+        <v>1.161335</v>
       </c>
       <c r="D62" t="n">
-        <v>1.336385</v>
+        <v>1.341465</v>
       </c>
       <c r="E62" t="n">
-        <v>7815.5</v>
+        <v>7815.3</v>
       </c>
       <c r="F62" t="n">
-        <v>22870.1</v>
+        <v>22889.8</v>
       </c>
       <c r="G62" t="n">
-        <v>46359.5</v>
+        <v>46448.5</v>
       </c>
       <c r="H62" t="n">
-        <v>10085.7</v>
+        <v>10015.1</v>
       </c>
       <c r="I62" t="n">
-        <v>25259.3</v>
+        <v>25050</v>
       </c>
       <c r="J62" t="n">
-        <v>24114.6</v>
+        <v>24204.9</v>
       </c>
       <c r="K62" t="n">
-        <v>53878.5</v>
+        <v>53498.1</v>
       </c>
       <c r="L62" t="n">
-        <v>2530.75</v>
+        <v>2535.85</v>
       </c>
       <c r="M62" t="n">
-        <v>6581</v>
+        <v>6599.72</v>
       </c>
       <c r="N62" t="n">
-        <v>5621.51</v>
+        <v>5645.38</v>
       </c>
     </row>
     <row r="63">
@@ -9510,7 +9878,7 @@
         <v>46106.16666666666</v>
       </c>
       <c r="B63" t="n">
-        <v>9117.700000000001</v>
+        <v>8856.6</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -9531,40 +9899,40 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.153495</v>
+        <v>1.156175</v>
       </c>
       <c r="D64" t="n">
-        <v>1.333415</v>
+        <v>1.336365</v>
       </c>
       <c r="E64" t="n">
-        <v>7780.5</v>
+        <v>7815.9</v>
       </c>
       <c r="F64" t="n">
-        <v>22692.5</v>
+        <v>22871.3</v>
       </c>
       <c r="G64" t="n">
-        <v>46181.1</v>
+        <v>46358.7</v>
       </c>
       <c r="H64" t="n">
-        <v>9965.799999999999</v>
+        <v>10085.8</v>
       </c>
       <c r="I64" t="n">
-        <v>24768.8</v>
+        <v>25259.7</v>
       </c>
       <c r="J64" t="n">
-        <v>23682.7</v>
+        <v>24114.4</v>
       </c>
       <c r="K64" t="n">
-        <v>52923.6</v>
+        <v>53886</v>
       </c>
       <c r="L64" t="n">
-        <v>2508.55</v>
+        <v>2530.85</v>
       </c>
       <c r="M64" t="n">
-        <v>6506.25</v>
+        <v>6581.25</v>
       </c>
       <c r="N64" t="n">
-        <v>5573</v>
+        <v>5621.81</v>
       </c>
     </row>
     <row r="65">
@@ -9572,7 +9940,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B65" t="n">
-        <v>9274.799999999999</v>
+        <v>9118.1</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -9593,40 +9961,40 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.15097</v>
+        <v>1.15342</v>
       </c>
       <c r="D66" t="n">
-        <v>1.3264</v>
+        <v>1.333305</v>
       </c>
       <c r="E66" t="n">
-        <v>7646.4</v>
+        <v>7780.9</v>
       </c>
       <c r="F66" t="n">
-        <v>22101.1</v>
+        <v>22693.7</v>
       </c>
       <c r="G66" t="n">
-        <v>45061.5</v>
+        <v>46185</v>
       </c>
       <c r="H66" t="n">
-        <v>9895.299999999999</v>
+        <v>9966</v>
       </c>
       <c r="I66" t="n">
-        <v>24627.5</v>
+        <v>24769.2</v>
       </c>
       <c r="J66" t="n">
-        <v>23069.6</v>
+        <v>23682.9</v>
       </c>
       <c r="K66" t="n">
-        <v>51137.7</v>
+        <v>52941.1</v>
       </c>
       <c r="L66" t="n">
-        <v>2443.2</v>
+        <v>2508.75</v>
       </c>
       <c r="M66" t="n">
-        <v>6355.25</v>
+        <v>6506.5</v>
       </c>
       <c r="N66" t="n">
-        <v>5455.22</v>
+        <v>5573.3</v>
       </c>
     </row>
     <row r="67">
@@ -9634,7 +10002,7 @@
         <v>46108.16666666666</v>
       </c>
       <c r="B67" t="n">
-        <v>9977.299999999999</v>
+        <v>9273.9</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -9655,40 +10023,40 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.148835</v>
+        <v>1.15081</v>
       </c>
       <c r="D68" t="n">
-        <v>1.323875</v>
+        <v>1.32634</v>
       </c>
       <c r="E68" t="n">
-        <v>7618.7</v>
+        <v>7623.5</v>
       </c>
       <c r="F68" t="n">
-        <v>22031.4</v>
+        <v>22033.7</v>
       </c>
       <c r="G68" t="n">
-        <v>44945.6</v>
+        <v>44942.8</v>
       </c>
       <c r="H68" t="n">
-        <v>9879.4</v>
+        <v>9881.700000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>24593.4</v>
+        <v>24599.6</v>
       </c>
       <c r="J68" t="n">
-        <v>23027.2</v>
+        <v>23006</v>
       </c>
       <c r="K68" t="n">
-        <v>50609</v>
+        <v>50871.5</v>
       </c>
       <c r="L68" t="n">
-        <v>2430.85</v>
+        <v>2435.15</v>
       </c>
       <c r="M68" t="n">
-        <v>6340.21</v>
+        <v>6337.22</v>
       </c>
       <c r="N68" t="n">
-        <v>5435.4</v>
+        <v>5438.9</v>
       </c>
     </row>
     <row r="69">
@@ -9696,7 +10064,7 @@
         <v>46110.20833333334</v>
       </c>
       <c r="B69" t="n">
-        <v>9976.4</v>
+        <v>10049.7</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -9717,40 +10085,40 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1.145975</v>
+        <v>1.148845</v>
       </c>
       <c r="D70" t="n">
-        <v>1.317995</v>
+        <v>1.323865</v>
       </c>
       <c r="E70" t="n">
-        <v>7722.7</v>
+        <v>7618.6</v>
       </c>
       <c r="F70" t="n">
-        <v>22434.6</v>
+        <v>22030.8</v>
       </c>
       <c r="G70" t="n">
-        <v>45225.5</v>
+        <v>44943.2</v>
       </c>
       <c r="H70" t="n">
-        <v>10070.4</v>
+        <v>9879.299999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>24724.4</v>
+        <v>24593.1</v>
       </c>
       <c r="J70" t="n">
-        <v>22920.3</v>
+        <v>23027</v>
       </c>
       <c r="K70" t="n">
-        <v>51054.8</v>
+        <v>50611.5</v>
       </c>
       <c r="L70" t="n">
-        <v>2409.85</v>
+        <v>2430.65</v>
       </c>
       <c r="M70" t="n">
-        <v>6341.38</v>
+        <v>6340.08</v>
       </c>
       <c r="N70" t="n">
-        <v>5500.9</v>
+        <v>5435.2</v>
       </c>
     </row>
     <row r="71">
@@ -9758,7 +10126,7 @@
         <v>46111.20833333334</v>
       </c>
       <c r="B71" t="n">
-        <v>10068.9</v>
+        <v>9975.9</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -9779,40 +10147,40 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.155875</v>
+        <v>1.145925</v>
       </c>
       <c r="D72" t="n">
-        <v>1.323055</v>
+        <v>1.317965</v>
       </c>
       <c r="E72" t="n">
-        <v>7921.4</v>
+        <v>7722.4</v>
       </c>
       <c r="F72" t="n">
-        <v>23026.2</v>
+        <v>22434.1</v>
       </c>
       <c r="G72" t="n">
-        <v>46230.95</v>
+        <v>45226</v>
       </c>
       <c r="H72" t="n">
-        <v>10279.9</v>
+        <v>10070.3</v>
       </c>
       <c r="I72" t="n">
-        <v>25317.1</v>
+        <v>24724.2</v>
       </c>
       <c r="J72" t="n">
-        <v>23777.1</v>
+        <v>22920</v>
       </c>
       <c r="K72" t="n">
-        <v>53050.8</v>
+        <v>51049.8</v>
       </c>
       <c r="L72" t="n">
-        <v>2494.15</v>
+        <v>2409.75</v>
       </c>
       <c r="M72" t="n">
-        <v>6530.15</v>
+        <v>6341.26</v>
       </c>
       <c r="N72" t="n">
-        <v>5653.5</v>
+        <v>5500.7</v>
       </c>
     </row>
     <row r="73">
@@ -9820,7 +10188,7 @@
         <v>46112.20833333334</v>
       </c>
       <c r="B73" t="n">
-        <v>9969.1</v>
+        <v>10068.6</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -9841,40 +10209,40 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1.159095</v>
+        <v>1.155885</v>
       </c>
       <c r="D74" t="n">
-        <v>1.330625</v>
+        <v>1.32306</v>
       </c>
       <c r="E74" t="n">
-        <v>7976.6</v>
+        <v>7921</v>
       </c>
       <c r="F74" t="n">
-        <v>23289</v>
+        <v>23025</v>
       </c>
       <c r="G74" t="n">
-        <v>46561.8</v>
+        <v>46313.4</v>
       </c>
       <c r="H74" t="n">
-        <v>10416.2</v>
+        <v>10279.8</v>
       </c>
       <c r="I74" t="n">
-        <v>25315.3</v>
+        <v>25316.6</v>
       </c>
       <c r="J74" t="n">
-        <v>23996.1</v>
+        <v>23775.3</v>
       </c>
       <c r="K74" t="n">
-        <v>54233.9</v>
+        <v>53025.8</v>
       </c>
       <c r="L74" t="n">
-        <v>2510.15</v>
+        <v>2494.05</v>
       </c>
       <c r="M74" t="n">
-        <v>6572.13</v>
+        <v>6529.9</v>
       </c>
       <c r="N74" t="n">
-        <v>5720.9</v>
+        <v>5653.2</v>
       </c>
     </row>
     <row r="75">
@@ -9882,7 +10250,7 @@
         <v>46113.20833333334</v>
       </c>
       <c r="B75" t="n">
-        <v>10095.1</v>
+        <v>9968.9</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -9903,40 +10271,40 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1.154015</v>
+        <v>1.159125</v>
       </c>
       <c r="D76" t="n">
-        <v>1.322585</v>
+        <v>1.33069</v>
       </c>
       <c r="E76" t="n">
-        <v>7990.9</v>
+        <v>7977.1</v>
       </c>
       <c r="F76" t="n">
-        <v>23217.6</v>
+        <v>23290.2</v>
       </c>
       <c r="G76" t="n">
-        <v>46522.4</v>
+        <v>46564.3</v>
       </c>
       <c r="H76" t="n">
-        <v>10451.6</v>
+        <v>10416.3</v>
       </c>
       <c r="I76" t="n">
-        <v>25270.4</v>
+        <v>25315.7</v>
       </c>
       <c r="J76" t="n">
-        <v>24030.5</v>
+        <v>23997.5</v>
       </c>
       <c r="K76" t="n">
-        <v>53247.5</v>
+        <v>54235.3</v>
       </c>
       <c r="L76" t="n">
-        <v>2530.55</v>
+        <v>2510.35</v>
       </c>
       <c r="M76" t="n">
-        <v>6583.360000000001</v>
+        <v>6572.38</v>
       </c>
       <c r="N76" t="n">
-        <v>5701.47</v>
+        <v>5721.2</v>
       </c>
     </row>
     <row r="77">
@@ -9944,7 +10312,7 @@
         <v>46114.20833333334</v>
       </c>
       <c r="B77" t="n">
-        <v>10581</v>
+        <v>10094.8</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -9965,40 +10333,40 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.15187</v>
+        <v>1.154005</v>
       </c>
       <c r="D78" t="n">
-        <v>1.320465</v>
+        <v>1.322595</v>
       </c>
       <c r="E78" t="n">
-        <v>7960.4</v>
+        <v>7991</v>
       </c>
       <c r="F78" t="n">
-        <v>23127.3</v>
+        <v>23218.1</v>
       </c>
       <c r="G78" t="n">
-        <v>46407.7</v>
+        <v>46522.1</v>
       </c>
       <c r="H78" t="n">
-        <v>10432</v>
+        <v>10451.7</v>
       </c>
       <c r="I78" t="n">
-        <v>25188.7</v>
+        <v>25270.6</v>
       </c>
       <c r="J78" t="n">
-        <v>23957.4</v>
+        <v>24030.1</v>
       </c>
       <c r="K78" t="n">
-        <v>53165.2</v>
+        <v>53243.7</v>
       </c>
       <c r="L78" t="n">
-        <v>2519.65</v>
+        <v>2530.45</v>
       </c>
       <c r="M78" t="n">
-        <v>6563.67</v>
+        <v>6583.43</v>
       </c>
       <c r="N78" t="n">
-        <v>5679.77</v>
+        <v>5701.57</v>
       </c>
     </row>
     <row r="79">
@@ -10009,34 +10377,34 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>7934.5</v>
+        <v>7931.5</v>
       </c>
       <c r="F79" t="n">
-        <v>23052.9</v>
+        <v>23043.8</v>
       </c>
       <c r="G79" t="n">
-        <v>46258.3</v>
+        <v>46240.7</v>
       </c>
       <c r="H79" t="n">
-        <v>10416.4</v>
+        <v>10414.5</v>
       </c>
       <c r="I79" t="n">
-        <v>25153.9</v>
+        <v>25149.7</v>
       </c>
       <c r="J79" t="n">
-        <v>23907.8</v>
+        <v>23893</v>
       </c>
       <c r="K79" t="n">
-        <v>52872.6</v>
+        <v>53059.2</v>
       </c>
       <c r="L79" t="n">
-        <v>2510.85</v>
+        <v>2508.95</v>
       </c>
       <c r="M79" t="n">
-        <v>6547.57</v>
+        <v>6541.72</v>
       </c>
       <c r="N79" t="n">
-        <v>5661.8</v>
+        <v>5659.6</v>
       </c>
     </row>
     <row r="80">
@@ -10044,7 +10412,7 @@
         <v>46117.20833333334</v>
       </c>
       <c r="B80" t="n">
-        <v>10420.3</v>
+        <v>10542.1</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -10065,40 +10433,40 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1.154265</v>
+        <v>1.151625</v>
       </c>
       <c r="D81" t="n">
-        <v>1.323355</v>
+        <v>1.319585</v>
       </c>
       <c r="E81" t="n">
-        <v>8026.1</v>
+        <v>7934.6</v>
       </c>
       <c r="F81" t="n">
-        <v>23295.1</v>
+        <v>23053.5</v>
       </c>
       <c r="G81" t="n">
-        <v>46709.5</v>
+        <v>46257.8</v>
       </c>
       <c r="H81" t="n">
-        <v>10477.6</v>
+        <v>10416.5</v>
       </c>
       <c r="I81" t="n">
-        <v>25312</v>
+        <v>25154.1</v>
       </c>
       <c r="J81" t="n">
-        <v>24134.7</v>
+        <v>23908.4</v>
       </c>
       <c r="K81" t="n">
-        <v>53883.7</v>
+        <v>52875.1</v>
       </c>
       <c r="L81" t="n">
-        <v>2536.65</v>
+        <v>2510.95</v>
       </c>
       <c r="M81" t="n">
-        <v>6603.96</v>
+        <v>6547.7</v>
       </c>
       <c r="N81" t="n">
-        <v>5727.1</v>
+        <v>5662</v>
       </c>
     </row>
     <row r="82">
@@ -10106,7 +10474,7 @@
         <v>46118.20833333334</v>
       </c>
       <c r="B82" t="n">
-        <v>10675.7</v>
+        <v>10421</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -10127,40 +10495,40 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1.166825</v>
+        <v>1.154235</v>
       </c>
       <c r="D83" t="n">
-        <v>1.337355</v>
+        <v>1.323335</v>
       </c>
       <c r="E83" t="n">
-        <v>8193.700000000001</v>
+        <v>8026.3</v>
       </c>
       <c r="F83" t="n">
-        <v>23802.3</v>
+        <v>23295.6</v>
       </c>
       <c r="G83" t="n">
-        <v>47545.8</v>
+        <v>46712</v>
       </c>
       <c r="H83" t="n">
-        <v>10557.1</v>
+        <v>10477.7</v>
       </c>
       <c r="I83" t="n">
-        <v>25620.5</v>
+        <v>25312.2</v>
       </c>
       <c r="J83" t="n">
-        <v>24748.9</v>
+        <v>24134.8</v>
       </c>
       <c r="K83" t="n">
-        <v>55942.4</v>
+        <v>53882.5</v>
       </c>
       <c r="L83" t="n">
-        <v>2623.75</v>
+        <v>2536.45</v>
       </c>
       <c r="M83" t="n">
-        <v>6752.42</v>
+        <v>6604.09</v>
       </c>
       <c r="N83" t="n">
-        <v>5845.7</v>
+        <v>5727.2</v>
       </c>
     </row>
     <row r="84">
@@ -10168,7 +10536,7 @@
         <v>46119.20833333334</v>
       </c>
       <c r="B84" t="n">
-        <v>9110.700000000001</v>
+        <v>10675.9</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -10189,40 +10557,40 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1.166275</v>
+        <v>1.16686</v>
       </c>
       <c r="D85" t="n">
-        <v>1.339785</v>
+        <v>1.337415</v>
       </c>
       <c r="E85" t="n">
-        <v>8274.200000000001</v>
+        <v>8193.6</v>
       </c>
       <c r="F85" t="n">
-        <v>24005.2</v>
+        <v>23801.8</v>
       </c>
       <c r="G85" t="n">
-        <v>47886.5</v>
+        <v>47546.3</v>
       </c>
       <c r="H85" t="n">
-        <v>10659.2</v>
+        <v>10557</v>
       </c>
       <c r="I85" t="n">
-        <v>25877.5</v>
+        <v>25620.3</v>
       </c>
       <c r="J85" t="n">
-        <v>24864</v>
+        <v>24748.8</v>
       </c>
       <c r="K85" t="n">
-        <v>56750.7</v>
+        <v>55944</v>
       </c>
       <c r="L85" t="n">
-        <v>2621.15</v>
+        <v>2623.35</v>
       </c>
       <c r="M85" t="n">
-        <v>6775.84</v>
+        <v>6752.54</v>
       </c>
       <c r="N85" t="n">
-        <v>5913.6</v>
+        <v>5845.6</v>
       </c>
     </row>
     <row r="86">
@@ -10230,7 +10598,7 @@
         <v>46120.20833333334</v>
       </c>
       <c r="B86" t="n">
-        <v>9245.299999999999</v>
+        <v>9110.5</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -10251,40 +10619,40 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.169405</v>
+        <v>1.166245</v>
       </c>
       <c r="D87" t="n">
-        <v>1.342805</v>
+        <v>1.339775</v>
       </c>
       <c r="E87" t="n">
-        <v>8252.299999999999</v>
+        <v>8273.9</v>
       </c>
       <c r="F87" t="n">
-        <v>23860.1</v>
+        <v>24005.1</v>
       </c>
       <c r="G87" t="n">
-        <v>48155.1</v>
+        <v>47885.9</v>
       </c>
       <c r="H87" t="n">
-        <v>10594.9</v>
+        <v>10659</v>
       </c>
       <c r="I87" t="n">
-        <v>25916.1</v>
+        <v>25877.4</v>
       </c>
       <c r="J87" t="n">
-        <v>25042.9</v>
+        <v>24863.4</v>
       </c>
       <c r="K87" t="n">
-        <v>56487.1</v>
+        <v>56735.7</v>
       </c>
       <c r="L87" t="n">
-        <v>2635.65</v>
+        <v>2621.05</v>
       </c>
       <c r="M87" t="n">
-        <v>6816.9</v>
+        <v>6775.83</v>
       </c>
       <c r="N87" t="n">
-        <v>5900.9</v>
+        <v>5913.4</v>
       </c>
     </row>
     <row r="88">
@@ -10292,7 +10660,7 @@
         <v>46121.20833333334</v>
       </c>
       <c r="B88" t="n">
-        <v>9242.700000000001</v>
+        <v>9244.799999999999</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -10313,40 +10681,40 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.1726</v>
+        <v>1.169385</v>
       </c>
       <c r="D89" t="n">
-        <v>1.346235</v>
+        <v>1.342795</v>
       </c>
       <c r="E89" t="n">
-        <v>8266.799999999999</v>
+        <v>8252.5</v>
       </c>
       <c r="F89" t="n">
-        <v>23823.9</v>
+        <v>23860.6</v>
       </c>
       <c r="G89" t="n">
-        <v>47972</v>
+        <v>48155.6</v>
       </c>
       <c r="H89" t="n">
-        <v>10605.1</v>
+        <v>10595</v>
       </c>
       <c r="I89" t="n">
-        <v>25948.9</v>
+        <v>25916.3</v>
       </c>
       <c r="J89" t="n">
-        <v>25164.7</v>
+        <v>25043.1</v>
       </c>
       <c r="K89" t="n">
-        <v>57406.8</v>
+        <v>56495.2</v>
       </c>
       <c r="L89" t="n">
-        <v>2636.3</v>
+        <v>2635.55</v>
       </c>
       <c r="M89" t="n">
-        <v>6825.55</v>
+        <v>6817.02</v>
       </c>
       <c r="N89" t="n">
-        <v>5928.91</v>
+        <v>5901</v>
       </c>
     </row>
     <row r="90">
@@ -10354,7 +10722,7 @@
         <v>46122.20833333334</v>
       </c>
       <c r="B90" t="n">
-        <v>9114.700000000001</v>
+        <v>9243</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -10375,40 +10743,40 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.167255</v>
+        <v>1.1676</v>
       </c>
       <c r="D91" t="n">
-        <v>1.339455</v>
+        <v>1.34652</v>
       </c>
       <c r="E91" t="n">
-        <v>8130.9</v>
+        <v>8147</v>
       </c>
       <c r="F91" t="n">
-        <v>23438.1</v>
+        <v>23474</v>
       </c>
       <c r="G91" t="n">
-        <v>47403</v>
+        <v>47455.9</v>
       </c>
       <c r="H91" t="n">
-        <v>10523</v>
+        <v>10530.4</v>
       </c>
       <c r="I91" t="n">
-        <v>25770.2</v>
+        <v>25787.6</v>
       </c>
       <c r="J91" t="n">
-        <v>24791.8</v>
+        <v>24777</v>
       </c>
       <c r="K91" t="n">
-        <v>56085.5</v>
+        <v>56086.6</v>
       </c>
       <c r="L91" t="n">
-        <v>2587.85</v>
+        <v>2592.45</v>
       </c>
       <c r="M91" t="n">
-        <v>6740.55</v>
+        <v>6743.52</v>
       </c>
       <c r="N91" t="n">
-        <v>5831.8</v>
+        <v>5843.5</v>
       </c>
     </row>
     <row r="92">
@@ -10416,7 +10784,7 @@
         <v>46124.20833333334</v>
       </c>
       <c r="B92" t="n">
-        <v>9809.4</v>
+        <v>9660.4</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -10437,40 +10805,40 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.176135</v>
+        <v>1.167225</v>
       </c>
       <c r="D93" t="n">
-        <v>1.351065</v>
+        <v>1.339425</v>
       </c>
       <c r="E93" t="n">
-        <v>8268.299999999999</v>
+        <v>8130.6</v>
       </c>
       <c r="F93" t="n">
-        <v>23965.5</v>
+        <v>23437.6</v>
       </c>
       <c r="G93" t="n">
-        <v>48227.7</v>
+        <v>47402.5</v>
       </c>
       <c r="H93" t="n">
-        <v>10617.9</v>
+        <v>10522.9</v>
       </c>
       <c r="I93" t="n">
-        <v>25968.2</v>
+        <v>25770</v>
       </c>
       <c r="J93" t="n">
-        <v>25435.7</v>
+        <v>24791.7</v>
       </c>
       <c r="K93" t="n">
-        <v>57698.9</v>
+        <v>56100.3</v>
       </c>
       <c r="L93" t="n">
-        <v>2678.15</v>
+        <v>2587.75</v>
       </c>
       <c r="M93" t="n">
-        <v>6890.15</v>
+        <v>6740.42</v>
       </c>
       <c r="N93" t="n">
-        <v>5947.3</v>
+        <v>5831.6</v>
       </c>
     </row>
     <row r="94">
@@ -10478,7 +10846,7 @@
         <v>46125.20833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>9266.200000000001</v>
+        <v>9809.9</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -10499,40 +10867,40 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.179485</v>
+        <v>1.176105</v>
       </c>
       <c r="D95" t="n">
-        <v>1.356875</v>
+        <v>1.351055</v>
       </c>
       <c r="E95" t="n">
-        <v>8326.9</v>
+        <v>8268.4</v>
       </c>
       <c r="F95" t="n">
-        <v>24054.9</v>
+        <v>23966.1</v>
       </c>
       <c r="G95" t="n">
-        <v>48537.7</v>
+        <v>48228.3</v>
       </c>
       <c r="H95" t="n">
-        <v>10624.6</v>
+        <v>10618</v>
       </c>
       <c r="I95" t="n">
-        <v>26212.7</v>
+        <v>25968.4</v>
       </c>
       <c r="J95" t="n">
-        <v>25830.8</v>
+        <v>25435.8</v>
       </c>
       <c r="K95" t="n">
-        <v>58706</v>
+        <v>57701.4</v>
       </c>
       <c r="L95" t="n">
-        <v>2705.55</v>
+        <v>2678.25</v>
       </c>
       <c r="M95" t="n">
-        <v>6967.77</v>
+        <v>6890.22</v>
       </c>
       <c r="N95" t="n">
-        <v>5986.4</v>
+        <v>5947.4</v>
       </c>
     </row>
     <row r="96">
@@ -10540,7 +10908,7 @@
         <v>46126.20833333334</v>
       </c>
       <c r="B96" t="n">
-        <v>8869</v>
+        <v>9266.6</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -10561,40 +10929,40 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.180235</v>
+        <v>1.179485</v>
       </c>
       <c r="D97" t="n">
-        <v>1.356785</v>
+        <v>1.356865</v>
       </c>
       <c r="E97" t="n">
-        <v>8264.799999999999</v>
+        <v>8327</v>
       </c>
       <c r="F97" t="n">
-        <v>24107.1</v>
+        <v>24055.4</v>
       </c>
       <c r="G97" t="n">
-        <v>48527.8</v>
+        <v>48538.2</v>
       </c>
       <c r="H97" t="n">
-        <v>10556.1</v>
+        <v>10624.7</v>
       </c>
       <c r="I97" t="n">
-        <v>26130.4</v>
+        <v>26212.9</v>
       </c>
       <c r="J97" t="n">
-        <v>26229.3</v>
+        <v>25830.9</v>
       </c>
       <c r="K97" t="n">
-        <v>58563.8</v>
+        <v>58703.5</v>
       </c>
       <c r="L97" t="n">
-        <v>2716.35</v>
+        <v>2705.65</v>
       </c>
       <c r="M97" t="n">
-        <v>7028.29</v>
+        <v>6967.84</v>
       </c>
       <c r="N97" t="n">
-        <v>5946.9</v>
+        <v>5986.5</v>
       </c>
     </row>
     <row r="98">
@@ -10602,7 +10970,7 @@
         <v>46127.20833333334</v>
       </c>
       <c r="B98" t="n">
-        <v>8868.4</v>
+        <v>8869.299999999999</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -10623,40 +10991,40 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.178545</v>
+        <v>1.180245</v>
       </c>
       <c r="D99" t="n">
-        <v>1.353215</v>
+        <v>1.356845</v>
       </c>
       <c r="E99" t="n">
-        <v>8266.4</v>
+        <v>8264.700000000001</v>
       </c>
       <c r="F99" t="n">
-        <v>24140.9</v>
+        <v>24107.7</v>
       </c>
       <c r="G99" t="n">
-        <v>48661.1</v>
+        <v>48526.8</v>
       </c>
       <c r="H99" t="n">
-        <v>10590.9</v>
+        <v>10556</v>
       </c>
       <c r="I99" t="n">
-        <v>26236.3</v>
+        <v>26130.7</v>
       </c>
       <c r="J99" t="n">
-        <v>26321.7</v>
+        <v>26229.9</v>
       </c>
       <c r="K99" t="n">
-        <v>59430.4</v>
+        <v>58576.3</v>
       </c>
       <c r="L99" t="n">
-        <v>2725.15</v>
+        <v>2716.45</v>
       </c>
       <c r="M99" t="n">
-        <v>7046.74</v>
+        <v>7028.42</v>
       </c>
       <c r="N99" t="n">
-        <v>5920.67</v>
+        <v>5947.1</v>
       </c>
     </row>
     <row r="100">
@@ -10664,7 +11032,7 @@
         <v>46128.20833333334</v>
       </c>
       <c r="B100" t="n">
-        <v>9030.200000000001</v>
+        <v>8868.1</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -10685,40 +11053,40 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.176345</v>
+        <v>1.178535</v>
       </c>
       <c r="D101" t="n">
-        <v>1.351615</v>
+        <v>1.353225</v>
       </c>
       <c r="E101" t="n">
-        <v>8407.9</v>
+        <v>8266.200000000001</v>
       </c>
       <c r="F101" t="n">
-        <v>24651.9</v>
+        <v>24139.8</v>
       </c>
       <c r="G101" t="n">
-        <v>49453</v>
+        <v>48661.6</v>
       </c>
       <c r="H101" t="n">
-        <v>10697.9</v>
+        <v>10590.7</v>
       </c>
       <c r="I101" t="n">
-        <v>26504.1</v>
+        <v>26235.9</v>
       </c>
       <c r="J101" t="n">
-        <v>26684.1</v>
+        <v>26321.6</v>
       </c>
       <c r="K101" t="n">
-        <v>59693.4</v>
+        <v>59431</v>
       </c>
       <c r="L101" t="n">
-        <v>2777.8</v>
+        <v>2725.05</v>
       </c>
       <c r="M101" t="n">
-        <v>7126.42</v>
+        <v>7046.58</v>
       </c>
       <c r="N101" t="n">
-        <v>6036.51</v>
+        <v>5920.47</v>
       </c>
     </row>
     <row r="102">
@@ -10726,7 +11094,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B102" t="n">
-        <v>8417.5</v>
+        <v>9031.1</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -10747,23 +11115,23 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.173945</v>
+        <v>1.17366</v>
       </c>
       <c r="D103" t="n">
-        <v>1.348705</v>
+        <v>1.35162</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>10633.2</v>
+        <v>10619.4</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>7073.76</v>
+        <v>7062.22</v>
       </c>
       <c r="N103" t="inlineStr"/>
     </row>
@@ -10772,7 +11140,7 @@
         <v>46131.20833333334</v>
       </c>
       <c r="B104" t="n">
-        <v>8910.9</v>
+        <v>9006.299999999999</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -10793,23 +11161,23 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.179005</v>
+        <v>1.173945</v>
       </c>
       <c r="D105" t="n">
-        <v>1.353895</v>
+        <v>1.348665</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>10627.6</v>
+        <v>10633.3</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>7121.9</v>
+        <v>7073.88</v>
       </c>
       <c r="N105" t="inlineStr"/>
     </row>
@@ -10818,7 +11186,7 @@
         <v>46132.20833333334</v>
       </c>
       <c r="B106" t="n">
-        <v>8670.9</v>
+        <v>8910.4</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -10839,23 +11207,23 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.173925</v>
+        <v>1.179025</v>
       </c>
       <c r="D107" t="n">
-        <v>1.350235</v>
+        <v>1.353905</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>10466.5</v>
+        <v>10627.5</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>7088.99</v>
+        <v>7121.77</v>
       </c>
       <c r="N107" t="inlineStr"/>
     </row>
@@ -10864,7 +11232,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B108" t="n">
-        <v>8926.9</v>
+        <v>8669.9</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -10885,23 +11253,23 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>1.170595</v>
+        <v>1.173935</v>
       </c>
       <c r="D109" t="n">
-        <v>1.350215</v>
+        <v>1.350255</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>10460.2</v>
+        <v>10466.6</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>7127.22</v>
+        <v>7089.07</v>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
@@ -10910,7 +11278,7 @@
         <v>46134.20833333334</v>
       </c>
       <c r="B110" t="n">
-        <v>9453.1</v>
+        <v>8926.9</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -10931,23 +11299,23 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1.168635</v>
+        <v>1.170605</v>
       </c>
       <c r="D111" t="n">
-        <v>1.346735</v>
+        <v>1.350245</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10417.5</v>
+        <v>10460.3</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>7114.23</v>
+        <v>7127.34</v>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
@@ -10956,7 +11324,7 @@
         <v>46135.20833333334</v>
       </c>
       <c r="B112" t="n">
-        <v>9661.1</v>
+        <v>9453.6</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -10977,23 +11345,23 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1.171835</v>
+        <v>1.168645</v>
       </c>
       <c r="D113" t="n">
-        <v>1.353095</v>
+        <v>1.346725</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>10387.5</v>
+        <v>10417.3</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>7163.69</v>
+        <v>7114.110000000001</v>
       </c>
       <c r="N113" t="inlineStr"/>
     </row>
@@ -11002,7 +11370,7 @@
         <v>46136.20833333334</v>
       </c>
       <c r="B114" t="n">
-        <v>9486.799999999999</v>
+        <v>9660.1</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -11023,23 +11391,23 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1.170825</v>
+        <v>1.17021</v>
       </c>
       <c r="D115" t="n">
-        <v>1.351595</v>
+        <v>1.35339</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>10370.5</v>
+        <v>10372.1</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>7151.27</v>
+        <v>7156.71</v>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
@@ -11048,7 +11416,7 @@
         <v>46138.20833333334</v>
       </c>
       <c r="B116" t="n">
-        <v>9529.1</v>
+        <v>9544.4</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -11069,23 +11437,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.17246</v>
+        <v>1.170835</v>
       </c>
       <c r="D117" t="n">
-        <v>1.353605</v>
+        <v>1.351595</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10337.9</v>
+        <v>10370.6</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7176.440000000001</v>
+        <v>7151.34</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -11094,7 +11462,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9605.1</v>
+        <v>9530.299999999999</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -11109,6 +11477,190 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
     </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="n">
+        <v>1.172195</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.353565</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="n">
+        <v>10332.6</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>7186.08</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46140.20833333334</v>
+      </c>
+      <c r="B120" t="n">
+        <v>9760.4</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="n">
+        <v>1.171595</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.352155</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>10311.7</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>7145.49</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46141.20833333334</v>
+      </c>
+      <c r="B122" t="n">
+        <v>9930.6</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="n">
+        <v>1.167785</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1.347995</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>10207.4</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>7154.78</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46142.20833333334</v>
+      </c>
+      <c r="B124" t="n">
+        <v>10911.3</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="n">
+        <v>1.173175</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1.360465</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>10363.5</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>7220.53</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46143.20833333334</v>
+      </c>
+      <c r="B126" t="n">
+        <v>10552.4</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/input/universe_series.xlsx
+++ b/data/input/universe_series.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="bid_close" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mid_close" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="mid_close" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="bid_close" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="mid_open" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -495,10 +495,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.17877</v>
+        <v>1.178815</v>
       </c>
       <c r="D2" t="n">
-        <v>1.34943</v>
+        <v>1.349475</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -509,7 +509,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6878.66</v>
+        <v>6878.96</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -518,7 +518,7 @@
         <v>46071.20833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>6519.3</v>
+        <v>6521.200000000001</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -539,40 +539,40 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.17683</v>
+        <v>1.17686</v>
       </c>
       <c r="D4" t="n">
-        <v>1.34592</v>
+        <v>1.345965</v>
       </c>
       <c r="E4" t="n">
-        <v>8415.9</v>
+        <v>8417.9</v>
       </c>
       <c r="F4" t="n">
-        <v>25030.1</v>
+        <v>25033.6</v>
       </c>
       <c r="G4" t="n">
-        <v>49407.6</v>
+        <v>49410</v>
       </c>
       <c r="H4" t="n">
-        <v>10668.2</v>
+        <v>10670.2</v>
       </c>
       <c r="I4" t="n">
-        <v>26781.7</v>
+        <v>26796.7</v>
       </c>
       <c r="J4" t="n">
-        <v>24816.3</v>
+        <v>24817.3</v>
       </c>
       <c r="K4" t="n">
-        <v>57080.7</v>
+        <v>57084.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2661.8</v>
+        <v>2661.95</v>
       </c>
       <c r="M4" t="n">
-        <v>6865.54</v>
+        <v>6865.84</v>
       </c>
       <c r="N4" t="n">
-        <v>6063.9</v>
+        <v>6065.4</v>
       </c>
     </row>
     <row r="5">
@@ -580,7 +580,7 @@
         <v>46072.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>6670.8</v>
+        <v>6672.200000000001</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -601,40 +601,40 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.17797</v>
+        <v>1.17822</v>
       </c>
       <c r="D6" t="n">
-        <v>1.34765</v>
+        <v>1.348245</v>
       </c>
       <c r="E6" t="n">
-        <v>8533.4</v>
+        <v>8535.4</v>
       </c>
       <c r="F6" t="n">
-        <v>25233.1</v>
+        <v>25236.6</v>
       </c>
       <c r="G6" t="n">
-        <v>49619.9</v>
+        <v>49624.8</v>
       </c>
       <c r="H6" t="n">
-        <v>10718.4</v>
+        <v>10720.4</v>
       </c>
       <c r="I6" t="n">
-        <v>26848.4</v>
+        <v>26863.4</v>
       </c>
       <c r="J6" t="n">
-        <v>25013.7</v>
+        <v>25016.2</v>
       </c>
       <c r="K6" t="n">
-        <v>57073.3</v>
+        <v>57088.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2661.7</v>
+        <v>2662.2</v>
       </c>
       <c r="M6" t="n">
-        <v>6909.88</v>
+        <v>6910.63</v>
       </c>
       <c r="N6" t="n">
-        <v>6133.6</v>
+        <v>6135.1</v>
       </c>
     </row>
     <row r="7">
@@ -642,7 +642,7 @@
         <v>46073.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>6628.3</v>
+        <v>6630.200000000001</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -663,40 +663,40 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.18328</v>
+        <v>1.18331</v>
       </c>
       <c r="D8" t="n">
-        <v>1.35316</v>
+        <v>1.353205</v>
       </c>
       <c r="E8" t="n">
-        <v>8513.200000000001</v>
+        <v>8515.200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>25172.5</v>
+        <v>25176</v>
       </c>
       <c r="G8" t="n">
-        <v>49526</v>
+        <v>49528.4</v>
       </c>
       <c r="H8" t="n">
-        <v>10701.4</v>
+        <v>10703.4</v>
       </c>
       <c r="I8" t="n">
-        <v>26811.4</v>
+        <v>26826.4</v>
       </c>
       <c r="J8" t="n">
-        <v>24910.3</v>
+        <v>24911.3</v>
       </c>
       <c r="K8" t="n">
-        <v>56978.1</v>
+        <v>56981.6</v>
       </c>
       <c r="L8" t="n">
-        <v>2652.5</v>
+        <v>2652.65</v>
       </c>
       <c r="M8" t="n">
-        <v>6891.98</v>
+        <v>6892.28</v>
       </c>
       <c r="N8" t="n">
-        <v>6118.9</v>
+        <v>6120.4</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         <v>46075.20833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>6556.3</v>
+        <v>6557.700000000001</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -725,40 +725,40 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.17928</v>
+        <v>1.179325</v>
       </c>
       <c r="D10" t="n">
-        <v>1.34948</v>
+        <v>1.349555</v>
       </c>
       <c r="E10" t="n">
-        <v>8504.6</v>
+        <v>8506.6</v>
       </c>
       <c r="F10" t="n">
-        <v>24993</v>
+        <v>24996.5</v>
       </c>
       <c r="G10" t="n">
-        <v>48837.1</v>
+        <v>48839.5</v>
       </c>
       <c r="H10" t="n">
-        <v>10690.7</v>
+        <v>10692.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26876.9</v>
+        <v>26891.9</v>
       </c>
       <c r="J10" t="n">
-        <v>24734.3</v>
+        <v>24735.3</v>
       </c>
       <c r="K10" t="n">
-        <v>56662.3</v>
+        <v>56665.8</v>
       </c>
       <c r="L10" t="n">
-        <v>2621.3</v>
+        <v>2621.45</v>
       </c>
       <c r="M10" t="n">
-        <v>6844.01</v>
+        <v>6844.309999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>6121.8</v>
+        <v>6123.3</v>
       </c>
     </row>
     <row r="11">
@@ -766,7 +766,7 @@
         <v>46076.20833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>6674.9</v>
+        <v>6676.299999999999</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -787,40 +787,40 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.1774</v>
+        <v>1.17743</v>
       </c>
       <c r="D12" t="n">
-        <v>1.34956</v>
+        <v>1.349605</v>
       </c>
       <c r="E12" t="n">
-        <v>8537.9</v>
+        <v>8539.9</v>
       </c>
       <c r="F12" t="n">
-        <v>25035.8</v>
+        <v>25039.3</v>
       </c>
       <c r="G12" t="n">
-        <v>49175.1</v>
+        <v>49177.5</v>
       </c>
       <c r="H12" t="n">
-        <v>10710.4</v>
+        <v>10712.4</v>
       </c>
       <c r="I12" t="n">
-        <v>26751.2</v>
+        <v>26766.2</v>
       </c>
       <c r="J12" t="n">
-        <v>24994.3</v>
+        <v>24995.3</v>
       </c>
       <c r="K12" t="n">
-        <v>57908.5</v>
+        <v>57912</v>
       </c>
       <c r="L12" t="n">
-        <v>2651.4</v>
+        <v>2651.55</v>
       </c>
       <c r="M12" t="n">
-        <v>6891.78</v>
+        <v>6892.08</v>
       </c>
       <c r="N12" t="n">
-        <v>6134.6</v>
+        <v>6136.1</v>
       </c>
     </row>
     <row r="13">
@@ -828,7 +828,7 @@
         <v>46077.20833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>6597.5</v>
+        <v>6598.9</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -849,40 +849,40 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.18151</v>
+        <v>1.18154</v>
       </c>
       <c r="D14" t="n">
-        <v>1.35576</v>
+        <v>1.355805</v>
       </c>
       <c r="E14" t="n">
-        <v>8567.6</v>
+        <v>8569.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25177.8</v>
+        <v>25181.3</v>
       </c>
       <c r="G14" t="n">
-        <v>49389.6</v>
+        <v>49392</v>
       </c>
       <c r="H14" t="n">
-        <v>10802.4</v>
+        <v>10804.4</v>
       </c>
       <c r="I14" t="n">
-        <v>26935</v>
+        <v>26950</v>
       </c>
       <c r="J14" t="n">
-        <v>25269</v>
+        <v>25270</v>
       </c>
       <c r="K14" t="n">
-        <v>59281.6</v>
+        <v>59285.1</v>
       </c>
       <c r="L14" t="n">
-        <v>2660.5</v>
+        <v>2660.65</v>
       </c>
       <c r="M14" t="n">
-        <v>6937.36</v>
+        <v>6937.66</v>
       </c>
       <c r="N14" t="n">
-        <v>6174.2</v>
+        <v>6175.7</v>
       </c>
     </row>
     <row r="15">
@@ -890,7 +890,7 @@
         <v>46078.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>6555.2</v>
+        <v>6556.6</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -911,40 +911,40 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.18032</v>
+        <v>1.180365</v>
       </c>
       <c r="D16" t="n">
-        <v>1.34911</v>
+        <v>1.349155</v>
       </c>
       <c r="E16" t="n">
-        <v>8609.700000000001</v>
+        <v>8611.700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>25249.8</v>
+        <v>25253.3</v>
       </c>
       <c r="G16" t="n">
-        <v>49227.2</v>
+        <v>49229.6</v>
       </c>
       <c r="H16" t="n">
-        <v>10833.1</v>
+        <v>10835.1</v>
       </c>
       <c r="I16" t="n">
-        <v>26374.6</v>
+        <v>26389.6</v>
       </c>
       <c r="J16" t="n">
-        <v>24954.6</v>
+        <v>24955.6</v>
       </c>
       <c r="K16" t="n">
-        <v>58431.5</v>
+        <v>58435</v>
       </c>
       <c r="L16" t="n">
-        <v>2655.4</v>
+        <v>2655.55</v>
       </c>
       <c r="M16" t="n">
-        <v>6882.06</v>
+        <v>6882.360000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>6149.2</v>
+        <v>6150.7</v>
       </c>
     </row>
     <row r="17">
@@ -952,7 +952,7 @@
         <v>46079.20833333334</v>
       </c>
       <c r="B17" t="n">
-        <v>6530.4</v>
+        <v>6531.799999999999</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -973,40 +973,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.18146</v>
+        <v>1.18179</v>
       </c>
       <c r="D18" t="n">
-        <v>1.34768</v>
+        <v>1.34806</v>
       </c>
       <c r="E18" t="n">
-        <v>8528.6</v>
+        <v>8530.6</v>
       </c>
       <c r="F18" t="n">
-        <v>25140.2</v>
+        <v>25143.7</v>
       </c>
       <c r="G18" t="n">
-        <v>48853.6</v>
+        <v>48858.5</v>
       </c>
       <c r="H18" t="n">
-        <v>10860.7</v>
+        <v>10862.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26475.4</v>
+        <v>26490.4</v>
       </c>
       <c r="J18" t="n">
-        <v>24913.4</v>
+        <v>24914.4</v>
       </c>
       <c r="K18" t="n">
-        <v>58609.2</v>
+        <v>58612.7</v>
       </c>
       <c r="L18" t="n">
-        <v>2626.5</v>
+        <v>2626.65</v>
       </c>
       <c r="M18" t="n">
-        <v>6864.83</v>
+        <v>6865.58</v>
       </c>
       <c r="N18" t="n">
-        <v>6093.88</v>
+        <v>6095.38</v>
       </c>
     </row>
     <row r="19">
@@ -1014,7 +1014,7 @@
         <v>46080.20833333334</v>
       </c>
       <c r="B19" t="n">
-        <v>6724.1</v>
+        <v>6725.5</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -1035,40 +1035,40 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1.17591</v>
+        <v>1.17594</v>
       </c>
       <c r="D20" t="n">
-        <v>1.34048</v>
+        <v>1.340525</v>
       </c>
       <c r="E20" t="n">
-        <v>8464.4</v>
+        <v>8466.4</v>
       </c>
       <c r="F20" t="n">
-        <v>24942.8</v>
+        <v>24946.3</v>
       </c>
       <c r="G20" t="n">
-        <v>48366.4</v>
+        <v>48368.8</v>
       </c>
       <c r="H20" t="n">
-        <v>10809.6</v>
+        <v>10811.6</v>
       </c>
       <c r="I20" t="n">
-        <v>26335.6</v>
+        <v>26350.6</v>
       </c>
       <c r="J20" t="n">
-        <v>24695.7</v>
+        <v>24696.7</v>
       </c>
       <c r="K20" t="n">
-        <v>57484.6</v>
+        <v>57488.1</v>
       </c>
       <c r="L20" t="n">
-        <v>2591.1</v>
+        <v>2591.25</v>
       </c>
       <c r="M20" t="n">
-        <v>6805.65</v>
+        <v>6805.95</v>
       </c>
       <c r="N20" t="n">
-        <v>6048.08</v>
+        <v>6049.58</v>
       </c>
     </row>
     <row r="21">
@@ -1076,7 +1076,7 @@
         <v>46082.20833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>7098.9</v>
+        <v>7100.799999999999</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -1097,40 +1097,40 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.16939</v>
+        <v>1.169435</v>
       </c>
       <c r="D22" t="n">
-        <v>1.34077</v>
+        <v>1.340815</v>
       </c>
       <c r="E22" t="n">
-        <v>8385.700000000001</v>
+        <v>8387.700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>24578.7</v>
+        <v>24582.2</v>
       </c>
       <c r="G22" t="n">
-        <v>48821.2</v>
+        <v>48823.6</v>
       </c>
       <c r="H22" t="n">
-        <v>10787.5</v>
+        <v>10789.5</v>
       </c>
       <c r="I22" t="n">
-        <v>26141.8</v>
+        <v>26156.8</v>
       </c>
       <c r="J22" t="n">
-        <v>24934.3</v>
+        <v>24935.3</v>
       </c>
       <c r="K22" t="n">
-        <v>57709.6</v>
+        <v>57713.1</v>
       </c>
       <c r="L22" t="n">
-        <v>2650.7</v>
+        <v>2650.85</v>
       </c>
       <c r="M22" t="n">
-        <v>6867.64</v>
+        <v>6867.940000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>5980.7</v>
+        <v>5982.2</v>
       </c>
     </row>
     <row r="23">
@@ -1138,7 +1138,7 @@
         <v>46083.20833333334</v>
       </c>
       <c r="B23" t="n">
-        <v>7240.5</v>
+        <v>7242.4</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -1159,40 +1159,40 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1.16107</v>
+        <v>1.1611</v>
       </c>
       <c r="D24" t="n">
-        <v>1.33507</v>
+        <v>1.335115</v>
       </c>
       <c r="E24" t="n">
-        <v>8163.4</v>
+        <v>8165.4</v>
       </c>
       <c r="F24" t="n">
-        <v>23981.5</v>
+        <v>23985</v>
       </c>
       <c r="G24" t="n">
-        <v>48410.9</v>
+        <v>48413.3</v>
       </c>
       <c r="H24" t="n">
-        <v>10515.1</v>
+        <v>10517.1</v>
       </c>
       <c r="I24" t="n">
-        <v>25453.5</v>
+        <v>25468.5</v>
       </c>
       <c r="J24" t="n">
-        <v>24667</v>
+        <v>24668</v>
       </c>
       <c r="K24" t="n">
-        <v>54948.2</v>
+        <v>54951.7</v>
       </c>
       <c r="L24" t="n">
-        <v>2603.3</v>
+        <v>2603.45</v>
       </c>
       <c r="M24" t="n">
-        <v>6802.2</v>
+        <v>6802.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5811.8</v>
+        <v>5813.3</v>
       </c>
     </row>
     <row r="25">
@@ -1200,7 +1200,7 @@
         <v>46084.20833333334</v>
       </c>
       <c r="B25" t="n">
-        <v>7494.8</v>
+        <v>7496.700000000001</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -1221,40 +1221,40 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.16346</v>
+        <v>1.163505</v>
       </c>
       <c r="D26" t="n">
-        <v>1.33688</v>
+        <v>1.336925</v>
       </c>
       <c r="E26" t="n">
-        <v>8202</v>
+        <v>8204</v>
       </c>
       <c r="F26" t="n">
-        <v>24298.7</v>
+        <v>24302.2</v>
       </c>
       <c r="G26" t="n">
-        <v>48750.8</v>
+        <v>48753.2</v>
       </c>
       <c r="H26" t="n">
-        <v>10624.8</v>
+        <v>10626.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25587.8</v>
+        <v>25602.8</v>
       </c>
       <c r="J26" t="n">
-        <v>25136.1</v>
+        <v>25137.1</v>
       </c>
       <c r="K26" t="n">
-        <v>56229.4</v>
+        <v>56232.9</v>
       </c>
       <c r="L26" t="n">
-        <v>2635.7</v>
+        <v>2635.85</v>
       </c>
       <c r="M26" t="n">
-        <v>6877.74</v>
+        <v>6878.04</v>
       </c>
       <c r="N26" t="n">
-        <v>5900.4</v>
+        <v>5901.9</v>
       </c>
     </row>
     <row r="27">
@@ -1262,7 +1262,7 @@
         <v>46085.20833333334</v>
       </c>
       <c r="B27" t="n">
-        <v>7664.1</v>
+        <v>7666</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1283,40 +1283,40 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.16064</v>
+        <v>1.16067</v>
       </c>
       <c r="D28" t="n">
-        <v>1.33552</v>
+        <v>1.335565</v>
       </c>
       <c r="E28" t="n">
-        <v>8057.2</v>
+        <v>8059.2</v>
       </c>
       <c r="F28" t="n">
-        <v>23862.7</v>
+        <v>23866.2</v>
       </c>
       <c r="G28" t="n">
-        <v>48031.6</v>
+        <v>48034</v>
       </c>
       <c r="H28" t="n">
-        <v>10405.9</v>
+        <v>10407.9</v>
       </c>
       <c r="I28" t="n">
-        <v>25187.5</v>
+        <v>25202.5</v>
       </c>
       <c r="J28" t="n">
-        <v>25030.4</v>
+        <v>25031.4</v>
       </c>
       <c r="K28" t="n">
-        <v>54559.7</v>
+        <v>54563.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2592.7</v>
+        <v>2592.85</v>
       </c>
       <c r="M28" t="n">
-        <v>6834.13</v>
+        <v>6834.43</v>
       </c>
       <c r="N28" t="n">
-        <v>5792.1</v>
+        <v>5793.6</v>
       </c>
     </row>
     <row r="29">
@@ -1324,7 +1324,7 @@
         <v>46086.20833333334</v>
       </c>
       <c r="B29" t="n">
-        <v>7885.6</v>
+        <v>7887.5</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -1345,40 +1345,40 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1.16139</v>
+        <v>1.161695</v>
       </c>
       <c r="D30" t="n">
-        <v>1.34039</v>
+        <v>1.340985</v>
       </c>
       <c r="E30" t="n">
-        <v>8015.2</v>
+        <v>8017.2</v>
       </c>
       <c r="F30" t="n">
-        <v>23636.8</v>
+        <v>23640.3</v>
       </c>
       <c r="G30" t="n">
-        <v>47429.3</v>
+        <v>47434.2</v>
       </c>
       <c r="H30" t="n">
-        <v>10316.8</v>
+        <v>10318.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25310.2</v>
+        <v>25325.2</v>
       </c>
       <c r="J30" t="n">
-        <v>24631.7</v>
+        <v>24634.2</v>
       </c>
       <c r="K30" t="n">
-        <v>54014.9</v>
+        <v>54029.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2521.5</v>
+        <v>2522</v>
       </c>
       <c r="M30" t="n">
-        <v>6732.48</v>
+        <v>6733.23</v>
       </c>
       <c r="N30" t="n">
-        <v>5721.53</v>
+        <v>5723.03</v>
       </c>
     </row>
     <row r="31">
@@ -1386,7 +1386,7 @@
         <v>46087.20833333334</v>
       </c>
       <c r="B31" t="n">
-        <v>8943.9</v>
+        <v>8947.799999999999</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -1407,40 +1407,40 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.15241</v>
+        <v>1.152455</v>
       </c>
       <c r="D32" t="n">
-        <v>1.33047</v>
+        <v>1.330515</v>
       </c>
       <c r="E32" t="n">
-        <v>7871</v>
+        <v>7873</v>
       </c>
       <c r="F32" t="n">
-        <v>23218.8</v>
+        <v>23222.3</v>
       </c>
       <c r="G32" t="n">
-        <v>46610.6</v>
+        <v>46613</v>
       </c>
       <c r="H32" t="n">
-        <v>10193.8</v>
+        <v>10195.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25027.2</v>
+        <v>25042.2</v>
       </c>
       <c r="J32" t="n">
-        <v>24186.4</v>
+        <v>24187.4</v>
       </c>
       <c r="K32" t="n">
-        <v>52213</v>
+        <v>52216.5</v>
       </c>
       <c r="L32" t="n">
-        <v>2433.2</v>
+        <v>2433.35</v>
       </c>
       <c r="M32" t="n">
-        <v>6622.15</v>
+        <v>6622.45</v>
       </c>
       <c r="N32" t="n">
-        <v>5614.4</v>
+        <v>5615.9</v>
       </c>
     </row>
     <row r="33">
@@ -1448,7 +1448,7 @@
         <v>46089.20833333334</v>
       </c>
       <c r="B33" t="n">
-        <v>11224.7</v>
+        <v>11228.6</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -1469,40 +1469,40 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.16157</v>
+        <v>1.161615</v>
       </c>
       <c r="D34" t="n">
-        <v>1.3424</v>
+        <v>1.342445</v>
       </c>
       <c r="E34" t="n">
-        <v>7998.3</v>
+        <v>8000.3</v>
       </c>
       <c r="F34" t="n">
-        <v>23699.6</v>
+        <v>23703.1</v>
       </c>
       <c r="G34" t="n">
-        <v>47531.9</v>
+        <v>47534.3</v>
       </c>
       <c r="H34" t="n">
-        <v>10305.8</v>
+        <v>10307.8</v>
       </c>
       <c r="I34" t="n">
-        <v>25530.7</v>
+        <v>25545.7</v>
       </c>
       <c r="J34" t="n">
-        <v>24853.1</v>
+        <v>24854.1</v>
       </c>
       <c r="K34" t="n">
-        <v>54256.1</v>
+        <v>54259.6</v>
       </c>
       <c r="L34" t="n">
-        <v>2533.9</v>
+        <v>2534.05</v>
       </c>
       <c r="M34" t="n">
-        <v>6765.77</v>
+        <v>6766.07</v>
       </c>
       <c r="N34" t="n">
-        <v>5763.2</v>
+        <v>5764.7</v>
       </c>
     </row>
     <row r="35">
@@ -1510,7 +1510,7 @@
         <v>46090.16666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>8801.5</v>
+        <v>8805.4</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -1531,40 +1531,40 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.16115</v>
+        <v>1.161195</v>
       </c>
       <c r="D36" t="n">
-        <v>1.34194</v>
+        <v>1.341985</v>
       </c>
       <c r="E36" t="n">
-        <v>7994.9</v>
+        <v>7996.9</v>
       </c>
       <c r="F36" t="n">
-        <v>23805.6</v>
+        <v>23809.1</v>
       </c>
       <c r="G36" t="n">
-        <v>47742.1</v>
+        <v>47744.5</v>
       </c>
       <c r="H36" t="n">
-        <v>10383.1</v>
+        <v>10385.1</v>
       </c>
       <c r="I36" t="n">
-        <v>25930.2</v>
+        <v>25945.2</v>
       </c>
       <c r="J36" t="n">
-        <v>24989.4</v>
+        <v>24990.4</v>
       </c>
       <c r="K36" t="n">
-        <v>55063.4</v>
+        <v>55066.9</v>
       </c>
       <c r="L36" t="n">
-        <v>2551.9</v>
+        <v>2552.05</v>
       </c>
       <c r="M36" t="n">
-        <v>6790.95</v>
+        <v>6791.25</v>
       </c>
       <c r="N36" t="n">
-        <v>5785.4</v>
+        <v>5786.9</v>
       </c>
     </row>
     <row r="37">
@@ -1572,7 +1572,7 @@
         <v>46091.16666666666</v>
       </c>
       <c r="B37" t="n">
-        <v>8210.4</v>
+        <v>8214.299999999999</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -1593,40 +1593,40 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1.15422</v>
+        <v>1.154265</v>
       </c>
       <c r="D38" t="n">
-        <v>1.33821</v>
+        <v>1.338255</v>
       </c>
       <c r="E38" t="n">
-        <v>7974.9</v>
+        <v>7976.9</v>
       </c>
       <c r="F38" t="n">
-        <v>23461.7</v>
+        <v>23465.2</v>
       </c>
       <c r="G38" t="n">
-        <v>47027.9</v>
+        <v>47030.3</v>
       </c>
       <c r="H38" t="n">
-        <v>10270.4</v>
+        <v>10272.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25619.7</v>
+        <v>25634.7</v>
       </c>
       <c r="J38" t="n">
-        <v>24767.1</v>
+        <v>24768.1</v>
       </c>
       <c r="K38" t="n">
-        <v>54154.5</v>
+        <v>54158</v>
       </c>
       <c r="L38" t="n">
-        <v>2505.6</v>
+        <v>2505.75</v>
       </c>
       <c r="M38" t="n">
-        <v>6724.31</v>
+        <v>6724.610000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>5751.13</v>
+        <v>5752.63</v>
       </c>
     </row>
     <row r="39">
@@ -1634,7 +1634,7 @@
         <v>46092.16666666666</v>
       </c>
       <c r="B39" t="n">
-        <v>9363.9</v>
+        <v>9366.299999999999</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -1655,40 +1655,40 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1.15202</v>
+        <v>1.152065</v>
       </c>
       <c r="D40" t="n">
-        <v>1.33507</v>
+        <v>1.335115</v>
       </c>
       <c r="E40" t="n">
-        <v>7962.5</v>
+        <v>7964.5</v>
       </c>
       <c r="F40" t="n">
-        <v>23491.5</v>
+        <v>23495</v>
       </c>
       <c r="G40" t="n">
-        <v>46737.5</v>
+        <v>46739.9</v>
       </c>
       <c r="H40" t="n">
-        <v>10281.7</v>
+        <v>10283.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25438.6</v>
+        <v>25453.6</v>
       </c>
       <c r="J40" t="n">
-        <v>24513</v>
+        <v>24514</v>
       </c>
       <c r="K40" t="n">
-        <v>53458.7</v>
+        <v>53462.2</v>
       </c>
       <c r="L40" t="n">
-        <v>2490.8</v>
+        <v>2490.95</v>
       </c>
       <c r="M40" t="n">
-        <v>6675.71</v>
+        <v>6676.01</v>
       </c>
       <c r="N40" t="n">
-        <v>5723.8</v>
+        <v>5725.3</v>
       </c>
     </row>
     <row r="41">
@@ -1696,7 +1696,7 @@
         <v>46093.16666666666</v>
       </c>
       <c r="B41" t="n">
-        <v>9466</v>
+        <v>9468.4</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -1717,40 +1717,40 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.14162</v>
+        <v>1.141665</v>
       </c>
       <c r="D42" t="n">
-        <v>1.3218</v>
+        <v>1.32235</v>
       </c>
       <c r="E42" t="n">
-        <v>7874.6</v>
+        <v>7875.6</v>
       </c>
       <c r="F42" t="n">
-        <v>23327.9</v>
+        <v>23329.3</v>
       </c>
       <c r="G42" t="n">
-        <v>46470.2</v>
+        <v>46475.1</v>
       </c>
       <c r="H42" t="n">
-        <v>10238.1</v>
+        <v>10240.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25385.4</v>
+        <v>25400.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24318.7</v>
+        <v>24321.2</v>
       </c>
       <c r="K42" t="n">
-        <v>53135.3</v>
+        <v>53150.3</v>
       </c>
       <c r="L42" t="n">
-        <v>2474</v>
+        <v>2474.5</v>
       </c>
       <c r="M42" t="n">
-        <v>6620.29</v>
+        <v>6621.04</v>
       </c>
       <c r="N42" t="n">
-        <v>5688.61</v>
+        <v>5689.36</v>
       </c>
     </row>
     <row r="43">
@@ -1758,7 +1758,7 @@
         <v>46094.16666666666</v>
       </c>
       <c r="B43" t="n">
-        <v>9764</v>
+        <v>9766.4</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -1779,40 +1779,40 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1.14355</v>
+        <v>1.143595</v>
       </c>
       <c r="D44" t="n">
-        <v>1.3245</v>
+        <v>1.324575</v>
       </c>
       <c r="E44" t="n">
-        <v>7917.5</v>
+        <v>7919.5</v>
       </c>
       <c r="F44" t="n">
-        <v>23425.1</v>
+        <v>23428.6</v>
       </c>
       <c r="G44" t="n">
-        <v>46639.4</v>
+        <v>46641.8</v>
       </c>
       <c r="H44" t="n">
-        <v>10266.8</v>
+        <v>10268.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25435.7</v>
+        <v>25450.7</v>
       </c>
       <c r="J44" t="n">
-        <v>24423</v>
+        <v>24424</v>
       </c>
       <c r="K44" t="n">
-        <v>53648.4</v>
+        <v>53651.9</v>
       </c>
       <c r="L44" t="n">
-        <v>2489.3</v>
+        <v>2489.45</v>
       </c>
       <c r="M44" t="n">
-        <v>6645.18</v>
+        <v>6645.48</v>
       </c>
       <c r="N44" t="n">
-        <v>5712.4</v>
+        <v>5713.9</v>
       </c>
     </row>
     <row r="45">
@@ -1820,7 +1820,7 @@
         <v>46096.16666666666</v>
       </c>
       <c r="B45" t="n">
-        <v>9776.299999999999</v>
+        <v>9778.700000000001</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -1841,40 +1841,40 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1.14977</v>
+        <v>1.149815</v>
       </c>
       <c r="D46" t="n">
-        <v>1.33114</v>
+        <v>1.331215</v>
       </c>
       <c r="E46" t="n">
-        <v>7947</v>
+        <v>7949</v>
       </c>
       <c r="F46" t="n">
-        <v>23621.9</v>
+        <v>23625.4</v>
       </c>
       <c r="G46" t="n">
-        <v>46924.3</v>
+        <v>46926.7</v>
       </c>
       <c r="H46" t="n">
-        <v>10345</v>
+        <v>10347</v>
       </c>
       <c r="I46" t="n">
-        <v>25846.7</v>
+        <v>25861.7</v>
       </c>
       <c r="J46" t="n">
-        <v>24651</v>
+        <v>24652</v>
       </c>
       <c r="K46" t="n">
-        <v>54334.1</v>
+        <v>54337.6</v>
       </c>
       <c r="L46" t="n">
-        <v>2501.5</v>
+        <v>2501.65</v>
       </c>
       <c r="M46" t="n">
-        <v>6697.82</v>
+        <v>6698.12</v>
       </c>
       <c r="N46" t="n">
-        <v>5752.7</v>
+        <v>5754.2</v>
       </c>
     </row>
     <row r="47">
@@ -1882,7 +1882,7 @@
         <v>46097.16666666666</v>
       </c>
       <c r="B47" t="n">
-        <v>9525</v>
+        <v>9527.4</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -1903,40 +1903,40 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1.15383</v>
+        <v>1.153885</v>
       </c>
       <c r="D48" t="n">
-        <v>1.33558</v>
+        <v>1.33575</v>
       </c>
       <c r="E48" t="n">
-        <v>7954.2</v>
+        <v>7956.2</v>
       </c>
       <c r="F48" t="n">
-        <v>23667</v>
+        <v>23670.5</v>
       </c>
       <c r="G48" t="n">
-        <v>46942.2</v>
+        <v>46944.6</v>
       </c>
       <c r="H48" t="n">
-        <v>10360.5</v>
+        <v>10362.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25844.5</v>
+        <v>25859.5</v>
       </c>
       <c r="J48" t="n">
-        <v>24774.5</v>
+        <v>24775.5</v>
       </c>
       <c r="K48" t="n">
-        <v>54270.9</v>
+        <v>54274.4</v>
       </c>
       <c r="L48" t="n">
-        <v>2517.7</v>
+        <v>2517.85</v>
       </c>
       <c r="M48" t="n">
-        <v>6711.38</v>
+        <v>6711.68</v>
       </c>
       <c r="N48" t="n">
-        <v>5754.9</v>
+        <v>5756.4</v>
       </c>
     </row>
     <row r="49">
@@ -1944,7 +1944,7 @@
         <v>46098.16666666666</v>
       </c>
       <c r="B49" t="n">
-        <v>9247.700000000001</v>
+        <v>9250.1</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -1965,40 +1965,40 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.14628</v>
+        <v>1.146325</v>
       </c>
       <c r="D50" t="n">
-        <v>1.32638</v>
+        <v>1.326425</v>
       </c>
       <c r="E50" t="n">
-        <v>7895.7</v>
+        <v>7897.7</v>
       </c>
       <c r="F50" t="n">
-        <v>23166</v>
+        <v>23169.5</v>
       </c>
       <c r="G50" t="n">
-        <v>46154.6</v>
+        <v>46157</v>
       </c>
       <c r="H50" t="n">
-        <v>10219.1</v>
+        <v>10221.1</v>
       </c>
       <c r="I50" t="n">
-        <v>25401.9</v>
+        <v>25416.9</v>
       </c>
       <c r="J50" t="n">
-        <v>24394.2</v>
+        <v>24395.2</v>
       </c>
       <c r="K50" t="n">
-        <v>53596.1</v>
+        <v>53599.6</v>
       </c>
       <c r="L50" t="n">
-        <v>2474.3</v>
+        <v>2474.45</v>
       </c>
       <c r="M50" t="n">
-        <v>6698.79</v>
+        <v>6698.99</v>
       </c>
       <c r="N50" t="n">
-        <v>5654</v>
+        <v>5655.5</v>
       </c>
     </row>
     <row r="51">
@@ -2006,7 +2006,7 @@
         <v>46099.16666666666</v>
       </c>
       <c r="B51" t="n">
-        <v>9647.9</v>
+        <v>9650.299999999999</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -2027,38 +2027,38 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.15762</v>
+        <v>1.15765</v>
       </c>
       <c r="D52" t="n">
-        <v>1.34236</v>
+        <v>1.342435</v>
       </c>
       <c r="E52" t="n">
-        <v>7840.7</v>
+        <v>7842.7</v>
       </c>
       <c r="F52" t="n">
-        <v>23016.2</v>
+        <v>23019.7</v>
       </c>
       <c r="G52" t="n">
-        <v>46136.8</v>
+        <v>46139.2</v>
       </c>
       <c r="H52" t="n">
-        <v>10067.6</v>
+        <v>10069.6</v>
       </c>
       <c r="I52" t="n">
-        <v>25353.8</v>
+        <v>25368.8</v>
       </c>
       <c r="J52" t="n">
-        <v>24406.7</v>
+        <v>24407.7</v>
       </c>
       <c r="K52" t="n">
-        <v>53397.7</v>
+        <v>53401.2</v>
       </c>
       <c r="L52" t="n">
-        <v>2508.4</v>
+        <v>2508.55</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>5653.9</v>
+        <v>5655.4</v>
       </c>
     </row>
     <row r="53">
@@ -2066,7 +2066,7 @@
         <v>46100.16666666666</v>
       </c>
       <c r="B53" t="n">
-        <v>9384.4</v>
+        <v>9386.799999999999</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -2087,40 +2087,40 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.15679</v>
+        <v>1.15709</v>
       </c>
       <c r="D54" t="n">
-        <v>1.33356</v>
+        <v>1.33411</v>
       </c>
       <c r="E54" t="n">
-        <v>7611.8</v>
+        <v>7613.8</v>
       </c>
       <c r="F54" t="n">
-        <v>22210.8</v>
+        <v>22214.3</v>
       </c>
       <c r="G54" t="n">
-        <v>45798.2</v>
+        <v>45803.1</v>
       </c>
       <c r="H54" t="n">
-        <v>9837.299999999999</v>
+        <v>9839.299999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>24755.8</v>
+        <v>24770.8</v>
       </c>
       <c r="J54" t="n">
-        <v>23997.9</v>
+        <v>24000.4</v>
       </c>
       <c r="K54" t="n">
-        <v>51302.2</v>
+        <v>51317.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2451.6</v>
+        <v>2452.1</v>
       </c>
       <c r="M54" t="n">
-        <v>6536.37</v>
+        <v>6537.12</v>
       </c>
       <c r="N54" t="n">
-        <v>5473.45</v>
+        <v>5474.95</v>
       </c>
     </row>
     <row r="55">
@@ -2128,7 +2128,7 @@
         <v>46101.16666666666</v>
       </c>
       <c r="B55" t="n">
-        <v>9788.799999999999</v>
+        <v>9792.700000000001</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -2149,40 +2149,40 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.1562</v>
+        <v>1.156245</v>
       </c>
       <c r="D56" t="n">
-        <v>1.33332</v>
+        <v>1.333395</v>
       </c>
       <c r="E56" t="n">
-        <v>7538.6</v>
+        <v>7540.6</v>
       </c>
       <c r="F56" t="n">
-        <v>21972.1</v>
+        <v>21975.6</v>
       </c>
       <c r="G56" t="n">
-        <v>45536.2</v>
+        <v>45538.6</v>
       </c>
       <c r="H56" t="n">
-        <v>9792.1</v>
+        <v>9794.1</v>
       </c>
       <c r="I56" t="n">
-        <v>24644.3</v>
+        <v>24659.3</v>
       </c>
       <c r="J56" t="n">
-        <v>23793.4</v>
+        <v>23794.4</v>
       </c>
       <c r="K56" t="n">
-        <v>51177</v>
+        <v>51180.5</v>
       </c>
       <c r="L56" t="n">
-        <v>2432.5</v>
+        <v>2432.65</v>
       </c>
       <c r="M56" t="n">
-        <v>6488.2</v>
+        <v>6488.5</v>
       </c>
       <c r="N56" t="n">
-        <v>5418.1</v>
+        <v>5419.6</v>
       </c>
     </row>
     <row r="57">
@@ -2190,7 +2190,7 @@
         <v>46103.16666666666</v>
       </c>
       <c r="B57" t="n">
-        <v>9883.200000000001</v>
+        <v>9885.6</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -2211,40 +2211,40 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.16077</v>
+        <v>1.1608</v>
       </c>
       <c r="D58" t="n">
-        <v>1.34255</v>
+        <v>1.342625</v>
       </c>
       <c r="E58" t="n">
-        <v>7796.8</v>
+        <v>7798.8</v>
       </c>
       <c r="F58" t="n">
-        <v>22841.5</v>
+        <v>22845</v>
       </c>
       <c r="G58" t="n">
-        <v>46288.2</v>
+        <v>46290.6</v>
       </c>
       <c r="H58" t="n">
-        <v>9961.6</v>
+        <v>9963.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24967.7</v>
+        <v>24982.7</v>
       </c>
       <c r="J58" t="n">
-        <v>24240.8</v>
+        <v>24241.8</v>
       </c>
       <c r="K58" t="n">
-        <v>53014.7</v>
+        <v>53018.2</v>
       </c>
       <c r="L58" t="n">
-        <v>2500.4</v>
+        <v>2500.55</v>
       </c>
       <c r="M58" t="n">
-        <v>6593.77</v>
+        <v>6594.07</v>
       </c>
       <c r="N58" t="n">
-        <v>5616.2</v>
+        <v>5617.7</v>
       </c>
     </row>
     <row r="59">
@@ -2252,7 +2252,7 @@
         <v>46104.16666666666</v>
       </c>
       <c r="B59" t="n">
-        <v>9121</v>
+        <v>9123.4</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -2273,40 +2273,40 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.1613</v>
+        <v>1.161345</v>
       </c>
       <c r="D60" t="n">
-        <v>1.34141</v>
+        <v>1.341485</v>
       </c>
       <c r="E60" t="n">
-        <v>7813.7</v>
+        <v>7815.7</v>
       </c>
       <c r="F60" t="n">
-        <v>22887.5</v>
+        <v>22891</v>
       </c>
       <c r="G60" t="n">
-        <v>46445.6</v>
+        <v>46448</v>
       </c>
       <c r="H60" t="n">
-        <v>10013.3</v>
+        <v>10015.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25035.4</v>
+        <v>25050.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24204</v>
+        <v>24205</v>
       </c>
       <c r="K60" t="n">
-        <v>53497.1</v>
+        <v>53500.6</v>
       </c>
       <c r="L60" t="n">
-        <v>2535.6</v>
+        <v>2535.75</v>
       </c>
       <c r="M60" t="n">
-        <v>6599.67</v>
+        <v>6599.97</v>
       </c>
       <c r="N60" t="n">
-        <v>5644.18</v>
+        <v>5645.68</v>
       </c>
     </row>
     <row r="61">
@@ -2314,7 +2314,7 @@
         <v>46105.16666666666</v>
       </c>
       <c r="B61" t="n">
-        <v>8852.799999999999</v>
+        <v>8855.200000000001</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -2335,40 +2335,40 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.15614</v>
+        <v>1.156185</v>
       </c>
       <c r="D62" t="n">
-        <v>1.33631</v>
+        <v>1.336385</v>
       </c>
       <c r="E62" t="n">
-        <v>7813.5</v>
+        <v>7815.5</v>
       </c>
       <c r="F62" t="n">
-        <v>22866.6</v>
+        <v>22870.1</v>
       </c>
       <c r="G62" t="n">
-        <v>46357.1</v>
+        <v>46359.5</v>
       </c>
       <c r="H62" t="n">
-        <v>10083.7</v>
+        <v>10085.7</v>
       </c>
       <c r="I62" t="n">
-        <v>25244.3</v>
+        <v>25259.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24113.6</v>
+        <v>24114.6</v>
       </c>
       <c r="K62" t="n">
-        <v>53875</v>
+        <v>53878.5</v>
       </c>
       <c r="L62" t="n">
-        <v>2530.6</v>
+        <v>2530.75</v>
       </c>
       <c r="M62" t="n">
-        <v>6580.7</v>
+        <v>6581</v>
       </c>
       <c r="N62" t="n">
-        <v>5620.01</v>
+        <v>5621.51</v>
       </c>
     </row>
     <row r="63">
@@ -2376,7 +2376,7 @@
         <v>46106.16666666666</v>
       </c>
       <c r="B63" t="n">
-        <v>9115.299999999999</v>
+        <v>9117.700000000001</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -2397,40 +2397,40 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.15345</v>
+        <v>1.153495</v>
       </c>
       <c r="D64" t="n">
-        <v>1.33334</v>
+        <v>1.333415</v>
       </c>
       <c r="E64" t="n">
-        <v>7778.5</v>
+        <v>7780.5</v>
       </c>
       <c r="F64" t="n">
-        <v>22689</v>
+        <v>22692.5</v>
       </c>
       <c r="G64" t="n">
-        <v>46178.7</v>
+        <v>46181.1</v>
       </c>
       <c r="H64" t="n">
-        <v>9963.799999999999</v>
+        <v>9965.799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>24753.8</v>
+        <v>24768.8</v>
       </c>
       <c r="J64" t="n">
-        <v>23681.7</v>
+        <v>23682.7</v>
       </c>
       <c r="K64" t="n">
-        <v>52920.1</v>
+        <v>52923.6</v>
       </c>
       <c r="L64" t="n">
-        <v>2508.4</v>
+        <v>2508.55</v>
       </c>
       <c r="M64" t="n">
-        <v>6505.95</v>
+        <v>6506.25</v>
       </c>
       <c r="N64" t="n">
-        <v>5571.5</v>
+        <v>5573</v>
       </c>
     </row>
     <row r="65">
@@ -2438,7 +2438,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B65" t="n">
-        <v>9272.4</v>
+        <v>9274.799999999999</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -2459,40 +2459,40 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.15067</v>
+        <v>1.15097</v>
       </c>
       <c r="D66" t="n">
-        <v>1.32591</v>
+        <v>1.3264</v>
       </c>
       <c r="E66" t="n">
-        <v>7644.4</v>
+        <v>7646.4</v>
       </c>
       <c r="F66" t="n">
-        <v>22097.6</v>
+        <v>22101.1</v>
       </c>
       <c r="G66" t="n">
-        <v>45056.6</v>
+        <v>45061.5</v>
       </c>
       <c r="H66" t="n">
-        <v>9893.299999999999</v>
+        <v>9895.299999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24612.5</v>
+        <v>24627.5</v>
       </c>
       <c r="J66" t="n">
-        <v>23067.1</v>
+        <v>23069.6</v>
       </c>
       <c r="K66" t="n">
-        <v>51122.7</v>
+        <v>51137.7</v>
       </c>
       <c r="L66" t="n">
-        <v>2442.7</v>
+        <v>2443.2</v>
       </c>
       <c r="M66" t="n">
-        <v>6354.5</v>
+        <v>6355.25</v>
       </c>
       <c r="N66" t="n">
-        <v>5453.72</v>
+        <v>5455.22</v>
       </c>
     </row>
     <row r="67">
@@ -2500,7 +2500,7 @@
         <v>46108.16666666666</v>
       </c>
       <c r="B67" t="n">
-        <v>9973.4</v>
+        <v>9977.299999999999</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -2521,40 +2521,40 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.14879</v>
+        <v>1.148835</v>
       </c>
       <c r="D68" t="n">
-        <v>1.32377</v>
+        <v>1.323875</v>
       </c>
       <c r="E68" t="n">
-        <v>7616.7</v>
+        <v>7618.7</v>
       </c>
       <c r="F68" t="n">
-        <v>22027.9</v>
+        <v>22031.4</v>
       </c>
       <c r="G68" t="n">
-        <v>44943.2</v>
+        <v>44945.6</v>
       </c>
       <c r="H68" t="n">
-        <v>9877.4</v>
+        <v>9879.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24578.4</v>
+        <v>24593.4</v>
       </c>
       <c r="J68" t="n">
-        <v>23026.2</v>
+        <v>23027.2</v>
       </c>
       <c r="K68" t="n">
-        <v>50601.5</v>
+        <v>50609</v>
       </c>
       <c r="L68" t="n">
-        <v>2430.7</v>
+        <v>2430.85</v>
       </c>
       <c r="M68" t="n">
-        <v>6339.91</v>
+        <v>6340.21</v>
       </c>
       <c r="N68" t="n">
-        <v>5433.9</v>
+        <v>5435.4</v>
       </c>
     </row>
     <row r="69">
@@ -2562,7 +2562,7 @@
         <v>46110.20833333334</v>
       </c>
       <c r="B69" t="n">
-        <v>9974</v>
+        <v>9976.4</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -2583,40 +2583,40 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1.14593</v>
+        <v>1.145975</v>
       </c>
       <c r="D70" t="n">
-        <v>1.31792</v>
+        <v>1.317995</v>
       </c>
       <c r="E70" t="n">
-        <v>7720.7</v>
+        <v>7722.7</v>
       </c>
       <c r="F70" t="n">
-        <v>22431.1</v>
+        <v>22434.6</v>
       </c>
       <c r="G70" t="n">
-        <v>45223.1</v>
+        <v>45225.5</v>
       </c>
       <c r="H70" t="n">
-        <v>10068.4</v>
+        <v>10070.4</v>
       </c>
       <c r="I70" t="n">
-        <v>24709.4</v>
+        <v>24724.4</v>
       </c>
       <c r="J70" t="n">
-        <v>22919.3</v>
+        <v>22920.3</v>
       </c>
       <c r="K70" t="n">
-        <v>51047.3</v>
+        <v>51054.8</v>
       </c>
       <c r="L70" t="n">
-        <v>2409.7</v>
+        <v>2409.85</v>
       </c>
       <c r="M70" t="n">
-        <v>6341.08</v>
+        <v>6341.38</v>
       </c>
       <c r="N70" t="n">
-        <v>5499.4</v>
+        <v>5500.9</v>
       </c>
     </row>
     <row r="71">
@@ -2624,7 +2624,7 @@
         <v>46111.20833333334</v>
       </c>
       <c r="B71" t="n">
-        <v>10066.5</v>
+        <v>10068.9</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -2645,40 +2645,40 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.15583</v>
+        <v>1.155875</v>
       </c>
       <c r="D72" t="n">
-        <v>1.32294</v>
+        <v>1.323055</v>
       </c>
       <c r="E72" t="n">
-        <v>7919.4</v>
+        <v>7921.4</v>
       </c>
       <c r="F72" t="n">
-        <v>23022.7</v>
+        <v>23026.2</v>
       </c>
       <c r="G72" t="n">
-        <v>46229.5</v>
+        <v>46230.95</v>
       </c>
       <c r="H72" t="n">
-        <v>10277.9</v>
+        <v>10279.9</v>
       </c>
       <c r="I72" t="n">
-        <v>25302.1</v>
+        <v>25317.1</v>
       </c>
       <c r="J72" t="n">
-        <v>23776.1</v>
+        <v>23777.1</v>
       </c>
       <c r="K72" t="n">
-        <v>53043.3</v>
+        <v>53050.8</v>
       </c>
       <c r="L72" t="n">
-        <v>2494</v>
+        <v>2494.15</v>
       </c>
       <c r="M72" t="n">
-        <v>6529.85</v>
+        <v>6530.15</v>
       </c>
       <c r="N72" t="n">
-        <v>5652</v>
+        <v>5653.5</v>
       </c>
     </row>
     <row r="73">
@@ -2686,7 +2686,7 @@
         <v>46112.20833333334</v>
       </c>
       <c r="B73" t="n">
-        <v>9966.700000000001</v>
+        <v>9969.1</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -2707,40 +2707,40 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1.15905</v>
+        <v>1.159095</v>
       </c>
       <c r="D74" t="n">
-        <v>1.33055</v>
+        <v>1.330625</v>
       </c>
       <c r="E74" t="n">
-        <v>7974.6</v>
+        <v>7976.6</v>
       </c>
       <c r="F74" t="n">
-        <v>23285.5</v>
+        <v>23289</v>
       </c>
       <c r="G74" t="n">
-        <v>46559.4</v>
+        <v>46561.8</v>
       </c>
       <c r="H74" t="n">
-        <v>10414.2</v>
+        <v>10416.2</v>
       </c>
       <c r="I74" t="n">
-        <v>25300.3</v>
+        <v>25315.3</v>
       </c>
       <c r="J74" t="n">
-        <v>23995.1</v>
+        <v>23996.1</v>
       </c>
       <c r="K74" t="n">
-        <v>54226.4</v>
+        <v>54233.9</v>
       </c>
       <c r="L74" t="n">
-        <v>2510</v>
+        <v>2510.15</v>
       </c>
       <c r="M74" t="n">
-        <v>6571.83</v>
+        <v>6572.13</v>
       </c>
       <c r="N74" t="n">
-        <v>5719.4</v>
+        <v>5720.9</v>
       </c>
     </row>
     <row r="75">
@@ -2748,7 +2748,7 @@
         <v>46113.20833333334</v>
       </c>
       <c r="B75" t="n">
-        <v>10092.7</v>
+        <v>10095.1</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -2769,40 +2769,40 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1.15397</v>
+        <v>1.154015</v>
       </c>
       <c r="D76" t="n">
-        <v>1.32248</v>
+        <v>1.322585</v>
       </c>
       <c r="E76" t="n">
-        <v>7988.9</v>
+        <v>7990.9</v>
       </c>
       <c r="F76" t="n">
-        <v>23214.1</v>
+        <v>23217.6</v>
       </c>
       <c r="G76" t="n">
-        <v>46520</v>
+        <v>46522.4</v>
       </c>
       <c r="H76" t="n">
-        <v>10449.6</v>
+        <v>10451.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25255.4</v>
+        <v>25270.4</v>
       </c>
       <c r="J76" t="n">
-        <v>24029.5</v>
+        <v>24030.5</v>
       </c>
       <c r="K76" t="n">
-        <v>53240</v>
+        <v>53247.5</v>
       </c>
       <c r="L76" t="n">
-        <v>2530.4</v>
+        <v>2530.55</v>
       </c>
       <c r="M76" t="n">
-        <v>6583.06</v>
+        <v>6583.360000000001</v>
       </c>
       <c r="N76" t="n">
-        <v>5699.97</v>
+        <v>5701.47</v>
       </c>
     </row>
     <row r="77">
@@ -2810,7 +2810,7 @@
         <v>46114.20833333334</v>
       </c>
       <c r="B77" t="n">
-        <v>10578.6</v>
+        <v>10581</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -2831,40 +2831,40 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.15154</v>
+        <v>1.15187</v>
       </c>
       <c r="D78" t="n">
-        <v>1.31987</v>
+        <v>1.320465</v>
       </c>
       <c r="E78" t="n">
-        <v>7958.4</v>
+        <v>7960.4</v>
       </c>
       <c r="F78" t="n">
-        <v>23123.8</v>
+        <v>23127.3</v>
       </c>
       <c r="G78" t="n">
-        <v>46405.9</v>
+        <v>46407.7</v>
       </c>
       <c r="H78" t="n">
-        <v>10430</v>
+        <v>10432</v>
       </c>
       <c r="I78" t="n">
-        <v>25173.7</v>
+        <v>25188.7</v>
       </c>
       <c r="J78" t="n">
-        <v>23956.4</v>
+        <v>23957.4</v>
       </c>
       <c r="K78" t="n">
-        <v>53150.2</v>
+        <v>53165.2</v>
       </c>
       <c r="L78" t="n">
-        <v>2519.5</v>
+        <v>2519.65</v>
       </c>
       <c r="M78" t="n">
-        <v>6563.37</v>
+        <v>6563.67</v>
       </c>
       <c r="N78" t="n">
-        <v>5678.27</v>
+        <v>5679.77</v>
       </c>
     </row>
     <row r="79">
@@ -2875,34 +2875,34 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>7932.5</v>
+        <v>7934.5</v>
       </c>
       <c r="F79" t="n">
-        <v>23049.4</v>
+        <v>23052.9</v>
       </c>
       <c r="G79" t="n">
-        <v>46255.9</v>
+        <v>46258.3</v>
       </c>
       <c r="H79" t="n">
-        <v>10414.4</v>
+        <v>10416.4</v>
       </c>
       <c r="I79" t="n">
-        <v>25138.9</v>
+        <v>25153.9</v>
       </c>
       <c r="J79" t="n">
-        <v>23906.8</v>
+        <v>23907.8</v>
       </c>
       <c r="K79" t="n">
-        <v>52865.1</v>
+        <v>52872.6</v>
       </c>
       <c r="L79" t="n">
-        <v>2510.7</v>
+        <v>2510.85</v>
       </c>
       <c r="M79" t="n">
-        <v>6547.27</v>
+        <v>6547.57</v>
       </c>
       <c r="N79" t="n">
-        <v>5660.3</v>
+        <v>5661.8</v>
       </c>
     </row>
     <row r="80">
@@ -2910,7 +2910,7 @@
         <v>46117.20833333334</v>
       </c>
       <c r="B80" t="n">
-        <v>10417.9</v>
+        <v>10420.3</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -2931,40 +2931,40 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1.15422</v>
+        <v>1.154265</v>
       </c>
       <c r="D81" t="n">
-        <v>1.32328</v>
+        <v>1.323355</v>
       </c>
       <c r="E81" t="n">
-        <v>8024.1</v>
+        <v>8026.1</v>
       </c>
       <c r="F81" t="n">
-        <v>23291.6</v>
+        <v>23295.1</v>
       </c>
       <c r="G81" t="n">
-        <v>46707.1</v>
+        <v>46709.5</v>
       </c>
       <c r="H81" t="n">
-        <v>10475.6</v>
+        <v>10477.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25297</v>
+        <v>25312</v>
       </c>
       <c r="J81" t="n">
-        <v>24133.7</v>
+        <v>24134.7</v>
       </c>
       <c r="K81" t="n">
-        <v>53876.2</v>
+        <v>53883.7</v>
       </c>
       <c r="L81" t="n">
-        <v>2536.5</v>
+        <v>2536.65</v>
       </c>
       <c r="M81" t="n">
-        <v>6603.66</v>
+        <v>6603.96</v>
       </c>
       <c r="N81" t="n">
-        <v>5725.6</v>
+        <v>5727.1</v>
       </c>
     </row>
     <row r="82">
@@ -2972,7 +2972,7 @@
         <v>46118.20833333334</v>
       </c>
       <c r="B82" t="n">
-        <v>10673.3</v>
+        <v>10675.7</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -2993,40 +2993,40 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1.16675</v>
+        <v>1.166825</v>
       </c>
       <c r="D83" t="n">
-        <v>1.33725</v>
+        <v>1.337355</v>
       </c>
       <c r="E83" t="n">
-        <v>8191.7</v>
+        <v>8193.700000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>23798.8</v>
+        <v>23802.3</v>
       </c>
       <c r="G83" t="n">
-        <v>47543.4</v>
+        <v>47545.8</v>
       </c>
       <c r="H83" t="n">
-        <v>10555.1</v>
+        <v>10557.1</v>
       </c>
       <c r="I83" t="n">
-        <v>25605.5</v>
+        <v>25620.5</v>
       </c>
       <c r="J83" t="n">
-        <v>24747.9</v>
+        <v>24748.9</v>
       </c>
       <c r="K83" t="n">
-        <v>55934.9</v>
+        <v>55942.4</v>
       </c>
       <c r="L83" t="n">
-        <v>2623.6</v>
+        <v>2623.75</v>
       </c>
       <c r="M83" t="n">
-        <v>6752.12</v>
+        <v>6752.42</v>
       </c>
       <c r="N83" t="n">
-        <v>5844.2</v>
+        <v>5845.7</v>
       </c>
     </row>
     <row r="84">
@@ -3034,7 +3034,7 @@
         <v>46119.20833333334</v>
       </c>
       <c r="B84" t="n">
-        <v>9108.299999999999</v>
+        <v>9110.700000000001</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -3055,40 +3055,40 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1.16623</v>
+        <v>1.166275</v>
       </c>
       <c r="D85" t="n">
-        <v>1.33971</v>
+        <v>1.339785</v>
       </c>
       <c r="E85" t="n">
-        <v>8272.200000000001</v>
+        <v>8274.200000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>24001.7</v>
+        <v>24005.2</v>
       </c>
       <c r="G85" t="n">
-        <v>47884.1</v>
+        <v>47886.5</v>
       </c>
       <c r="H85" t="n">
-        <v>10657.2</v>
+        <v>10659.2</v>
       </c>
       <c r="I85" t="n">
-        <v>25862.5</v>
+        <v>25877.5</v>
       </c>
       <c r="J85" t="n">
-        <v>24863</v>
+        <v>24864</v>
       </c>
       <c r="K85" t="n">
-        <v>56743.2</v>
+        <v>56750.7</v>
       </c>
       <c r="L85" t="n">
-        <v>2621</v>
+        <v>2621.15</v>
       </c>
       <c r="M85" t="n">
-        <v>6775.54</v>
+        <v>6775.84</v>
       </c>
       <c r="N85" t="n">
-        <v>5912.1</v>
+        <v>5913.6</v>
       </c>
     </row>
     <row r="86">
@@ -3096,7 +3096,7 @@
         <v>46120.20833333334</v>
       </c>
       <c r="B86" t="n">
-        <v>9242.9</v>
+        <v>9245.299999999999</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -3117,40 +3117,40 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.16936</v>
+        <v>1.169405</v>
       </c>
       <c r="D87" t="n">
-        <v>1.34273</v>
+        <v>1.342805</v>
       </c>
       <c r="E87" t="n">
-        <v>8250.299999999999</v>
+        <v>8252.299999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>23856.6</v>
+        <v>23860.1</v>
       </c>
       <c r="G87" t="n">
-        <v>48152.7</v>
+        <v>48155.1</v>
       </c>
       <c r="H87" t="n">
-        <v>10592.9</v>
+        <v>10594.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25901.1</v>
+        <v>25916.1</v>
       </c>
       <c r="J87" t="n">
-        <v>25041.9</v>
+        <v>25042.9</v>
       </c>
       <c r="K87" t="n">
-        <v>56479.6</v>
+        <v>56487.1</v>
       </c>
       <c r="L87" t="n">
-        <v>2635.5</v>
+        <v>2635.65</v>
       </c>
       <c r="M87" t="n">
-        <v>6816.6</v>
+        <v>6816.9</v>
       </c>
       <c r="N87" t="n">
-        <v>5899.4</v>
+        <v>5900.9</v>
       </c>
     </row>
     <row r="88">
@@ -3158,7 +3158,7 @@
         <v>46121.20833333334</v>
       </c>
       <c r="B88" t="n">
-        <v>9240.299999999999</v>
+        <v>9242.700000000001</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -3179,40 +3179,40 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.17227</v>
+        <v>1.1726</v>
       </c>
       <c r="D89" t="n">
-        <v>1.34564</v>
+        <v>1.346235</v>
       </c>
       <c r="E89" t="n">
-        <v>8264.799999999999</v>
+        <v>8266.799999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>23820.4</v>
+        <v>23823.9</v>
       </c>
       <c r="G89" t="n">
-        <v>47967.1</v>
+        <v>47972</v>
       </c>
       <c r="H89" t="n">
-        <v>10603.1</v>
+        <v>10605.1</v>
       </c>
       <c r="I89" t="n">
-        <v>25933.9</v>
+        <v>25948.9</v>
       </c>
       <c r="J89" t="n">
-        <v>25162.2</v>
+        <v>25164.7</v>
       </c>
       <c r="K89" t="n">
-        <v>57391.8</v>
+        <v>57406.8</v>
       </c>
       <c r="L89" t="n">
-        <v>2635.8</v>
+        <v>2636.3</v>
       </c>
       <c r="M89" t="n">
-        <v>6824.8</v>
+        <v>6825.55</v>
       </c>
       <c r="N89" t="n">
-        <v>5927.41</v>
+        <v>5928.91</v>
       </c>
     </row>
     <row r="90">
@@ -3220,7 +3220,7 @@
         <v>46122.20833333334</v>
       </c>
       <c r="B90" t="n">
-        <v>9110.799999999999</v>
+        <v>9114.700000000001</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -3241,40 +3241,40 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.16721</v>
+        <v>1.167255</v>
       </c>
       <c r="D91" t="n">
-        <v>1.33938</v>
+        <v>1.339455</v>
       </c>
       <c r="E91" t="n">
-        <v>8128.9</v>
+        <v>8130.9</v>
       </c>
       <c r="F91" t="n">
-        <v>23434.6</v>
+        <v>23438.1</v>
       </c>
       <c r="G91" t="n">
-        <v>47400.6</v>
+        <v>47403</v>
       </c>
       <c r="H91" t="n">
-        <v>10521</v>
+        <v>10523</v>
       </c>
       <c r="I91" t="n">
-        <v>25755.2</v>
+        <v>25770.2</v>
       </c>
       <c r="J91" t="n">
-        <v>24790.8</v>
+        <v>24791.8</v>
       </c>
       <c r="K91" t="n">
-        <v>56078</v>
+        <v>56085.5</v>
       </c>
       <c r="L91" t="n">
-        <v>2587.7</v>
+        <v>2587.85</v>
       </c>
       <c r="M91" t="n">
-        <v>6740.25</v>
+        <v>6740.55</v>
       </c>
       <c r="N91" t="n">
-        <v>5830.3</v>
+        <v>5831.8</v>
       </c>
     </row>
     <row r="92">
@@ -3282,7 +3282,7 @@
         <v>46124.20833333334</v>
       </c>
       <c r="B92" t="n">
-        <v>9807</v>
+        <v>9809.4</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -3303,40 +3303,40 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.17609</v>
+        <v>1.176135</v>
       </c>
       <c r="D93" t="n">
-        <v>1.35099</v>
+        <v>1.351065</v>
       </c>
       <c r="E93" t="n">
-        <v>8266.299999999999</v>
+        <v>8268.299999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>23962</v>
+        <v>23965.5</v>
       </c>
       <c r="G93" t="n">
-        <v>48225.3</v>
+        <v>48227.7</v>
       </c>
       <c r="H93" t="n">
-        <v>10615.9</v>
+        <v>10617.9</v>
       </c>
       <c r="I93" t="n">
-        <v>25953.2</v>
+        <v>25968.2</v>
       </c>
       <c r="J93" t="n">
-        <v>25434.7</v>
+        <v>25435.7</v>
       </c>
       <c r="K93" t="n">
-        <v>57691.4</v>
+        <v>57698.9</v>
       </c>
       <c r="L93" t="n">
-        <v>2678</v>
+        <v>2678.15</v>
       </c>
       <c r="M93" t="n">
-        <v>6889.85</v>
+        <v>6890.15</v>
       </c>
       <c r="N93" t="n">
-        <v>5945.8</v>
+        <v>5947.3</v>
       </c>
     </row>
     <row r="94">
@@ -3344,7 +3344,7 @@
         <v>46125.20833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>9263.799999999999</v>
+        <v>9266.200000000001</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -3365,40 +3365,40 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.17944</v>
+        <v>1.179485</v>
       </c>
       <c r="D95" t="n">
-        <v>1.3568</v>
+        <v>1.356875</v>
       </c>
       <c r="E95" t="n">
-        <v>8324.9</v>
+        <v>8326.9</v>
       </c>
       <c r="F95" t="n">
-        <v>24051.4</v>
+        <v>24054.9</v>
       </c>
       <c r="G95" t="n">
-        <v>48535.3</v>
+        <v>48537.7</v>
       </c>
       <c r="H95" t="n">
-        <v>10622.6</v>
+        <v>10624.6</v>
       </c>
       <c r="I95" t="n">
-        <v>26197.7</v>
+        <v>26212.7</v>
       </c>
       <c r="J95" t="n">
-        <v>25829.8</v>
+        <v>25830.8</v>
       </c>
       <c r="K95" t="n">
-        <v>58698.5</v>
+        <v>58706</v>
       </c>
       <c r="L95" t="n">
-        <v>2705.4</v>
+        <v>2705.55</v>
       </c>
       <c r="M95" t="n">
-        <v>6967.47</v>
+        <v>6967.77</v>
       </c>
       <c r="N95" t="n">
-        <v>5984.9</v>
+        <v>5986.4</v>
       </c>
     </row>
     <row r="96">
@@ -3406,7 +3406,7 @@
         <v>46126.20833333334</v>
       </c>
       <c r="B96" t="n">
-        <v>8866.6</v>
+        <v>8869</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -3427,40 +3427,40 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.18019</v>
+        <v>1.180235</v>
       </c>
       <c r="D97" t="n">
-        <v>1.35671</v>
+        <v>1.356785</v>
       </c>
       <c r="E97" t="n">
-        <v>8262.799999999999</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>24103.6</v>
+        <v>24107.1</v>
       </c>
       <c r="G97" t="n">
-        <v>48525.4</v>
+        <v>48527.8</v>
       </c>
       <c r="H97" t="n">
-        <v>10554.1</v>
+        <v>10556.1</v>
       </c>
       <c r="I97" t="n">
-        <v>26115.4</v>
+        <v>26130.4</v>
       </c>
       <c r="J97" t="n">
-        <v>26228.3</v>
+        <v>26229.3</v>
       </c>
       <c r="K97" t="n">
-        <v>58556.3</v>
+        <v>58563.8</v>
       </c>
       <c r="L97" t="n">
-        <v>2716.2</v>
+        <v>2716.35</v>
       </c>
       <c r="M97" t="n">
-        <v>7027.99</v>
+        <v>7028.29</v>
       </c>
       <c r="N97" t="n">
-        <v>5945.4</v>
+        <v>5946.9</v>
       </c>
     </row>
     <row r="98">
@@ -3468,7 +3468,7 @@
         <v>46127.20833333334</v>
       </c>
       <c r="B98" t="n">
-        <v>8866</v>
+        <v>8868.4</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -3489,40 +3489,40 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.1785</v>
+        <v>1.178545</v>
       </c>
       <c r="D99" t="n">
-        <v>1.35314</v>
+        <v>1.353215</v>
       </c>
       <c r="E99" t="n">
-        <v>8264.4</v>
+        <v>8266.4</v>
       </c>
       <c r="F99" t="n">
-        <v>24137.4</v>
+        <v>24140.9</v>
       </c>
       <c r="G99" t="n">
-        <v>48658.7</v>
+        <v>48661.1</v>
       </c>
       <c r="H99" t="n">
-        <v>10588.9</v>
+        <v>10590.9</v>
       </c>
       <c r="I99" t="n">
-        <v>26221.3</v>
+        <v>26236.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26320.7</v>
+        <v>26321.7</v>
       </c>
       <c r="K99" t="n">
-        <v>59422.9</v>
+        <v>59430.4</v>
       </c>
       <c r="L99" t="n">
-        <v>2725</v>
+        <v>2725.15</v>
       </c>
       <c r="M99" t="n">
-        <v>7046.44</v>
+        <v>7046.74</v>
       </c>
       <c r="N99" t="n">
-        <v>5919.17</v>
+        <v>5920.67</v>
       </c>
     </row>
     <row r="100">
@@ -3530,7 +3530,7 @@
         <v>46128.20833333334</v>
       </c>
       <c r="B100" t="n">
-        <v>9027.799999999999</v>
+        <v>9030.200000000001</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -3551,40 +3551,40 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.17606</v>
+        <v>1.176345</v>
       </c>
       <c r="D101" t="n">
-        <v>1.35102</v>
+        <v>1.351615</v>
       </c>
       <c r="E101" t="n">
-        <v>8405.9</v>
+        <v>8407.9</v>
       </c>
       <c r="F101" t="n">
-        <v>24648.4</v>
+        <v>24651.9</v>
       </c>
       <c r="G101" t="n">
-        <v>49448.1</v>
+        <v>49453</v>
       </c>
       <c r="H101" t="n">
-        <v>10695.9</v>
+        <v>10697.9</v>
       </c>
       <c r="I101" t="n">
-        <v>26489.1</v>
+        <v>26504.1</v>
       </c>
       <c r="J101" t="n">
-        <v>26681.6</v>
+        <v>26684.1</v>
       </c>
       <c r="K101" t="n">
-        <v>59678.4</v>
+        <v>59693.4</v>
       </c>
       <c r="L101" t="n">
-        <v>2777.3</v>
+        <v>2777.8</v>
       </c>
       <c r="M101" t="n">
-        <v>7125.67</v>
+        <v>7126.42</v>
       </c>
       <c r="N101" t="n">
-        <v>6035.01</v>
+        <v>6036.51</v>
       </c>
     </row>
     <row r="102">
@@ -3592,7 +3592,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B102" t="n">
-        <v>8413.6</v>
+        <v>8417.5</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -3613,23 +3613,23 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.1739</v>
+        <v>1.173945</v>
       </c>
       <c r="D103" t="n">
-        <v>1.34863</v>
+        <v>1.348705</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>10631.2</v>
+        <v>10633.2</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>7073.46</v>
+        <v>7073.76</v>
       </c>
       <c r="N103" t="inlineStr"/>
     </row>
@@ -3638,7 +3638,7 @@
         <v>46131.20833333334</v>
       </c>
       <c r="B104" t="n">
-        <v>8908.5</v>
+        <v>8910.9</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -3659,23 +3659,23 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.17896</v>
+        <v>1.179005</v>
       </c>
       <c r="D105" t="n">
-        <v>1.35382</v>
+        <v>1.353895</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>10625.6</v>
+        <v>10627.6</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>7121.6</v>
+        <v>7121.9</v>
       </c>
       <c r="N105" t="inlineStr"/>
     </row>
@@ -3684,7 +3684,7 @@
         <v>46132.20833333334</v>
       </c>
       <c r="B106" t="n">
-        <v>8668.5</v>
+        <v>8670.9</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -3705,23 +3705,23 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.17388</v>
+        <v>1.173925</v>
       </c>
       <c r="D107" t="n">
-        <v>1.35016</v>
+        <v>1.350235</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>10464.5</v>
+        <v>10466.5</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>7088.69</v>
+        <v>7088.99</v>
       </c>
       <c r="N107" t="inlineStr"/>
     </row>
@@ -3730,7 +3730,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B108" t="n">
-        <v>8925.5</v>
+        <v>8926.9</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -3751,23 +3751,23 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>1.17055</v>
+        <v>1.170595</v>
       </c>
       <c r="D109" t="n">
-        <v>1.35014</v>
+        <v>1.350215</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>10458.2</v>
+        <v>10460.2</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>7126.92</v>
+        <v>7127.22</v>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
@@ -3776,7 +3776,7 @@
         <v>46134.20833333334</v>
       </c>
       <c r="B110" t="n">
-        <v>9450.700000000001</v>
+        <v>9453.1</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -3797,23 +3797,23 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1.16859</v>
+        <v>1.168635</v>
       </c>
       <c r="D111" t="n">
-        <v>1.34666</v>
+        <v>1.346735</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10415.5</v>
+        <v>10417.5</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>7113.93</v>
+        <v>7114.23</v>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
@@ -3822,7 +3822,7 @@
         <v>46135.20833333334</v>
       </c>
       <c r="B112" t="n">
-        <v>9658.700000000001</v>
+        <v>9661.1</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -3843,23 +3843,23 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1.17154</v>
+        <v>1.171835</v>
       </c>
       <c r="D113" t="n">
-        <v>1.3525</v>
+        <v>1.353095</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>10385.5</v>
+        <v>10387.5</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>7162.94</v>
+        <v>7163.69</v>
       </c>
       <c r="N113" t="inlineStr"/>
     </row>
@@ -3868,7 +3868,7 @@
         <v>46136.20833333334</v>
       </c>
       <c r="B114" t="n">
-        <v>9484.4</v>
+        <v>9486.799999999999</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -3889,23 +3889,23 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1.17078</v>
+        <v>1.170825</v>
       </c>
       <c r="D115" t="n">
-        <v>1.35149</v>
+        <v>1.351595</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>10368.5</v>
+        <v>10370.5</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>7150.97</v>
+        <v>7151.27</v>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
@@ -3914,7 +3914,7 @@
         <v>46138.20833333334</v>
       </c>
       <c r="B116" t="n">
-        <v>9527.700000000001</v>
+        <v>9529.1</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -3935,23 +3935,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.17216</v>
+        <v>1.172205</v>
       </c>
       <c r="D117" t="n">
-        <v>1.3535</v>
+        <v>1.353575</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10330.5</v>
+        <v>10332.5</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7185.65</v>
+        <v>7185.95</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -3960,7 +3960,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9759.5</v>
+        <v>9761.9</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -3981,23 +3981,23 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>1.17154</v>
+        <v>1.171585</v>
       </c>
       <c r="D119" t="n">
-        <v>1.35207</v>
+        <v>1.352145</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>10309.6</v>
+        <v>10311.6</v>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
-        <v>7145.07</v>
+        <v>7145.37</v>
       </c>
       <c r="N119" t="inlineStr"/>
     </row>
@@ -4006,7 +4006,7 @@
         <v>46140.20833333334</v>
       </c>
       <c r="B120" t="n">
-        <v>9928.700000000001</v>
+        <v>9931.1</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
@@ -4027,23 +4027,23 @@
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>1.16778</v>
+        <v>1.167825</v>
       </c>
       <c r="D121" t="n">
-        <v>1.34793</v>
+        <v>1.348005</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>10205.5</v>
+        <v>10207.5</v>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
-        <v>7154.52</v>
+        <v>7154.82</v>
       </c>
       <c r="N121" t="inlineStr"/>
     </row>
@@ -4052,7 +4052,7 @@
         <v>46141.20833333334</v>
       </c>
       <c r="B122" t="n">
-        <v>10909.4</v>
+        <v>10911.8</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
@@ -4073,23 +4073,23 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>1.17314</v>
+        <v>1.173185</v>
       </c>
       <c r="D123" t="n">
-        <v>1.36038</v>
+        <v>1.360455</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>10361.4</v>
+        <v>10363.4</v>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>7220.22</v>
+        <v>7220.52</v>
       </c>
       <c r="N123" t="inlineStr"/>
     </row>
@@ -4098,7 +4098,7 @@
         <v>46142.20833333334</v>
       </c>
       <c r="B124" t="n">
-        <v>10549</v>
+        <v>10551.4</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
@@ -4119,23 +4119,23 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>1.17168</v>
+        <v>1.171725</v>
       </c>
       <c r="D125" t="n">
-        <v>1.357</v>
+        <v>1.357075</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>10349</v>
+        <v>10351</v>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
-        <v>7218.63</v>
+        <v>7218.93</v>
       </c>
       <c r="N125" t="inlineStr"/>
     </row>
@@ -4144,7 +4144,7 @@
         <v>46143.20833333334</v>
       </c>
       <c r="B126" t="n">
-        <v>10257</v>
+        <v>10259.4</v>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
@@ -4246,10 +4246,10 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.178815</v>
+        <v>1.17877</v>
       </c>
       <c r="D2" t="n">
-        <v>1.349475</v>
+        <v>1.34943</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -4260,7 +4260,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>6878.96</v>
+        <v>6878.66</v>
       </c>
       <c r="N2" t="inlineStr"/>
     </row>
@@ -4269,7 +4269,7 @@
         <v>46071.20833333334</v>
       </c>
       <c r="B3" t="n">
-        <v>6521.200000000001</v>
+        <v>6519.3</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -4290,40 +4290,40 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.17686</v>
+        <v>1.17683</v>
       </c>
       <c r="D4" t="n">
-        <v>1.345965</v>
+        <v>1.34592</v>
       </c>
       <c r="E4" t="n">
-        <v>8417.9</v>
+        <v>8415.9</v>
       </c>
       <c r="F4" t="n">
-        <v>25033.6</v>
+        <v>25030.1</v>
       </c>
       <c r="G4" t="n">
-        <v>49410</v>
+        <v>49407.6</v>
       </c>
       <c r="H4" t="n">
-        <v>10670.2</v>
+        <v>10668.2</v>
       </c>
       <c r="I4" t="n">
-        <v>26796.7</v>
+        <v>26781.7</v>
       </c>
       <c r="J4" t="n">
-        <v>24817.3</v>
+        <v>24816.3</v>
       </c>
       <c r="K4" t="n">
-        <v>57084.2</v>
+        <v>57080.7</v>
       </c>
       <c r="L4" t="n">
-        <v>2661.95</v>
+        <v>2661.8</v>
       </c>
       <c r="M4" t="n">
-        <v>6865.84</v>
+        <v>6865.54</v>
       </c>
       <c r="N4" t="n">
-        <v>6065.4</v>
+        <v>6063.9</v>
       </c>
     </row>
     <row r="5">
@@ -4331,7 +4331,7 @@
         <v>46072.20833333334</v>
       </c>
       <c r="B5" t="n">
-        <v>6672.200000000001</v>
+        <v>6670.8</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -4352,40 +4352,40 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.17822</v>
+        <v>1.17797</v>
       </c>
       <c r="D6" t="n">
-        <v>1.348245</v>
+        <v>1.34765</v>
       </c>
       <c r="E6" t="n">
-        <v>8535.4</v>
+        <v>8533.4</v>
       </c>
       <c r="F6" t="n">
-        <v>25236.6</v>
+        <v>25233.1</v>
       </c>
       <c r="G6" t="n">
-        <v>49624.8</v>
+        <v>49619.9</v>
       </c>
       <c r="H6" t="n">
-        <v>10720.4</v>
+        <v>10718.4</v>
       </c>
       <c r="I6" t="n">
-        <v>26863.4</v>
+        <v>26848.4</v>
       </c>
       <c r="J6" t="n">
-        <v>25016.2</v>
+        <v>25013.7</v>
       </c>
       <c r="K6" t="n">
-        <v>57088.3</v>
+        <v>57073.3</v>
       </c>
       <c r="L6" t="n">
-        <v>2662.2</v>
+        <v>2661.7</v>
       </c>
       <c r="M6" t="n">
-        <v>6910.63</v>
+        <v>6909.88</v>
       </c>
       <c r="N6" t="n">
-        <v>6135.1</v>
+        <v>6133.6</v>
       </c>
     </row>
     <row r="7">
@@ -4393,7 +4393,7 @@
         <v>46073.20833333334</v>
       </c>
       <c r="B7" t="n">
-        <v>6630.200000000001</v>
+        <v>6628.3</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -4414,40 +4414,40 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.18331</v>
+        <v>1.18328</v>
       </c>
       <c r="D8" t="n">
-        <v>1.353205</v>
+        <v>1.35316</v>
       </c>
       <c r="E8" t="n">
-        <v>8515.200000000001</v>
+        <v>8513.200000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>25176</v>
+        <v>25172.5</v>
       </c>
       <c r="G8" t="n">
-        <v>49528.4</v>
+        <v>49526</v>
       </c>
       <c r="H8" t="n">
-        <v>10703.4</v>
+        <v>10701.4</v>
       </c>
       <c r="I8" t="n">
-        <v>26826.4</v>
+        <v>26811.4</v>
       </c>
       <c r="J8" t="n">
-        <v>24911.3</v>
+        <v>24910.3</v>
       </c>
       <c r="K8" t="n">
-        <v>56981.6</v>
+        <v>56978.1</v>
       </c>
       <c r="L8" t="n">
-        <v>2652.65</v>
+        <v>2652.5</v>
       </c>
       <c r="M8" t="n">
-        <v>6892.28</v>
+        <v>6891.98</v>
       </c>
       <c r="N8" t="n">
-        <v>6120.4</v>
+        <v>6118.9</v>
       </c>
     </row>
     <row r="9">
@@ -4455,7 +4455,7 @@
         <v>46075.20833333334</v>
       </c>
       <c r="B9" t="n">
-        <v>6557.700000000001</v>
+        <v>6556.3</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -4476,40 +4476,40 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.179325</v>
+        <v>1.17928</v>
       </c>
       <c r="D10" t="n">
-        <v>1.349555</v>
+        <v>1.34948</v>
       </c>
       <c r="E10" t="n">
-        <v>8506.6</v>
+        <v>8504.6</v>
       </c>
       <c r="F10" t="n">
-        <v>24996.5</v>
+        <v>24993</v>
       </c>
       <c r="G10" t="n">
-        <v>48839.5</v>
+        <v>48837.1</v>
       </c>
       <c r="H10" t="n">
-        <v>10692.7</v>
+        <v>10690.7</v>
       </c>
       <c r="I10" t="n">
-        <v>26891.9</v>
+        <v>26876.9</v>
       </c>
       <c r="J10" t="n">
-        <v>24735.3</v>
+        <v>24734.3</v>
       </c>
       <c r="K10" t="n">
-        <v>56665.8</v>
+        <v>56662.3</v>
       </c>
       <c r="L10" t="n">
-        <v>2621.45</v>
+        <v>2621.3</v>
       </c>
       <c r="M10" t="n">
-        <v>6844.309999999999</v>
+        <v>6844.01</v>
       </c>
       <c r="N10" t="n">
-        <v>6123.3</v>
+        <v>6121.8</v>
       </c>
     </row>
     <row r="11">
@@ -4517,7 +4517,7 @@
         <v>46076.20833333334</v>
       </c>
       <c r="B11" t="n">
-        <v>6676.299999999999</v>
+        <v>6674.9</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -4538,40 +4538,40 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.17743</v>
+        <v>1.1774</v>
       </c>
       <c r="D12" t="n">
-        <v>1.349605</v>
+        <v>1.34956</v>
       </c>
       <c r="E12" t="n">
-        <v>8539.9</v>
+        <v>8537.9</v>
       </c>
       <c r="F12" t="n">
-        <v>25039.3</v>
+        <v>25035.8</v>
       </c>
       <c r="G12" t="n">
-        <v>49177.5</v>
+        <v>49175.1</v>
       </c>
       <c r="H12" t="n">
-        <v>10712.4</v>
+        <v>10710.4</v>
       </c>
       <c r="I12" t="n">
-        <v>26766.2</v>
+        <v>26751.2</v>
       </c>
       <c r="J12" t="n">
-        <v>24995.3</v>
+        <v>24994.3</v>
       </c>
       <c r="K12" t="n">
-        <v>57912</v>
+        <v>57908.5</v>
       </c>
       <c r="L12" t="n">
-        <v>2651.55</v>
+        <v>2651.4</v>
       </c>
       <c r="M12" t="n">
-        <v>6892.08</v>
+        <v>6891.78</v>
       </c>
       <c r="N12" t="n">
-        <v>6136.1</v>
+        <v>6134.6</v>
       </c>
     </row>
     <row r="13">
@@ -4579,7 +4579,7 @@
         <v>46077.20833333334</v>
       </c>
       <c r="B13" t="n">
-        <v>6598.9</v>
+        <v>6597.5</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -4600,40 +4600,40 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.18154</v>
+        <v>1.18151</v>
       </c>
       <c r="D14" t="n">
-        <v>1.355805</v>
+        <v>1.35576</v>
       </c>
       <c r="E14" t="n">
-        <v>8569.6</v>
+        <v>8567.6</v>
       </c>
       <c r="F14" t="n">
-        <v>25181.3</v>
+        <v>25177.8</v>
       </c>
       <c r="G14" t="n">
-        <v>49392</v>
+        <v>49389.6</v>
       </c>
       <c r="H14" t="n">
-        <v>10804.4</v>
+        <v>10802.4</v>
       </c>
       <c r="I14" t="n">
-        <v>26950</v>
+        <v>26935</v>
       </c>
       <c r="J14" t="n">
-        <v>25270</v>
+        <v>25269</v>
       </c>
       <c r="K14" t="n">
-        <v>59285.1</v>
+        <v>59281.6</v>
       </c>
       <c r="L14" t="n">
-        <v>2660.65</v>
+        <v>2660.5</v>
       </c>
       <c r="M14" t="n">
-        <v>6937.66</v>
+        <v>6937.36</v>
       </c>
       <c r="N14" t="n">
-        <v>6175.7</v>
+        <v>6174.2</v>
       </c>
     </row>
     <row r="15">
@@ -4641,7 +4641,7 @@
         <v>46078.20833333334</v>
       </c>
       <c r="B15" t="n">
-        <v>6556.6</v>
+        <v>6555.2</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -4662,40 +4662,40 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.180365</v>
+        <v>1.18032</v>
       </c>
       <c r="D16" t="n">
-        <v>1.349155</v>
+        <v>1.34911</v>
       </c>
       <c r="E16" t="n">
-        <v>8611.700000000001</v>
+        <v>8609.700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>25253.3</v>
+        <v>25249.8</v>
       </c>
       <c r="G16" t="n">
-        <v>49229.6</v>
+        <v>49227.2</v>
       </c>
       <c r="H16" t="n">
-        <v>10835.1</v>
+        <v>10833.1</v>
       </c>
       <c r="I16" t="n">
-        <v>26389.6</v>
+        <v>26374.6</v>
       </c>
       <c r="J16" t="n">
-        <v>24955.6</v>
+        <v>24954.6</v>
       </c>
       <c r="K16" t="n">
-        <v>58435</v>
+        <v>58431.5</v>
       </c>
       <c r="L16" t="n">
-        <v>2655.55</v>
+        <v>2655.4</v>
       </c>
       <c r="M16" t="n">
-        <v>6882.360000000001</v>
+        <v>6882.06</v>
       </c>
       <c r="N16" t="n">
-        <v>6150.7</v>
+        <v>6149.2</v>
       </c>
     </row>
     <row r="17">
@@ -4703,7 +4703,7 @@
         <v>46079.20833333334</v>
       </c>
       <c r="B17" t="n">
-        <v>6531.799999999999</v>
+        <v>6530.4</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -4724,40 +4724,40 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>1.18179</v>
+        <v>1.18146</v>
       </c>
       <c r="D18" t="n">
-        <v>1.34806</v>
+        <v>1.34768</v>
       </c>
       <c r="E18" t="n">
-        <v>8530.6</v>
+        <v>8528.6</v>
       </c>
       <c r="F18" t="n">
-        <v>25143.7</v>
+        <v>25140.2</v>
       </c>
       <c r="G18" t="n">
-        <v>48858.5</v>
+        <v>48853.6</v>
       </c>
       <c r="H18" t="n">
-        <v>10862.7</v>
+        <v>10860.7</v>
       </c>
       <c r="I18" t="n">
-        <v>26490.4</v>
+        <v>26475.4</v>
       </c>
       <c r="J18" t="n">
-        <v>24914.4</v>
+        <v>24913.4</v>
       </c>
       <c r="K18" t="n">
-        <v>58612.7</v>
+        <v>58609.2</v>
       </c>
       <c r="L18" t="n">
-        <v>2626.65</v>
+        <v>2626.5</v>
       </c>
       <c r="M18" t="n">
-        <v>6865.58</v>
+        <v>6864.83</v>
       </c>
       <c r="N18" t="n">
-        <v>6095.38</v>
+        <v>6093.88</v>
       </c>
     </row>
     <row r="19">
@@ -4765,7 +4765,7 @@
         <v>46080.20833333334</v>
       </c>
       <c r="B19" t="n">
-        <v>6725.5</v>
+        <v>6724.1</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -4786,40 +4786,40 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1.17594</v>
+        <v>1.17591</v>
       </c>
       <c r="D20" t="n">
-        <v>1.340525</v>
+        <v>1.34048</v>
       </c>
       <c r="E20" t="n">
-        <v>8466.4</v>
+        <v>8464.4</v>
       </c>
       <c r="F20" t="n">
-        <v>24946.3</v>
+        <v>24942.8</v>
       </c>
       <c r="G20" t="n">
-        <v>48368.8</v>
+        <v>48366.4</v>
       </c>
       <c r="H20" t="n">
-        <v>10811.6</v>
+        <v>10809.6</v>
       </c>
       <c r="I20" t="n">
-        <v>26350.6</v>
+        <v>26335.6</v>
       </c>
       <c r="J20" t="n">
-        <v>24696.7</v>
+        <v>24695.7</v>
       </c>
       <c r="K20" t="n">
-        <v>57488.1</v>
+        <v>57484.6</v>
       </c>
       <c r="L20" t="n">
-        <v>2591.25</v>
+        <v>2591.1</v>
       </c>
       <c r="M20" t="n">
-        <v>6805.95</v>
+        <v>6805.65</v>
       </c>
       <c r="N20" t="n">
-        <v>6049.58</v>
+        <v>6048.08</v>
       </c>
     </row>
     <row r="21">
@@ -4827,7 +4827,7 @@
         <v>46082.20833333334</v>
       </c>
       <c r="B21" t="n">
-        <v>7100.799999999999</v>
+        <v>7098.9</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -4848,40 +4848,40 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1.169435</v>
+        <v>1.16939</v>
       </c>
       <c r="D22" t="n">
-        <v>1.340815</v>
+        <v>1.34077</v>
       </c>
       <c r="E22" t="n">
-        <v>8387.700000000001</v>
+        <v>8385.700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>24582.2</v>
+        <v>24578.7</v>
       </c>
       <c r="G22" t="n">
-        <v>48823.6</v>
+        <v>48821.2</v>
       </c>
       <c r="H22" t="n">
-        <v>10789.5</v>
+        <v>10787.5</v>
       </c>
       <c r="I22" t="n">
-        <v>26156.8</v>
+        <v>26141.8</v>
       </c>
       <c r="J22" t="n">
-        <v>24935.3</v>
+        <v>24934.3</v>
       </c>
       <c r="K22" t="n">
-        <v>57713.1</v>
+        <v>57709.6</v>
       </c>
       <c r="L22" t="n">
-        <v>2650.85</v>
+        <v>2650.7</v>
       </c>
       <c r="M22" t="n">
-        <v>6867.940000000001</v>
+        <v>6867.64</v>
       </c>
       <c r="N22" t="n">
-        <v>5982.2</v>
+        <v>5980.7</v>
       </c>
     </row>
     <row r="23">
@@ -4889,7 +4889,7 @@
         <v>46083.20833333334</v>
       </c>
       <c r="B23" t="n">
-        <v>7242.4</v>
+        <v>7240.5</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -4910,40 +4910,40 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>1.1611</v>
+        <v>1.16107</v>
       </c>
       <c r="D24" t="n">
-        <v>1.335115</v>
+        <v>1.33507</v>
       </c>
       <c r="E24" t="n">
-        <v>8165.4</v>
+        <v>8163.4</v>
       </c>
       <c r="F24" t="n">
-        <v>23985</v>
+        <v>23981.5</v>
       </c>
       <c r="G24" t="n">
-        <v>48413.3</v>
+        <v>48410.9</v>
       </c>
       <c r="H24" t="n">
-        <v>10517.1</v>
+        <v>10515.1</v>
       </c>
       <c r="I24" t="n">
-        <v>25468.5</v>
+        <v>25453.5</v>
       </c>
       <c r="J24" t="n">
-        <v>24668</v>
+        <v>24667</v>
       </c>
       <c r="K24" t="n">
-        <v>54951.7</v>
+        <v>54948.2</v>
       </c>
       <c r="L24" t="n">
-        <v>2603.45</v>
+        <v>2603.3</v>
       </c>
       <c r="M24" t="n">
-        <v>6802.5</v>
+        <v>6802.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5813.3</v>
+        <v>5811.8</v>
       </c>
     </row>
     <row r="25">
@@ -4951,7 +4951,7 @@
         <v>46084.20833333334</v>
       </c>
       <c r="B25" t="n">
-        <v>7496.700000000001</v>
+        <v>7494.8</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
@@ -4972,40 +4972,40 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.163505</v>
+        <v>1.16346</v>
       </c>
       <c r="D26" t="n">
-        <v>1.336925</v>
+        <v>1.33688</v>
       </c>
       <c r="E26" t="n">
-        <v>8204</v>
+        <v>8202</v>
       </c>
       <c r="F26" t="n">
-        <v>24302.2</v>
+        <v>24298.7</v>
       </c>
       <c r="G26" t="n">
-        <v>48753.2</v>
+        <v>48750.8</v>
       </c>
       <c r="H26" t="n">
-        <v>10626.8</v>
+        <v>10624.8</v>
       </c>
       <c r="I26" t="n">
-        <v>25602.8</v>
+        <v>25587.8</v>
       </c>
       <c r="J26" t="n">
-        <v>25137.1</v>
+        <v>25136.1</v>
       </c>
       <c r="K26" t="n">
-        <v>56232.9</v>
+        <v>56229.4</v>
       </c>
       <c r="L26" t="n">
-        <v>2635.85</v>
+        <v>2635.7</v>
       </c>
       <c r="M26" t="n">
-        <v>6878.04</v>
+        <v>6877.74</v>
       </c>
       <c r="N26" t="n">
-        <v>5901.9</v>
+        <v>5900.4</v>
       </c>
     </row>
     <row r="27">
@@ -5013,7 +5013,7 @@
         <v>46085.20833333334</v>
       </c>
       <c r="B27" t="n">
-        <v>7666</v>
+        <v>7664.1</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -5034,40 +5034,40 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>1.16067</v>
+        <v>1.16064</v>
       </c>
       <c r="D28" t="n">
-        <v>1.335565</v>
+        <v>1.33552</v>
       </c>
       <c r="E28" t="n">
-        <v>8059.2</v>
+        <v>8057.2</v>
       </c>
       <c r="F28" t="n">
-        <v>23866.2</v>
+        <v>23862.7</v>
       </c>
       <c r="G28" t="n">
-        <v>48034</v>
+        <v>48031.6</v>
       </c>
       <c r="H28" t="n">
-        <v>10407.9</v>
+        <v>10405.9</v>
       </c>
       <c r="I28" t="n">
-        <v>25202.5</v>
+        <v>25187.5</v>
       </c>
       <c r="J28" t="n">
-        <v>25031.4</v>
+        <v>25030.4</v>
       </c>
       <c r="K28" t="n">
-        <v>54563.2</v>
+        <v>54559.7</v>
       </c>
       <c r="L28" t="n">
-        <v>2592.85</v>
+        <v>2592.7</v>
       </c>
       <c r="M28" t="n">
-        <v>6834.43</v>
+        <v>6834.13</v>
       </c>
       <c r="N28" t="n">
-        <v>5793.6</v>
+        <v>5792.1</v>
       </c>
     </row>
     <row r="29">
@@ -5075,7 +5075,7 @@
         <v>46086.20833333334</v>
       </c>
       <c r="B29" t="n">
-        <v>7887.5</v>
+        <v>7885.6</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
@@ -5096,40 +5096,40 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1.161695</v>
+        <v>1.16139</v>
       </c>
       <c r="D30" t="n">
-        <v>1.340985</v>
+        <v>1.34039</v>
       </c>
       <c r="E30" t="n">
-        <v>8017.2</v>
+        <v>8015.2</v>
       </c>
       <c r="F30" t="n">
-        <v>23640.3</v>
+        <v>23636.8</v>
       </c>
       <c r="G30" t="n">
-        <v>47434.2</v>
+        <v>47429.3</v>
       </c>
       <c r="H30" t="n">
-        <v>10318.8</v>
+        <v>10316.8</v>
       </c>
       <c r="I30" t="n">
-        <v>25325.2</v>
+        <v>25310.2</v>
       </c>
       <c r="J30" t="n">
-        <v>24634.2</v>
+        <v>24631.7</v>
       </c>
       <c r="K30" t="n">
-        <v>54029.9</v>
+        <v>54014.9</v>
       </c>
       <c r="L30" t="n">
-        <v>2522</v>
+        <v>2521.5</v>
       </c>
       <c r="M30" t="n">
-        <v>6733.23</v>
+        <v>6732.48</v>
       </c>
       <c r="N30" t="n">
-        <v>5723.03</v>
+        <v>5721.53</v>
       </c>
     </row>
     <row r="31">
@@ -5137,7 +5137,7 @@
         <v>46087.20833333334</v>
       </c>
       <c r="B31" t="n">
-        <v>8947.799999999999</v>
+        <v>8943.9</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
@@ -5158,40 +5158,40 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1.152455</v>
+        <v>1.15241</v>
       </c>
       <c r="D32" t="n">
-        <v>1.330515</v>
+        <v>1.33047</v>
       </c>
       <c r="E32" t="n">
-        <v>7873</v>
+        <v>7871</v>
       </c>
       <c r="F32" t="n">
-        <v>23222.3</v>
+        <v>23218.8</v>
       </c>
       <c r="G32" t="n">
-        <v>46613</v>
+        <v>46610.6</v>
       </c>
       <c r="H32" t="n">
-        <v>10195.8</v>
+        <v>10193.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25042.2</v>
+        <v>25027.2</v>
       </c>
       <c r="J32" t="n">
-        <v>24187.4</v>
+        <v>24186.4</v>
       </c>
       <c r="K32" t="n">
-        <v>52216.5</v>
+        <v>52213</v>
       </c>
       <c r="L32" t="n">
-        <v>2433.35</v>
+        <v>2433.2</v>
       </c>
       <c r="M32" t="n">
-        <v>6622.45</v>
+        <v>6622.15</v>
       </c>
       <c r="N32" t="n">
-        <v>5615.9</v>
+        <v>5614.4</v>
       </c>
     </row>
     <row r="33">
@@ -5199,7 +5199,7 @@
         <v>46089.20833333334</v>
       </c>
       <c r="B33" t="n">
-        <v>11228.6</v>
+        <v>11224.7</v>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
@@ -5220,40 +5220,40 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1.161615</v>
+        <v>1.16157</v>
       </c>
       <c r="D34" t="n">
-        <v>1.342445</v>
+        <v>1.3424</v>
       </c>
       <c r="E34" t="n">
-        <v>8000.3</v>
+        <v>7998.3</v>
       </c>
       <c r="F34" t="n">
-        <v>23703.1</v>
+        <v>23699.6</v>
       </c>
       <c r="G34" t="n">
-        <v>47534.3</v>
+        <v>47531.9</v>
       </c>
       <c r="H34" t="n">
-        <v>10307.8</v>
+        <v>10305.8</v>
       </c>
       <c r="I34" t="n">
-        <v>25545.7</v>
+        <v>25530.7</v>
       </c>
       <c r="J34" t="n">
-        <v>24854.1</v>
+        <v>24853.1</v>
       </c>
       <c r="K34" t="n">
-        <v>54259.6</v>
+        <v>54256.1</v>
       </c>
       <c r="L34" t="n">
-        <v>2534.05</v>
+        <v>2533.9</v>
       </c>
       <c r="M34" t="n">
-        <v>6766.07</v>
+        <v>6765.77</v>
       </c>
       <c r="N34" t="n">
-        <v>5764.7</v>
+        <v>5763.2</v>
       </c>
     </row>
     <row r="35">
@@ -5261,7 +5261,7 @@
         <v>46090.16666666666</v>
       </c>
       <c r="B35" t="n">
-        <v>8805.4</v>
+        <v>8801.5</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
@@ -5282,40 +5282,40 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>1.161195</v>
+        <v>1.16115</v>
       </c>
       <c r="D36" t="n">
-        <v>1.341985</v>
+        <v>1.34194</v>
       </c>
       <c r="E36" t="n">
-        <v>7996.9</v>
+        <v>7994.9</v>
       </c>
       <c r="F36" t="n">
-        <v>23809.1</v>
+        <v>23805.6</v>
       </c>
       <c r="G36" t="n">
-        <v>47744.5</v>
+        <v>47742.1</v>
       </c>
       <c r="H36" t="n">
-        <v>10385.1</v>
+        <v>10383.1</v>
       </c>
       <c r="I36" t="n">
-        <v>25945.2</v>
+        <v>25930.2</v>
       </c>
       <c r="J36" t="n">
-        <v>24990.4</v>
+        <v>24989.4</v>
       </c>
       <c r="K36" t="n">
-        <v>55066.9</v>
+        <v>55063.4</v>
       </c>
       <c r="L36" t="n">
-        <v>2552.05</v>
+        <v>2551.9</v>
       </c>
       <c r="M36" t="n">
-        <v>6791.25</v>
+        <v>6790.95</v>
       </c>
       <c r="N36" t="n">
-        <v>5786.9</v>
+        <v>5785.4</v>
       </c>
     </row>
     <row r="37">
@@ -5323,7 +5323,7 @@
         <v>46091.16666666666</v>
       </c>
       <c r="B37" t="n">
-        <v>8214.299999999999</v>
+        <v>8210.4</v>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
@@ -5344,40 +5344,40 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1.154265</v>
+        <v>1.15422</v>
       </c>
       <c r="D38" t="n">
-        <v>1.338255</v>
+        <v>1.33821</v>
       </c>
       <c r="E38" t="n">
-        <v>7976.9</v>
+        <v>7974.9</v>
       </c>
       <c r="F38" t="n">
-        <v>23465.2</v>
+        <v>23461.7</v>
       </c>
       <c r="G38" t="n">
-        <v>47030.3</v>
+        <v>47027.9</v>
       </c>
       <c r="H38" t="n">
-        <v>10272.4</v>
+        <v>10270.4</v>
       </c>
       <c r="I38" t="n">
-        <v>25634.7</v>
+        <v>25619.7</v>
       </c>
       <c r="J38" t="n">
-        <v>24768.1</v>
+        <v>24767.1</v>
       </c>
       <c r="K38" t="n">
-        <v>54158</v>
+        <v>54154.5</v>
       </c>
       <c r="L38" t="n">
-        <v>2505.75</v>
+        <v>2505.6</v>
       </c>
       <c r="M38" t="n">
-        <v>6724.610000000001</v>
+        <v>6724.31</v>
       </c>
       <c r="N38" t="n">
-        <v>5752.63</v>
+        <v>5751.13</v>
       </c>
     </row>
     <row r="39">
@@ -5385,7 +5385,7 @@
         <v>46092.16666666666</v>
       </c>
       <c r="B39" t="n">
-        <v>9366.299999999999</v>
+        <v>9363.9</v>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
@@ -5406,40 +5406,40 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>1.152065</v>
+        <v>1.15202</v>
       </c>
       <c r="D40" t="n">
-        <v>1.335115</v>
+        <v>1.33507</v>
       </c>
       <c r="E40" t="n">
-        <v>7964.5</v>
+        <v>7962.5</v>
       </c>
       <c r="F40" t="n">
-        <v>23495</v>
+        <v>23491.5</v>
       </c>
       <c r="G40" t="n">
-        <v>46739.9</v>
+        <v>46737.5</v>
       </c>
       <c r="H40" t="n">
-        <v>10283.7</v>
+        <v>10281.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25453.6</v>
+        <v>25438.6</v>
       </c>
       <c r="J40" t="n">
-        <v>24514</v>
+        <v>24513</v>
       </c>
       <c r="K40" t="n">
-        <v>53462.2</v>
+        <v>53458.7</v>
       </c>
       <c r="L40" t="n">
-        <v>2490.95</v>
+        <v>2490.8</v>
       </c>
       <c r="M40" t="n">
-        <v>6676.01</v>
+        <v>6675.71</v>
       </c>
       <c r="N40" t="n">
-        <v>5725.3</v>
+        <v>5723.8</v>
       </c>
     </row>
     <row r="41">
@@ -5447,7 +5447,7 @@
         <v>46093.16666666666</v>
       </c>
       <c r="B41" t="n">
-        <v>9468.4</v>
+        <v>9466</v>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
@@ -5468,40 +5468,40 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.141665</v>
+        <v>1.14162</v>
       </c>
       <c r="D42" t="n">
-        <v>1.32235</v>
+        <v>1.3218</v>
       </c>
       <c r="E42" t="n">
-        <v>7875.6</v>
+        <v>7874.6</v>
       </c>
       <c r="F42" t="n">
-        <v>23329.3</v>
+        <v>23327.9</v>
       </c>
       <c r="G42" t="n">
-        <v>46475.1</v>
+        <v>46470.2</v>
       </c>
       <c r="H42" t="n">
-        <v>10240.1</v>
+        <v>10238.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25400.4</v>
+        <v>25385.4</v>
       </c>
       <c r="J42" t="n">
-        <v>24321.2</v>
+        <v>24318.7</v>
       </c>
       <c r="K42" t="n">
-        <v>53150.3</v>
+        <v>53135.3</v>
       </c>
       <c r="L42" t="n">
-        <v>2474.5</v>
+        <v>2474</v>
       </c>
       <c r="M42" t="n">
-        <v>6621.04</v>
+        <v>6620.29</v>
       </c>
       <c r="N42" t="n">
-        <v>5689.36</v>
+        <v>5688.61</v>
       </c>
     </row>
     <row r="43">
@@ -5509,7 +5509,7 @@
         <v>46094.16666666666</v>
       </c>
       <c r="B43" t="n">
-        <v>9766.4</v>
+        <v>9764</v>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
@@ -5530,40 +5530,40 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1.143595</v>
+        <v>1.14355</v>
       </c>
       <c r="D44" t="n">
-        <v>1.324575</v>
+        <v>1.3245</v>
       </c>
       <c r="E44" t="n">
-        <v>7919.5</v>
+        <v>7917.5</v>
       </c>
       <c r="F44" t="n">
-        <v>23428.6</v>
+        <v>23425.1</v>
       </c>
       <c r="G44" t="n">
-        <v>46641.8</v>
+        <v>46639.4</v>
       </c>
       <c r="H44" t="n">
-        <v>10268.8</v>
+        <v>10266.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25450.7</v>
+        <v>25435.7</v>
       </c>
       <c r="J44" t="n">
-        <v>24424</v>
+        <v>24423</v>
       </c>
       <c r="K44" t="n">
-        <v>53651.9</v>
+        <v>53648.4</v>
       </c>
       <c r="L44" t="n">
-        <v>2489.45</v>
+        <v>2489.3</v>
       </c>
       <c r="M44" t="n">
-        <v>6645.48</v>
+        <v>6645.18</v>
       </c>
       <c r="N44" t="n">
-        <v>5713.9</v>
+        <v>5712.4</v>
       </c>
     </row>
     <row r="45">
@@ -5571,7 +5571,7 @@
         <v>46096.16666666666</v>
       </c>
       <c r="B45" t="n">
-        <v>9778.700000000001</v>
+        <v>9776.299999999999</v>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
@@ -5592,40 +5592,40 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1.149815</v>
+        <v>1.14977</v>
       </c>
       <c r="D46" t="n">
-        <v>1.331215</v>
+        <v>1.33114</v>
       </c>
       <c r="E46" t="n">
-        <v>7949</v>
+        <v>7947</v>
       </c>
       <c r="F46" t="n">
-        <v>23625.4</v>
+        <v>23621.9</v>
       </c>
       <c r="G46" t="n">
-        <v>46926.7</v>
+        <v>46924.3</v>
       </c>
       <c r="H46" t="n">
-        <v>10347</v>
+        <v>10345</v>
       </c>
       <c r="I46" t="n">
-        <v>25861.7</v>
+        <v>25846.7</v>
       </c>
       <c r="J46" t="n">
-        <v>24652</v>
+        <v>24651</v>
       </c>
       <c r="K46" t="n">
-        <v>54337.6</v>
+        <v>54334.1</v>
       </c>
       <c r="L46" t="n">
-        <v>2501.65</v>
+        <v>2501.5</v>
       </c>
       <c r="M46" t="n">
-        <v>6698.12</v>
+        <v>6697.82</v>
       </c>
       <c r="N46" t="n">
-        <v>5754.2</v>
+        <v>5752.7</v>
       </c>
     </row>
     <row r="47">
@@ -5633,7 +5633,7 @@
         <v>46097.16666666666</v>
       </c>
       <c r="B47" t="n">
-        <v>9527.4</v>
+        <v>9525</v>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
@@ -5654,40 +5654,40 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>1.153885</v>
+        <v>1.15383</v>
       </c>
       <c r="D48" t="n">
-        <v>1.33575</v>
+        <v>1.33558</v>
       </c>
       <c r="E48" t="n">
-        <v>7956.2</v>
+        <v>7954.2</v>
       </c>
       <c r="F48" t="n">
-        <v>23670.5</v>
+        <v>23667</v>
       </c>
       <c r="G48" t="n">
-        <v>46944.6</v>
+        <v>46942.2</v>
       </c>
       <c r="H48" t="n">
-        <v>10362.5</v>
+        <v>10360.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25859.5</v>
+        <v>25844.5</v>
       </c>
       <c r="J48" t="n">
-        <v>24775.5</v>
+        <v>24774.5</v>
       </c>
       <c r="K48" t="n">
-        <v>54274.4</v>
+        <v>54270.9</v>
       </c>
       <c r="L48" t="n">
-        <v>2517.85</v>
+        <v>2517.7</v>
       </c>
       <c r="M48" t="n">
-        <v>6711.68</v>
+        <v>6711.38</v>
       </c>
       <c r="N48" t="n">
-        <v>5756.4</v>
+        <v>5754.9</v>
       </c>
     </row>
     <row r="49">
@@ -5695,7 +5695,7 @@
         <v>46098.16666666666</v>
       </c>
       <c r="B49" t="n">
-        <v>9250.1</v>
+        <v>9247.700000000001</v>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
@@ -5716,40 +5716,40 @@
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>1.146325</v>
+        <v>1.14628</v>
       </c>
       <c r="D50" t="n">
-        <v>1.326425</v>
+        <v>1.32638</v>
       </c>
       <c r="E50" t="n">
-        <v>7897.7</v>
+        <v>7895.7</v>
       </c>
       <c r="F50" t="n">
-        <v>23169.5</v>
+        <v>23166</v>
       </c>
       <c r="G50" t="n">
-        <v>46157</v>
+        <v>46154.6</v>
       </c>
       <c r="H50" t="n">
-        <v>10221.1</v>
+        <v>10219.1</v>
       </c>
       <c r="I50" t="n">
-        <v>25416.9</v>
+        <v>25401.9</v>
       </c>
       <c r="J50" t="n">
-        <v>24395.2</v>
+        <v>24394.2</v>
       </c>
       <c r="K50" t="n">
-        <v>53599.6</v>
+        <v>53596.1</v>
       </c>
       <c r="L50" t="n">
-        <v>2474.45</v>
+        <v>2474.3</v>
       </c>
       <c r="M50" t="n">
-        <v>6698.99</v>
+        <v>6698.79</v>
       </c>
       <c r="N50" t="n">
-        <v>5655.5</v>
+        <v>5654</v>
       </c>
     </row>
     <row r="51">
@@ -5757,7 +5757,7 @@
         <v>46099.16666666666</v>
       </c>
       <c r="B51" t="n">
-        <v>9650.299999999999</v>
+        <v>9647.9</v>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
@@ -5778,38 +5778,38 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>1.15765</v>
+        <v>1.15762</v>
       </c>
       <c r="D52" t="n">
-        <v>1.342435</v>
+        <v>1.34236</v>
       </c>
       <c r="E52" t="n">
-        <v>7842.7</v>
+        <v>7840.7</v>
       </c>
       <c r="F52" t="n">
-        <v>23019.7</v>
+        <v>23016.2</v>
       </c>
       <c r="G52" t="n">
-        <v>46139.2</v>
+        <v>46136.8</v>
       </c>
       <c r="H52" t="n">
-        <v>10069.6</v>
+        <v>10067.6</v>
       </c>
       <c r="I52" t="n">
-        <v>25368.8</v>
+        <v>25353.8</v>
       </c>
       <c r="J52" t="n">
-        <v>24407.7</v>
+        <v>24406.7</v>
       </c>
       <c r="K52" t="n">
-        <v>53401.2</v>
+        <v>53397.7</v>
       </c>
       <c r="L52" t="n">
-        <v>2508.55</v>
+        <v>2508.4</v>
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>5655.4</v>
+        <v>5653.9</v>
       </c>
     </row>
     <row r="53">
@@ -5817,7 +5817,7 @@
         <v>46100.16666666666</v>
       </c>
       <c r="B53" t="n">
-        <v>9386.799999999999</v>
+        <v>9384.4</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
@@ -5838,40 +5838,40 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.15709</v>
+        <v>1.15679</v>
       </c>
       <c r="D54" t="n">
-        <v>1.33411</v>
+        <v>1.33356</v>
       </c>
       <c r="E54" t="n">
-        <v>7613.8</v>
+        <v>7611.8</v>
       </c>
       <c r="F54" t="n">
-        <v>22214.3</v>
+        <v>22210.8</v>
       </c>
       <c r="G54" t="n">
-        <v>45803.1</v>
+        <v>45798.2</v>
       </c>
       <c r="H54" t="n">
-        <v>9839.299999999999</v>
+        <v>9837.299999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>24770.8</v>
+        <v>24755.8</v>
       </c>
       <c r="J54" t="n">
-        <v>24000.4</v>
+        <v>23997.9</v>
       </c>
       <c r="K54" t="n">
-        <v>51317.2</v>
+        <v>51302.2</v>
       </c>
       <c r="L54" t="n">
-        <v>2452.1</v>
+        <v>2451.6</v>
       </c>
       <c r="M54" t="n">
-        <v>6537.12</v>
+        <v>6536.37</v>
       </c>
       <c r="N54" t="n">
-        <v>5474.95</v>
+        <v>5473.45</v>
       </c>
     </row>
     <row r="55">
@@ -5879,7 +5879,7 @@
         <v>46101.16666666666</v>
       </c>
       <c r="B55" t="n">
-        <v>9792.700000000001</v>
+        <v>9788.799999999999</v>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
@@ -5900,40 +5900,40 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1.156245</v>
+        <v>1.1562</v>
       </c>
       <c r="D56" t="n">
-        <v>1.333395</v>
+        <v>1.33332</v>
       </c>
       <c r="E56" t="n">
-        <v>7540.6</v>
+        <v>7538.6</v>
       </c>
       <c r="F56" t="n">
-        <v>21975.6</v>
+        <v>21972.1</v>
       </c>
       <c r="G56" t="n">
-        <v>45538.6</v>
+        <v>45536.2</v>
       </c>
       <c r="H56" t="n">
-        <v>9794.1</v>
+        <v>9792.1</v>
       </c>
       <c r="I56" t="n">
-        <v>24659.3</v>
+        <v>24644.3</v>
       </c>
       <c r="J56" t="n">
-        <v>23794.4</v>
+        <v>23793.4</v>
       </c>
       <c r="K56" t="n">
-        <v>51180.5</v>
+        <v>51177</v>
       </c>
       <c r="L56" t="n">
-        <v>2432.65</v>
+        <v>2432.5</v>
       </c>
       <c r="M56" t="n">
-        <v>6488.5</v>
+        <v>6488.2</v>
       </c>
       <c r="N56" t="n">
-        <v>5419.6</v>
+        <v>5418.1</v>
       </c>
     </row>
     <row r="57">
@@ -5941,7 +5941,7 @@
         <v>46103.16666666666</v>
       </c>
       <c r="B57" t="n">
-        <v>9885.6</v>
+        <v>9883.200000000001</v>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
@@ -5962,40 +5962,40 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1.1608</v>
+        <v>1.16077</v>
       </c>
       <c r="D58" t="n">
-        <v>1.342625</v>
+        <v>1.34255</v>
       </c>
       <c r="E58" t="n">
-        <v>7798.8</v>
+        <v>7796.8</v>
       </c>
       <c r="F58" t="n">
-        <v>22845</v>
+        <v>22841.5</v>
       </c>
       <c r="G58" t="n">
-        <v>46290.6</v>
+        <v>46288.2</v>
       </c>
       <c r="H58" t="n">
-        <v>9963.6</v>
+        <v>9961.6</v>
       </c>
       <c r="I58" t="n">
-        <v>24982.7</v>
+        <v>24967.7</v>
       </c>
       <c r="J58" t="n">
-        <v>24241.8</v>
+        <v>24240.8</v>
       </c>
       <c r="K58" t="n">
-        <v>53018.2</v>
+        <v>53014.7</v>
       </c>
       <c r="L58" t="n">
-        <v>2500.55</v>
+        <v>2500.4</v>
       </c>
       <c r="M58" t="n">
-        <v>6594.07</v>
+        <v>6593.77</v>
       </c>
       <c r="N58" t="n">
-        <v>5617.7</v>
+        <v>5616.2</v>
       </c>
     </row>
     <row r="59">
@@ -6003,7 +6003,7 @@
         <v>46104.16666666666</v>
       </c>
       <c r="B59" t="n">
-        <v>9123.4</v>
+        <v>9121</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
@@ -6024,40 +6024,40 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1.161345</v>
+        <v>1.1613</v>
       </c>
       <c r="D60" t="n">
-        <v>1.341485</v>
+        <v>1.34141</v>
       </c>
       <c r="E60" t="n">
-        <v>7815.7</v>
+        <v>7813.7</v>
       </c>
       <c r="F60" t="n">
-        <v>22891</v>
+        <v>22887.5</v>
       </c>
       <c r="G60" t="n">
-        <v>46448</v>
+        <v>46445.6</v>
       </c>
       <c r="H60" t="n">
-        <v>10015.3</v>
+        <v>10013.3</v>
       </c>
       <c r="I60" t="n">
-        <v>25050.4</v>
+        <v>25035.4</v>
       </c>
       <c r="J60" t="n">
-        <v>24205</v>
+        <v>24204</v>
       </c>
       <c r="K60" t="n">
-        <v>53500.6</v>
+        <v>53497.1</v>
       </c>
       <c r="L60" t="n">
-        <v>2535.75</v>
+        <v>2535.6</v>
       </c>
       <c r="M60" t="n">
-        <v>6599.97</v>
+        <v>6599.67</v>
       </c>
       <c r="N60" t="n">
-        <v>5645.68</v>
+        <v>5644.18</v>
       </c>
     </row>
     <row r="61">
@@ -6065,7 +6065,7 @@
         <v>46105.16666666666</v>
       </c>
       <c r="B61" t="n">
-        <v>8855.200000000001</v>
+        <v>8852.799999999999</v>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
@@ -6086,40 +6086,40 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>1.156185</v>
+        <v>1.15614</v>
       </c>
       <c r="D62" t="n">
-        <v>1.336385</v>
+        <v>1.33631</v>
       </c>
       <c r="E62" t="n">
-        <v>7815.5</v>
+        <v>7813.5</v>
       </c>
       <c r="F62" t="n">
-        <v>22870.1</v>
+        <v>22866.6</v>
       </c>
       <c r="G62" t="n">
-        <v>46359.5</v>
+        <v>46357.1</v>
       </c>
       <c r="H62" t="n">
-        <v>10085.7</v>
+        <v>10083.7</v>
       </c>
       <c r="I62" t="n">
-        <v>25259.3</v>
+        <v>25244.3</v>
       </c>
       <c r="J62" t="n">
-        <v>24114.6</v>
+        <v>24113.6</v>
       </c>
       <c r="K62" t="n">
-        <v>53878.5</v>
+        <v>53875</v>
       </c>
       <c r="L62" t="n">
-        <v>2530.75</v>
+        <v>2530.6</v>
       </c>
       <c r="M62" t="n">
-        <v>6581</v>
+        <v>6580.7</v>
       </c>
       <c r="N62" t="n">
-        <v>5621.51</v>
+        <v>5620.01</v>
       </c>
     </row>
     <row r="63">
@@ -6127,7 +6127,7 @@
         <v>46106.16666666666</v>
       </c>
       <c r="B63" t="n">
-        <v>9117.700000000001</v>
+        <v>9115.299999999999</v>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
@@ -6148,40 +6148,40 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1.153495</v>
+        <v>1.15345</v>
       </c>
       <c r="D64" t="n">
-        <v>1.333415</v>
+        <v>1.33334</v>
       </c>
       <c r="E64" t="n">
-        <v>7780.5</v>
+        <v>7778.5</v>
       </c>
       <c r="F64" t="n">
-        <v>22692.5</v>
+        <v>22689</v>
       </c>
       <c r="G64" t="n">
-        <v>46181.1</v>
+        <v>46178.7</v>
       </c>
       <c r="H64" t="n">
-        <v>9965.799999999999</v>
+        <v>9963.799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>24768.8</v>
+        <v>24753.8</v>
       </c>
       <c r="J64" t="n">
-        <v>23682.7</v>
+        <v>23681.7</v>
       </c>
       <c r="K64" t="n">
-        <v>52923.6</v>
+        <v>52920.1</v>
       </c>
       <c r="L64" t="n">
-        <v>2508.55</v>
+        <v>2508.4</v>
       </c>
       <c r="M64" t="n">
-        <v>6506.25</v>
+        <v>6505.95</v>
       </c>
       <c r="N64" t="n">
-        <v>5573</v>
+        <v>5571.5</v>
       </c>
     </row>
     <row r="65">
@@ -6189,7 +6189,7 @@
         <v>46107.16666666666</v>
       </c>
       <c r="B65" t="n">
-        <v>9274.799999999999</v>
+        <v>9272.4</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
@@ -6210,40 +6210,40 @@
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>1.15097</v>
+        <v>1.15067</v>
       </c>
       <c r="D66" t="n">
-        <v>1.3264</v>
+        <v>1.32591</v>
       </c>
       <c r="E66" t="n">
-        <v>7646.4</v>
+        <v>7644.4</v>
       </c>
       <c r="F66" t="n">
-        <v>22101.1</v>
+        <v>22097.6</v>
       </c>
       <c r="G66" t="n">
-        <v>45061.5</v>
+        <v>45056.6</v>
       </c>
       <c r="H66" t="n">
-        <v>9895.299999999999</v>
+        <v>9893.299999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>24627.5</v>
+        <v>24612.5</v>
       </c>
       <c r="J66" t="n">
-        <v>23069.6</v>
+        <v>23067.1</v>
       </c>
       <c r="K66" t="n">
-        <v>51137.7</v>
+        <v>51122.7</v>
       </c>
       <c r="L66" t="n">
-        <v>2443.2</v>
+        <v>2442.7</v>
       </c>
       <c r="M66" t="n">
-        <v>6355.25</v>
+        <v>6354.5</v>
       </c>
       <c r="N66" t="n">
-        <v>5455.22</v>
+        <v>5453.72</v>
       </c>
     </row>
     <row r="67">
@@ -6251,7 +6251,7 @@
         <v>46108.16666666666</v>
       </c>
       <c r="B67" t="n">
-        <v>9977.299999999999</v>
+        <v>9973.4</v>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
@@ -6272,40 +6272,40 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1.148835</v>
+        <v>1.14879</v>
       </c>
       <c r="D68" t="n">
-        <v>1.323875</v>
+        <v>1.32377</v>
       </c>
       <c r="E68" t="n">
-        <v>7618.7</v>
+        <v>7616.7</v>
       </c>
       <c r="F68" t="n">
-        <v>22031.4</v>
+        <v>22027.9</v>
       </c>
       <c r="G68" t="n">
-        <v>44945.6</v>
+        <v>44943.2</v>
       </c>
       <c r="H68" t="n">
-        <v>9879.4</v>
+        <v>9877.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24593.4</v>
+        <v>24578.4</v>
       </c>
       <c r="J68" t="n">
-        <v>23027.2</v>
+        <v>23026.2</v>
       </c>
       <c r="K68" t="n">
-        <v>50609</v>
+        <v>50601.5</v>
       </c>
       <c r="L68" t="n">
-        <v>2430.85</v>
+        <v>2430.7</v>
       </c>
       <c r="M68" t="n">
-        <v>6340.21</v>
+        <v>6339.91</v>
       </c>
       <c r="N68" t="n">
-        <v>5435.4</v>
+        <v>5433.9</v>
       </c>
     </row>
     <row r="69">
@@ -6313,7 +6313,7 @@
         <v>46110.20833333334</v>
       </c>
       <c r="B69" t="n">
-        <v>9976.4</v>
+        <v>9974</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
@@ -6334,40 +6334,40 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>1.145975</v>
+        <v>1.14593</v>
       </c>
       <c r="D70" t="n">
-        <v>1.317995</v>
+        <v>1.31792</v>
       </c>
       <c r="E70" t="n">
-        <v>7722.7</v>
+        <v>7720.7</v>
       </c>
       <c r="F70" t="n">
-        <v>22434.6</v>
+        <v>22431.1</v>
       </c>
       <c r="G70" t="n">
-        <v>45225.5</v>
+        <v>45223.1</v>
       </c>
       <c r="H70" t="n">
-        <v>10070.4</v>
+        <v>10068.4</v>
       </c>
       <c r="I70" t="n">
-        <v>24724.4</v>
+        <v>24709.4</v>
       </c>
       <c r="J70" t="n">
-        <v>22920.3</v>
+        <v>22919.3</v>
       </c>
       <c r="K70" t="n">
-        <v>51054.8</v>
+        <v>51047.3</v>
       </c>
       <c r="L70" t="n">
-        <v>2409.85</v>
+        <v>2409.7</v>
       </c>
       <c r="M70" t="n">
-        <v>6341.38</v>
+        <v>6341.08</v>
       </c>
       <c r="N70" t="n">
-        <v>5500.9</v>
+        <v>5499.4</v>
       </c>
     </row>
     <row r="71">
@@ -6375,7 +6375,7 @@
         <v>46111.20833333334</v>
       </c>
       <c r="B71" t="n">
-        <v>10068.9</v>
+        <v>10066.5</v>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
@@ -6396,40 +6396,40 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1.155875</v>
+        <v>1.15583</v>
       </c>
       <c r="D72" t="n">
-        <v>1.323055</v>
+        <v>1.32294</v>
       </c>
       <c r="E72" t="n">
-        <v>7921.4</v>
+        <v>7919.4</v>
       </c>
       <c r="F72" t="n">
-        <v>23026.2</v>
+        <v>23022.7</v>
       </c>
       <c r="G72" t="n">
-        <v>46230.95</v>
+        <v>46229.5</v>
       </c>
       <c r="H72" t="n">
-        <v>10279.9</v>
+        <v>10277.9</v>
       </c>
       <c r="I72" t="n">
-        <v>25317.1</v>
+        <v>25302.1</v>
       </c>
       <c r="J72" t="n">
-        <v>23777.1</v>
+        <v>23776.1</v>
       </c>
       <c r="K72" t="n">
-        <v>53050.8</v>
+        <v>53043.3</v>
       </c>
       <c r="L72" t="n">
-        <v>2494.15</v>
+        <v>2494</v>
       </c>
       <c r="M72" t="n">
-        <v>6530.15</v>
+        <v>6529.85</v>
       </c>
       <c r="N72" t="n">
-        <v>5653.5</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="73">
@@ -6437,7 +6437,7 @@
         <v>46112.20833333334</v>
       </c>
       <c r="B73" t="n">
-        <v>9969.1</v>
+        <v>9966.700000000001</v>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
@@ -6458,40 +6458,40 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>1.159095</v>
+        <v>1.15905</v>
       </c>
       <c r="D74" t="n">
-        <v>1.330625</v>
+        <v>1.33055</v>
       </c>
       <c r="E74" t="n">
-        <v>7976.6</v>
+        <v>7974.6</v>
       </c>
       <c r="F74" t="n">
-        <v>23289</v>
+        <v>23285.5</v>
       </c>
       <c r="G74" t="n">
-        <v>46561.8</v>
+        <v>46559.4</v>
       </c>
       <c r="H74" t="n">
-        <v>10416.2</v>
+        <v>10414.2</v>
       </c>
       <c r="I74" t="n">
-        <v>25315.3</v>
+        <v>25300.3</v>
       </c>
       <c r="J74" t="n">
-        <v>23996.1</v>
+        <v>23995.1</v>
       </c>
       <c r="K74" t="n">
-        <v>54233.9</v>
+        <v>54226.4</v>
       </c>
       <c r="L74" t="n">
-        <v>2510.15</v>
+        <v>2510</v>
       </c>
       <c r="M74" t="n">
-        <v>6572.13</v>
+        <v>6571.83</v>
       </c>
       <c r="N74" t="n">
-        <v>5720.9</v>
+        <v>5719.4</v>
       </c>
     </row>
     <row r="75">
@@ -6499,7 +6499,7 @@
         <v>46113.20833333334</v>
       </c>
       <c r="B75" t="n">
-        <v>10095.1</v>
+        <v>10092.7</v>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
@@ -6520,40 +6520,40 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1.154015</v>
+        <v>1.15397</v>
       </c>
       <c r="D76" t="n">
-        <v>1.322585</v>
+        <v>1.32248</v>
       </c>
       <c r="E76" t="n">
-        <v>7990.9</v>
+        <v>7988.9</v>
       </c>
       <c r="F76" t="n">
-        <v>23217.6</v>
+        <v>23214.1</v>
       </c>
       <c r="G76" t="n">
-        <v>46522.4</v>
+        <v>46520</v>
       </c>
       <c r="H76" t="n">
-        <v>10451.6</v>
+        <v>10449.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25270.4</v>
+        <v>25255.4</v>
       </c>
       <c r="J76" t="n">
-        <v>24030.5</v>
+        <v>24029.5</v>
       </c>
       <c r="K76" t="n">
-        <v>53247.5</v>
+        <v>53240</v>
       </c>
       <c r="L76" t="n">
-        <v>2530.55</v>
+        <v>2530.4</v>
       </c>
       <c r="M76" t="n">
-        <v>6583.360000000001</v>
+        <v>6583.06</v>
       </c>
       <c r="N76" t="n">
-        <v>5701.47</v>
+        <v>5699.97</v>
       </c>
     </row>
     <row r="77">
@@ -6561,7 +6561,7 @@
         <v>46114.20833333334</v>
       </c>
       <c r="B77" t="n">
-        <v>10581</v>
+        <v>10578.6</v>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -6582,40 +6582,40 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1.15187</v>
+        <v>1.15154</v>
       </c>
       <c r="D78" t="n">
-        <v>1.320465</v>
+        <v>1.31987</v>
       </c>
       <c r="E78" t="n">
-        <v>7960.4</v>
+        <v>7958.4</v>
       </c>
       <c r="F78" t="n">
-        <v>23127.3</v>
+        <v>23123.8</v>
       </c>
       <c r="G78" t="n">
-        <v>46407.7</v>
+        <v>46405.9</v>
       </c>
       <c r="H78" t="n">
-        <v>10432</v>
+        <v>10430</v>
       </c>
       <c r="I78" t="n">
-        <v>25188.7</v>
+        <v>25173.7</v>
       </c>
       <c r="J78" t="n">
-        <v>23957.4</v>
+        <v>23956.4</v>
       </c>
       <c r="K78" t="n">
-        <v>53165.2</v>
+        <v>53150.2</v>
       </c>
       <c r="L78" t="n">
-        <v>2519.65</v>
+        <v>2519.5</v>
       </c>
       <c r="M78" t="n">
-        <v>6563.67</v>
+        <v>6563.37</v>
       </c>
       <c r="N78" t="n">
-        <v>5679.77</v>
+        <v>5678.27</v>
       </c>
     </row>
     <row r="79">
@@ -6626,34 +6626,34 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>7934.5</v>
+        <v>7932.5</v>
       </c>
       <c r="F79" t="n">
-        <v>23052.9</v>
+        <v>23049.4</v>
       </c>
       <c r="G79" t="n">
-        <v>46258.3</v>
+        <v>46255.9</v>
       </c>
       <c r="H79" t="n">
-        <v>10416.4</v>
+        <v>10414.4</v>
       </c>
       <c r="I79" t="n">
-        <v>25153.9</v>
+        <v>25138.9</v>
       </c>
       <c r="J79" t="n">
-        <v>23907.8</v>
+        <v>23906.8</v>
       </c>
       <c r="K79" t="n">
-        <v>52872.6</v>
+        <v>52865.1</v>
       </c>
       <c r="L79" t="n">
-        <v>2510.85</v>
+        <v>2510.7</v>
       </c>
       <c r="M79" t="n">
-        <v>6547.57</v>
+        <v>6547.27</v>
       </c>
       <c r="N79" t="n">
-        <v>5661.8</v>
+        <v>5660.3</v>
       </c>
     </row>
     <row r="80">
@@ -6661,7 +6661,7 @@
         <v>46117.20833333334</v>
       </c>
       <c r="B80" t="n">
-        <v>10420.3</v>
+        <v>10417.9</v>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
@@ -6682,40 +6682,40 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>1.154265</v>
+        <v>1.15422</v>
       </c>
       <c r="D81" t="n">
-        <v>1.323355</v>
+        <v>1.32328</v>
       </c>
       <c r="E81" t="n">
-        <v>8026.1</v>
+        <v>8024.1</v>
       </c>
       <c r="F81" t="n">
-        <v>23295.1</v>
+        <v>23291.6</v>
       </c>
       <c r="G81" t="n">
-        <v>46709.5</v>
+        <v>46707.1</v>
       </c>
       <c r="H81" t="n">
-        <v>10477.6</v>
+        <v>10475.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25312</v>
+        <v>25297</v>
       </c>
       <c r="J81" t="n">
-        <v>24134.7</v>
+        <v>24133.7</v>
       </c>
       <c r="K81" t="n">
-        <v>53883.7</v>
+        <v>53876.2</v>
       </c>
       <c r="L81" t="n">
-        <v>2536.65</v>
+        <v>2536.5</v>
       </c>
       <c r="M81" t="n">
-        <v>6603.96</v>
+        <v>6603.66</v>
       </c>
       <c r="N81" t="n">
-        <v>5727.1</v>
+        <v>5725.6</v>
       </c>
     </row>
     <row r="82">
@@ -6723,7 +6723,7 @@
         <v>46118.20833333334</v>
       </c>
       <c r="B82" t="n">
-        <v>10675.7</v>
+        <v>10673.3</v>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
@@ -6744,40 +6744,40 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1.166825</v>
+        <v>1.16675</v>
       </c>
       <c r="D83" t="n">
-        <v>1.337355</v>
+        <v>1.33725</v>
       </c>
       <c r="E83" t="n">
-        <v>8193.700000000001</v>
+        <v>8191.7</v>
       </c>
       <c r="F83" t="n">
-        <v>23802.3</v>
+        <v>23798.8</v>
       </c>
       <c r="G83" t="n">
-        <v>47545.8</v>
+        <v>47543.4</v>
       </c>
       <c r="H83" t="n">
-        <v>10557.1</v>
+        <v>10555.1</v>
       </c>
       <c r="I83" t="n">
-        <v>25620.5</v>
+        <v>25605.5</v>
       </c>
       <c r="J83" t="n">
-        <v>24748.9</v>
+        <v>24747.9</v>
       </c>
       <c r="K83" t="n">
-        <v>55942.4</v>
+        <v>55934.9</v>
       </c>
       <c r="L83" t="n">
-        <v>2623.75</v>
+        <v>2623.6</v>
       </c>
       <c r="M83" t="n">
-        <v>6752.42</v>
+        <v>6752.12</v>
       </c>
       <c r="N83" t="n">
-        <v>5845.7</v>
+        <v>5844.2</v>
       </c>
     </row>
     <row r="84">
@@ -6785,7 +6785,7 @@
         <v>46119.20833333334</v>
       </c>
       <c r="B84" t="n">
-        <v>9110.700000000001</v>
+        <v>9108.299999999999</v>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
@@ -6806,40 +6806,40 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>1.166275</v>
+        <v>1.16623</v>
       </c>
       <c r="D85" t="n">
-        <v>1.339785</v>
+        <v>1.33971</v>
       </c>
       <c r="E85" t="n">
-        <v>8274.200000000001</v>
+        <v>8272.200000000001</v>
       </c>
       <c r="F85" t="n">
-        <v>24005.2</v>
+        <v>24001.7</v>
       </c>
       <c r="G85" t="n">
-        <v>47886.5</v>
+        <v>47884.1</v>
       </c>
       <c r="H85" t="n">
-        <v>10659.2</v>
+        <v>10657.2</v>
       </c>
       <c r="I85" t="n">
-        <v>25877.5</v>
+        <v>25862.5</v>
       </c>
       <c r="J85" t="n">
-        <v>24864</v>
+        <v>24863</v>
       </c>
       <c r="K85" t="n">
-        <v>56750.7</v>
+        <v>56743.2</v>
       </c>
       <c r="L85" t="n">
-        <v>2621.15</v>
+        <v>2621</v>
       </c>
       <c r="M85" t="n">
-        <v>6775.84</v>
+        <v>6775.54</v>
       </c>
       <c r="N85" t="n">
-        <v>5913.6</v>
+        <v>5912.1</v>
       </c>
     </row>
     <row r="86">
@@ -6847,7 +6847,7 @@
         <v>46120.20833333334</v>
       </c>
       <c r="B86" t="n">
-        <v>9245.299999999999</v>
+        <v>9242.9</v>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
@@ -6868,40 +6868,40 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1.169405</v>
+        <v>1.16936</v>
       </c>
       <c r="D87" t="n">
-        <v>1.342805</v>
+        <v>1.34273</v>
       </c>
       <c r="E87" t="n">
-        <v>8252.299999999999</v>
+        <v>8250.299999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>23860.1</v>
+        <v>23856.6</v>
       </c>
       <c r="G87" t="n">
-        <v>48155.1</v>
+        <v>48152.7</v>
       </c>
       <c r="H87" t="n">
-        <v>10594.9</v>
+        <v>10592.9</v>
       </c>
       <c r="I87" t="n">
-        <v>25916.1</v>
+        <v>25901.1</v>
       </c>
       <c r="J87" t="n">
-        <v>25042.9</v>
+        <v>25041.9</v>
       </c>
       <c r="K87" t="n">
-        <v>56487.1</v>
+        <v>56479.6</v>
       </c>
       <c r="L87" t="n">
-        <v>2635.65</v>
+        <v>2635.5</v>
       </c>
       <c r="M87" t="n">
-        <v>6816.9</v>
+        <v>6816.6</v>
       </c>
       <c r="N87" t="n">
-        <v>5900.9</v>
+        <v>5899.4</v>
       </c>
     </row>
     <row r="88">
@@ -6909,7 +6909,7 @@
         <v>46121.20833333334</v>
       </c>
       <c r="B88" t="n">
-        <v>9242.700000000001</v>
+        <v>9240.299999999999</v>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
@@ -6930,40 +6930,40 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1.1726</v>
+        <v>1.17227</v>
       </c>
       <c r="D89" t="n">
-        <v>1.346235</v>
+        <v>1.34564</v>
       </c>
       <c r="E89" t="n">
-        <v>8266.799999999999</v>
+        <v>8264.799999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>23823.9</v>
+        <v>23820.4</v>
       </c>
       <c r="G89" t="n">
-        <v>47972</v>
+        <v>47967.1</v>
       </c>
       <c r="H89" t="n">
-        <v>10605.1</v>
+        <v>10603.1</v>
       </c>
       <c r="I89" t="n">
-        <v>25948.9</v>
+        <v>25933.9</v>
       </c>
       <c r="J89" t="n">
-        <v>25164.7</v>
+        <v>25162.2</v>
       </c>
       <c r="K89" t="n">
-        <v>57406.8</v>
+        <v>57391.8</v>
       </c>
       <c r="L89" t="n">
-        <v>2636.3</v>
+        <v>2635.8</v>
       </c>
       <c r="M89" t="n">
-        <v>6825.55</v>
+        <v>6824.8</v>
       </c>
       <c r="N89" t="n">
-        <v>5928.91</v>
+        <v>5927.41</v>
       </c>
     </row>
     <row r="90">
@@ -6971,7 +6971,7 @@
         <v>46122.20833333334</v>
       </c>
       <c r="B90" t="n">
-        <v>9114.700000000001</v>
+        <v>9110.799999999999</v>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
@@ -6992,40 +6992,40 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1.167255</v>
+        <v>1.16721</v>
       </c>
       <c r="D91" t="n">
-        <v>1.339455</v>
+        <v>1.33938</v>
       </c>
       <c r="E91" t="n">
-        <v>8130.9</v>
+        <v>8128.9</v>
       </c>
       <c r="F91" t="n">
-        <v>23438.1</v>
+        <v>23434.6</v>
       </c>
       <c r="G91" t="n">
-        <v>47403</v>
+        <v>47400.6</v>
       </c>
       <c r="H91" t="n">
-        <v>10523</v>
+        <v>10521</v>
       </c>
       <c r="I91" t="n">
-        <v>25770.2</v>
+        <v>25755.2</v>
       </c>
       <c r="J91" t="n">
-        <v>24791.8</v>
+        <v>24790.8</v>
       </c>
       <c r="K91" t="n">
-        <v>56085.5</v>
+        <v>56078</v>
       </c>
       <c r="L91" t="n">
-        <v>2587.85</v>
+        <v>2587.7</v>
       </c>
       <c r="M91" t="n">
-        <v>6740.55</v>
+        <v>6740.25</v>
       </c>
       <c r="N91" t="n">
-        <v>5831.8</v>
+        <v>5830.3</v>
       </c>
     </row>
     <row r="92">
@@ -7033,7 +7033,7 @@
         <v>46124.20833333334</v>
       </c>
       <c r="B92" t="n">
-        <v>9809.4</v>
+        <v>9807</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
@@ -7054,40 +7054,40 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1.176135</v>
+        <v>1.17609</v>
       </c>
       <c r="D93" t="n">
-        <v>1.351065</v>
+        <v>1.35099</v>
       </c>
       <c r="E93" t="n">
-        <v>8268.299999999999</v>
+        <v>8266.299999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>23965.5</v>
+        <v>23962</v>
       </c>
       <c r="G93" t="n">
-        <v>48227.7</v>
+        <v>48225.3</v>
       </c>
       <c r="H93" t="n">
-        <v>10617.9</v>
+        <v>10615.9</v>
       </c>
       <c r="I93" t="n">
-        <v>25968.2</v>
+        <v>25953.2</v>
       </c>
       <c r="J93" t="n">
-        <v>25435.7</v>
+        <v>25434.7</v>
       </c>
       <c r="K93" t="n">
-        <v>57698.9</v>
+        <v>57691.4</v>
       </c>
       <c r="L93" t="n">
-        <v>2678.15</v>
+        <v>2678</v>
       </c>
       <c r="M93" t="n">
-        <v>6890.15</v>
+        <v>6889.85</v>
       </c>
       <c r="N93" t="n">
-        <v>5947.3</v>
+        <v>5945.8</v>
       </c>
     </row>
     <row r="94">
@@ -7095,7 +7095,7 @@
         <v>46125.20833333334</v>
       </c>
       <c r="B94" t="n">
-        <v>9266.200000000001</v>
+        <v>9263.799999999999</v>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
@@ -7116,40 +7116,40 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>1.179485</v>
+        <v>1.17944</v>
       </c>
       <c r="D95" t="n">
-        <v>1.356875</v>
+        <v>1.3568</v>
       </c>
       <c r="E95" t="n">
-        <v>8326.9</v>
+        <v>8324.9</v>
       </c>
       <c r="F95" t="n">
-        <v>24054.9</v>
+        <v>24051.4</v>
       </c>
       <c r="G95" t="n">
-        <v>48537.7</v>
+        <v>48535.3</v>
       </c>
       <c r="H95" t="n">
-        <v>10624.6</v>
+        <v>10622.6</v>
       </c>
       <c r="I95" t="n">
-        <v>26212.7</v>
+        <v>26197.7</v>
       </c>
       <c r="J95" t="n">
-        <v>25830.8</v>
+        <v>25829.8</v>
       </c>
       <c r="K95" t="n">
-        <v>58706</v>
+        <v>58698.5</v>
       </c>
       <c r="L95" t="n">
-        <v>2705.55</v>
+        <v>2705.4</v>
       </c>
       <c r="M95" t="n">
-        <v>6967.77</v>
+        <v>6967.47</v>
       </c>
       <c r="N95" t="n">
-        <v>5986.4</v>
+        <v>5984.9</v>
       </c>
     </row>
     <row r="96">
@@ -7157,7 +7157,7 @@
         <v>46126.20833333334</v>
       </c>
       <c r="B96" t="n">
-        <v>8869</v>
+        <v>8866.6</v>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
@@ -7178,40 +7178,40 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1.180235</v>
+        <v>1.18019</v>
       </c>
       <c r="D97" t="n">
-        <v>1.356785</v>
+        <v>1.35671</v>
       </c>
       <c r="E97" t="n">
-        <v>8264.799999999999</v>
+        <v>8262.799999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>24107.1</v>
+        <v>24103.6</v>
       </c>
       <c r="G97" t="n">
-        <v>48527.8</v>
+        <v>48525.4</v>
       </c>
       <c r="H97" t="n">
-        <v>10556.1</v>
+        <v>10554.1</v>
       </c>
       <c r="I97" t="n">
-        <v>26130.4</v>
+        <v>26115.4</v>
       </c>
       <c r="J97" t="n">
-        <v>26229.3</v>
+        <v>26228.3</v>
       </c>
       <c r="K97" t="n">
-        <v>58563.8</v>
+        <v>58556.3</v>
       </c>
       <c r="L97" t="n">
-        <v>2716.35</v>
+        <v>2716.2</v>
       </c>
       <c r="M97" t="n">
-        <v>7028.29</v>
+        <v>7027.99</v>
       </c>
       <c r="N97" t="n">
-        <v>5946.9</v>
+        <v>5945.4</v>
       </c>
     </row>
     <row r="98">
@@ -7219,7 +7219,7 @@
         <v>46127.20833333334</v>
       </c>
       <c r="B98" t="n">
-        <v>8868.4</v>
+        <v>8866</v>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
@@ -7240,40 +7240,40 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>1.178545</v>
+        <v>1.1785</v>
       </c>
       <c r="D99" t="n">
-        <v>1.353215</v>
+        <v>1.35314</v>
       </c>
       <c r="E99" t="n">
-        <v>8266.4</v>
+        <v>8264.4</v>
       </c>
       <c r="F99" t="n">
-        <v>24140.9</v>
+        <v>24137.4</v>
       </c>
       <c r="G99" t="n">
-        <v>48661.1</v>
+        <v>48658.7</v>
       </c>
       <c r="H99" t="n">
-        <v>10590.9</v>
+        <v>10588.9</v>
       </c>
       <c r="I99" t="n">
-        <v>26236.3</v>
+        <v>26221.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26321.7</v>
+        <v>26320.7</v>
       </c>
       <c r="K99" t="n">
-        <v>59430.4</v>
+        <v>59422.9</v>
       </c>
       <c r="L99" t="n">
-        <v>2725.15</v>
+        <v>2725</v>
       </c>
       <c r="M99" t="n">
-        <v>7046.74</v>
+        <v>7046.44</v>
       </c>
       <c r="N99" t="n">
-        <v>5920.67</v>
+        <v>5919.17</v>
       </c>
     </row>
     <row r="100">
@@ -7281,7 +7281,7 @@
         <v>46128.20833333334</v>
       </c>
       <c r="B100" t="n">
-        <v>9030.200000000001</v>
+        <v>9027.799999999999</v>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
@@ -7302,40 +7302,40 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1.176345</v>
+        <v>1.17606</v>
       </c>
       <c r="D101" t="n">
-        <v>1.351615</v>
+        <v>1.35102</v>
       </c>
       <c r="E101" t="n">
-        <v>8407.9</v>
+        <v>8405.9</v>
       </c>
       <c r="F101" t="n">
-        <v>24651.9</v>
+        <v>24648.4</v>
       </c>
       <c r="G101" t="n">
-        <v>49453</v>
+        <v>49448.1</v>
       </c>
       <c r="H101" t="n">
-        <v>10697.9</v>
+        <v>10695.9</v>
       </c>
       <c r="I101" t="n">
-        <v>26504.1</v>
+        <v>26489.1</v>
       </c>
       <c r="J101" t="n">
-        <v>26684.1</v>
+        <v>26681.6</v>
       </c>
       <c r="K101" t="n">
-        <v>59693.4</v>
+        <v>59678.4</v>
       </c>
       <c r="L101" t="n">
-        <v>2777.8</v>
+        <v>2777.3</v>
       </c>
       <c r="M101" t="n">
-        <v>7126.42</v>
+        <v>7125.67</v>
       </c>
       <c r="N101" t="n">
-        <v>6036.51</v>
+        <v>6035.01</v>
       </c>
     </row>
     <row r="102">
@@ -7343,7 +7343,7 @@
         <v>46129.20833333334</v>
       </c>
       <c r="B102" t="n">
-        <v>8417.5</v>
+        <v>8413.6</v>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
@@ -7364,23 +7364,23 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>1.173945</v>
+        <v>1.1739</v>
       </c>
       <c r="D103" t="n">
-        <v>1.348705</v>
+        <v>1.34863</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>10633.2</v>
+        <v>10631.2</v>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>7073.76</v>
+        <v>7073.46</v>
       </c>
       <c r="N103" t="inlineStr"/>
     </row>
@@ -7389,7 +7389,7 @@
         <v>46131.20833333334</v>
       </c>
       <c r="B104" t="n">
-        <v>8910.9</v>
+        <v>8908.5</v>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
@@ -7410,23 +7410,23 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1.179005</v>
+        <v>1.17896</v>
       </c>
       <c r="D105" t="n">
-        <v>1.353895</v>
+        <v>1.35382</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>10627.6</v>
+        <v>10625.6</v>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>7121.9</v>
+        <v>7121.6</v>
       </c>
       <c r="N105" t="inlineStr"/>
     </row>
@@ -7435,7 +7435,7 @@
         <v>46132.20833333334</v>
       </c>
       <c r="B106" t="n">
-        <v>8670.9</v>
+        <v>8668.5</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
@@ -7456,23 +7456,23 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1.173925</v>
+        <v>1.17388</v>
       </c>
       <c r="D107" t="n">
-        <v>1.350235</v>
+        <v>1.35016</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>10466.5</v>
+        <v>10464.5</v>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>7088.99</v>
+        <v>7088.69</v>
       </c>
       <c r="N107" t="inlineStr"/>
     </row>
@@ -7481,7 +7481,7 @@
         <v>46133.20833333334</v>
       </c>
       <c r="B108" t="n">
-        <v>8926.9</v>
+        <v>8925.5</v>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
@@ -7502,23 +7502,23 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>1.170595</v>
+        <v>1.17055</v>
       </c>
       <c r="D109" t="n">
-        <v>1.350215</v>
+        <v>1.35014</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>10460.2</v>
+        <v>10458.2</v>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>7127.22</v>
+        <v>7126.92</v>
       </c>
       <c r="N109" t="inlineStr"/>
     </row>
@@ -7527,7 +7527,7 @@
         <v>46134.20833333334</v>
       </c>
       <c r="B110" t="n">
-        <v>9453.1</v>
+        <v>9450.700000000001</v>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
@@ -7548,23 +7548,23 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1.168635</v>
+        <v>1.16859</v>
       </c>
       <c r="D111" t="n">
-        <v>1.346735</v>
+        <v>1.34666</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>10417.5</v>
+        <v>10415.5</v>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>7114.23</v>
+        <v>7113.93</v>
       </c>
       <c r="N111" t="inlineStr"/>
     </row>
@@ -7573,7 +7573,7 @@
         <v>46135.20833333334</v>
       </c>
       <c r="B112" t="n">
-        <v>9661.1</v>
+        <v>9658.700000000001</v>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
@@ -7594,23 +7594,23 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1.171835</v>
+        <v>1.17154</v>
       </c>
       <c r="D113" t="n">
-        <v>1.353095</v>
+        <v>1.3525</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>10387.5</v>
+        <v>10385.5</v>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>7163.69</v>
+        <v>7162.94</v>
       </c>
       <c r="N113" t="inlineStr"/>
     </row>
@@ -7619,7 +7619,7 @@
         <v>46136.20833333334</v>
       </c>
       <c r="B114" t="n">
-        <v>9486.799999999999</v>
+        <v>9484.4</v>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
@@ -7640,23 +7640,23 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>1.170825</v>
+        <v>1.17078</v>
       </c>
       <c r="D115" t="n">
-        <v>1.351595</v>
+        <v>1.35149</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>10370.5</v>
+        <v>10368.5</v>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>7151.27</v>
+        <v>7150.97</v>
       </c>
       <c r="N115" t="inlineStr"/>
     </row>
@@ -7665,7 +7665,7 @@
         <v>46138.20833333334</v>
       </c>
       <c r="B116" t="n">
-        <v>9529.1</v>
+        <v>9527.700000000001</v>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
@@ -7686,23 +7686,23 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>1.172205</v>
+        <v>1.17216</v>
       </c>
       <c r="D117" t="n">
-        <v>1.353575</v>
+        <v>1.3535</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>10332.5</v>
+        <v>10330.5</v>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="n">
-        <v>7185.95</v>
+        <v>7185.65</v>
       </c>
       <c r="N117" t="inlineStr"/>
     </row>
@@ -7711,7 +7711,7 @@
         <v>46139.20833333334</v>
       </c>
       <c r="B118" t="n">
-        <v>9761.9</v>
+        <v>9759.5</v>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
@@ -7732,23 +7732,23 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>1.171585</v>
+        <v>1.17154</v>
       </c>
       <c r="D119" t="n">
-        <v>1.352145</v>
+        <v>1.35207</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>10311.6</v>
+        <v>10309.6</v>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="n">
-        <v>7145.37</v>
+        <v>7145.07</v>
       </c>
       <c r="N119" t="inlineStr"/>
     </row>
@@ -7757,7 +7757,7 @@
         <v>46140.20833333334</v>
       </c>
       <c r="B120" t="n">
-        <v>9931.1</v>
+        <v>9928.700000000001</v>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
@@ -7778,23 +7778,23 @@
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>1.167825</v>
+        <v>1.16778</v>
       </c>
       <c r="D121" t="n">
-        <v>1.348005</v>
+        <v>1.34793</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>10207.5</v>
+        <v>10205.5</v>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="n">
-        <v>7154.82</v>
+        <v>7154.52</v>
       </c>
       <c r="N121" t="inlineStr"/>
     </row>
@@ -7803,7 +7803,7 @@
         <v>46141.20833333334</v>
       </c>
       <c r="B122" t="n">
-        <v>10911.8</v>
+        <v>10909.4</v>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
@@ -7824,23 +7824,23 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>1.173185</v>
+        <v>1.17314</v>
       </c>
       <c r="D123" t="n">
-        <v>1.360455</v>
+        <v>1.36038</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>10363.4</v>
+        <v>10361.4</v>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="n">
-        <v>7220.52</v>
+        <v>7220.22</v>
       </c>
       <c r="N123" t="inlineStr"/>
     </row>
@@ -7849,7 +7849,7 @@
         <v>46142.20833333334</v>
       </c>
       <c r="B124" t="n">
-        <v>10551.4</v>
+        <v>10549</v>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
@@ -7870,23 +7870,23 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>1.171725</v>
+        <v>1.17168</v>
       </c>
       <c r="D125" t="n">
-        <v>1.357075</v>
+        <v>1.357</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>10351</v>
+        <v>10349</v>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
-        <v>7218.93</v>
+        <v>7218.63</v>
       </c>
       <c r="N125" t="inlineStr"/>
     </row>
@@ -7895,7 +7895,7 @@
         <v>46143.20833333334</v>
       </c>
       <c r="B126" t="n">
-        <v>10259.4</v>
+        <v>10257</v>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>

--- a/data/input/universe_series.xlsx
+++ b/data/input/universe_series.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC141"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,110 +453,220 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>IX.D.DOW.DAILY.IP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CS.D.USDJPY.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>CS.D.AUDUSD.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>CS.D.USDCAD.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CS.D.EURGBP.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>CC.D.S.USS.IP</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>CC.D.SM.USS.IP</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>CC.D.BO.USS.IP</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>CC.D.KC.USS.IP</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>CC.D.CC.USS.IP</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>CC.D.SB.USS.IP</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>CC.D.OJ.USS.IP</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>CC.D.CT.USS.IP</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>CS.D.USCGC.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>CS.D.USCSI.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>MT.D.GC.Month2.IP</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>MT.D.HG.Month1.IP</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>MT.D.PL.Month2.IP</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>MT.D.PA.Month1.IP</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>EN.D.CL.Month1.IP</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>EN.D.LCO.Month4.IP</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>CS.D.EURCHF.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>CS.D.EURAUD.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>CS.D.EURCAD.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>CS.D.EURNZD.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>CS.D.EURNOK.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>CS.D.EURSEK.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>CS.D.EURDKK.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>CS.D.EURPLN.MINI.IP</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>CS.D.EURJPY.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>CS.D.EURCHF.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>CS.D.CHFJPY.TODAY.IP</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
           <t>CS.D.GBPDKK.MINI.IP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>CS.D.GBPPLN.MINI.IP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>CS.D.GBPZAR.MINI.IP</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>MT.D.HG.Month2.IP</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>CS.D.BITCOIN.CFD.IP</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>CS.D.ETHUSD.CFD.IP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>IX.D.DOW.DAILY.IP</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>CS.D.USDJPY.MINI.IP</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>CC.D.LCO.UMP.IP</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>IX.D.CAC.DAILY.IP</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>IX.D.NIKKEI.DAILY.IP</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>CS.D.AUDUSD.MINI.IP</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>CS.D.EURGBP.MINI.IP</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>IX.D.RUSSELL.DAILY.IP</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>CS.D.USDCAD.MINI.IP</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>CS.D.EURJPY.MINI.IP</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>CS.D.USDCHF.MINI.IP</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>CS.D.NZDUSD.MINI.IP</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>IX.D.DAX.IFD.IP</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>IX.D.HANGSENG.DAILY.IP</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>IX.D.NASDAQ.CASH.IP</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>IX.D.STXE.CASH.IP</t>
         </is>
@@ -600,6 +710,28 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -635,6 +767,28 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -654,42 +808,58 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>49410</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>49410</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>8417.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>57084.2</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="n">
-        <v>2661.95</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
         <v>25033.6</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AW4" t="n">
         <v>26796.7</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AX4" t="n">
         <v>24817.3</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AY4" t="n">
         <v>6065.4</v>
       </c>
     </row>
@@ -727,6 +897,28 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -746,42 +938,58 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>49624.8</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>49624.8</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
-        <v>8535.4</v>
-      </c>
-      <c r="R6" t="n">
-        <v>57088.3</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="n">
-        <v>2662.2</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
         <v>25236.6</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AW6" t="n">
         <v>26863.4</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AX6" t="n">
         <v>25016.2</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AY6" t="n">
         <v>6135.1</v>
       </c>
     </row>
@@ -819,6 +1027,28 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -838,42 +1068,58 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>49528.4</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>49528.4</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>8515.200000000001</v>
-      </c>
-      <c r="R8" t="n">
-        <v>56981.6</v>
-      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
-        <v>2652.65</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
         <v>25176</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AW8" t="n">
         <v>26826.4</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AX8" t="n">
         <v>24911.3</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AY8" t="n">
         <v>6120.4</v>
       </c>
     </row>
@@ -911,6 +1157,28 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -930,42 +1198,58 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>48839.5</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>48839.5</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>8506.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>56665.8</v>
-      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>2621.45</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="n">
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
         <v>24996.5</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AW10" t="n">
         <v>26891.9</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AX10" t="n">
         <v>24735.3</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AY10" t="n">
         <v>6123.3</v>
       </c>
     </row>
@@ -1003,6 +1287,28 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1022,42 +1328,58 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>49177.5</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>49177.5</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>8539.9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>57912</v>
-      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="n">
-        <v>2651.55</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="n">
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
         <v>25039.3</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AW12" t="n">
         <v>26766.2</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AX12" t="n">
         <v>24995.3</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AY12" t="n">
         <v>6136.1</v>
       </c>
     </row>
@@ -1095,6 +1417,28 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1114,42 +1458,58 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>49392</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>49392</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>8569.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>59285.1</v>
-      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="n">
-        <v>2660.65</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="n">
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
         <v>25181.3</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AW14" t="n">
         <v>26950</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AX14" t="n">
         <v>25270</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AY14" t="n">
         <v>6175.7</v>
       </c>
     </row>
@@ -1187,6 +1547,28 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1206,42 +1588,58 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>49229.6</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>49229.6</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>8611.700000000001</v>
-      </c>
-      <c r="R16" t="n">
-        <v>58435</v>
-      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
-        <v>2655.55</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="n">
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
         <v>25253.3</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AW16" t="n">
         <v>26389.6</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AX16" t="n">
         <v>24955.6</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AY16" t="n">
         <v>6150.7</v>
       </c>
     </row>
@@ -1279,6 +1677,28 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1298,42 +1718,58 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>48858.5</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>48858.5</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>8530.6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>58612.7</v>
-      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="n">
-        <v>2626.65</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
         <v>25143.7</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AW18" t="n">
         <v>26490.4</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AX18" t="n">
         <v>24914.4</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AY18" t="n">
         <v>6095.38</v>
       </c>
     </row>
@@ -1371,6 +1807,28 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1390,42 +1848,58 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>48368.8</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>48368.8</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>8466.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>57488.1</v>
-      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="n">
-        <v>2591.25</v>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="n">
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="n">
         <v>24946.3</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AW20" t="n">
         <v>26350.6</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AX20" t="n">
         <v>24696.7</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AY20" t="n">
         <v>6049.58</v>
       </c>
     </row>
@@ -1463,6 +1937,28 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1482,42 +1978,58 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>48823.6</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>48823.6</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
-        <v>8387.700000000001</v>
-      </c>
-      <c r="R22" t="n">
-        <v>57713.1</v>
-      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="n">
-        <v>2650.85</v>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="n">
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="n">
         <v>24582.2</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AW22" t="n">
         <v>26156.8</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AX22" t="n">
         <v>24935.3</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AY22" t="n">
         <v>5982.2</v>
       </c>
     </row>
@@ -1555,6 +2067,28 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1574,42 +2108,58 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>48413.3</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>48413.3</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>8165.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>54951.7</v>
-      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="n">
-        <v>2603.45</v>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="n">
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="n">
         <v>23985</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AW24" t="n">
         <v>25468.5</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AX24" t="n">
         <v>24668</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AY24" t="n">
         <v>5813.3</v>
       </c>
     </row>
@@ -1647,6 +2197,28 @@
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1666,42 +2238,58 @@
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>48753.2</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>48753.2</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>8204</v>
-      </c>
-      <c r="R26" t="n">
-        <v>56232.9</v>
-      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="n">
-        <v>2635.85</v>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="n">
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="n">
         <v>24302.2</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AW26" t="n">
         <v>25602.8</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AX26" t="n">
         <v>25137.1</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AY26" t="n">
         <v>5901.9</v>
       </c>
     </row>
@@ -1739,6 +2327,28 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1758,42 +2368,58 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>48034</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>48034</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>8059.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>54563.2</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="n">
-        <v>2592.85</v>
-      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="n">
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="n">
         <v>23866.2</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AW28" t="n">
         <v>25202.5</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AX28" t="n">
         <v>25031.4</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AY28" t="n">
         <v>5793.6</v>
       </c>
     </row>
@@ -1831,6 +2457,28 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1850,42 +2498,58 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>47434.2</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>47434.2</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>8017.2</v>
-      </c>
-      <c r="R30" t="n">
-        <v>54029.9</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="n">
-        <v>2522</v>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="n">
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="n">
         <v>23640.3</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AW30" t="n">
         <v>25325.2</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AX30" t="n">
         <v>24634.2</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AY30" t="n">
         <v>5723.03</v>
       </c>
     </row>
@@ -1923,6 +2587,28 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1942,42 +2628,58 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>46613</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>46613</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
-        <v>7873</v>
-      </c>
-      <c r="R32" t="n">
-        <v>52216.5</v>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="n">
-        <v>2433.35</v>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="n">
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="n">
         <v>23222.3</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AW32" t="n">
         <v>25042.2</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AX32" t="n">
         <v>24187.4</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AY32" t="n">
         <v>5615.9</v>
       </c>
     </row>
@@ -2015,6 +2717,28 @@
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2034,42 +2758,58 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>47534.3</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>47534.3</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
-        <v>8000.3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>54259.6</v>
-      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="n">
-        <v>2534.05</v>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="n">
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="inlineStr"/>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="n">
         <v>23703.1</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AW34" t="n">
         <v>25545.7</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AX34" t="n">
         <v>24854.1</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AY34" t="n">
         <v>5764.7</v>
       </c>
     </row>
@@ -2107,6 +2847,28 @@
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="inlineStr"/>
+      <c r="AS35" t="inlineStr"/>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2126,42 +2888,58 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>47744.5</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>47744.5</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
-        <v>7996.9</v>
-      </c>
-      <c r="R36" t="n">
-        <v>55066.9</v>
-      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="n">
-        <v>2552.05</v>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="n">
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="inlineStr"/>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="n">
         <v>23809.1</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AW36" t="n">
         <v>25945.2</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AX36" t="n">
         <v>24990.4</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AY36" t="n">
         <v>5786.9</v>
       </c>
     </row>
@@ -2199,6 +2977,28 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
+      <c r="AQ37" t="inlineStr"/>
+      <c r="AR37" t="inlineStr"/>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2218,42 +3018,58 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>47030.3</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>47030.3</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>7976.9</v>
-      </c>
-      <c r="R38" t="n">
-        <v>54158</v>
-      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="n">
-        <v>2505.75</v>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="n">
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
+      <c r="AQ38" t="inlineStr"/>
+      <c r="AR38" t="inlineStr"/>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="n">
         <v>23465.2</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AW38" t="n">
         <v>25634.7</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AX38" t="n">
         <v>24768.1</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AY38" t="n">
         <v>5752.63</v>
       </c>
     </row>
@@ -2291,6 +3107,28 @@
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
+      <c r="AQ39" t="inlineStr"/>
+      <c r="AR39" t="inlineStr"/>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2310,42 +3148,58 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>46739.9</v>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>46739.9</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>7964.5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>53462.2</v>
-      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="n">
-        <v>2490.95</v>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="n">
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
+      <c r="AQ40" t="inlineStr"/>
+      <c r="AR40" t="inlineStr"/>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="n">
         <v>23495</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AW40" t="n">
         <v>25453.6</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AX40" t="n">
         <v>24514</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AY40" t="n">
         <v>5725.3</v>
       </c>
     </row>
@@ -2383,6 +3237,28 @@
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
+      <c r="AQ41" t="inlineStr"/>
+      <c r="AR41" t="inlineStr"/>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr"/>
+      <c r="AX41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2402,42 +3278,58 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>46475.1</v>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>46475.1</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
-        <v>7875.6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>53150.3</v>
-      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="n">
-        <v>2474.5</v>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="n">
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
+      <c r="AQ42" t="inlineStr"/>
+      <c r="AR42" t="inlineStr"/>
+      <c r="AS42" t="inlineStr"/>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="n">
         <v>23329.3</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AW42" t="n">
         <v>25400.4</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AX42" t="n">
         <v>24321.2</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AY42" t="n">
         <v>5689.36</v>
       </c>
     </row>
@@ -2475,6 +3367,28 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
+      <c r="AQ43" t="inlineStr"/>
+      <c r="AR43" t="inlineStr"/>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr"/>
+      <c r="AX43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2494,42 +3408,58 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>46641.8</v>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>46641.8</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
-        <v>7919.5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>53651.9</v>
-      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="n">
-        <v>2489.45</v>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="n">
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
+      <c r="AQ44" t="inlineStr"/>
+      <c r="AR44" t="inlineStr"/>
+      <c r="AS44" t="inlineStr"/>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="n">
         <v>23428.6</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AW44" t="n">
         <v>25450.7</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AX44" t="n">
         <v>24424</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AY44" t="n">
         <v>5713.9</v>
       </c>
     </row>
@@ -2567,6 +3497,28 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
+      <c r="AQ45" t="inlineStr"/>
+      <c r="AR45" t="inlineStr"/>
+      <c r="AS45" t="inlineStr"/>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr"/>
+      <c r="AX45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2586,42 +3538,58 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>46926.7</v>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>46926.7</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
-        <v>7949</v>
-      </c>
-      <c r="R46" t="n">
-        <v>54337.6</v>
-      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="n">
-        <v>2501.65</v>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="n">
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
+      <c r="AQ46" t="inlineStr"/>
+      <c r="AR46" t="inlineStr"/>
+      <c r="AS46" t="inlineStr"/>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="n">
         <v>23625.4</v>
       </c>
-      <c r="AA46" t="n">
+      <c r="AW46" t="n">
         <v>25861.7</v>
       </c>
-      <c r="AB46" t="n">
+      <c r="AX46" t="n">
         <v>24652</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AY46" t="n">
         <v>5754.2</v>
       </c>
     </row>
@@ -2659,6 +3627,28 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -2678,42 +3668,58 @@
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>46944.6</v>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>46944.6</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
-        <v>7956.2</v>
-      </c>
-      <c r="R48" t="n">
-        <v>54274.4</v>
-      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="n">
-        <v>2517.85</v>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="n">
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="n">
         <v>23670.5</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AW48" t="n">
         <v>25859.5</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AX48" t="n">
         <v>24775.5</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AY48" t="n">
         <v>5756.4</v>
       </c>
     </row>
@@ -2751,6 +3757,28 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -2770,42 +3798,58 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>46157</v>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="n">
-        <v>46157</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="n">
-        <v>7897.7</v>
-      </c>
-      <c r="R50" t="n">
-        <v>53599.6</v>
-      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="n">
-        <v>2474.45</v>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="n">
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="n">
         <v>23169.5</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AW50" t="n">
         <v>25416.9</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AX50" t="n">
         <v>24395.2</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AY50" t="n">
         <v>5655.5</v>
       </c>
     </row>
@@ -2843,6 +3887,28 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -2860,42 +3926,58 @@
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>46139.2</v>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>46139.2</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
-        <v>7842.7</v>
-      </c>
-      <c r="R52" t="n">
-        <v>53401.2</v>
-      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="n">
-        <v>2508.55</v>
-      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="n">
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="n">
         <v>23019.7</v>
       </c>
-      <c r="AA52" t="n">
+      <c r="AW52" t="n">
         <v>25368.8</v>
       </c>
-      <c r="AB52" t="n">
+      <c r="AX52" t="n">
         <v>24407.7</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AY52" t="n">
         <v>5655.4</v>
       </c>
     </row>
@@ -2933,6 +4015,28 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -2952,42 +4056,58 @@
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>45803.1</v>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="n">
-        <v>45803.1</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="n">
-        <v>7613.8</v>
-      </c>
-      <c r="R54" t="n">
-        <v>51317.2</v>
-      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="n">
-        <v>2452.1</v>
-      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="n">
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="n">
         <v>22214.3</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AW54" t="n">
         <v>24770.8</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AX54" t="n">
         <v>24000.4</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AY54" t="n">
         <v>5474.95</v>
       </c>
     </row>
@@ -3025,6 +4145,28 @@
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3044,42 +4186,58 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>45538.6</v>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>45538.6</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="n">
-        <v>7540.6</v>
-      </c>
-      <c r="R56" t="n">
-        <v>51180.5</v>
-      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="n">
-        <v>2432.65</v>
-      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="n">
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="n">
         <v>21975.6</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AW56" t="n">
         <v>24659.3</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AX56" t="n">
         <v>23794.4</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AY56" t="n">
         <v>5419.6</v>
       </c>
     </row>
@@ -3117,6 +4275,28 @@
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
+      <c r="AQ57" t="inlineStr"/>
+      <c r="AR57" t="inlineStr"/>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -3136,42 +4316,58 @@
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>46290.6</v>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="n">
-        <v>46290.6</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="n">
-        <v>7798.8</v>
-      </c>
-      <c r="R58" t="n">
-        <v>53018.2</v>
-      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="n">
-        <v>2500.55</v>
-      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="n">
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
+      <c r="AQ58" t="inlineStr"/>
+      <c r="AR58" t="inlineStr"/>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="n">
         <v>22845</v>
       </c>
-      <c r="AA58" t="n">
+      <c r="AW58" t="n">
         <v>24982.7</v>
       </c>
-      <c r="AB58" t="n">
+      <c r="AX58" t="n">
         <v>24241.8</v>
       </c>
-      <c r="AC58" t="n">
+      <c r="AY58" t="n">
         <v>5617.7</v>
       </c>
     </row>
@@ -3209,6 +4405,28 @@
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
+      <c r="AQ59" t="inlineStr"/>
+      <c r="AR59" t="inlineStr"/>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -3228,42 +4446,58 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>46448</v>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="n">
-        <v>46448</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
-        <v>7815.7</v>
-      </c>
-      <c r="R60" t="n">
-        <v>53500.6</v>
-      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="n">
-        <v>2535.75</v>
-      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="n">
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
+      <c r="AQ60" t="inlineStr"/>
+      <c r="AR60" t="inlineStr"/>
+      <c r="AS60" t="inlineStr"/>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="n">
         <v>22891</v>
       </c>
-      <c r="AA60" t="n">
+      <c r="AW60" t="n">
         <v>25050.4</v>
       </c>
-      <c r="AB60" t="n">
+      <c r="AX60" t="n">
         <v>24205</v>
       </c>
-      <c r="AC60" t="n">
+      <c r="AY60" t="n">
         <v>5645.68</v>
       </c>
     </row>
@@ -3301,6 +4535,28 @@
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -3320,42 +4576,58 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>46359.5</v>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>46359.5</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="n">
-        <v>7815.5</v>
-      </c>
-      <c r="R62" t="n">
-        <v>53878.5</v>
-      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="n">
-        <v>2530.75</v>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="n">
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="n">
         <v>22870.1</v>
       </c>
-      <c r="AA62" t="n">
+      <c r="AW62" t="n">
         <v>25259.3</v>
       </c>
-      <c r="AB62" t="n">
+      <c r="AX62" t="n">
         <v>24114.6</v>
       </c>
-      <c r="AC62" t="n">
+      <c r="AY62" t="n">
         <v>5621.51</v>
       </c>
     </row>
@@ -3393,6 +4665,28 @@
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -3412,42 +4706,58 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>46181.1</v>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="n">
-        <v>46181.1</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
-        <v>7780.5</v>
-      </c>
-      <c r="R64" t="n">
-        <v>52923.6</v>
-      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="n">
-        <v>2508.55</v>
-      </c>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="n">
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="n">
         <v>22692.5</v>
       </c>
-      <c r="AA64" t="n">
+      <c r="AW64" t="n">
         <v>24768.8</v>
       </c>
-      <c r="AB64" t="n">
+      <c r="AX64" t="n">
         <v>23682.7</v>
       </c>
-      <c r="AC64" t="n">
+      <c r="AY64" t="n">
         <v>5573</v>
       </c>
     </row>
@@ -3485,6 +4795,28 @@
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -3504,42 +4836,58 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>45061.5</v>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>45061.5</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
-        <v>7646.4</v>
-      </c>
-      <c r="R66" t="n">
-        <v>51137.7</v>
-      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="n">
-        <v>2443.2</v>
-      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="n">
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="n">
         <v>22101.1</v>
       </c>
-      <c r="AA66" t="n">
+      <c r="AW66" t="n">
         <v>24627.5</v>
       </c>
-      <c r="AB66" t="n">
+      <c r="AX66" t="n">
         <v>23069.6</v>
       </c>
-      <c r="AC66" t="n">
+      <c r="AY66" t="n">
         <v>5455.22</v>
       </c>
     </row>
@@ -3577,6 +4925,28 @@
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -3596,42 +4966,58 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>44945.6</v>
+      </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="n">
-        <v>44945.6</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
-        <v>7618.7</v>
-      </c>
-      <c r="R68" t="n">
-        <v>50609</v>
-      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
-      <c r="U68" t="n">
-        <v>2430.85</v>
-      </c>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="n">
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="n">
         <v>22031.4</v>
       </c>
-      <c r="AA68" t="n">
+      <c r="AW68" t="n">
         <v>24593.4</v>
       </c>
-      <c r="AB68" t="n">
+      <c r="AX68" t="n">
         <v>23027.2</v>
       </c>
-      <c r="AC68" t="n">
+      <c r="AY68" t="n">
         <v>5435.4</v>
       </c>
     </row>
@@ -3669,6 +5055,28 @@
       <c r="AA69" t="inlineStr"/>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -3688,42 +5096,58 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>45225.5</v>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="n">
-        <v>45225.5</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="n">
-        <v>7722.7</v>
-      </c>
-      <c r="R70" t="n">
-        <v>51054.8</v>
-      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
-      <c r="U70" t="n">
-        <v>2409.85</v>
-      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="n">
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="n">
         <v>22434.6</v>
       </c>
-      <c r="AA70" t="n">
+      <c r="AW70" t="n">
         <v>24724.4</v>
       </c>
-      <c r="AB70" t="n">
+      <c r="AX70" t="n">
         <v>22920.3</v>
       </c>
-      <c r="AC70" t="n">
+      <c r="AY70" t="n">
         <v>5500.9</v>
       </c>
     </row>
@@ -3761,6 +5185,28 @@
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -3780,42 +5226,58 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>46230.95</v>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="n">
-        <v>46230.95</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="n">
-        <v>7921.4</v>
-      </c>
-      <c r="R72" t="n">
-        <v>53050.8</v>
-      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
-      <c r="U72" t="n">
-        <v>2494.15</v>
-      </c>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="n">
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="n">
         <v>23026.2</v>
       </c>
-      <c r="AA72" t="n">
+      <c r="AW72" t="n">
         <v>25317.1</v>
       </c>
-      <c r="AB72" t="n">
+      <c r="AX72" t="n">
         <v>23777.1</v>
       </c>
-      <c r="AC72" t="n">
+      <c r="AY72" t="n">
         <v>5653.5</v>
       </c>
     </row>
@@ -3853,6 +5315,28 @@
       <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -3872,42 +5356,58 @@
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>46561.8</v>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="n">
-        <v>46561.8</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
-        <v>7976.6</v>
-      </c>
-      <c r="R74" t="n">
-        <v>54233.9</v>
-      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="n">
-        <v>2510.15</v>
-      </c>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="n">
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr"/>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="n">
         <v>23289</v>
       </c>
-      <c r="AA74" t="n">
+      <c r="AW74" t="n">
         <v>25315.3</v>
       </c>
-      <c r="AB74" t="n">
+      <c r="AX74" t="n">
         <v>23996.1</v>
       </c>
-      <c r="AC74" t="n">
+      <c r="AY74" t="n">
         <v>5720.9</v>
       </c>
     </row>
@@ -3945,6 +5445,28 @@
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -3964,42 +5486,58 @@
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>46522.4</v>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
-        <v>46522.4</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="n">
-        <v>7990.9</v>
-      </c>
-      <c r="R76" t="n">
-        <v>53247.5</v>
-      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="n">
-        <v>2530.55</v>
-      </c>
+      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="n">
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="n">
         <v>23217.6</v>
       </c>
-      <c r="AA76" t="n">
+      <c r="AW76" t="n">
         <v>25270.4</v>
       </c>
-      <c r="AB76" t="n">
+      <c r="AX76" t="n">
         <v>24030.5</v>
       </c>
-      <c r="AC76" t="n">
+      <c r="AY76" t="n">
         <v>5701.47</v>
       </c>
     </row>
@@ -4037,6 +5575,28 @@
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -4056,42 +5616,58 @@
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>46407.7</v>
+      </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="n">
-        <v>46407.7</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="n">
-        <v>7960.4</v>
-      </c>
-      <c r="R78" t="n">
-        <v>53165.2</v>
-      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="n">
-        <v>2519.65</v>
-      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="n">
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="n">
         <v>23127.3</v>
       </c>
-      <c r="AA78" t="n">
+      <c r="AW78" t="n">
         <v>25188.7</v>
       </c>
-      <c r="AB78" t="n">
+      <c r="AX78" t="n">
         <v>23957.4</v>
       </c>
-      <c r="AC78" t="n">
+      <c r="AY78" t="n">
         <v>5679.77</v>
       </c>
     </row>
@@ -4109,42 +5685,58 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>46258.3</v>
+      </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="n">
-        <v>46258.3</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="n">
-        <v>7934.5</v>
-      </c>
-      <c r="R79" t="n">
-        <v>52872.6</v>
-      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="n">
-        <v>2510.85</v>
-      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="n">
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="n">
         <v>23052.9</v>
       </c>
-      <c r="AA79" t="n">
+      <c r="AW79" t="n">
         <v>25153.9</v>
       </c>
-      <c r="AB79" t="n">
+      <c r="AX79" t="n">
         <v>23907.8</v>
       </c>
-      <c r="AC79" t="n">
+      <c r="AY79" t="n">
         <v>5661.8</v>
       </c>
     </row>
@@ -4182,6 +5774,28 @@
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -4201,42 +5815,58 @@
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>46709.5</v>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="n">
-        <v>46709.5</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="n">
-        <v>8026.1</v>
-      </c>
-      <c r="R81" t="n">
-        <v>53883.7</v>
-      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
-      <c r="U81" t="n">
-        <v>2536.65</v>
-      </c>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="n">
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="n">
         <v>23295.1</v>
       </c>
-      <c r="AA81" t="n">
+      <c r="AW81" t="n">
         <v>25312</v>
       </c>
-      <c r="AB81" t="n">
+      <c r="AX81" t="n">
         <v>24134.7</v>
       </c>
-      <c r="AC81" t="n">
+      <c r="AY81" t="n">
         <v>5727.1</v>
       </c>
     </row>
@@ -4274,6 +5904,28 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -4293,42 +5945,58 @@
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>47545.8</v>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="n">
-        <v>47545.8</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="n">
-        <v>8193.700000000001</v>
-      </c>
-      <c r="R83" t="n">
-        <v>55942.4</v>
-      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
-      <c r="U83" t="n">
-        <v>2623.75</v>
-      </c>
+      <c r="U83" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="n">
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="n">
         <v>23802.3</v>
       </c>
-      <c r="AA83" t="n">
+      <c r="AW83" t="n">
         <v>25620.5</v>
       </c>
-      <c r="AB83" t="n">
+      <c r="AX83" t="n">
         <v>24748.9</v>
       </c>
-      <c r="AC83" t="n">
+      <c r="AY83" t="n">
         <v>5845.7</v>
       </c>
     </row>
@@ -4366,6 +6034,28 @@
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr"/>
+      <c r="AR84" t="inlineStr"/>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr"/>
+      <c r="AX84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -4385,42 +6075,58 @@
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>47886.5</v>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="n">
-        <v>47886.5</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="n">
-        <v>8274.200000000001</v>
-      </c>
-      <c r="R85" t="n">
-        <v>56750.7</v>
-      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
-      <c r="U85" t="n">
-        <v>2621.15</v>
-      </c>
+      <c r="U85" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
-      <c r="Z85" t="n">
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="inlineStr"/>
+      <c r="AP85" t="inlineStr"/>
+      <c r="AQ85" t="inlineStr"/>
+      <c r="AR85" t="inlineStr"/>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AU85" t="inlineStr"/>
+      <c r="AV85" t="n">
         <v>24005.2</v>
       </c>
-      <c r="AA85" t="n">
+      <c r="AW85" t="n">
         <v>25877.5</v>
       </c>
-      <c r="AB85" t="n">
+      <c r="AX85" t="n">
         <v>24864</v>
       </c>
-      <c r="AC85" t="n">
+      <c r="AY85" t="n">
         <v>5913.6</v>
       </c>
     </row>
@@ -4458,6 +6164,28 @@
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="inlineStr"/>
+      <c r="AR86" t="inlineStr"/>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AU86" t="inlineStr"/>
+      <c r="AV86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr"/>
+      <c r="AX86" t="inlineStr"/>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -4477,42 +6205,58 @@
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>48155.1</v>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="n">
-        <v>48155.1</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="n">
-        <v>8252.299999999999</v>
-      </c>
-      <c r="R87" t="n">
-        <v>56487.1</v>
-      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="n">
-        <v>2635.65</v>
-      </c>
+      <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
-      <c r="Z87" t="n">
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr"/>
+      <c r="AR87" t="inlineStr"/>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AU87" t="inlineStr"/>
+      <c r="AV87" t="n">
         <v>23860.1</v>
       </c>
-      <c r="AA87" t="n">
+      <c r="AW87" t="n">
         <v>25916.1</v>
       </c>
-      <c r="AB87" t="n">
+      <c r="AX87" t="n">
         <v>25042.9</v>
       </c>
-      <c r="AC87" t="n">
+      <c r="AY87" t="n">
         <v>5900.9</v>
       </c>
     </row>
@@ -4550,6 +6294,28 @@
       <c r="AA88" t="inlineStr"/>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
+      <c r="AQ88" t="inlineStr"/>
+      <c r="AR88" t="inlineStr"/>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
+      <c r="AX88" t="inlineStr"/>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -4569,42 +6335,58 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>47972</v>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="n">
-        <v>47972</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
-        <v>8266.799999999999</v>
-      </c>
-      <c r="R89" t="n">
-        <v>57406.8</v>
-      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
-      <c r="U89" t="n">
-        <v>2636.3</v>
-      </c>
+      <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="n">
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
+      <c r="AP89" t="inlineStr"/>
+      <c r="AQ89" t="inlineStr"/>
+      <c r="AR89" t="inlineStr"/>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AU89" t="inlineStr"/>
+      <c r="AV89" t="n">
         <v>23823.9</v>
       </c>
-      <c r="AA89" t="n">
+      <c r="AW89" t="n">
         <v>25948.9</v>
       </c>
-      <c r="AB89" t="n">
+      <c r="AX89" t="n">
         <v>25164.7</v>
       </c>
-      <c r="AC89" t="n">
+      <c r="AY89" t="n">
         <v>5928.91</v>
       </c>
     </row>
@@ -4642,6 +6424,28 @@
       <c r="AA90" t="inlineStr"/>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
+      <c r="AQ90" t="inlineStr"/>
+      <c r="AR90" t="inlineStr"/>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AU90" t="inlineStr"/>
+      <c r="AV90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr"/>
+      <c r="AX90" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -4661,42 +6465,58 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>47403</v>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="n">
-        <v>47403</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="n">
-        <v>8130.9</v>
-      </c>
-      <c r="R91" t="n">
-        <v>56085.5</v>
-      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
-      <c r="U91" t="n">
-        <v>2587.85</v>
-      </c>
+      <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="n">
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
+      <c r="AP91" t="inlineStr"/>
+      <c r="AQ91" t="inlineStr"/>
+      <c r="AR91" t="inlineStr"/>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AU91" t="inlineStr"/>
+      <c r="AV91" t="n">
         <v>23438.1</v>
       </c>
-      <c r="AA91" t="n">
+      <c r="AW91" t="n">
         <v>25770.2</v>
       </c>
-      <c r="AB91" t="n">
+      <c r="AX91" t="n">
         <v>24791.8</v>
       </c>
-      <c r="AC91" t="n">
+      <c r="AY91" t="n">
         <v>5831.8</v>
       </c>
     </row>
@@ -4734,6 +6554,28 @@
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr"/>
+      <c r="AO92" t="inlineStr"/>
+      <c r="AP92" t="inlineStr"/>
+      <c r="AQ92" t="inlineStr"/>
+      <c r="AR92" t="inlineStr"/>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AU92" t="inlineStr"/>
+      <c r="AV92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr"/>
+      <c r="AX92" t="inlineStr"/>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -4753,42 +6595,58 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>48227.7</v>
+      </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="n">
-        <v>48227.7</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="n">
-        <v>8268.299999999999</v>
-      </c>
-      <c r="R93" t="n">
-        <v>57698.9</v>
-      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
-      <c r="U93" t="n">
-        <v>2678.15</v>
-      </c>
+      <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="n">
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
+      <c r="AQ93" t="inlineStr"/>
+      <c r="AR93" t="inlineStr"/>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AU93" t="inlineStr"/>
+      <c r="AV93" t="n">
         <v>23965.5</v>
       </c>
-      <c r="AA93" t="n">
+      <c r="AW93" t="n">
         <v>25968.2</v>
       </c>
-      <c r="AB93" t="n">
+      <c r="AX93" t="n">
         <v>25435.7</v>
       </c>
-      <c r="AC93" t="n">
+      <c r="AY93" t="n">
         <v>5947.3</v>
       </c>
     </row>
@@ -4826,6 +6684,28 @@
       <c r="AA94" t="inlineStr"/>
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="inlineStr"/>
+      <c r="AP94" t="inlineStr"/>
+      <c r="AQ94" t="inlineStr"/>
+      <c r="AR94" t="inlineStr"/>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AU94" t="inlineStr"/>
+      <c r="AV94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr"/>
+      <c r="AX94" t="inlineStr"/>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -4845,42 +6725,58 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>48537.7</v>
+      </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="n">
-        <v>48537.7</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="n">
-        <v>8326.9</v>
-      </c>
-      <c r="R95" t="n">
-        <v>58706</v>
-      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
-      <c r="U95" t="n">
-        <v>2705.55</v>
-      </c>
+      <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="n">
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr"/>
+      <c r="AO95" t="inlineStr"/>
+      <c r="AP95" t="inlineStr"/>
+      <c r="AQ95" t="inlineStr"/>
+      <c r="AR95" t="inlineStr"/>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AU95" t="inlineStr"/>
+      <c r="AV95" t="n">
         <v>24054.9</v>
       </c>
-      <c r="AA95" t="n">
+      <c r="AW95" t="n">
         <v>26212.7</v>
       </c>
-      <c r="AB95" t="n">
+      <c r="AX95" t="n">
         <v>25830.8</v>
       </c>
-      <c r="AC95" t="n">
+      <c r="AY95" t="n">
         <v>5986.4</v>
       </c>
     </row>
@@ -4918,6 +6814,28 @@
       <c r="AA96" t="inlineStr"/>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr"/>
+      <c r="AO96" t="inlineStr"/>
+      <c r="AP96" t="inlineStr"/>
+      <c r="AQ96" t="inlineStr"/>
+      <c r="AR96" t="inlineStr"/>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AU96" t="inlineStr"/>
+      <c r="AV96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr"/>
+      <c r="AX96" t="inlineStr"/>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -4937,42 +6855,58 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>48527.8</v>
+      </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="n">
-        <v>48527.8</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="n">
-        <v>8264.799999999999</v>
-      </c>
-      <c r="R97" t="n">
-        <v>58563.8</v>
-      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
-      <c r="U97" t="n">
-        <v>2716.35</v>
-      </c>
+      <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="n">
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
+      <c r="AP97" t="inlineStr"/>
+      <c r="AQ97" t="inlineStr"/>
+      <c r="AR97" t="inlineStr"/>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AU97" t="inlineStr"/>
+      <c r="AV97" t="n">
         <v>24107.1</v>
       </c>
-      <c r="AA97" t="n">
+      <c r="AW97" t="n">
         <v>26130.4</v>
       </c>
-      <c r="AB97" t="n">
+      <c r="AX97" t="n">
         <v>26229.3</v>
       </c>
-      <c r="AC97" t="n">
+      <c r="AY97" t="n">
         <v>5946.9</v>
       </c>
     </row>
@@ -5010,6 +6944,28 @@
       <c r="AA98" t="inlineStr"/>
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
+      <c r="AQ98" t="inlineStr"/>
+      <c r="AR98" t="inlineStr"/>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AU98" t="inlineStr"/>
+      <c r="AV98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr"/>
+      <c r="AX98" t="inlineStr"/>
+      <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -5029,42 +6985,58 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>48661.1</v>
+      </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="n">
-        <v>48661.1</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
-        <v>8266.4</v>
-      </c>
-      <c r="R99" t="n">
-        <v>59430.4</v>
-      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
-      <c r="U99" t="n">
-        <v>2725.15</v>
-      </c>
+      <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="n">
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
+      <c r="AQ99" t="inlineStr"/>
+      <c r="AR99" t="inlineStr"/>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AU99" t="inlineStr"/>
+      <c r="AV99" t="n">
         <v>24140.9</v>
       </c>
-      <c r="AA99" t="n">
+      <c r="AW99" t="n">
         <v>26236.3</v>
       </c>
-      <c r="AB99" t="n">
+      <c r="AX99" t="n">
         <v>26321.7</v>
       </c>
-      <c r="AC99" t="n">
+      <c r="AY99" t="n">
         <v>5920.67</v>
       </c>
     </row>
@@ -5102,6 +7074,28 @@
       <c r="AA100" t="inlineStr"/>
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr"/>
+      <c r="AO100" t="inlineStr"/>
+      <c r="AP100" t="inlineStr"/>
+      <c r="AQ100" t="inlineStr"/>
+      <c r="AR100" t="inlineStr"/>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AU100" t="inlineStr"/>
+      <c r="AV100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr"/>
+      <c r="AX100" t="inlineStr"/>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -5121,42 +7115,58 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>49453</v>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="n">
-        <v>49453</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="n">
-        <v>8407.9</v>
-      </c>
-      <c r="R101" t="n">
-        <v>59693.4</v>
-      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
-      <c r="U101" t="n">
-        <v>2777.8</v>
-      </c>
+      <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="n">
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
+      <c r="AQ101" t="inlineStr"/>
+      <c r="AR101" t="inlineStr"/>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AU101" t="inlineStr"/>
+      <c r="AV101" t="n">
         <v>24651.9</v>
       </c>
-      <c r="AA101" t="n">
+      <c r="AW101" t="n">
         <v>26504.1</v>
       </c>
-      <c r="AB101" t="n">
+      <c r="AX101" t="n">
         <v>26684.1</v>
       </c>
-      <c r="AC101" t="n">
+      <c r="AY101" t="n">
         <v>6036.51</v>
       </c>
     </row>
@@ -5194,6 +7204,28 @@
       <c r="AA102" t="inlineStr"/>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr"/>
+      <c r="AP102" t="inlineStr"/>
+      <c r="AQ102" t="inlineStr"/>
+      <c r="AR102" t="inlineStr"/>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AU102" t="inlineStr"/>
+      <c r="AV102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr"/>
+      <c r="AX102" t="inlineStr"/>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -5235,6 +7267,28 @@
       <c r="AA103" t="inlineStr"/>
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
+      <c r="AQ103" t="inlineStr"/>
+      <c r="AR103" t="inlineStr"/>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AU103" t="inlineStr"/>
+      <c r="AV103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr"/>
+      <c r="AX103" t="inlineStr"/>
+      <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -5270,6 +7324,28 @@
       <c r="AA104" t="inlineStr"/>
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
+      <c r="AQ104" t="inlineStr"/>
+      <c r="AR104" t="inlineStr"/>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AU104" t="inlineStr"/>
+      <c r="AV104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr"/>
+      <c r="AX104" t="inlineStr"/>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -5311,6 +7387,28 @@
       <c r="AA105" t="inlineStr"/>
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr"/>
+      <c r="AP105" t="inlineStr"/>
+      <c r="AQ105" t="inlineStr"/>
+      <c r="AR105" t="inlineStr"/>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AU105" t="inlineStr"/>
+      <c r="AV105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr"/>
+      <c r="AX105" t="inlineStr"/>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -5346,6 +7444,28 @@
       <c r="AA106" t="inlineStr"/>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr"/>
+      <c r="AP106" t="inlineStr"/>
+      <c r="AQ106" t="inlineStr"/>
+      <c r="AR106" t="inlineStr"/>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AU106" t="inlineStr"/>
+      <c r="AV106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr"/>
+      <c r="AX106" t="inlineStr"/>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -5387,6 +7507,28 @@
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
+      <c r="AD107" t="inlineStr"/>
+      <c r="AE107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr"/>
+      <c r="AP107" t="inlineStr"/>
+      <c r="AQ107" t="inlineStr"/>
+      <c r="AR107" t="inlineStr"/>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AU107" t="inlineStr"/>
+      <c r="AV107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr"/>
+      <c r="AX107" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -5422,6 +7564,28 @@
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
+      <c r="AQ108" t="inlineStr"/>
+      <c r="AR108" t="inlineStr"/>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AU108" t="inlineStr"/>
+      <c r="AV108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr"/>
+      <c r="AX108" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -5463,6 +7627,28 @@
       <c r="AA109" t="inlineStr"/>
       <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr"/>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="inlineStr"/>
+      <c r="AH109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr"/>
+      <c r="AJ109" t="inlineStr"/>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr"/>
+      <c r="AP109" t="inlineStr"/>
+      <c r="AQ109" t="inlineStr"/>
+      <c r="AR109" t="inlineStr"/>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AU109" t="inlineStr"/>
+      <c r="AV109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr"/>
+      <c r="AX109" t="inlineStr"/>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -5498,6 +7684,28 @@
       <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr"/>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="inlineStr"/>
+      <c r="AH110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr"/>
+      <c r="AJ110" t="inlineStr"/>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr"/>
+      <c r="AO110" t="inlineStr"/>
+      <c r="AP110" t="inlineStr"/>
+      <c r="AQ110" t="inlineStr"/>
+      <c r="AR110" t="inlineStr"/>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AU110" t="inlineStr"/>
+      <c r="AV110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr"/>
+      <c r="AX110" t="inlineStr"/>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -5539,6 +7747,28 @@
       <c r="AA111" t="inlineStr"/>
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="inlineStr"/>
+      <c r="AH111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr"/>
+      <c r="AJ111" t="inlineStr"/>
+      <c r="AK111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="inlineStr"/>
+      <c r="AN111" t="inlineStr"/>
+      <c r="AO111" t="inlineStr"/>
+      <c r="AP111" t="inlineStr"/>
+      <c r="AQ111" t="inlineStr"/>
+      <c r="AR111" t="inlineStr"/>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AU111" t="inlineStr"/>
+      <c r="AV111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr"/>
+      <c r="AX111" t="inlineStr"/>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -5574,6 +7804,28 @@
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr"/>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr"/>
+      <c r="AO112" t="inlineStr"/>
+      <c r="AP112" t="inlineStr"/>
+      <c r="AQ112" t="inlineStr"/>
+      <c r="AR112" t="inlineStr"/>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AU112" t="inlineStr"/>
+      <c r="AV112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr"/>
+      <c r="AX112" t="inlineStr"/>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -5615,6 +7867,28 @@
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr"/>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr"/>
+      <c r="AP113" t="inlineStr"/>
+      <c r="AQ113" t="inlineStr"/>
+      <c r="AR113" t="inlineStr"/>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AU113" t="inlineStr"/>
+      <c r="AV113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr"/>
+      <c r="AX113" t="inlineStr"/>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -5650,6 +7924,28 @@
       <c r="AA114" t="inlineStr"/>
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr"/>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr"/>
+      <c r="AP114" t="inlineStr"/>
+      <c r="AQ114" t="inlineStr"/>
+      <c r="AR114" t="inlineStr"/>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AU114" t="inlineStr"/>
+      <c r="AV114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr"/>
+      <c r="AX114" t="inlineStr"/>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -5691,6 +7987,28 @@
       <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr"/>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr"/>
+      <c r="AO115" t="inlineStr"/>
+      <c r="AP115" t="inlineStr"/>
+      <c r="AQ115" t="inlineStr"/>
+      <c r="AR115" t="inlineStr"/>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AU115" t="inlineStr"/>
+      <c r="AV115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr"/>
+      <c r="AX115" t="inlineStr"/>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -5726,6 +8044,28 @@
       <c r="AA116" t="inlineStr"/>
       <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr"/>
+      <c r="AO116" t="inlineStr"/>
+      <c r="AP116" t="inlineStr"/>
+      <c r="AQ116" t="inlineStr"/>
+      <c r="AR116" t="inlineStr"/>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AU116" t="inlineStr"/>
+      <c r="AV116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr"/>
+      <c r="AX116" t="inlineStr"/>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -5767,6 +8107,28 @@
       <c r="AA117" t="inlineStr"/>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr"/>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr"/>
+      <c r="AP117" t="inlineStr"/>
+      <c r="AQ117" t="inlineStr"/>
+      <c r="AR117" t="inlineStr"/>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AU117" t="inlineStr"/>
+      <c r="AV117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr"/>
+      <c r="AX117" t="inlineStr"/>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -5802,6 +8164,28 @@
       <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr"/>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr"/>
+      <c r="AP118" t="inlineStr"/>
+      <c r="AQ118" t="inlineStr"/>
+      <c r="AR118" t="inlineStr"/>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AU118" t="inlineStr"/>
+      <c r="AV118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr"/>
+      <c r="AX118" t="inlineStr"/>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -5843,6 +8227,28 @@
       <c r="AA119" t="inlineStr"/>
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr"/>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
+      <c r="AQ119" t="inlineStr"/>
+      <c r="AR119" t="inlineStr"/>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AU119" t="inlineStr"/>
+      <c r="AV119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr"/>
+      <c r="AX119" t="inlineStr"/>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -5878,6 +8284,28 @@
       <c r="AA120" t="inlineStr"/>
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr"/>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
+      <c r="AP120" t="inlineStr"/>
+      <c r="AQ120" t="inlineStr"/>
+      <c r="AR120" t="inlineStr"/>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AU120" t="inlineStr"/>
+      <c r="AV120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr"/>
+      <c r="AX120" t="inlineStr"/>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -5899,50 +8327,56 @@
       <c r="G121" t="n">
         <v>23864</v>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="n">
+        <v>48705.4</v>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="n">
-        <v>48705.4</v>
-      </c>
-      <c r="O121" t="n">
-        <v>160.3335</v>
-      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="n">
-        <v>8044.4</v>
-      </c>
-      <c r="R121" t="n">
-        <v>58961.3</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0.711865</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0.8662749999999999</v>
-      </c>
-      <c r="U121" t="n">
-        <v>2734.35</v>
-      </c>
-      <c r="V121" t="n">
-        <v>1.368105</v>
-      </c>
-      <c r="W121" t="n">
-        <v>187.2525</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0.79134</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>0.58326</v>
-      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr"/>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
+      <c r="AP121" t="inlineStr"/>
+      <c r="AQ121" t="inlineStr"/>
+      <c r="AR121" t="inlineStr"/>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0.79134</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.58326</v>
+      </c>
+      <c r="AV121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr"/>
+      <c r="AX121" t="inlineStr"/>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -5964,9 +8398,7 @@
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="n">
-        <v>11291.6</v>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
@@ -5980,6 +8412,28 @@
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="inlineStr"/>
+      <c r="AK122" t="inlineStr"/>
+      <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr"/>
+      <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr"/>
+      <c r="AP122" t="inlineStr"/>
+      <c r="AQ122" t="inlineStr"/>
+      <c r="AR122" t="inlineStr"/>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AU122" t="inlineStr"/>
+      <c r="AV122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr"/>
+      <c r="AX122" t="inlineStr"/>
+      <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -6001,50 +8455,56 @@
       <c r="G123" t="n">
         <v>24304.9</v>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="n">
+        <v>49762</v>
+      </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" t="n">
-        <v>49762</v>
-      </c>
-      <c r="O123" t="n">
-        <v>156.6665</v>
-      </c>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="n">
-        <v>8128.5</v>
-      </c>
-      <c r="R123" t="n">
-        <v>59750.8</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0.7200150000000001</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0.8624149999999999</v>
-      </c>
-      <c r="U123" t="n">
-        <v>2805.25</v>
-      </c>
-      <c r="V123" t="n">
-        <v>1.358165</v>
-      </c>
-      <c r="W123" t="n">
-        <v>183.8075</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0.7815</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0.59061</v>
-      </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr"/>
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="inlineStr"/>
+      <c r="AK123" t="inlineStr"/>
+      <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="inlineStr"/>
+      <c r="AP123" t="inlineStr"/>
+      <c r="AQ123" t="inlineStr"/>
+      <c r="AR123" t="inlineStr"/>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.59061</v>
+      </c>
+      <c r="AV123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr"/>
+      <c r="AX123" t="inlineStr"/>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -6066,9 +8526,7 @@
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="n">
-        <v>11146.5</v>
-      </c>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr"/>
@@ -6082,6 +8540,28 @@
       <c r="AA124" t="inlineStr"/>
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="inlineStr"/>
+      <c r="AK124" t="inlineStr"/>
+      <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr"/>
+      <c r="AN124" t="inlineStr"/>
+      <c r="AO124" t="inlineStr"/>
+      <c r="AP124" t="inlineStr"/>
+      <c r="AQ124" t="inlineStr"/>
+      <c r="AR124" t="inlineStr"/>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AU124" t="inlineStr"/>
+      <c r="AV124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr"/>
+      <c r="AX124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -6103,50 +8583,56 @@
       <c r="G125" t="n">
         <v>24292.9</v>
       </c>
-      <c r="H125" t="inlineStr"/>
+      <c r="H125" t="n">
+        <v>49456.2</v>
+      </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" t="n">
-        <v>49456.2</v>
-      </c>
-      <c r="O125" t="n">
-        <v>157.016</v>
-      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="n">
-        <v>8117.9</v>
-      </c>
-      <c r="R125" t="n">
-        <v>59246.4</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0.720065</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0.863375</v>
-      </c>
-      <c r="U125" t="n">
-        <v>2806.1</v>
-      </c>
-      <c r="V125" t="n">
-        <v>1.358645</v>
-      </c>
-      <c r="W125" t="n">
-        <v>184.0355</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0.782265</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0.58975</v>
-      </c>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr"/>
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
+      <c r="AJ125" t="inlineStr"/>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr"/>
+      <c r="AR125" t="inlineStr"/>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0.782265</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.58975</v>
+      </c>
+      <c r="AV125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr"/>
+      <c r="AX125" t="inlineStr"/>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -6168,9 +8654,7 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="n">
-        <v>10884.6</v>
-      </c>
+      <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
@@ -6184,6 +8668,28 @@
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="inlineStr"/>
+      <c r="AK126" t="inlineStr"/>
+      <c r="AL126" t="inlineStr"/>
+      <c r="AM126" t="inlineStr"/>
+      <c r="AN126" t="inlineStr"/>
+      <c r="AO126" t="inlineStr"/>
+      <c r="AP126" t="inlineStr"/>
+      <c r="AQ126" t="inlineStr"/>
+      <c r="AR126" t="inlineStr"/>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AU126" t="inlineStr"/>
+      <c r="AV126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr"/>
+      <c r="AX126" t="inlineStr"/>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -6205,50 +8711,56 @@
       <c r="G127" t="n">
         <v>24411.3</v>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>49602.6</v>
+      </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
-      <c r="N127" t="n">
-        <v>49602.6</v>
-      </c>
-      <c r="O127" t="n">
-        <v>156.84</v>
-      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="n">
-        <v>8157.7</v>
-      </c>
-      <c r="R127" t="n">
-        <v>59574.9</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0.72144</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0.863405</v>
-      </c>
-      <c r="U127" t="n">
-        <v>2819.95</v>
-      </c>
-      <c r="V127" t="n">
-        <v>1.358445</v>
-      </c>
-      <c r="W127" t="n">
-        <v>184.0255</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0.78072</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0.59068</v>
-      </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr"/>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="inlineStr"/>
+      <c r="AK127" t="inlineStr"/>
+      <c r="AL127" t="inlineStr"/>
+      <c r="AM127" t="inlineStr"/>
+      <c r="AN127" t="inlineStr"/>
+      <c r="AO127" t="inlineStr"/>
+      <c r="AP127" t="inlineStr"/>
+      <c r="AQ127" t="inlineStr"/>
+      <c r="AR127" t="inlineStr"/>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0.78072</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.59068</v>
+      </c>
+      <c r="AV127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr"/>
+      <c r="AX127" t="inlineStr"/>
+      <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -6270,9 +8782,7 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="n">
-        <v>10842.1</v>
-      </c>
+      <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr"/>
@@ -6286,6 +8796,28 @@
       <c r="AA128" t="inlineStr"/>
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="inlineStr"/>
+      <c r="AK128" t="inlineStr"/>
+      <c r="AL128" t="inlineStr"/>
+      <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr"/>
+      <c r="AO128" t="inlineStr"/>
+      <c r="AP128" t="inlineStr"/>
+      <c r="AQ128" t="inlineStr"/>
+      <c r="AR128" t="inlineStr"/>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AU128" t="inlineStr"/>
+      <c r="AV128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr"/>
+      <c r="AX128" t="inlineStr"/>
+      <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -6307,50 +8839,56 @@
       <c r="G129" t="n">
         <v>23904.4</v>
       </c>
-      <c r="H129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>48982.6</v>
+      </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" t="n">
-        <v>48982.6</v>
-      </c>
-      <c r="O129" t="n">
-        <v>157.228</v>
-      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="n">
-        <v>7926.4</v>
-      </c>
-      <c r="R129" t="n">
-        <v>59402.2</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0.716735</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0.8641350000000001</v>
-      </c>
-      <c r="U129" t="n">
-        <v>2797.15</v>
-      </c>
-      <c r="V129" t="n">
-        <v>1.362535</v>
-      </c>
-      <c r="W129" t="n">
-        <v>183.8065</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0.78405</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0.58707</v>
-      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="inlineStr"/>
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
+      <c r="AJ129" t="inlineStr"/>
+      <c r="AK129" t="inlineStr"/>
+      <c r="AL129" t="inlineStr"/>
+      <c r="AM129" t="inlineStr"/>
+      <c r="AN129" t="inlineStr"/>
+      <c r="AO129" t="inlineStr"/>
+      <c r="AP129" t="inlineStr"/>
+      <c r="AQ129" t="inlineStr"/>
+      <c r="AR129" t="inlineStr"/>
+      <c r="AS129" t="inlineStr"/>
+      <c r="AT129" t="n">
+        <v>0.78405</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.58707</v>
+      </c>
+      <c r="AV129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr"/>
+      <c r="AX129" t="inlineStr"/>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -6369,16 +8907,30 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="N130" t="n">
+        <v>32165</v>
+      </c>
+      <c r="O130" t="n">
+        <v>7632.5</v>
+      </c>
       <c r="P130" t="n">
-        <v>11322.4</v>
-      </c>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
+        <v>28660</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>3905</v>
+      </c>
+      <c r="R130" t="n">
+        <v>1531.5</v>
+      </c>
+      <c r="S130" t="n">
+        <v>18980</v>
+      </c>
+      <c r="T130" t="n">
+        <v>8317</v>
+      </c>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr"/>
@@ -6388,6 +8940,28 @@
       <c r="AA130" t="inlineStr"/>
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr"/>
+      <c r="AJ130" t="inlineStr"/>
+      <c r="AK130" t="inlineStr"/>
+      <c r="AL130" t="inlineStr"/>
+      <c r="AM130" t="inlineStr"/>
+      <c r="AN130" t="inlineStr"/>
+      <c r="AO130" t="inlineStr"/>
+      <c r="AP130" t="inlineStr"/>
+      <c r="AQ130" t="inlineStr"/>
+      <c r="AR130" t="inlineStr"/>
+      <c r="AS130" t="inlineStr"/>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AU130" t="inlineStr"/>
+      <c r="AV130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr"/>
+      <c r="AX130" t="inlineStr"/>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -6410,55 +8984,85 @@
         <v>24556.4</v>
       </c>
       <c r="H131" t="n">
-        <v>8.6546</v>
-      </c>
-      <c r="I131" t="n">
-        <v>4.91747</v>
-      </c>
-      <c r="J131" t="n">
-        <v>22.549675</v>
-      </c>
+        <v>49398.8</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>8634.25</v>
+      </c>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" t="n">
-        <v>49398.8</v>
-      </c>
-      <c r="O131" t="n">
-        <v>157.726</v>
-      </c>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="n">
-        <v>8127</v>
-      </c>
-      <c r="R131" t="n">
-        <v>61033.3</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0.71962</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0.863425</v>
-      </c>
-      <c r="U131" t="n">
-        <v>2862.35</v>
-      </c>
-      <c r="V131" t="n">
-        <v>1.361075</v>
-      </c>
-      <c r="W131" t="n">
-        <v>184.6435</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0.78224</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0.58957</v>
-      </c>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr"/>
-      <c r="AC131" t="inlineStr"/>
+      <c r="AC131" t="n">
+        <v>0.91561</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>1.62654</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>1.593095</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>1.98545</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>10.834495</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>10.83113</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>7.47256</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>4.24594</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>18464.35</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>9156.1</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>20165.15</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>8.6546</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>4.91747</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>22.549675</v>
+      </c>
+      <c r="AQ131" t="inlineStr"/>
+      <c r="AR131" t="inlineStr"/>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0.78224</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.58957</v>
+      </c>
+      <c r="AV131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr"/>
+      <c r="AX131" t="inlineStr"/>
+      <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -6475,29 +9079,77 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="n">
-        <v>62292.5</v>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>1210.1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>32155</v>
+      </c>
+      <c r="O132" t="n">
+        <v>7617.5</v>
+      </c>
       <c r="P132" t="n">
-        <v>10813.4</v>
-      </c>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
+        <v>28922.5</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>4060.5</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="S132" t="n">
+        <v>18200</v>
+      </c>
+      <c r="T132" t="n">
+        <v>8416</v>
+      </c>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
-      <c r="Y132" t="inlineStr"/>
-      <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
-      <c r="AB132" t="inlineStr"/>
+      <c r="W132" t="n">
+        <v>4756.65</v>
+      </c>
+      <c r="X132" t="n">
+        <v>61417.5</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>2011.85</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>1560.75</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>10058.5</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>9852.5</v>
+      </c>
       <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr"/>
+      <c r="AJ132" t="inlineStr"/>
+      <c r="AK132" t="inlineStr"/>
+      <c r="AL132" t="inlineStr"/>
+      <c r="AM132" t="inlineStr"/>
+      <c r="AN132" t="inlineStr"/>
+      <c r="AO132" t="inlineStr"/>
+      <c r="AP132" t="inlineStr"/>
+      <c r="AQ132" t="n">
+        <v>62292.5</v>
+      </c>
+      <c r="AR132" t="inlineStr"/>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AU132" t="inlineStr"/>
+      <c r="AV132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr"/>
+      <c r="AX132" t="inlineStr"/>
+      <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -6520,59 +9172,99 @@
         <v>24917.1</v>
       </c>
       <c r="H133" t="n">
-        <v>8.64536</v>
+        <v>49876.8</v>
       </c>
       <c r="I133" t="n">
-        <v>4.8963</v>
+        <v>15634.6</v>
       </c>
       <c r="J133" t="n">
-        <v>22.30122</v>
-      </c>
-      <c r="K133" t="inlineStr"/>
+        <v>7238.25</v>
+      </c>
+      <c r="K133" t="n">
+        <v>13632.95</v>
+      </c>
       <c r="L133" t="n">
-        <v>81320.5</v>
-      </c>
-      <c r="M133" t="n">
-        <v>2346.6</v>
-      </c>
-      <c r="N133" t="n">
-        <v>49876.8</v>
-      </c>
-      <c r="O133" t="n">
-        <v>156.346</v>
-      </c>
+        <v>8643.549999999999</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="n">
-        <v>8316.299999999999</v>
-      </c>
-      <c r="R133" t="n">
-        <v>61858.3</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0.7238249999999999</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0.864355</v>
-      </c>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
       <c r="U133" t="n">
-        <v>2883.95</v>
+        <v>4695.12</v>
       </c>
       <c r="V133" t="n">
-        <v>1.363295</v>
-      </c>
-      <c r="W133" t="n">
-        <v>183.7105</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0.77866</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0.59565</v>
-      </c>
+        <v>7741.05</v>
+      </c>
+      <c r="W133" t="inlineStr"/>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
       <c r="AA133" t="inlineStr"/>
       <c r="AB133" t="inlineStr"/>
-      <c r="AC133" t="inlineStr"/>
+      <c r="AC133" t="n">
+        <v>0.91487</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>1.6235</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>1.601785</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>1.97276</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>10.921995</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>10.85146</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>7.47276</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>4.23221</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>18371.05</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>9148.700000000001</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>20080.3</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>8.64536</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>4.8963</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>22.30122</v>
+      </c>
+      <c r="AQ133" t="inlineStr"/>
+      <c r="AR133" t="n">
+        <v>81320.5</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2346.6</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.77866</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.59565</v>
+      </c>
+      <c r="AV133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr"/>
+      <c r="AX133" t="inlineStr"/>
+      <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -6589,29 +9281,77 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="n">
-        <v>63350</v>
-      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>1189.5</v>
+      </c>
+      <c r="N134" t="n">
+        <v>31615</v>
+      </c>
+      <c r="O134" t="n">
+        <v>7484</v>
+      </c>
       <c r="P134" t="n">
-        <v>10204</v>
-      </c>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
+        <v>28372.5</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>4274.5</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1482.5</v>
+      </c>
+      <c r="S134" t="n">
+        <v>17975</v>
+      </c>
+      <c r="T134" t="n">
+        <v>8308.5</v>
+      </c>
       <c r="U134" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
-      <c r="Y134" t="inlineStr"/>
-      <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr"/>
-      <c r="AB134" t="inlineStr"/>
+      <c r="W134" t="n">
+        <v>4811.9</v>
+      </c>
+      <c r="X134" t="n">
+        <v>62480</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>2071.65</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1578.75</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>9581.5</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>9347.5</v>
+      </c>
       <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="inlineStr"/>
+      <c r="AK134" t="inlineStr"/>
+      <c r="AL134" t="inlineStr"/>
+      <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr"/>
+      <c r="AO134" t="inlineStr"/>
+      <c r="AP134" t="inlineStr"/>
+      <c r="AQ134" t="n">
+        <v>63350</v>
+      </c>
+      <c r="AR134" t="inlineStr"/>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AU134" t="inlineStr"/>
+      <c r="AV134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr"/>
+      <c r="AX134" t="inlineStr"/>
+      <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -6634,59 +9374,99 @@
         <v>24385.1</v>
       </c>
       <c r="H135" t="n">
-        <v>8.63369</v>
+        <v>49556.1</v>
       </c>
       <c r="I135" t="n">
-        <v>4.889089999999999</v>
+        <v>15688.5</v>
       </c>
       <c r="J135" t="n">
-        <v>22.32867</v>
-      </c>
-      <c r="K135" t="inlineStr"/>
+        <v>7203.25</v>
+      </c>
+      <c r="K135" t="n">
+        <v>13663.95</v>
+      </c>
       <c r="L135" t="n">
-        <v>79908.5</v>
-      </c>
-      <c r="M135" t="n">
-        <v>2287.6</v>
-      </c>
-      <c r="N135" t="n">
-        <v>49556.1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>156.885</v>
-      </c>
+        <v>8654.950000000001</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="n">
-        <v>8115.5</v>
-      </c>
-      <c r="R135" t="n">
-        <v>62156.2</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0.720325</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0.8654949999999999</v>
-      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr"/>
       <c r="U135" t="n">
-        <v>2833.75</v>
+        <v>4685.84</v>
       </c>
       <c r="V135" t="n">
-        <v>1.366395</v>
-      </c>
-      <c r="W135" t="n">
-        <v>183.9675</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0.78081</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0.59345</v>
-      </c>
+        <v>7855.35</v>
+      </c>
+      <c r="W135" t="inlineStr"/>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr"/>
-      <c r="AC135" t="inlineStr"/>
+      <c r="AC135" t="n">
+        <v>0.91545</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>1.62781</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>1.601995</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>1.97579</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>10.91348</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>10.88157</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>7.47253</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>4.23144</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>18396.75</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>9154.5</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>20094.95</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>8.63369</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>4.889089999999999</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>22.32867</v>
+      </c>
+      <c r="AQ135" t="inlineStr"/>
+      <c r="AR135" t="n">
+        <v>79908.5</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>2287.6</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.78081</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.59345</v>
+      </c>
+      <c r="AV135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr"/>
+      <c r="AX135" t="inlineStr"/>
+      <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -6703,29 +9483,77 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="n">
-        <v>63232.5</v>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>1190.1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>31775</v>
+      </c>
+      <c r="O136" t="n">
+        <v>7456</v>
+      </c>
       <c r="P136" t="n">
-        <v>10117.1</v>
-      </c>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
+        <v>27242.5</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>4360.5</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1455.5</v>
+      </c>
+      <c r="S136" t="n">
+        <v>17550</v>
+      </c>
+      <c r="T136" t="n">
+        <v>8297</v>
+      </c>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
-      <c r="Y136" t="inlineStr"/>
-      <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
-      <c r="AB136" t="inlineStr"/>
+      <c r="W136" t="n">
+        <v>4833.1</v>
+      </c>
+      <c r="X136" t="n">
+        <v>62367.5</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>2062.55</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>9570.5</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>9356</v>
+      </c>
       <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr"/>
+      <c r="AJ136" t="inlineStr"/>
+      <c r="AK136" t="inlineStr"/>
+      <c r="AL136" t="inlineStr"/>
+      <c r="AM136" t="inlineStr"/>
+      <c r="AN136" t="inlineStr"/>
+      <c r="AO136" t="inlineStr"/>
+      <c r="AP136" t="inlineStr"/>
+      <c r="AQ136" t="n">
+        <v>63232.5</v>
+      </c>
+      <c r="AR136" t="inlineStr"/>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AU136" t="inlineStr"/>
+      <c r="AV136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr"/>
+      <c r="AX136" t="inlineStr"/>
+      <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -6748,59 +9576,99 @@
         <v>24406.2</v>
       </c>
       <c r="H137" t="n">
-        <v>8.646585</v>
+        <v>49643.2</v>
       </c>
       <c r="I137" t="n">
-        <v>4.902855</v>
+        <v>15669</v>
       </c>
       <c r="J137" t="n">
-        <v>22.36081</v>
-      </c>
-      <c r="K137" t="inlineStr"/>
+        <v>7247.5</v>
+      </c>
+      <c r="K137" t="n">
+        <v>13675.25</v>
+      </c>
       <c r="L137" t="n">
-        <v>80142.5</v>
-      </c>
-      <c r="M137" t="n">
-        <v>2305.8</v>
-      </c>
-      <c r="N137" t="n">
-        <v>49643.2</v>
-      </c>
-      <c r="O137" t="n">
-        <v>156.69</v>
-      </c>
+        <v>8646</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="n">
-        <v>8101.3</v>
-      </c>
-      <c r="R137" t="n">
-        <v>63774.5</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0.72475</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0.8646</v>
-      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr"/>
       <c r="U137" t="n">
-        <v>2861.2</v>
+        <v>4714.32</v>
       </c>
       <c r="V137" t="n">
-        <v>1.367525</v>
-      </c>
-      <c r="W137" t="n">
-        <v>184.6515</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0.7766649999999999</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0.59662</v>
-      </c>
+        <v>8032.549999999999</v>
+      </c>
+      <c r="W137" t="inlineStr"/>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr"/>
-      <c r="AC137" t="inlineStr"/>
+      <c r="AC137" t="n">
+        <v>0.9151</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>1.62619</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>1.611685</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>1.97524</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>10.852745</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>10.86325</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>7.47287</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>4.237925000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>18465.15</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>9151</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>20178.1</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>8.646585</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>4.902855</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>22.36081</v>
+      </c>
+      <c r="AQ137" t="inlineStr"/>
+      <c r="AR137" t="n">
+        <v>80142.5</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>2305.8</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.7766649999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AV137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr"/>
+      <c r="AX137" t="inlineStr"/>
+      <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -6817,29 +9685,77 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="n">
-        <v>64305</v>
-      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>1206</v>
+      </c>
+      <c r="N138" t="n">
+        <v>31950</v>
+      </c>
+      <c r="O138" t="n">
+        <v>7415</v>
+      </c>
       <c r="P138" t="n">
-        <v>10056.2</v>
-      </c>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
+        <v>27415</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>4238.5</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1469.5</v>
+      </c>
+      <c r="S138" t="n">
+        <v>18287.5</v>
+      </c>
+      <c r="T138" t="n">
+        <v>8473.5</v>
+      </c>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
-      <c r="Y138" t="inlineStr"/>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
-      <c r="AB138" t="inlineStr"/>
+      <c r="W138" t="n">
+        <v>4837.6</v>
+      </c>
+      <c r="X138" t="n">
+        <v>63440</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>2069.3</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1527.5</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>9468</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>9335</v>
+      </c>
       <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr"/>
+      <c r="AJ138" t="inlineStr"/>
+      <c r="AK138" t="inlineStr"/>
+      <c r="AL138" t="inlineStr"/>
+      <c r="AM138" t="inlineStr"/>
+      <c r="AN138" t="inlineStr"/>
+      <c r="AO138" t="inlineStr"/>
+      <c r="AP138" t="inlineStr"/>
+      <c r="AQ138" t="n">
+        <v>64305</v>
+      </c>
+      <c r="AR138" t="inlineStr"/>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AU138" t="inlineStr"/>
+      <c r="AV138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr"/>
+      <c r="AX138" t="inlineStr"/>
+      <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -6855,12 +9771,8 @@
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="n">
-        <v>80768.5</v>
-      </c>
-      <c r="M139" t="n">
-        <v>2330.3</v>
-      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
@@ -6877,43 +9789,69 @@
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr"/>
+      <c r="AJ139" t="inlineStr"/>
+      <c r="AK139" t="inlineStr"/>
+      <c r="AL139" t="inlineStr"/>
+      <c r="AM139" t="inlineStr"/>
+      <c r="AN139" t="inlineStr"/>
+      <c r="AO139" t="inlineStr"/>
+      <c r="AP139" t="inlineStr"/>
+      <c r="AQ139" t="inlineStr"/>
+      <c r="AR139" t="n">
+        <v>80768.5</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>2330.3</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AU139" t="inlineStr"/>
+      <c r="AV139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr"/>
+      <c r="AX139" t="inlineStr"/>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
         <v>46152</v>
       </c>
       <c r="B140" t="n">
-        <v>10239.4</v>
+        <v>10244.8</v>
       </c>
       <c r="C140" t="n">
-        <v>7375.74</v>
+        <v>7380.75</v>
       </c>
       <c r="D140" t="n">
-        <v>1.17642</v>
+        <v>1.17638</v>
       </c>
       <c r="E140" t="n">
-        <v>1.358745</v>
+        <v>1.358925</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>24316.4</v>
+        <v>24338.9</v>
       </c>
       <c r="H140" t="n">
-        <v>8.630189999999999</v>
+        <v>49483.5</v>
       </c>
       <c r="I140" t="n">
-        <v>4.896100000000001</v>
+        <v>15689.4</v>
       </c>
       <c r="J140" t="n">
-        <v>22.35412</v>
-      </c>
-      <c r="K140" t="inlineStr"/>
+        <v>7234.05</v>
+      </c>
+      <c r="K140" t="n">
+        <v>13689.85</v>
+      </c>
       <c r="L140" t="n">
-        <v>82017.5</v>
-      </c>
-      <c r="M140" t="n">
-        <v>2369.1</v>
-      </c>
+        <v>8656.549999999999</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
@@ -6921,15 +9859,73 @@
       <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr"/>
       <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
+      <c r="U140" t="n">
+        <v>4692.12</v>
+      </c>
+      <c r="V140" t="n">
+        <v>7998.1</v>
+      </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr"/>
-      <c r="AC140" t="inlineStr"/>
+      <c r="AC140" t="n">
+        <v>0.9151199999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>1.62628</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>1.610285</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>1.97721</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>10.83832</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>10.87505</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>7.47252</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>4.23899</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>18457.75</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>9151.5</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>20168.35</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>8.630140000000001</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>4.89592</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>22.35697</v>
+      </c>
+      <c r="AQ140" t="inlineStr"/>
+      <c r="AR140" t="n">
+        <v>81942.5</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>2363</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AU140" t="inlineStr"/>
+      <c r="AV140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr"/>
+      <c r="AX140" t="inlineStr"/>
+      <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -6940,33 +9936,239 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="n">
-        <v>9755.6</v>
+        <v>9954.6</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="n">
-        <v>64202.5</v>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>1216.3</v>
+      </c>
+      <c r="N141" t="n">
+        <v>32125.8</v>
+      </c>
+      <c r="O141" t="n">
+        <v>7483.6</v>
+      </c>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
+      <c r="T141" t="n">
+        <v>8476.5</v>
+      </c>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
-      <c r="Y141" t="inlineStr"/>
-      <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
-      <c r="AB141" t="inlineStr"/>
+      <c r="W141" t="n">
+        <v>4790.299999999999</v>
+      </c>
+      <c r="X141" t="n">
+        <v>64015</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>2057.05</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>1516.25</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>9995</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>9743.5</v>
+      </c>
       <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr"/>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr"/>
+      <c r="AJ141" t="inlineStr"/>
+      <c r="AK141" t="inlineStr"/>
+      <c r="AL141" t="inlineStr"/>
+      <c r="AM141" t="inlineStr"/>
+      <c r="AN141" t="inlineStr"/>
+      <c r="AO141" t="inlineStr"/>
+      <c r="AP141" t="inlineStr"/>
+      <c r="AQ141" t="n">
+        <v>64212.5</v>
+      </c>
+      <c r="AR141" t="inlineStr"/>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AU141" t="inlineStr"/>
+      <c r="AV141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr"/>
+      <c r="AX141" t="inlineStr"/>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B142" t="n">
+        <v>10222.4</v>
+      </c>
+      <c r="C142" t="n">
+        <v>7404.29</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.1776</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.362095</v>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="n">
+        <v>24244.3</v>
+      </c>
+      <c r="H142" t="n">
+        <v>49635.2</v>
+      </c>
+      <c r="I142" t="n">
+        <v>15726.6</v>
+      </c>
+      <c r="J142" t="n">
+        <v>7247.9</v>
+      </c>
+      <c r="K142" t="n">
+        <v>13676.65</v>
+      </c>
+      <c r="L142" t="n">
+        <v>8645.75</v>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="n">
+        <v>4727.99</v>
+      </c>
+      <c r="V142" t="n">
+        <v>8601.6</v>
+      </c>
+      <c r="W142" t="inlineStr"/>
+      <c r="X142" t="inlineStr"/>
+      <c r="Y142" t="inlineStr"/>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr"/>
+      <c r="AJ142" t="inlineStr"/>
+      <c r="AK142" t="inlineStr"/>
+      <c r="AL142" t="inlineStr"/>
+      <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr"/>
+      <c r="AO142" t="inlineStr"/>
+      <c r="AP142" t="inlineStr"/>
+      <c r="AQ142" t="inlineStr"/>
+      <c r="AR142" t="inlineStr"/>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AU142" t="inlineStr"/>
+      <c r="AV142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr"/>
+      <c r="AX142" t="inlineStr"/>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46153.20833333334</v>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>9802.700000000001</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>1210.9</v>
+      </c>
+      <c r="N143" t="n">
+        <v>32505</v>
+      </c>
+      <c r="O143" t="n">
+        <v>7364.5</v>
+      </c>
+      <c r="P143" t="n">
+        <v>28127.5</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4692</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1494.5</v>
+      </c>
+      <c r="S143" t="n">
+        <v>18270</v>
+      </c>
+      <c r="T143" t="n">
+        <v>8817</v>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+      <c r="W143" t="n">
+        <v>4842</v>
+      </c>
+      <c r="X143" t="n">
+        <v>65377.5</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>2148.05</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1549.25</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>9801.5</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>9688.5</v>
+      </c>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="inlineStr"/>
+      <c r="AK143" t="inlineStr"/>
+      <c r="AL143" t="inlineStr"/>
+      <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr"/>
+      <c r="AO143" t="inlineStr"/>
+      <c r="AP143" t="inlineStr"/>
+      <c r="AQ143" t="inlineStr"/>
+      <c r="AR143" t="inlineStr"/>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AU143" t="inlineStr"/>
+      <c r="AV143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr"/>
+      <c r="AX143" t="inlineStr"/>
+      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
